--- a/CHECKLIST_TRIEN_KHAI_FULL.xlsx
+++ b/CHECKLIST_TRIEN_KHAI_FULL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ssl_detection_xray_v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94C1B6A2-C32D-4C7B-918F-D55D72487E8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09207129-1A4B-46C1-B7D5-6D3EF425D170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/CHECKLIST_TRIEN_KHAI_FULL.xlsx
+++ b/CHECKLIST_TRIEN_KHAI_FULL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ssl_detection_xray_v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09207129-1A4B-46C1-B7D5-6D3EF425D170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5790F303-62CD-4FE9-A75D-210CB7B4C7F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B4" s="2">
         <f>COUNTIF(Checklist!$F:$F,"Chưa làm")</f>
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>4</v>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Checklist!$F:$F,"Hoàn thành")</f>
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>10</v>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="B8" s="5">
         <f>IFERROR(B6/B3,0)</f>
-        <v>0.1111111111111111</v>
+        <v>0.13131313131313133</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>16</v>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="C14">
         <f>'Phase Summary'!C4</f>
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D14">
         <f>'Phase Summary'!D4</f>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="E14">
         <f>'Phase Summary'!E4</f>
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F14">
         <f>'Phase Summary'!F4</f>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="H14" s="6">
         <f>'Phase Summary'!H4</f>
-        <v>0.5490196078431373</v>
+        <v>0.74509803921568629</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -4883,7 +4883,7 @@
         <v>120</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G61" s="10" t="s">
         <v>52</v>
@@ -4897,7 +4897,7 @@
       <c r="L61" s="10"/>
       <c r="M61" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="27.6">
@@ -4917,7 +4917,7 @@
         <v>121</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G62" s="10" t="s">
         <v>52</v>
@@ -4931,7 +4931,7 @@
       <c r="L62" s="10"/>
       <c r="M62" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="27.6">
@@ -4951,7 +4951,7 @@
         <v>122</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G63" s="10" t="s">
         <v>52</v>
@@ -4965,7 +4965,7 @@
       <c r="L63" s="10"/>
       <c r="M63" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="27.6">
@@ -4985,7 +4985,7 @@
         <v>123</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G64" s="10" t="s">
         <v>52</v>
@@ -4999,7 +4999,7 @@
       <c r="L64" s="10"/>
       <c r="M64" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="27.6">
@@ -5019,7 +5019,7 @@
         <v>124</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G65" s="10" t="s">
         <v>52</v>
@@ -5033,7 +5033,7 @@
       <c r="L65" s="10"/>
       <c r="M65" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="27.6">
@@ -5053,7 +5053,7 @@
         <v>125</v>
       </c>
       <c r="F66" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G66" s="10" t="s">
         <v>63</v>
@@ -5067,7 +5067,7 @@
       <c r="L66" s="10"/>
       <c r="M66" s="10">
         <f t="shared" ref="M66:M129" si="1">IF(F66="Hoàn thành",1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="27.6">
@@ -5087,7 +5087,7 @@
         <v>126</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G67" s="10" t="s">
         <v>63</v>
@@ -5101,7 +5101,7 @@
       <c r="L67" s="10"/>
       <c r="M67" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="27.6">
@@ -5121,7 +5121,7 @@
         <v>127</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G68" s="10" t="s">
         <v>52</v>
@@ -5135,7 +5135,7 @@
       <c r="L68" s="10"/>
       <c r="M68" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="27.6">
@@ -5155,7 +5155,7 @@
         <v>128</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G69" s="10" t="s">
         <v>52</v>
@@ -5169,7 +5169,7 @@
       <c r="L69" s="10"/>
       <c r="M69" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="27.6">
@@ -5189,7 +5189,7 @@
         <v>129</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G70" s="10" t="s">
         <v>52</v>
@@ -5203,7 +5203,7 @@
       <c r="L70" s="10"/>
       <c r="M70" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="27.6">
@@ -19854,7 +19854,7 @@
       </c>
       <c r="C4">
         <f>COUNTIFS(Checklist!$B:$B,A4,Checklist!$F:$F,"Chưa làm")</f>
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D4">
         <f>COUNTIFS(Checklist!$B:$B,A4,Checklist!$F:$F,"Đang làm")</f>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="E4">
         <f>COUNTIFS(Checklist!$B:$B,A4,Checklist!$F:$F,"Hoàn thành")</f>
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F4">
         <f>COUNTIFS(Checklist!$B:$B,A4,Checklist!$F:$F,"Bị chặn")</f>
@@ -19874,7 +19874,7 @@
       </c>
       <c r="H4" s="6">
         <f t="shared" si="0"/>
-        <v>0.5490196078431373</v>
+        <v>0.74509803921568629</v>
       </c>
     </row>
     <row r="5" spans="1:8">

--- a/CHECKLIST_TRIEN_KHAI_FULL.xlsx
+++ b/CHECKLIST_TRIEN_KHAI_FULL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ssl_detection_xray_v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5790F303-62CD-4FE9-A75D-210CB7B4C7F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C88A3FC6-CA18-4D31-8C61-3F2AA2D38875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B4" s="2">
         <f>COUNTIF(Checklist!$F:$F,"Chưa làm")</f>
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>4</v>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Checklist!$F:$F,"Hoàn thành")</f>
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>10</v>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="B8" s="5">
         <f>IFERROR(B6/B3,0)</f>
-        <v>0.13131313131313133</v>
+        <v>0.15757575757575756</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>16</v>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="C14">
         <f>'Phase Summary'!C4</f>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <f>'Phase Summary'!D4</f>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="E14">
         <f>'Phase Summary'!E4</f>
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="F14">
         <f>'Phase Summary'!F4</f>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="H14" s="6">
         <f>'Phase Summary'!H4</f>
-        <v>0.74509803921568629</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -5223,7 +5223,7 @@
         <v>131</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G71" s="10" t="s">
         <v>63</v>
@@ -5237,7 +5237,7 @@
       <c r="L71" s="10"/>
       <c r="M71" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="27.6">
@@ -5257,7 +5257,7 @@
         <v>132</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G72" s="10" t="s">
         <v>63</v>
@@ -5271,7 +5271,7 @@
       <c r="L72" s="10"/>
       <c r="M72" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="27.6">
@@ -5291,7 +5291,7 @@
         <v>133</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G73" s="10" t="s">
         <v>63</v>
@@ -5305,7 +5305,7 @@
       <c r="L73" s="10"/>
       <c r="M73" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="27.6">
@@ -5325,7 +5325,7 @@
         <v>134</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G74" s="10" t="s">
         <v>63</v>
@@ -5339,7 +5339,7 @@
       <c r="L74" s="10"/>
       <c r="M74" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:13" ht="27.6">
@@ -5359,7 +5359,7 @@
         <v>135</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G75" s="10" t="s">
         <v>63</v>
@@ -5373,7 +5373,7 @@
       <c r="L75" s="10"/>
       <c r="M75" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:13" ht="27.6">
@@ -5393,7 +5393,7 @@
         <v>136</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G76" s="10" t="s">
         <v>52</v>
@@ -5407,7 +5407,7 @@
       <c r="L76" s="10"/>
       <c r="M76" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:13" ht="27.6">
@@ -5427,7 +5427,7 @@
         <v>137</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G77" s="10" t="s">
         <v>63</v>
@@ -5441,7 +5441,7 @@
       <c r="L77" s="10"/>
       <c r="M77" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:13" ht="27.6">
@@ -5461,7 +5461,7 @@
         <v>138</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G78" s="10" t="s">
         <v>63</v>
@@ -5475,7 +5475,7 @@
       <c r="L78" s="10"/>
       <c r="M78" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:13" ht="27.6">
@@ -5495,7 +5495,7 @@
         <v>139</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G79" s="10" t="s">
         <v>63</v>
@@ -5509,7 +5509,7 @@
       <c r="L79" s="10"/>
       <c r="M79" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:13" ht="27.6">
@@ -5529,7 +5529,7 @@
         <v>140</v>
       </c>
       <c r="F80" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G80" s="10" t="s">
         <v>63</v>
@@ -5543,7 +5543,7 @@
       <c r="L80" s="10"/>
       <c r="M80" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:13" ht="27.6">
@@ -5563,7 +5563,7 @@
         <v>141</v>
       </c>
       <c r="F81" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G81" s="10" t="s">
         <v>52</v>
@@ -5577,7 +5577,7 @@
       <c r="L81" s="10"/>
       <c r="M81" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:13" ht="27.6">
@@ -5597,7 +5597,7 @@
         <v>142</v>
       </c>
       <c r="F82" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G82" s="10" t="s">
         <v>52</v>
@@ -5611,7 +5611,7 @@
       <c r="L82" s="10"/>
       <c r="M82" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="27.6">
@@ -5631,7 +5631,7 @@
         <v>143</v>
       </c>
       <c r="F83" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G83" s="10" t="s">
         <v>52</v>
@@ -5645,7 +5645,7 @@
       <c r="L83" s="10"/>
       <c r="M83" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:13" ht="27.6">
@@ -19854,7 +19854,7 @@
       </c>
       <c r="C4">
         <f>COUNTIFS(Checklist!$B:$B,A4,Checklist!$F:$F,"Chưa làm")</f>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <f>COUNTIFS(Checklist!$B:$B,A4,Checklist!$F:$F,"Đang làm")</f>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="E4">
         <f>COUNTIFS(Checklist!$B:$B,A4,Checklist!$F:$F,"Hoàn thành")</f>
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="F4">
         <f>COUNTIFS(Checklist!$B:$B,A4,Checklist!$F:$F,"Bị chặn")</f>
@@ -19874,7 +19874,7 @@
       </c>
       <c r="H4" s="6">
         <f t="shared" si="0"/>
-        <v>0.74509803921568629</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8">

--- a/CHECKLIST_TRIEN_KHAI_FULL.xlsx
+++ b/CHECKLIST_TRIEN_KHAI_FULL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ssl_detection_xray_v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C88A3FC6-CA18-4D31-8C61-3F2AA2D38875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AC21191-9E08-4C57-829A-5847C3F45687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B4" s="2">
         <f>COUNTIF(Checklist!$F:$F,"Chưa làm")</f>
-        <v>415</v>
+        <v>399</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>4</v>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Checklist!$F:$F,"Hoàn thành")</f>
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>10</v>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="B8" s="5">
         <f>IFERROR(B6/B3,0)</f>
-        <v>0.15757575757575756</v>
+        <v>0.1898989898989899</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>16</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="C15">
         <f>'Phase Summary'!C5</f>
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="D15">
         <f>'Phase Summary'!D5</f>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="E15">
         <f>'Phase Summary'!E5</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F15">
         <f>'Phase Summary'!F5</f>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="H15" s="6">
         <f>'Phase Summary'!H5</f>
-        <v>0</v>
+        <v>0.1391304347826087</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -5665,7 +5665,7 @@
         <v>145</v>
       </c>
       <c r="F84" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G84" s="10" t="s">
         <v>63</v>
@@ -5679,7 +5679,7 @@
       <c r="L84" s="10"/>
       <c r="M84" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="27.6">
@@ -5699,7 +5699,7 @@
         <v>146</v>
       </c>
       <c r="F85" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G85" s="10" t="s">
         <v>63</v>
@@ -5713,7 +5713,7 @@
       <c r="L85" s="10"/>
       <c r="M85" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="27.6">
@@ -5733,7 +5733,7 @@
         <v>147</v>
       </c>
       <c r="F86" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G86" s="10" t="s">
         <v>63</v>
@@ -5747,7 +5747,7 @@
       <c r="L86" s="10"/>
       <c r="M86" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:13" ht="27.6">
@@ -5767,7 +5767,7 @@
         <v>148</v>
       </c>
       <c r="F87" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G87" s="10" t="s">
         <v>63</v>
@@ -5781,7 +5781,7 @@
       <c r="L87" s="10"/>
       <c r="M87" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="27.6">
@@ -5801,7 +5801,7 @@
         <v>149</v>
       </c>
       <c r="F88" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G88" s="10" t="s">
         <v>63</v>
@@ -5815,7 +5815,7 @@
       <c r="L88" s="10"/>
       <c r="M88" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:13" ht="27.6">
@@ -5835,7 +5835,7 @@
         <v>150</v>
       </c>
       <c r="F89" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G89" s="10" t="s">
         <v>63</v>
@@ -5849,7 +5849,7 @@
       <c r="L89" s="10"/>
       <c r="M89" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:13" ht="27.6">
@@ -5869,7 +5869,7 @@
         <v>151</v>
       </c>
       <c r="F90" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G90" s="10" t="s">
         <v>52</v>
@@ -5883,7 +5883,7 @@
       <c r="L90" s="10"/>
       <c r="M90" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:13" ht="27.6">
@@ -5903,7 +5903,7 @@
         <v>152</v>
       </c>
       <c r="F91" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G91" s="10" t="s">
         <v>52</v>
@@ -5917,7 +5917,7 @@
       <c r="L91" s="10"/>
       <c r="M91" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:13" ht="27.6">
@@ -5937,7 +5937,7 @@
         <v>153</v>
       </c>
       <c r="F92" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G92" s="10" t="s">
         <v>63</v>
@@ -5951,7 +5951,7 @@
       <c r="L92" s="10"/>
       <c r="M92" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:13" ht="27.6">
@@ -5971,7 +5971,7 @@
         <v>154</v>
       </c>
       <c r="F93" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G93" s="10" t="s">
         <v>63</v>
@@ -5985,7 +5985,7 @@
       <c r="L93" s="10"/>
       <c r="M93" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="27.6">
@@ -6005,7 +6005,7 @@
         <v>155</v>
       </c>
       <c r="F94" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G94" s="10" t="s">
         <v>63</v>
@@ -6019,7 +6019,7 @@
       <c r="L94" s="10"/>
       <c r="M94" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:13" ht="27.6">
@@ -6039,7 +6039,7 @@
         <v>156</v>
       </c>
       <c r="F95" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G95" s="10" t="s">
         <v>63</v>
@@ -6053,7 +6053,7 @@
       <c r="L95" s="10"/>
       <c r="M95" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:13" ht="27.6">
@@ -6073,7 +6073,7 @@
         <v>157</v>
       </c>
       <c r="F96" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G96" s="10" t="s">
         <v>52</v>
@@ -6087,7 +6087,7 @@
       <c r="L96" s="10"/>
       <c r="M96" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:13" ht="27.6">
@@ -6107,7 +6107,7 @@
         <v>158</v>
       </c>
       <c r="F97" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G97" s="10" t="s">
         <v>52</v>
@@ -6121,7 +6121,7 @@
       <c r="L97" s="10"/>
       <c r="M97" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:13" ht="27.6">
@@ -6141,7 +6141,7 @@
         <v>159</v>
       </c>
       <c r="F98" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G98" s="10" t="s">
         <v>52</v>
@@ -6155,7 +6155,7 @@
       <c r="L98" s="10"/>
       <c r="M98" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:13" ht="27.6">
@@ -6175,7 +6175,7 @@
         <v>160</v>
       </c>
       <c r="F99" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G99" s="10" t="s">
         <v>52</v>
@@ -6189,7 +6189,7 @@
       <c r="L99" s="10"/>
       <c r="M99" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:13" ht="27.6">
@@ -19887,7 +19887,7 @@
       </c>
       <c r="C5">
         <f>COUNTIFS(Checklist!$B:$B,A5,Checklist!$F:$F,"Chưa làm")</f>
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="D5">
         <f>COUNTIFS(Checklist!$B:$B,A5,Checklist!$F:$F,"Đang làm")</f>
@@ -19895,7 +19895,7 @@
       </c>
       <c r="E5">
         <f>COUNTIFS(Checklist!$B:$B,A5,Checklist!$F:$F,"Hoàn thành")</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F5">
         <f>COUNTIFS(Checklist!$B:$B,A5,Checklist!$F:$F,"Bị chặn")</f>
@@ -19907,7 +19907,7 @@
       </c>
       <c r="H5" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.1391304347826087</v>
       </c>
     </row>
     <row r="6" spans="1:8">

--- a/CHECKLIST_TRIEN_KHAI_FULL.xlsx
+++ b/CHECKLIST_TRIEN_KHAI_FULL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ssl_detection_xray_v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AC21191-9E08-4C57-829A-5847C3F45687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F767C65C-3E04-4648-9ADA-3154C7F8F888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B4" s="2">
         <f>COUNTIF(Checklist!$F:$F,"Chưa làm")</f>
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>4</v>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Checklist!$F:$F,"Hoàn thành")</f>
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>10</v>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="B8" s="5">
         <f>IFERROR(B6/B3,0)</f>
-        <v>0.1898989898989899</v>
+        <v>0.21414141414141413</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>16</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="C15">
         <f>'Phase Summary'!C5</f>
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="D15">
         <f>'Phase Summary'!D5</f>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="E15">
         <f>'Phase Summary'!E5</f>
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F15">
         <f>'Phase Summary'!F5</f>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="H15" s="6">
         <f>'Phase Summary'!H5</f>
-        <v>0.1391304347826087</v>
+        <v>0.24347826086956523</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -6209,7 +6209,7 @@
         <v>162</v>
       </c>
       <c r="F100" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G100" s="10" t="s">
         <v>63</v>
@@ -6223,7 +6223,7 @@
       <c r="L100" s="10"/>
       <c r="M100" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:13" ht="27.6">
@@ -6243,7 +6243,7 @@
         <v>163</v>
       </c>
       <c r="F101" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G101" s="10" t="s">
         <v>63</v>
@@ -6257,7 +6257,7 @@
       <c r="L101" s="10"/>
       <c r="M101" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:13" ht="27.6">
@@ -6277,7 +6277,7 @@
         <v>164</v>
       </c>
       <c r="F102" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G102" s="10" t="s">
         <v>63</v>
@@ -6291,7 +6291,7 @@
       <c r="L102" s="10"/>
       <c r="M102" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:13" ht="27.6">
@@ -6311,7 +6311,7 @@
         <v>165</v>
       </c>
       <c r="F103" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G103" s="10" t="s">
         <v>63</v>
@@ -6325,7 +6325,7 @@
       <c r="L103" s="10"/>
       <c r="M103" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:13" ht="27.6">
@@ -6345,7 +6345,7 @@
         <v>166</v>
       </c>
       <c r="F104" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G104" s="10" t="s">
         <v>63</v>
@@ -6359,7 +6359,7 @@
       <c r="L104" s="10"/>
       <c r="M104" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:13" ht="27.6">
@@ -6379,7 +6379,7 @@
         <v>167</v>
       </c>
       <c r="F105" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G105" s="10" t="s">
         <v>63</v>
@@ -6393,7 +6393,7 @@
       <c r="L105" s="10"/>
       <c r="M105" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:13" ht="27.6">
@@ -6413,7 +6413,7 @@
         <v>168</v>
       </c>
       <c r="F106" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G106" s="10" t="s">
         <v>63</v>
@@ -6427,7 +6427,7 @@
       <c r="L106" s="10"/>
       <c r="M106" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:13" ht="27.6">
@@ -6447,7 +6447,7 @@
         <v>169</v>
       </c>
       <c r="F107" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G107" s="10" t="s">
         <v>63</v>
@@ -6461,7 +6461,7 @@
       <c r="L107" s="10"/>
       <c r="M107" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:13" ht="27.6">
@@ -6481,7 +6481,7 @@
         <v>170</v>
       </c>
       <c r="F108" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G108" s="10" t="s">
         <v>63</v>
@@ -6495,7 +6495,7 @@
       <c r="L108" s="10"/>
       <c r="M108" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:13" ht="27.6">
@@ -6515,7 +6515,7 @@
         <v>171</v>
       </c>
       <c r="F109" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G109" s="10" t="s">
         <v>52</v>
@@ -6529,7 +6529,7 @@
       <c r="L109" s="10"/>
       <c r="M109" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:13" ht="27.6">
@@ -6549,7 +6549,7 @@
         <v>172</v>
       </c>
       <c r="F110" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G110" s="10" t="s">
         <v>52</v>
@@ -6563,7 +6563,7 @@
       <c r="L110" s="10"/>
       <c r="M110" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:13" ht="27.6">
@@ -6583,7 +6583,7 @@
         <v>173</v>
       </c>
       <c r="F111" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G111" s="10" t="s">
         <v>52</v>
@@ -6597,7 +6597,7 @@
       <c r="L111" s="10"/>
       <c r="M111" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:13" ht="27.6">
@@ -19887,7 +19887,7 @@
       </c>
       <c r="C5">
         <f>COUNTIFS(Checklist!$B:$B,A5,Checklist!$F:$F,"Chưa làm")</f>
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="D5">
         <f>COUNTIFS(Checklist!$B:$B,A5,Checklist!$F:$F,"Đang làm")</f>
@@ -19895,7 +19895,7 @@
       </c>
       <c r="E5">
         <f>COUNTIFS(Checklist!$B:$B,A5,Checklist!$F:$F,"Hoàn thành")</f>
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F5">
         <f>COUNTIFS(Checklist!$B:$B,A5,Checklist!$F:$F,"Bị chặn")</f>
@@ -19907,7 +19907,7 @@
       </c>
       <c r="H5" s="6">
         <f t="shared" si="0"/>
-        <v>0.1391304347826087</v>
+        <v>0.24347826086956523</v>
       </c>
     </row>
     <row r="6" spans="1:8">

--- a/CHECKLIST_TRIEN_KHAI_FULL.xlsx
+++ b/CHECKLIST_TRIEN_KHAI_FULL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ssl_detection_xray_v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F767C65C-3E04-4648-9ADA-3154C7F8F888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{722D5090-6DDA-46AC-9235-E1EDB014D092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B4" s="2">
         <f>COUNTIF(Checklist!$F:$F,"Chưa làm")</f>
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>4</v>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Checklist!$F:$F,"Hoàn thành")</f>
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>10</v>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="B8" s="5">
         <f>IFERROR(B6/B3,0)</f>
-        <v>0.21414141414141413</v>
+        <v>0.23636363636363636</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>16</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="C15">
         <f>'Phase Summary'!C5</f>
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="D15">
         <f>'Phase Summary'!D5</f>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="E15">
         <f>'Phase Summary'!E5</f>
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F15">
         <f>'Phase Summary'!F5</f>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="H15" s="6">
         <f>'Phase Summary'!H5</f>
-        <v>0.24347826086956523</v>
+        <v>0.33913043478260868</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -6617,7 +6617,7 @@
         <v>175</v>
       </c>
       <c r="F112" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G112" s="10" t="s">
         <v>52</v>
@@ -6631,7 +6631,7 @@
       <c r="L112" s="10"/>
       <c r="M112" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:13" ht="27.6">
@@ -6651,7 +6651,7 @@
         <v>176</v>
       </c>
       <c r="F113" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G113" s="10" t="s">
         <v>52</v>
@@ -6665,7 +6665,7 @@
       <c r="L113" s="10"/>
       <c r="M113" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:13" ht="27.6">
@@ -6685,7 +6685,7 @@
         <v>177</v>
       </c>
       <c r="F114" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G114" s="10" t="s">
         <v>52</v>
@@ -6699,7 +6699,7 @@
       <c r="L114" s="10"/>
       <c r="M114" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:13" ht="27.6">
@@ -6719,7 +6719,7 @@
         <v>178</v>
       </c>
       <c r="F115" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G115" s="10" t="s">
         <v>52</v>
@@ -6733,7 +6733,7 @@
       <c r="L115" s="10"/>
       <c r="M115" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:13" ht="27.6">
@@ -6753,7 +6753,7 @@
         <v>179</v>
       </c>
       <c r="F116" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G116" s="10" t="s">
         <v>52</v>
@@ -6767,7 +6767,7 @@
       <c r="L116" s="10"/>
       <c r="M116" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:13" ht="27.6">
@@ -6787,7 +6787,7 @@
         <v>180</v>
       </c>
       <c r="F117" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G117" s="10" t="s">
         <v>52</v>
@@ -6801,7 +6801,7 @@
       <c r="L117" s="10"/>
       <c r="M117" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:13" ht="27.6">
@@ -6821,7 +6821,7 @@
         <v>181</v>
       </c>
       <c r="F118" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G118" s="10" t="s">
         <v>63</v>
@@ -6835,7 +6835,7 @@
       <c r="L118" s="10"/>
       <c r="M118" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:13" ht="27.6">
@@ -6855,7 +6855,7 @@
         <v>182</v>
       </c>
       <c r="F119" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G119" s="10" t="s">
         <v>63</v>
@@ -6869,7 +6869,7 @@
       <c r="L119" s="10"/>
       <c r="M119" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:13" ht="27.6">
@@ -6889,7 +6889,7 @@
         <v>183</v>
       </c>
       <c r="F120" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G120" s="10" t="s">
         <v>63</v>
@@ -6903,7 +6903,7 @@
       <c r="L120" s="10"/>
       <c r="M120" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:13" ht="27.6">
@@ -6923,7 +6923,7 @@
         <v>184</v>
       </c>
       <c r="F121" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G121" s="10" t="s">
         <v>52</v>
@@ -6937,7 +6937,7 @@
       <c r="L121" s="10"/>
       <c r="M121" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:13" ht="27.6">
@@ -6957,7 +6957,7 @@
         <v>185</v>
       </c>
       <c r="F122" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G122" s="10" t="s">
         <v>52</v>
@@ -6971,7 +6971,7 @@
       <c r="L122" s="10"/>
       <c r="M122" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:13" ht="27.6">
@@ -19887,7 +19887,7 @@
       </c>
       <c r="C5">
         <f>COUNTIFS(Checklist!$B:$B,A5,Checklist!$F:$F,"Chưa làm")</f>
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="D5">
         <f>COUNTIFS(Checklist!$B:$B,A5,Checklist!$F:$F,"Đang làm")</f>
@@ -19895,7 +19895,7 @@
       </c>
       <c r="E5">
         <f>COUNTIFS(Checklist!$B:$B,A5,Checklist!$F:$F,"Hoàn thành")</f>
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F5">
         <f>COUNTIFS(Checklist!$B:$B,A5,Checklist!$F:$F,"Bị chặn")</f>
@@ -19907,7 +19907,7 @@
       </c>
       <c r="H5" s="6">
         <f t="shared" si="0"/>
-        <v>0.24347826086956523</v>
+        <v>0.33913043478260868</v>
       </c>
     </row>
     <row r="6" spans="1:8">

--- a/CHECKLIST_TRIEN_KHAI_FULL.xlsx
+++ b/CHECKLIST_TRIEN_KHAI_FULL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ssl_detection_xray_v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{722D5090-6DDA-46AC-9235-E1EDB014D092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D15C2F80-0E3F-49F1-B12A-7E591C4EA284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -610,9 +610,6 @@
     <t>data/processed/coco/coco_master.json</t>
   </si>
   <si>
-    <t>reports/coco_validation_report.json</t>
-  </si>
-  <si>
     <t>COCO validator pass 100%.</t>
   </si>
   <si>
@@ -1769,6 +1766,10 @@
   </si>
   <si>
     <t>Tạo repo tên: ssl_detection_xray_v2</t>
+  </si>
+  <si>
+    <t>reports/phase2D_coco_master_validation.json
+reports/phase2D_coco_master_validation.md</t>
   </si>
 </sst>
 </file>
@@ -2226,7 +2227,7 @@
       </c>
       <c r="B4" s="2">
         <f>COUNTIF(Checklist!$F:$F,"Chưa làm")</f>
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>4</v>
@@ -2262,7 +2263,7 @@
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Checklist!$F:$F,"Hoàn thành")</f>
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>10</v>
@@ -2298,7 +2299,7 @@
       </c>
       <c r="B8" s="5">
         <f>IFERROR(B6/B3,0)</f>
-        <v>0.23636363636363636</v>
+        <v>0.26262626262626265</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>16</v>
@@ -2467,7 +2468,7 @@
       </c>
       <c r="C15">
         <f>'Phase Summary'!C5</f>
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="D15">
         <f>'Phase Summary'!D5</f>
@@ -2475,7 +2476,7 @@
       </c>
       <c r="E15">
         <f>'Phase Summary'!E5</f>
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="F15">
         <f>'Phase Summary'!F5</f>
@@ -2487,7 +2488,7 @@
       </c>
       <c r="H15" s="6">
         <f>'Phase Summary'!H5</f>
-        <v>0.33913043478260868</v>
+        <v>0.45217391304347826</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -3146,7 +3147,7 @@
         <v>62</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>9</v>
@@ -6991,7 +6992,7 @@
         <v>187</v>
       </c>
       <c r="F123" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G123" s="10" t="s">
         <v>63</v>
@@ -7005,7 +7006,7 @@
       <c r="L123" s="10"/>
       <c r="M123" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:13" ht="27.6">
@@ -7025,7 +7026,7 @@
         <v>188</v>
       </c>
       <c r="F124" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G124" s="10" t="s">
         <v>63</v>
@@ -7039,7 +7040,7 @@
       <c r="L124" s="10"/>
       <c r="M124" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:13" ht="27.6">
@@ -7059,7 +7060,7 @@
         <v>189</v>
       </c>
       <c r="F125" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G125" s="10" t="s">
         <v>63</v>
@@ -7073,7 +7074,7 @@
       <c r="L125" s="10"/>
       <c r="M125" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:13" ht="27.6">
@@ -7093,7 +7094,7 @@
         <v>190</v>
       </c>
       <c r="F126" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G126" s="10" t="s">
         <v>63</v>
@@ -7107,7 +7108,7 @@
       <c r="L126" s="10"/>
       <c r="M126" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:13" ht="27.6">
@@ -7127,7 +7128,7 @@
         <v>191</v>
       </c>
       <c r="F127" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G127" s="10" t="s">
         <v>52</v>
@@ -7141,7 +7142,7 @@
       <c r="L127" s="10"/>
       <c r="M127" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:13" ht="27.6">
@@ -7161,7 +7162,7 @@
         <v>192</v>
       </c>
       <c r="F128" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G128" s="10" t="s">
         <v>63</v>
@@ -7175,7 +7176,7 @@
       <c r="L128" s="10"/>
       <c r="M128" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:13" ht="27.6">
@@ -7195,7 +7196,7 @@
         <v>193</v>
       </c>
       <c r="F129" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G129" s="10" t="s">
         <v>52</v>
@@ -7209,7 +7210,7 @@
       <c r="L129" s="10"/>
       <c r="M129" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:13" ht="27.6">
@@ -7229,7 +7230,7 @@
         <v>194</v>
       </c>
       <c r="F130" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G130" s="10" t="s">
         <v>63</v>
@@ -7243,7 +7244,7 @@
       <c r="L130" s="10"/>
       <c r="M130" s="10">
         <f t="shared" ref="M130:M193" si="2">IF(F130="Hoàn thành",1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:13" ht="27.6">
@@ -7260,10 +7261,10 @@
         <v>77</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>195</v>
+        <v>581</v>
       </c>
       <c r="F131" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G131" s="10" t="s">
         <v>63</v>
@@ -7277,7 +7278,7 @@
       <c r="L131" s="10"/>
       <c r="M131" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:13" ht="27.6">
@@ -7294,10 +7295,10 @@
         <v>83</v>
       </c>
       <c r="E132" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F132" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G132" s="10" t="s">
         <v>52</v>
@@ -7311,7 +7312,7 @@
       <c r="L132" s="10"/>
       <c r="M132" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:13" ht="27.6">
@@ -7328,10 +7329,10 @@
         <v>83</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F133" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G133" s="10" t="s">
         <v>52</v>
@@ -7345,7 +7346,7 @@
       <c r="L133" s="10"/>
       <c r="M133" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:13" ht="27.6">
@@ -7362,10 +7363,10 @@
         <v>83</v>
       </c>
       <c r="E134" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F134" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G134" s="10" t="s">
         <v>52</v>
@@ -7379,7 +7380,7 @@
       <c r="L134" s="10"/>
       <c r="M134" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:13" ht="27.6">
@@ -7396,10 +7397,10 @@
         <v>83</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F135" s="10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G135" s="10" t="s">
         <v>52</v>
@@ -7413,7 +7414,7 @@
       <c r="L135" s="10"/>
       <c r="M135" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:13" ht="27.6">
@@ -7424,13 +7425,13 @@
         <v>29</v>
       </c>
       <c r="C136" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="D136" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E136" s="10" t="s">
         <v>200</v>
-      </c>
-      <c r="D136" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E136" s="10" t="s">
-        <v>201</v>
       </c>
       <c r="F136" s="10" t="s">
         <v>3</v>
@@ -7458,13 +7459,13 @@
         <v>29</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D137" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>3</v>
@@ -7492,13 +7493,13 @@
         <v>29</v>
       </c>
       <c r="C138" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D138" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E138" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F138" s="10" t="s">
         <v>3</v>
@@ -7526,13 +7527,13 @@
         <v>29</v>
       </c>
       <c r="C139" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D139" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>3</v>
@@ -7560,13 +7561,13 @@
         <v>29</v>
       </c>
       <c r="C140" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D140" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E140" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F140" s="10" t="s">
         <v>3</v>
@@ -7594,13 +7595,13 @@
         <v>29</v>
       </c>
       <c r="C141" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D141" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>3</v>
@@ -7628,13 +7629,13 @@
         <v>29</v>
       </c>
       <c r="C142" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D142" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E142" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F142" s="10" t="s">
         <v>3</v>
@@ -7662,13 +7663,13 @@
         <v>29</v>
       </c>
       <c r="C143" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D143" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>3</v>
@@ -7696,13 +7697,13 @@
         <v>29</v>
       </c>
       <c r="C144" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D144" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E144" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F144" s="10" t="s">
         <v>3</v>
@@ -7730,13 +7731,13 @@
         <v>29</v>
       </c>
       <c r="C145" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D145" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>3</v>
@@ -7764,13 +7765,13 @@
         <v>29</v>
       </c>
       <c r="C146" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="D146" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E146" s="10" t="s">
         <v>211</v>
-      </c>
-      <c r="D146" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E146" s="10" t="s">
-        <v>212</v>
       </c>
       <c r="F146" s="10" t="s">
         <v>3</v>
@@ -7798,13 +7799,13 @@
         <v>29</v>
       </c>
       <c r="C147" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D147" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>3</v>
@@ -7832,13 +7833,13 @@
         <v>29</v>
       </c>
       <c r="C148" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D148" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E148" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F148" s="10" t="s">
         <v>3</v>
@@ -7866,13 +7867,13 @@
         <v>29</v>
       </c>
       <c r="C149" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D149" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>3</v>
@@ -7900,13 +7901,13 @@
         <v>29</v>
       </c>
       <c r="C150" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D150" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E150" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F150" s="10" t="s">
         <v>3</v>
@@ -7934,13 +7935,13 @@
         <v>29</v>
       </c>
       <c r="C151" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D151" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>3</v>
@@ -7968,13 +7969,13 @@
         <v>29</v>
       </c>
       <c r="C152" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D152" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E152" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F152" s="10" t="s">
         <v>3</v>
@@ -8002,13 +8003,13 @@
         <v>29</v>
       </c>
       <c r="C153" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D153" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>3</v>
@@ -8036,13 +8037,13 @@
         <v>29</v>
       </c>
       <c r="C154" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D154" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E154" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F154" s="10" t="s">
         <v>3</v>
@@ -8070,13 +8071,13 @@
         <v>29</v>
       </c>
       <c r="C155" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D155" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>3</v>
@@ -8104,13 +8105,13 @@
         <v>29</v>
       </c>
       <c r="C156" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D156" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E156" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F156" s="10" t="s">
         <v>3</v>
@@ -8138,13 +8139,13 @@
         <v>29</v>
       </c>
       <c r="C157" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D157" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>3</v>
@@ -8172,13 +8173,13 @@
         <v>29</v>
       </c>
       <c r="C158" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D158" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E158" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F158" s="10" t="s">
         <v>3</v>
@@ -8206,13 +8207,13 @@
         <v>29</v>
       </c>
       <c r="C159" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D159" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>3</v>
@@ -8240,13 +8241,13 @@
         <v>29</v>
       </c>
       <c r="C160" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D160" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E160" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F160" s="10" t="s">
         <v>3</v>
@@ -8274,13 +8275,13 @@
         <v>29</v>
       </c>
       <c r="C161" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D161" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>3</v>
@@ -8308,13 +8309,13 @@
         <v>29</v>
       </c>
       <c r="C162" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D162" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E162" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F162" s="10" t="s">
         <v>3</v>
@@ -8342,13 +8343,13 @@
         <v>29</v>
       </c>
       <c r="C163" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D163" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>3</v>
@@ -8376,13 +8377,13 @@
         <v>29</v>
       </c>
       <c r="C164" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="D164" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E164" s="10" t="s">
         <v>230</v>
-      </c>
-      <c r="D164" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E164" s="10" t="s">
-        <v>231</v>
       </c>
       <c r="F164" s="10" t="s">
         <v>3</v>
@@ -8410,13 +8411,13 @@
         <v>29</v>
       </c>
       <c r="C165" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D165" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>3</v>
@@ -8444,13 +8445,13 @@
         <v>29</v>
       </c>
       <c r="C166" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D166" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E166" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F166" s="10" t="s">
         <v>3</v>
@@ -8478,13 +8479,13 @@
         <v>29</v>
       </c>
       <c r="C167" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D167" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>3</v>
@@ -8512,13 +8513,13 @@
         <v>29</v>
       </c>
       <c r="C168" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D168" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E168" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F168" s="10" t="s">
         <v>3</v>
@@ -8546,13 +8547,13 @@
         <v>29</v>
       </c>
       <c r="C169" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D169" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>3</v>
@@ -8580,13 +8581,13 @@
         <v>29</v>
       </c>
       <c r="C170" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D170" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E170" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F170" s="10" t="s">
         <v>3</v>
@@ -8614,13 +8615,13 @@
         <v>29</v>
       </c>
       <c r="C171" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D171" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>3</v>
@@ -8648,13 +8649,13 @@
         <v>29</v>
       </c>
       <c r="C172" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D172" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E172" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F172" s="10" t="s">
         <v>3</v>
@@ -8682,13 +8683,13 @@
         <v>29</v>
       </c>
       <c r="C173" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D173" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>3</v>
@@ -8716,13 +8717,13 @@
         <v>29</v>
       </c>
       <c r="C174" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D174" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E174" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F174" s="10" t="s">
         <v>3</v>
@@ -8750,13 +8751,13 @@
         <v>29</v>
       </c>
       <c r="C175" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D175" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>3</v>
@@ -8784,13 +8785,13 @@
         <v>29</v>
       </c>
       <c r="C176" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D176" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E176" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F176" s="10" t="s">
         <v>3</v>
@@ -8818,13 +8819,13 @@
         <v>29</v>
       </c>
       <c r="C177" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D177" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F177" s="10" t="s">
         <v>3</v>
@@ -8852,13 +8853,13 @@
         <v>29</v>
       </c>
       <c r="C178" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D178" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E178" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F178" s="10" t="s">
         <v>3</v>
@@ -8886,13 +8887,13 @@
         <v>29</v>
       </c>
       <c r="C179" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D179" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F179" s="10" t="s">
         <v>3</v>
@@ -8920,13 +8921,13 @@
         <v>29</v>
       </c>
       <c r="C180" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D180" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E180" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F180" s="10" t="s">
         <v>3</v>
@@ -8954,13 +8955,13 @@
         <v>29</v>
       </c>
       <c r="C181" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D181" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F181" s="10" t="s">
         <v>3</v>
@@ -8988,13 +8989,13 @@
         <v>29</v>
       </c>
       <c r="C182" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D182" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E182" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F182" s="10" t="s">
         <v>3</v>
@@ -9022,13 +9023,13 @@
         <v>29</v>
       </c>
       <c r="C183" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D183" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F183" s="10" t="s">
         <v>3</v>
@@ -9056,13 +9057,13 @@
         <v>29</v>
       </c>
       <c r="C184" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D184" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E184" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F184" s="10" t="s">
         <v>3</v>
@@ -9090,13 +9091,13 @@
         <v>29</v>
       </c>
       <c r="C185" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D185" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>3</v>
@@ -9124,13 +9125,13 @@
         <v>29</v>
       </c>
       <c r="C186" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D186" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E186" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F186" s="10" t="s">
         <v>3</v>
@@ -9158,13 +9159,13 @@
         <v>29</v>
       </c>
       <c r="C187" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="D187" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E187" s="10" t="s">
         <v>254</v>
-      </c>
-      <c r="D187" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E187" s="10" t="s">
-        <v>255</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>3</v>
@@ -9192,13 +9193,13 @@
         <v>29</v>
       </c>
       <c r="C188" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D188" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E188" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F188" s="10" t="s">
         <v>3</v>
@@ -9226,13 +9227,13 @@
         <v>29</v>
       </c>
       <c r="C189" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D189" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F189" s="10" t="s">
         <v>3</v>
@@ -9260,13 +9261,13 @@
         <v>29</v>
       </c>
       <c r="C190" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D190" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E190" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F190" s="10" t="s">
         <v>3</v>
@@ -9294,13 +9295,13 @@
         <v>29</v>
       </c>
       <c r="C191" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D191" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>3</v>
@@ -9328,13 +9329,13 @@
         <v>29</v>
       </c>
       <c r="C192" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D192" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E192" s="10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F192" s="10" t="s">
         <v>3</v>
@@ -9362,13 +9363,13 @@
         <v>29</v>
       </c>
       <c r="C193" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D193" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F193" s="10" t="s">
         <v>3</v>
@@ -9396,7 +9397,7 @@
         <v>29</v>
       </c>
       <c r="C194" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D194" s="10" t="s">
         <v>77</v>
@@ -9430,13 +9431,13 @@
         <v>29</v>
       </c>
       <c r="C195" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D195" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F195" s="10" t="s">
         <v>3</v>
@@ -9464,13 +9465,13 @@
         <v>29</v>
       </c>
       <c r="C196" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D196" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E196" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F196" s="10" t="s">
         <v>3</v>
@@ -9498,13 +9499,13 @@
         <v>29</v>
       </c>
       <c r="C197" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D197" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F197" s="10" t="s">
         <v>3</v>
@@ -9532,13 +9533,13 @@
         <v>29</v>
       </c>
       <c r="C198" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D198" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E198" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F198" s="10" t="s">
         <v>3</v>
@@ -9566,13 +9567,13 @@
         <v>30</v>
       </c>
       <c r="C199" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="D199" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E199" s="10" t="s">
         <v>266</v>
-      </c>
-      <c r="D199" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E199" s="10" t="s">
-        <v>267</v>
       </c>
       <c r="F199" s="10" t="s">
         <v>3</v>
@@ -9600,13 +9601,13 @@
         <v>30</v>
       </c>
       <c r="C200" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D200" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E200" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F200" s="10" t="s">
         <v>3</v>
@@ -9634,13 +9635,13 @@
         <v>30</v>
       </c>
       <c r="C201" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D201" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>3</v>
@@ -9668,13 +9669,13 @@
         <v>30</v>
       </c>
       <c r="C202" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D202" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E202" s="10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F202" s="10" t="s">
         <v>3</v>
@@ -9702,13 +9703,13 @@
         <v>30</v>
       </c>
       <c r="C203" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D203" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>3</v>
@@ -9736,13 +9737,13 @@
         <v>30</v>
       </c>
       <c r="C204" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D204" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E204" s="10" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F204" s="10" t="s">
         <v>3</v>
@@ -9770,13 +9771,13 @@
         <v>30</v>
       </c>
       <c r="C205" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D205" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>3</v>
@@ -9804,13 +9805,13 @@
         <v>30</v>
       </c>
       <c r="C206" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D206" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E206" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F206" s="10" t="s">
         <v>3</v>
@@ -9838,13 +9839,13 @@
         <v>30</v>
       </c>
       <c r="C207" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D207" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>3</v>
@@ -9872,13 +9873,13 @@
         <v>30</v>
       </c>
       <c r="C208" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D208" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E208" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F208" s="10" t="s">
         <v>3</v>
@@ -9906,13 +9907,13 @@
         <v>30</v>
       </c>
       <c r="C209" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D209" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>3</v>
@@ -9940,13 +9941,13 @@
         <v>30</v>
       </c>
       <c r="C210" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D210" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E210" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F210" s="10" t="s">
         <v>3</v>
@@ -9974,13 +9975,13 @@
         <v>30</v>
       </c>
       <c r="C211" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D211" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E211" s="10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F211" s="10" t="s">
         <v>3</v>
@@ -10008,13 +10009,13 @@
         <v>30</v>
       </c>
       <c r="C212" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D212" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E212" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F212" s="10" t="s">
         <v>3</v>
@@ -10042,13 +10043,13 @@
         <v>30</v>
       </c>
       <c r="C213" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D213" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E213" s="10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F213" s="10" t="s">
         <v>3</v>
@@ -10076,13 +10077,13 @@
         <v>30</v>
       </c>
       <c r="C214" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D214" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E214" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F214" s="10" t="s">
         <v>3</v>
@@ -10110,13 +10111,13 @@
         <v>30</v>
       </c>
       <c r="C215" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D215" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E215" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F215" s="10" t="s">
         <v>3</v>
@@ -10144,13 +10145,13 @@
         <v>31</v>
       </c>
       <c r="C216" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="D216" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E216" s="10" t="s">
         <v>284</v>
-      </c>
-      <c r="D216" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E216" s="10" t="s">
-        <v>285</v>
       </c>
       <c r="F216" s="10" t="s">
         <v>3</v>
@@ -10178,13 +10179,13 @@
         <v>31</v>
       </c>
       <c r="C217" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D217" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E217" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F217" s="10" t="s">
         <v>3</v>
@@ -10212,13 +10213,13 @@
         <v>31</v>
       </c>
       <c r="C218" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D218" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E218" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F218" s="10" t="s">
         <v>3</v>
@@ -10246,13 +10247,13 @@
         <v>31</v>
       </c>
       <c r="C219" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D219" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>3</v>
@@ -10280,13 +10281,13 @@
         <v>31</v>
       </c>
       <c r="C220" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D220" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E220" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F220" s="10" t="s">
         <v>3</v>
@@ -10314,13 +10315,13 @@
         <v>31</v>
       </c>
       <c r="C221" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D221" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E221" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F221" s="10" t="s">
         <v>3</v>
@@ -10348,13 +10349,13 @@
         <v>31</v>
       </c>
       <c r="C222" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D222" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E222" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F222" s="10" t="s">
         <v>3</v>
@@ -10382,13 +10383,13 @@
         <v>31</v>
       </c>
       <c r="C223" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D223" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E223" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F223" s="10" t="s">
         <v>3</v>
@@ -10416,13 +10417,13 @@
         <v>31</v>
       </c>
       <c r="C224" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D224" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="E224" s="10" t="s">
         <v>293</v>
-      </c>
-      <c r="E224" s="10" t="s">
-        <v>294</v>
       </c>
       <c r="F224" s="10" t="s">
         <v>3</v>
@@ -10450,13 +10451,13 @@
         <v>31</v>
       </c>
       <c r="C225" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D225" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E225" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F225" s="10" t="s">
         <v>3</v>
@@ -10484,13 +10485,13 @@
         <v>31</v>
       </c>
       <c r="C226" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D226" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E226" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F226" s="10" t="s">
         <v>3</v>
@@ -10518,13 +10519,13 @@
         <v>31</v>
       </c>
       <c r="C227" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D227" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E227" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F227" s="10" t="s">
         <v>3</v>
@@ -10552,13 +10553,13 @@
         <v>31</v>
       </c>
       <c r="C228" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D228" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E228" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F228" s="10" t="s">
         <v>3</v>
@@ -10586,13 +10587,13 @@
         <v>31</v>
       </c>
       <c r="C229" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D229" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E229" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F229" s="10" t="s">
         <v>3</v>
@@ -10620,13 +10621,13 @@
         <v>31</v>
       </c>
       <c r="C230" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D230" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E230" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F230" s="10" t="s">
         <v>3</v>
@@ -10654,13 +10655,13 @@
         <v>31</v>
       </c>
       <c r="C231" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D231" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E231" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F231" s="10" t="s">
         <v>3</v>
@@ -10688,13 +10689,13 @@
         <v>31</v>
       </c>
       <c r="C232" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D232" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E232" s="10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F232" s="10" t="s">
         <v>3</v>
@@ -10722,13 +10723,13 @@
         <v>31</v>
       </c>
       <c r="C233" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D233" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E233" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F233" s="10" t="s">
         <v>3</v>
@@ -10756,13 +10757,13 @@
         <v>31</v>
       </c>
       <c r="C234" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D234" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E234" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F234" s="10" t="s">
         <v>3</v>
@@ -10790,13 +10791,13 @@
         <v>31</v>
       </c>
       <c r="C235" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D235" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E235" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F235" s="10" t="s">
         <v>3</v>
@@ -10824,13 +10825,13 @@
         <v>31</v>
       </c>
       <c r="C236" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D236" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E236" s="10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F236" s="10" t="s">
         <v>3</v>
@@ -10858,13 +10859,13 @@
         <v>31</v>
       </c>
       <c r="C237" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D237" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E237" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F237" s="10" t="s">
         <v>3</v>
@@ -10892,13 +10893,13 @@
         <v>31</v>
       </c>
       <c r="C238" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="D238" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E238" s="10" t="s">
         <v>308</v>
-      </c>
-      <c r="D238" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E238" s="10" t="s">
-        <v>309</v>
       </c>
       <c r="F238" s="10" t="s">
         <v>3</v>
@@ -10926,13 +10927,13 @@
         <v>31</v>
       </c>
       <c r="C239" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D239" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E239" s="10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F239" s="10" t="s">
         <v>3</v>
@@ -10960,13 +10961,13 @@
         <v>31</v>
       </c>
       <c r="C240" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D240" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E240" s="10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F240" s="10" t="s">
         <v>3</v>
@@ -10994,13 +10995,13 @@
         <v>31</v>
       </c>
       <c r="C241" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D241" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E241" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F241" s="10" t="s">
         <v>3</v>
@@ -11028,13 +11029,13 @@
         <v>31</v>
       </c>
       <c r="C242" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D242" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E242" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F242" s="10" t="s">
         <v>3</v>
@@ -11062,13 +11063,13 @@
         <v>31</v>
       </c>
       <c r="C243" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D243" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E243" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F243" s="10" t="s">
         <v>3</v>
@@ -11096,13 +11097,13 @@
         <v>31</v>
       </c>
       <c r="C244" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D244" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E244" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F244" s="10" t="s">
         <v>3</v>
@@ -11130,13 +11131,13 @@
         <v>31</v>
       </c>
       <c r="C245" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D245" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E245" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F245" s="10" t="s">
         <v>3</v>
@@ -11164,13 +11165,13 @@
         <v>31</v>
       </c>
       <c r="C246" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D246" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E246" s="10" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F246" s="10" t="s">
         <v>3</v>
@@ -11198,13 +11199,13 @@
         <v>31</v>
       </c>
       <c r="C247" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D247" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E247" s="10" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F247" s="10" t="s">
         <v>3</v>
@@ -11232,13 +11233,13 @@
         <v>31</v>
       </c>
       <c r="C248" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D248" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E248" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F248" s="10" t="s">
         <v>3</v>
@@ -11266,13 +11267,13 @@
         <v>31</v>
       </c>
       <c r="C249" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D249" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E249" s="10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F249" s="10" t="s">
         <v>3</v>
@@ -11300,13 +11301,13 @@
         <v>31</v>
       </c>
       <c r="C250" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D250" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E250" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F250" s="10" t="s">
         <v>3</v>
@@ -11334,13 +11335,13 @@
         <v>31</v>
       </c>
       <c r="C251" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D251" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E251" s="10" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F251" s="10" t="s">
         <v>3</v>
@@ -11368,13 +11369,13 @@
         <v>31</v>
       </c>
       <c r="C252" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D252" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E252" s="10" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F252" s="10" t="s">
         <v>3</v>
@@ -11402,13 +11403,13 @@
         <v>31</v>
       </c>
       <c r="C253" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D253" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E253" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F253" s="10" t="s">
         <v>3</v>
@@ -11436,13 +11437,13 @@
         <v>31</v>
       </c>
       <c r="C254" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D254" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E254" s="10" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F254" s="10" t="s">
         <v>3</v>
@@ -11470,13 +11471,13 @@
         <v>31</v>
       </c>
       <c r="C255" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="D255" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E255" s="10" t="s">
         <v>326</v>
-      </c>
-      <c r="D255" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E255" s="10" t="s">
-        <v>327</v>
       </c>
       <c r="F255" s="10" t="s">
         <v>3</v>
@@ -11504,13 +11505,13 @@
         <v>31</v>
       </c>
       <c r="C256" s="10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D256" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E256" s="10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F256" s="10" t="s">
         <v>3</v>
@@ -11538,13 +11539,13 @@
         <v>31</v>
       </c>
       <c r="C257" s="10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D257" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E257" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F257" s="10" t="s">
         <v>3</v>
@@ -11572,13 +11573,13 @@
         <v>31</v>
       </c>
       <c r="C258" s="10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D258" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E258" s="10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F258" s="10" t="s">
         <v>3</v>
@@ -11606,13 +11607,13 @@
         <v>31</v>
       </c>
       <c r="C259" s="10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D259" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E259" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F259" s="10" t="s">
         <v>3</v>
@@ -11640,13 +11641,13 @@
         <v>31</v>
       </c>
       <c r="C260" s="10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D260" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E260" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F260" s="10" t="s">
         <v>3</v>
@@ -11674,13 +11675,13 @@
         <v>31</v>
       </c>
       <c r="C261" s="10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D261" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E261" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F261" s="10" t="s">
         <v>3</v>
@@ -11708,13 +11709,13 @@
         <v>31</v>
       </c>
       <c r="C262" s="10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D262" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E262" s="10" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F262" s="10" t="s">
         <v>3</v>
@@ -11742,13 +11743,13 @@
         <v>32</v>
       </c>
       <c r="C263" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="D263" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E263" s="10" t="s">
         <v>335</v>
-      </c>
-      <c r="D263" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E263" s="10" t="s">
-        <v>336</v>
       </c>
       <c r="F263" s="10" t="s">
         <v>3</v>
@@ -11776,13 +11777,13 @@
         <v>32</v>
       </c>
       <c r="C264" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D264" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E264" s="10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F264" s="10" t="s">
         <v>3</v>
@@ -11810,13 +11811,13 @@
         <v>32</v>
       </c>
       <c r="C265" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D265" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E265" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F265" s="10" t="s">
         <v>3</v>
@@ -11844,13 +11845,13 @@
         <v>32</v>
       </c>
       <c r="C266" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D266" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E266" s="10" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F266" s="10" t="s">
         <v>3</v>
@@ -11878,13 +11879,13 @@
         <v>32</v>
       </c>
       <c r="C267" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D267" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E267" s="10" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F267" s="10" t="s">
         <v>3</v>
@@ -11912,13 +11913,13 @@
         <v>32</v>
       </c>
       <c r="C268" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D268" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E268" s="10" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F268" s="10" t="s">
         <v>3</v>
@@ -11946,13 +11947,13 @@
         <v>32</v>
       </c>
       <c r="C269" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D269" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E269" s="10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F269" s="10" t="s">
         <v>3</v>
@@ -11980,13 +11981,13 @@
         <v>32</v>
       </c>
       <c r="C270" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D270" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E270" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F270" s="10" t="s">
         <v>3</v>
@@ -12014,13 +12015,13 @@
         <v>32</v>
       </c>
       <c r="C271" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D271" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E271" s="10" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F271" s="10" t="s">
         <v>3</v>
@@ -12048,13 +12049,13 @@
         <v>32</v>
       </c>
       <c r="C272" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D272" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E272" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F272" s="10" t="s">
         <v>3</v>
@@ -12082,13 +12083,13 @@
         <v>32</v>
       </c>
       <c r="C273" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D273" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E273" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F273" s="10" t="s">
         <v>3</v>
@@ -12116,13 +12117,13 @@
         <v>32</v>
       </c>
       <c r="C274" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D274" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E274" s="10" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F274" s="10" t="s">
         <v>3</v>
@@ -12150,13 +12151,13 @@
         <v>32</v>
       </c>
       <c r="C275" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D275" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E275" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F275" s="10" t="s">
         <v>3</v>
@@ -12184,13 +12185,13 @@
         <v>32</v>
       </c>
       <c r="C276" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D276" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E276" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F276" s="10" t="s">
         <v>3</v>
@@ -12218,13 +12219,13 @@
         <v>32</v>
       </c>
       <c r="C277" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D277" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E277" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F277" s="10" t="s">
         <v>3</v>
@@ -12252,13 +12253,13 @@
         <v>32</v>
       </c>
       <c r="C278" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D278" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E278" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F278" s="10" t="s">
         <v>3</v>
@@ -12286,13 +12287,13 @@
         <v>32</v>
       </c>
       <c r="C279" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="D279" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E279" s="10" t="s">
         <v>351</v>
-      </c>
-      <c r="D279" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E279" s="10" t="s">
-        <v>352</v>
       </c>
       <c r="F279" s="10" t="s">
         <v>3</v>
@@ -12320,13 +12321,13 @@
         <v>32</v>
       </c>
       <c r="C280" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D280" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E280" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F280" s="10" t="s">
         <v>3</v>
@@ -12354,13 +12355,13 @@
         <v>32</v>
       </c>
       <c r="C281" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D281" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E281" s="10" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F281" s="10" t="s">
         <v>3</v>
@@ -12388,13 +12389,13 @@
         <v>32</v>
       </c>
       <c r="C282" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D282" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E282" s="10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F282" s="10" t="s">
         <v>3</v>
@@ -12422,13 +12423,13 @@
         <v>32</v>
       </c>
       <c r="C283" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D283" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E283" s="10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F283" s="10" t="s">
         <v>3</v>
@@ -12456,13 +12457,13 @@
         <v>32</v>
       </c>
       <c r="C284" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D284" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E284" s="10" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F284" s="10" t="s">
         <v>3</v>
@@ -12490,13 +12491,13 @@
         <v>32</v>
       </c>
       <c r="C285" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D285" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E285" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F285" s="10" t="s">
         <v>3</v>
@@ -12524,13 +12525,13 @@
         <v>32</v>
       </c>
       <c r="C286" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D286" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E286" s="10" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F286" s="10" t="s">
         <v>3</v>
@@ -12558,13 +12559,13 @@
         <v>32</v>
       </c>
       <c r="C287" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D287" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E287" s="10" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F287" s="10" t="s">
         <v>3</v>
@@ -12592,13 +12593,13 @@
         <v>32</v>
       </c>
       <c r="C288" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D288" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E288" s="10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F288" s="10" t="s">
         <v>3</v>
@@ -12626,13 +12627,13 @@
         <v>32</v>
       </c>
       <c r="C289" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D289" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E289" s="10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F289" s="10" t="s">
         <v>3</v>
@@ -12660,13 +12661,13 @@
         <v>32</v>
       </c>
       <c r="C290" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D290" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E290" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F290" s="10" t="s">
         <v>3</v>
@@ -12694,13 +12695,13 @@
         <v>32</v>
       </c>
       <c r="C291" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D291" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E291" s="10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F291" s="10" t="s">
         <v>3</v>
@@ -12728,13 +12729,13 @@
         <v>32</v>
       </c>
       <c r="C292" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D292" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E292" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F292" s="10" t="s">
         <v>3</v>
@@ -12762,13 +12763,13 @@
         <v>32</v>
       </c>
       <c r="C293" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D293" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E293" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F293" s="10" t="s">
         <v>3</v>
@@ -12796,13 +12797,13 @@
         <v>32</v>
       </c>
       <c r="C294" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="D294" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E294" s="10" t="s">
         <v>367</v>
-      </c>
-      <c r="D294" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E294" s="10" t="s">
-        <v>368</v>
       </c>
       <c r="F294" s="10" t="s">
         <v>3</v>
@@ -12830,13 +12831,13 @@
         <v>32</v>
       </c>
       <c r="C295" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D295" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E295" s="10" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F295" s="10" t="s">
         <v>3</v>
@@ -12864,13 +12865,13 @@
         <v>32</v>
       </c>
       <c r="C296" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D296" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E296" s="10" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F296" s="10" t="s">
         <v>3</v>
@@ -12898,13 +12899,13 @@
         <v>32</v>
       </c>
       <c r="C297" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D297" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E297" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F297" s="10" t="s">
         <v>3</v>
@@ -12932,13 +12933,13 @@
         <v>32</v>
       </c>
       <c r="C298" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D298" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E298" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F298" s="10" t="s">
         <v>3</v>
@@ -12966,13 +12967,13 @@
         <v>32</v>
       </c>
       <c r="C299" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D299" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E299" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F299" s="10" t="s">
         <v>3</v>
@@ -13000,13 +13001,13 @@
         <v>32</v>
       </c>
       <c r="C300" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D300" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E300" s="10" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F300" s="10" t="s">
         <v>3</v>
@@ -13034,13 +13035,13 @@
         <v>32</v>
       </c>
       <c r="C301" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D301" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E301" s="10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F301" s="10" t="s">
         <v>3</v>
@@ -13068,13 +13069,13 @@
         <v>32</v>
       </c>
       <c r="C302" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D302" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E302" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F302" s="10" t="s">
         <v>3</v>
@@ -13102,13 +13103,13 @@
         <v>32</v>
       </c>
       <c r="C303" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D303" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E303" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F303" s="10" t="s">
         <v>3</v>
@@ -13136,13 +13137,13 @@
         <v>32</v>
       </c>
       <c r="C304" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D304" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E304" s="10" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F304" s="10" t="s">
         <v>3</v>
@@ -13170,13 +13171,13 @@
         <v>32</v>
       </c>
       <c r="C305" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D305" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E305" s="10" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F305" s="10" t="s">
         <v>3</v>
@@ -13204,13 +13205,13 @@
         <v>32</v>
       </c>
       <c r="C306" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D306" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E306" s="10" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F306" s="10" t="s">
         <v>3</v>
@@ -13238,13 +13239,13 @@
         <v>32</v>
       </c>
       <c r="C307" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D307" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E307" s="10" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F307" s="10" t="s">
         <v>3</v>
@@ -13272,13 +13273,13 @@
         <v>32</v>
       </c>
       <c r="C308" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="D308" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E308" s="10" t="s">
         <v>382</v>
-      </c>
-      <c r="D308" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E308" s="10" t="s">
-        <v>383</v>
       </c>
       <c r="F308" s="10" t="s">
         <v>3</v>
@@ -13306,13 +13307,13 @@
         <v>32</v>
       </c>
       <c r="C309" s="10" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D309" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E309" s="10" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F309" s="10" t="s">
         <v>3</v>
@@ -13340,13 +13341,13 @@
         <v>32</v>
       </c>
       <c r="C310" s="10" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D310" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E310" s="10" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F310" s="10" t="s">
         <v>3</v>
@@ -13374,13 +13375,13 @@
         <v>32</v>
       </c>
       <c r="C311" s="10" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D311" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E311" s="10" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F311" s="10" t="s">
         <v>3</v>
@@ -13408,13 +13409,13 @@
         <v>32</v>
       </c>
       <c r="C312" s="10" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D312" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E312" s="10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F312" s="10" t="s">
         <v>3</v>
@@ -13442,13 +13443,13 @@
         <v>32</v>
       </c>
       <c r="C313" s="10" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D313" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E313" s="10" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F313" s="10" t="s">
         <v>3</v>
@@ -13476,13 +13477,13 @@
         <v>32</v>
       </c>
       <c r="C314" s="10" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D314" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E314" s="10" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F314" s="10" t="s">
         <v>3</v>
@@ -13510,13 +13511,13 @@
         <v>32</v>
       </c>
       <c r="C315" s="10" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D315" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E315" s="10" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F315" s="10" t="s">
         <v>3</v>
@@ -13544,13 +13545,13 @@
         <v>32</v>
       </c>
       <c r="C316" s="10" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D316" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E316" s="10" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F316" s="10" t="s">
         <v>3</v>
@@ -13578,13 +13579,13 @@
         <v>32</v>
       </c>
       <c r="C317" s="10" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D317" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E317" s="10" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F317" s="10" t="s">
         <v>3</v>
@@ -13612,13 +13613,13 @@
         <v>32</v>
       </c>
       <c r="C318" s="10" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D318" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E318" s="10" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F318" s="10" t="s">
         <v>3</v>
@@ -13646,13 +13647,13 @@
         <v>32</v>
       </c>
       <c r="C319" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="D319" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E319" s="10" t="s">
         <v>394</v>
-      </c>
-      <c r="D319" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E319" s="10" t="s">
-        <v>395</v>
       </c>
       <c r="F319" s="10" t="s">
         <v>3</v>
@@ -13680,13 +13681,13 @@
         <v>32</v>
       </c>
       <c r="C320" s="10" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D320" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E320" s="10" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="F320" s="10" t="s">
         <v>3</v>
@@ -13714,13 +13715,13 @@
         <v>32</v>
       </c>
       <c r="C321" s="10" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D321" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E321" s="10" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F321" s="10" t="s">
         <v>3</v>
@@ -13748,13 +13749,13 @@
         <v>32</v>
       </c>
       <c r="C322" s="10" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D322" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E322" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F322" s="10" t="s">
         <v>3</v>
@@ -13782,13 +13783,13 @@
         <v>32</v>
       </c>
       <c r="C323" s="10" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D323" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E323" s="10" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F323" s="10" t="s">
         <v>3</v>
@@ -13816,13 +13817,13 @@
         <v>32</v>
       </c>
       <c r="C324" s="10" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D324" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E324" s="10" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F324" s="10" t="s">
         <v>3</v>
@@ -13850,13 +13851,13 @@
         <v>32</v>
       </c>
       <c r="C325" s="10" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D325" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E325" s="10" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F325" s="10" t="s">
         <v>3</v>
@@ -13884,13 +13885,13 @@
         <v>32</v>
       </c>
       <c r="C326" s="10" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D326" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E326" s="10" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F326" s="10" t="s">
         <v>3</v>
@@ -13918,13 +13919,13 @@
         <v>32</v>
       </c>
       <c r="C327" s="10" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D327" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E327" s="10" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F327" s="10" t="s">
         <v>3</v>
@@ -13952,13 +13953,13 @@
         <v>32</v>
       </c>
       <c r="C328" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="D328" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E328" s="10" t="s">
         <v>404</v>
-      </c>
-      <c r="D328" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E328" s="10" t="s">
-        <v>405</v>
       </c>
       <c r="F328" s="10" t="s">
         <v>3</v>
@@ -13986,13 +13987,13 @@
         <v>32</v>
       </c>
       <c r="C329" s="10" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D329" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E329" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F329" s="10" t="s">
         <v>3</v>
@@ -14020,13 +14021,13 @@
         <v>32</v>
       </c>
       <c r="C330" s="10" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D330" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E330" s="10" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F330" s="10" t="s">
         <v>3</v>
@@ -14054,13 +14055,13 @@
         <v>32</v>
       </c>
       <c r="C331" s="10" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D331" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E331" s="10" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F331" s="10" t="s">
         <v>3</v>
@@ -14088,13 +14089,13 @@
         <v>32</v>
       </c>
       <c r="C332" s="10" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D332" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E332" s="10" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F332" s="10" t="s">
         <v>3</v>
@@ -14122,13 +14123,13 @@
         <v>32</v>
       </c>
       <c r="C333" s="10" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D333" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E333" s="10" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F333" s="10" t="s">
         <v>3</v>
@@ -14156,13 +14157,13 @@
         <v>32</v>
       </c>
       <c r="C334" s="10" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D334" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E334" s="10" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F334" s="10" t="s">
         <v>3</v>
@@ -14190,13 +14191,13 @@
         <v>32</v>
       </c>
       <c r="C335" s="10" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D335" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E335" s="10" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F335" s="10" t="s">
         <v>3</v>
@@ -14224,13 +14225,13 @@
         <v>32</v>
       </c>
       <c r="C336" s="10" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D336" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E336" s="10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F336" s="10" t="s">
         <v>3</v>
@@ -14258,13 +14259,13 @@
         <v>32</v>
       </c>
       <c r="C337" s="10" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D337" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E337" s="10" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F337" s="10" t="s">
         <v>3</v>
@@ -14292,13 +14293,13 @@
         <v>32</v>
       </c>
       <c r="C338" s="10" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D338" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E338" s="10" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F338" s="10" t="s">
         <v>3</v>
@@ -14326,13 +14327,13 @@
         <v>32</v>
       </c>
       <c r="C339" s="10" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D339" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E339" s="10" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F339" s="10" t="s">
         <v>3</v>
@@ -14360,13 +14361,13 @@
         <v>32</v>
       </c>
       <c r="C340" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="D340" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E340" s="10" t="s">
         <v>417</v>
-      </c>
-      <c r="D340" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E340" s="10" t="s">
-        <v>418</v>
       </c>
       <c r="F340" s="10" t="s">
         <v>3</v>
@@ -14394,13 +14395,13 @@
         <v>32</v>
       </c>
       <c r="C341" s="10" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D341" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E341" s="10" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="F341" s="10" t="s">
         <v>3</v>
@@ -14428,13 +14429,13 @@
         <v>32</v>
       </c>
       <c r="C342" s="10" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D342" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E342" s="10" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F342" s="10" t="s">
         <v>3</v>
@@ -14462,13 +14463,13 @@
         <v>32</v>
       </c>
       <c r="C343" s="10" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D343" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E343" s="10" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F343" s="10" t="s">
         <v>3</v>
@@ -14496,13 +14497,13 @@
         <v>32</v>
       </c>
       <c r="C344" s="10" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D344" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E344" s="10" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F344" s="10" t="s">
         <v>3</v>
@@ -14530,13 +14531,13 @@
         <v>32</v>
       </c>
       <c r="C345" s="10" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D345" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E345" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F345" s="10" t="s">
         <v>3</v>
@@ -14564,13 +14565,13 @@
         <v>32</v>
       </c>
       <c r="C346" s="10" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D346" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E346" s="10" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="F346" s="10" t="s">
         <v>3</v>
@@ -14598,13 +14599,13 @@
         <v>32</v>
       </c>
       <c r="C347" s="10" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D347" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E347" s="10" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F347" s="10" t="s">
         <v>3</v>
@@ -14632,13 +14633,13 @@
         <v>32</v>
       </c>
       <c r="C348" s="10" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D348" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E348" s="10" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F348" s="10" t="s">
         <v>3</v>
@@ -14666,13 +14667,13 @@
         <v>32</v>
       </c>
       <c r="C349" s="10" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D349" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E349" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F349" s="10" t="s">
         <v>3</v>
@@ -14700,13 +14701,13 @@
         <v>32</v>
       </c>
       <c r="C350" s="10" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D350" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E350" s="10" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F350" s="10" t="s">
         <v>3</v>
@@ -14734,13 +14735,13 @@
         <v>32</v>
       </c>
       <c r="C351" s="10" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D351" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E351" s="10" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F351" s="10" t="s">
         <v>3</v>
@@ -14768,13 +14769,13 @@
         <v>32</v>
       </c>
       <c r="C352" s="10" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D352" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E352" s="10" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F352" s="10" t="s">
         <v>3</v>
@@ -14802,13 +14803,13 @@
         <v>32</v>
       </c>
       <c r="C353" s="10" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D353" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E353" s="10" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F353" s="10" t="s">
         <v>3</v>
@@ -14836,13 +14837,13 @@
         <v>32</v>
       </c>
       <c r="C354" s="10" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D354" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E354" s="10" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F354" s="10" t="s">
         <v>3</v>
@@ -14870,13 +14871,13 @@
         <v>32</v>
       </c>
       <c r="C355" s="10" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D355" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E355" s="10" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F355" s="10" t="s">
         <v>3</v>
@@ -14904,13 +14905,13 @@
         <v>32</v>
       </c>
       <c r="C356" s="10" t="s">
+        <v>432</v>
+      </c>
+      <c r="D356" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E356" s="10" t="s">
         <v>433</v>
-      </c>
-      <c r="D356" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E356" s="10" t="s">
-        <v>434</v>
       </c>
       <c r="F356" s="10" t="s">
         <v>3</v>
@@ -14938,13 +14939,13 @@
         <v>32</v>
       </c>
       <c r="C357" s="10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D357" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E357" s="10" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F357" s="10" t="s">
         <v>3</v>
@@ -14972,13 +14973,13 @@
         <v>32</v>
       </c>
       <c r="C358" s="10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D358" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E358" s="10" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F358" s="10" t="s">
         <v>3</v>
@@ -15006,13 +15007,13 @@
         <v>32</v>
       </c>
       <c r="C359" s="10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D359" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E359" s="10" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F359" s="10" t="s">
         <v>3</v>
@@ -15040,13 +15041,13 @@
         <v>32</v>
       </c>
       <c r="C360" s="10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D360" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E360" s="10" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F360" s="10" t="s">
         <v>3</v>
@@ -15074,13 +15075,13 @@
         <v>32</v>
       </c>
       <c r="C361" s="10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D361" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E361" s="10" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F361" s="10" t="s">
         <v>3</v>
@@ -15108,13 +15109,13 @@
         <v>32</v>
       </c>
       <c r="C362" s="10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D362" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E362" s="10" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F362" s="10" t="s">
         <v>3</v>
@@ -15142,13 +15143,13 @@
         <v>32</v>
       </c>
       <c r="C363" s="10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D363" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E363" s="10" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F363" s="10" t="s">
         <v>3</v>
@@ -15176,13 +15177,13 @@
         <v>33</v>
       </c>
       <c r="C364" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="D364" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E364" s="10" t="s">
         <v>442</v>
-      </c>
-      <c r="D364" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E364" s="10" t="s">
-        <v>443</v>
       </c>
       <c r="F364" s="10" t="s">
         <v>3</v>
@@ -15210,13 +15211,13 @@
         <v>33</v>
       </c>
       <c r="C365" s="10" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D365" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E365" s="10" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F365" s="10" t="s">
         <v>3</v>
@@ -15244,13 +15245,13 @@
         <v>33</v>
       </c>
       <c r="C366" s="10" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D366" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E366" s="10" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F366" s="10" t="s">
         <v>3</v>
@@ -15278,13 +15279,13 @@
         <v>33</v>
       </c>
       <c r="C367" s="10" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D367" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E367" s="10" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F367" s="10" t="s">
         <v>3</v>
@@ -15312,13 +15313,13 @@
         <v>33</v>
       </c>
       <c r="C368" s="10" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D368" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E368" s="10" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F368" s="10" t="s">
         <v>3</v>
@@ -15346,13 +15347,13 @@
         <v>33</v>
       </c>
       <c r="C369" s="10" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D369" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E369" s="10" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F369" s="10" t="s">
         <v>3</v>
@@ -15380,13 +15381,13 @@
         <v>33</v>
       </c>
       <c r="C370" s="10" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D370" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E370" s="10" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F370" s="10" t="s">
         <v>3</v>
@@ -15414,13 +15415,13 @@
         <v>33</v>
       </c>
       <c r="C371" s="10" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D371" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E371" s="10" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F371" s="10" t="s">
         <v>3</v>
@@ -15448,13 +15449,13 @@
         <v>33</v>
       </c>
       <c r="C372" s="10" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D372" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E372" s="10" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F372" s="10" t="s">
         <v>3</v>
@@ -15482,13 +15483,13 @@
         <v>33</v>
       </c>
       <c r="C373" s="10" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D373" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E373" s="10" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F373" s="10" t="s">
         <v>3</v>
@@ -15516,13 +15517,13 @@
         <v>33</v>
       </c>
       <c r="C374" s="10" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D374" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E374" s="10" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F374" s="10" t="s">
         <v>3</v>
@@ -15550,13 +15551,13 @@
         <v>33</v>
       </c>
       <c r="C375" s="10" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D375" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E375" s="10" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F375" s="10" t="s">
         <v>3</v>
@@ -15584,13 +15585,13 @@
         <v>33</v>
       </c>
       <c r="C376" s="10" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D376" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E376" s="10" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F376" s="10" t="s">
         <v>3</v>
@@ -15618,13 +15619,13 @@
         <v>33</v>
       </c>
       <c r="C377" s="10" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D377" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E377" s="10" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F377" s="10" t="s">
         <v>3</v>
@@ -15652,13 +15653,13 @@
         <v>33</v>
       </c>
       <c r="C378" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="D378" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E378" s="10" t="s">
         <v>456</v>
-      </c>
-      <c r="D378" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E378" s="10" t="s">
-        <v>457</v>
       </c>
       <c r="F378" s="10" t="s">
         <v>3</v>
@@ -15686,13 +15687,13 @@
         <v>33</v>
       </c>
       <c r="C379" s="10" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D379" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E379" s="10" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F379" s="10" t="s">
         <v>3</v>
@@ -15720,13 +15721,13 @@
         <v>33</v>
       </c>
       <c r="C380" s="10" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D380" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E380" s="10" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F380" s="10" t="s">
         <v>3</v>
@@ -15754,13 +15755,13 @@
         <v>33</v>
       </c>
       <c r="C381" s="10" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D381" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E381" s="10" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F381" s="10" t="s">
         <v>3</v>
@@ -15788,13 +15789,13 @@
         <v>33</v>
       </c>
       <c r="C382" s="10" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D382" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E382" s="10" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F382" s="10" t="s">
         <v>3</v>
@@ -15822,13 +15823,13 @@
         <v>33</v>
       </c>
       <c r="C383" s="10" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D383" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E383" s="10" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F383" s="10" t="s">
         <v>3</v>
@@ -15856,13 +15857,13 @@
         <v>33</v>
       </c>
       <c r="C384" s="10" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D384" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E384" s="10" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F384" s="10" t="s">
         <v>3</v>
@@ -15890,13 +15891,13 @@
         <v>33</v>
       </c>
       <c r="C385" s="10" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D385" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E385" s="10" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F385" s="10" t="s">
         <v>3</v>
@@ -15924,13 +15925,13 @@
         <v>33</v>
       </c>
       <c r="C386" s="10" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D386" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E386" s="10" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F386" s="10" t="s">
         <v>3</v>
@@ -15958,13 +15959,13 @@
         <v>33</v>
       </c>
       <c r="C387" s="10" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D387" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E387" s="10" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F387" s="10" t="s">
         <v>3</v>
@@ -15992,13 +15993,13 @@
         <v>33</v>
       </c>
       <c r="C388" s="10" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D388" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E388" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F388" s="10" t="s">
         <v>3</v>
@@ -16026,13 +16027,13 @@
         <v>33</v>
       </c>
       <c r="C389" s="10" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D389" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E389" s="10" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F389" s="10" t="s">
         <v>3</v>
@@ -16060,13 +16061,13 @@
         <v>33</v>
       </c>
       <c r="C390" s="10" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D390" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E390" s="10" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F390" s="10" t="s">
         <v>3</v>
@@ -16094,13 +16095,13 @@
         <v>33</v>
       </c>
       <c r="C391" s="10" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D391" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E391" s="10" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F391" s="10" t="s">
         <v>3</v>
@@ -16128,13 +16129,13 @@
         <v>33</v>
       </c>
       <c r="C392" s="10" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D392" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E392" s="10" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F392" s="10" t="s">
         <v>3</v>
@@ -16162,13 +16163,13 @@
         <v>33</v>
       </c>
       <c r="C393" s="10" t="s">
+        <v>471</v>
+      </c>
+      <c r="D393" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E393" s="10" t="s">
         <v>472</v>
-      </c>
-      <c r="D393" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E393" s="10" t="s">
-        <v>473</v>
       </c>
       <c r="F393" s="10" t="s">
         <v>3</v>
@@ -16196,13 +16197,13 @@
         <v>33</v>
       </c>
       <c r="C394" s="10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D394" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E394" s="10" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F394" s="10" t="s">
         <v>3</v>
@@ -16230,13 +16231,13 @@
         <v>33</v>
       </c>
       <c r="C395" s="10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D395" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E395" s="10" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F395" s="10" t="s">
         <v>3</v>
@@ -16264,13 +16265,13 @@
         <v>33</v>
       </c>
       <c r="C396" s="10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D396" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E396" s="10" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F396" s="10" t="s">
         <v>3</v>
@@ -16298,13 +16299,13 @@
         <v>33</v>
       </c>
       <c r="C397" s="10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D397" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E397" s="10" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F397" s="10" t="s">
         <v>3</v>
@@ -16332,13 +16333,13 @@
         <v>33</v>
       </c>
       <c r="C398" s="10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D398" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E398" s="10" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F398" s="10" t="s">
         <v>3</v>
@@ -16366,13 +16367,13 @@
         <v>33</v>
       </c>
       <c r="C399" s="10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D399" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E399" s="10" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F399" s="10" t="s">
         <v>3</v>
@@ -16400,13 +16401,13 @@
         <v>33</v>
       </c>
       <c r="C400" s="10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D400" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E400" s="10" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F400" s="10" t="s">
         <v>3</v>
@@ -16434,13 +16435,13 @@
         <v>33</v>
       </c>
       <c r="C401" s="10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D401" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E401" s="10" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F401" s="10" t="s">
         <v>3</v>
@@ -16468,13 +16469,13 @@
         <v>33</v>
       </c>
       <c r="C402" s="10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D402" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E402" s="10" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F402" s="10" t="s">
         <v>3</v>
@@ -16502,13 +16503,13 @@
         <v>33</v>
       </c>
       <c r="C403" s="10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D403" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E403" s="10" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F403" s="10" t="s">
         <v>3</v>
@@ -16536,13 +16537,13 @@
         <v>33</v>
       </c>
       <c r="C404" s="10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D404" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E404" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F404" s="10" t="s">
         <v>3</v>
@@ -16570,13 +16571,13 @@
         <v>33</v>
       </c>
       <c r="C405" s="10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D405" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E405" s="10" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F405" s="10" t="s">
         <v>3</v>
@@ -16604,13 +16605,13 @@
         <v>33</v>
       </c>
       <c r="C406" s="10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D406" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E406" s="10" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F406" s="10" t="s">
         <v>3</v>
@@ -16638,13 +16639,13 @@
         <v>33</v>
       </c>
       <c r="C407" s="10" t="s">
+        <v>485</v>
+      </c>
+      <c r="D407" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E407" s="10" t="s">
         <v>486</v>
-      </c>
-      <c r="D407" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E407" s="10" t="s">
-        <v>487</v>
       </c>
       <c r="F407" s="10" t="s">
         <v>3</v>
@@ -16672,13 +16673,13 @@
         <v>33</v>
       </c>
       <c r="C408" s="10" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D408" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E408" s="10" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F408" s="10" t="s">
         <v>3</v>
@@ -16706,13 +16707,13 @@
         <v>33</v>
       </c>
       <c r="C409" s="10" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D409" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E409" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F409" s="10" t="s">
         <v>3</v>
@@ -16740,13 +16741,13 @@
         <v>33</v>
       </c>
       <c r="C410" s="10" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D410" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E410" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F410" s="10" t="s">
         <v>3</v>
@@ -16774,13 +16775,13 @@
         <v>33</v>
       </c>
       <c r="C411" s="10" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D411" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E411" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F411" s="10" t="s">
         <v>3</v>
@@ -16808,13 +16809,13 @@
         <v>33</v>
       </c>
       <c r="C412" s="10" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D412" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E412" s="10" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F412" s="10" t="s">
         <v>3</v>
@@ -16842,13 +16843,13 @@
         <v>33</v>
       </c>
       <c r="C413" s="10" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D413" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E413" s="10" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F413" s="10" t="s">
         <v>3</v>
@@ -16876,13 +16877,13 @@
         <v>33</v>
       </c>
       <c r="C414" s="10" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D414" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E414" s="10" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F414" s="10" t="s">
         <v>3</v>
@@ -16910,13 +16911,13 @@
         <v>33</v>
       </c>
       <c r="C415" s="10" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D415" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E415" s="10" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F415" s="10" t="s">
         <v>3</v>
@@ -16944,13 +16945,13 @@
         <v>33</v>
       </c>
       <c r="C416" s="10" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D416" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E416" s="10" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F416" s="10" t="s">
         <v>3</v>
@@ -16978,13 +16979,13 @@
         <v>33</v>
       </c>
       <c r="C417" s="10" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D417" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E417" s="10" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F417" s="10" t="s">
         <v>3</v>
@@ -17012,13 +17013,13 @@
         <v>33</v>
       </c>
       <c r="C418" s="10" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D418" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E418" s="10" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F418" s="10" t="s">
         <v>3</v>
@@ -17046,13 +17047,13 @@
         <v>33</v>
       </c>
       <c r="C419" s="10" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D419" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E419" s="10" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F419" s="10" t="s">
         <v>3</v>
@@ -17080,13 +17081,13 @@
         <v>34</v>
       </c>
       <c r="C420" s="10" t="s">
+        <v>499</v>
+      </c>
+      <c r="D420" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E420" s="10" t="s">
         <v>500</v>
-      </c>
-      <c r="D420" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E420" s="10" t="s">
-        <v>501</v>
       </c>
       <c r="F420" s="10" t="s">
         <v>3</v>
@@ -17114,13 +17115,13 @@
         <v>34</v>
       </c>
       <c r="C421" s="10" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D421" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E421" s="10" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="F421" s="10" t="s">
         <v>3</v>
@@ -17148,13 +17149,13 @@
         <v>34</v>
       </c>
       <c r="C422" s="10" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D422" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E422" s="10" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F422" s="10" t="s">
         <v>3</v>
@@ -17182,13 +17183,13 @@
         <v>34</v>
       </c>
       <c r="C423" s="10" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D423" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E423" s="10" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F423" s="10" t="s">
         <v>3</v>
@@ -17216,13 +17217,13 @@
         <v>34</v>
       </c>
       <c r="C424" s="10" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D424" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E424" s="10" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="F424" s="10" t="s">
         <v>3</v>
@@ -17250,13 +17251,13 @@
         <v>34</v>
       </c>
       <c r="C425" s="10" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D425" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E425" s="10" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F425" s="10" t="s">
         <v>3</v>
@@ -17284,13 +17285,13 @@
         <v>34</v>
       </c>
       <c r="C426" s="10" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D426" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E426" s="10" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F426" s="10" t="s">
         <v>3</v>
@@ -17318,13 +17319,13 @@
         <v>34</v>
       </c>
       <c r="C427" s="10" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D427" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E427" s="10" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F427" s="10" t="s">
         <v>3</v>
@@ -17352,13 +17353,13 @@
         <v>34</v>
       </c>
       <c r="C428" s="10" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D428" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E428" s="10" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F428" s="10" t="s">
         <v>3</v>
@@ -17386,13 +17387,13 @@
         <v>34</v>
       </c>
       <c r="C429" s="10" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D429" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E429" s="10" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F429" s="10" t="s">
         <v>3</v>
@@ -17420,13 +17421,13 @@
         <v>34</v>
       </c>
       <c r="C430" s="10" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D430" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E430" s="10" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F430" s="10" t="s">
         <v>3</v>
@@ -17454,13 +17455,13 @@
         <v>34</v>
       </c>
       <c r="C431" s="10" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D431" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E431" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F431" s="10" t="s">
         <v>3</v>
@@ -17488,13 +17489,13 @@
         <v>34</v>
       </c>
       <c r="C432" s="10" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D432" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E432" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F432" s="10" t="s">
         <v>3</v>
@@ -17522,13 +17523,13 @@
         <v>34</v>
       </c>
       <c r="C433" s="10" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D433" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E433" s="10" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F433" s="10" t="s">
         <v>3</v>
@@ -17556,13 +17557,13 @@
         <v>34</v>
       </c>
       <c r="C434" s="10" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D434" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E434" s="10" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F434" s="10" t="s">
         <v>3</v>
@@ -17590,13 +17591,13 @@
         <v>34</v>
       </c>
       <c r="C435" s="10" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D435" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E435" s="10" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F435" s="10" t="s">
         <v>3</v>
@@ -17624,13 +17625,13 @@
         <v>34</v>
       </c>
       <c r="C436" s="10" t="s">
+        <v>515</v>
+      </c>
+      <c r="D436" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E436" s="10" t="s">
         <v>516</v>
-      </c>
-      <c r="D436" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E436" s="10" t="s">
-        <v>517</v>
       </c>
       <c r="F436" s="10" t="s">
         <v>3</v>
@@ -17658,13 +17659,13 @@
         <v>34</v>
       </c>
       <c r="C437" s="10" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D437" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E437" s="10" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F437" s="10" t="s">
         <v>3</v>
@@ -17692,13 +17693,13 @@
         <v>34</v>
       </c>
       <c r="C438" s="10" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D438" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E438" s="10" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F438" s="10" t="s">
         <v>3</v>
@@ -17726,13 +17727,13 @@
         <v>34</v>
       </c>
       <c r="C439" s="10" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D439" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E439" s="10" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F439" s="10" t="s">
         <v>3</v>
@@ -17760,13 +17761,13 @@
         <v>34</v>
       </c>
       <c r="C440" s="10" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D440" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E440" s="10" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F440" s="10" t="s">
         <v>3</v>
@@ -17794,13 +17795,13 @@
         <v>34</v>
       </c>
       <c r="C441" s="10" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D441" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E441" s="10" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F441" s="10" t="s">
         <v>3</v>
@@ -17828,13 +17829,13 @@
         <v>34</v>
       </c>
       <c r="C442" s="10" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D442" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E442" s="10" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="F442" s="10" t="s">
         <v>3</v>
@@ -17862,13 +17863,13 @@
         <v>34</v>
       </c>
       <c r="C443" s="10" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D443" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E443" s="10" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="F443" s="10" t="s">
         <v>3</v>
@@ -17896,13 +17897,13 @@
         <v>34</v>
       </c>
       <c r="C444" s="10" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D444" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E444" s="10" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F444" s="10" t="s">
         <v>3</v>
@@ -17930,13 +17931,13 @@
         <v>34</v>
       </c>
       <c r="C445" s="10" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D445" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E445" s="10" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F445" s="10" t="s">
         <v>3</v>
@@ -17964,13 +17965,13 @@
         <v>34</v>
       </c>
       <c r="C446" s="10" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D446" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E446" s="10" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="F446" s="10" t="s">
         <v>3</v>
@@ -17998,13 +17999,13 @@
         <v>34</v>
       </c>
       <c r="C447" s="10" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D447" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E447" s="10" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F447" s="10" t="s">
         <v>3</v>
@@ -18032,13 +18033,13 @@
         <v>34</v>
       </c>
       <c r="C448" s="10" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D448" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E448" s="10" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F448" s="10" t="s">
         <v>3</v>
@@ -18066,13 +18067,13 @@
         <v>34</v>
       </c>
       <c r="C449" s="10" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D449" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E449" s="10" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="F449" s="10" t="s">
         <v>3</v>
@@ -18100,13 +18101,13 @@
         <v>34</v>
       </c>
       <c r="C450" s="10" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D450" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E450" s="10" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F450" s="10" t="s">
         <v>3</v>
@@ -18134,13 +18135,13 @@
         <v>34</v>
       </c>
       <c r="C451" s="10" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D451" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E451" s="10" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F451" s="10" t="s">
         <v>3</v>
@@ -18168,13 +18169,13 @@
         <v>35</v>
       </c>
       <c r="C452" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="D452" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="D452" s="10" t="s">
+      <c r="E452" s="10" t="s">
         <v>534</v>
-      </c>
-      <c r="E452" s="10" t="s">
-        <v>535</v>
       </c>
       <c r="F452" s="10" t="s">
         <v>3</v>
@@ -18202,13 +18203,13 @@
         <v>35</v>
       </c>
       <c r="C453" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="D453" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="D453" s="10" t="s">
-        <v>534</v>
-      </c>
       <c r="E453" s="10" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F453" s="10" t="s">
         <v>3</v>
@@ -18236,13 +18237,13 @@
         <v>35</v>
       </c>
       <c r="C454" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="D454" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="D454" s="10" t="s">
-        <v>534</v>
-      </c>
       <c r="E454" s="10" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F454" s="10" t="s">
         <v>3</v>
@@ -18270,13 +18271,13 @@
         <v>35</v>
       </c>
       <c r="C455" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="D455" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="D455" s="10" t="s">
-        <v>534</v>
-      </c>
       <c r="E455" s="10" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F455" s="10" t="s">
         <v>3</v>
@@ -18304,13 +18305,13 @@
         <v>35</v>
       </c>
       <c r="C456" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="D456" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="D456" s="10" t="s">
-        <v>534</v>
-      </c>
       <c r="E456" s="10" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F456" s="10" t="s">
         <v>3</v>
@@ -18338,13 +18339,13 @@
         <v>35</v>
       </c>
       <c r="C457" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="D457" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="D457" s="10" t="s">
-        <v>534</v>
-      </c>
       <c r="E457" s="10" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="F457" s="10" t="s">
         <v>3</v>
@@ -18372,13 +18373,13 @@
         <v>35</v>
       </c>
       <c r="C458" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="D458" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="D458" s="10" t="s">
-        <v>534</v>
-      </c>
       <c r="E458" s="10" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="F458" s="10" t="s">
         <v>3</v>
@@ -18406,13 +18407,13 @@
         <v>35</v>
       </c>
       <c r="C459" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="D459" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="D459" s="10" t="s">
-        <v>534</v>
-      </c>
       <c r="E459" s="10" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F459" s="10" t="s">
         <v>3</v>
@@ -18440,13 +18441,13 @@
         <v>35</v>
       </c>
       <c r="C460" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="D460" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="D460" s="10" t="s">
-        <v>534</v>
-      </c>
       <c r="E460" s="10" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F460" s="10" t="s">
         <v>3</v>
@@ -18474,13 +18475,13 @@
         <v>35</v>
       </c>
       <c r="C461" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="D461" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="D461" s="10" t="s">
-        <v>534</v>
-      </c>
       <c r="E461" s="10" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F461" s="10" t="s">
         <v>3</v>
@@ -18508,13 +18509,13 @@
         <v>35</v>
       </c>
       <c r="C462" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="D462" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="D462" s="10" t="s">
-        <v>534</v>
-      </c>
       <c r="E462" s="10" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F462" s="10" t="s">
         <v>3</v>
@@ -18542,13 +18543,13 @@
         <v>35</v>
       </c>
       <c r="C463" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="D463" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="D463" s="10" t="s">
-        <v>534</v>
-      </c>
       <c r="E463" s="10" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="F463" s="10" t="s">
         <v>3</v>
@@ -18576,13 +18577,13 @@
         <v>35</v>
       </c>
       <c r="C464" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="D464" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="D464" s="10" t="s">
-        <v>534</v>
-      </c>
       <c r="E464" s="10" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F464" s="10" t="s">
         <v>3</v>
@@ -18610,13 +18611,13 @@
         <v>35</v>
       </c>
       <c r="C465" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="D465" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="D465" s="10" t="s">
-        <v>534</v>
-      </c>
       <c r="E465" s="10" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F465" s="10" t="s">
         <v>3</v>
@@ -18644,13 +18645,13 @@
         <v>35</v>
       </c>
       <c r="C466" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="D466" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="D466" s="10" t="s">
-        <v>534</v>
-      </c>
       <c r="E466" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F466" s="10" t="s">
         <v>3</v>
@@ -18678,13 +18679,13 @@
         <v>35</v>
       </c>
       <c r="C467" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="D467" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="D467" s="10" t="s">
-        <v>534</v>
-      </c>
       <c r="E467" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="F467" s="10" t="s">
         <v>3</v>
@@ -18712,13 +18713,13 @@
         <v>35</v>
       </c>
       <c r="C468" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="D468" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="D468" s="10" t="s">
-        <v>534</v>
-      </c>
       <c r="E468" s="10" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="F468" s="10" t="s">
         <v>3</v>
@@ -18746,10 +18747,10 @@
         <v>35</v>
       </c>
       <c r="C469" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="D469" s="10" t="s">
         <v>533</v>
-      </c>
-      <c r="D469" s="10" t="s">
-        <v>534</v>
       </c>
       <c r="E469" s="10" t="s">
         <v>17</v>
@@ -18780,13 +18781,13 @@
         <v>35</v>
       </c>
       <c r="C470" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="D470" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="D470" s="10" t="s">
-        <v>534</v>
-      </c>
       <c r="E470" s="10" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="F470" s="10" t="s">
         <v>3</v>
@@ -18814,13 +18815,13 @@
         <v>35</v>
       </c>
       <c r="C471" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="D471" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="D471" s="10" t="s">
-        <v>534</v>
-      </c>
       <c r="E471" s="10" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F471" s="10" t="s">
         <v>3</v>
@@ -18848,13 +18849,13 @@
         <v>36</v>
       </c>
       <c r="C472" s="10" t="s">
+        <v>553</v>
+      </c>
+      <c r="D472" s="10" t="s">
+        <v>533</v>
+      </c>
+      <c r="E472" s="10" t="s">
         <v>554</v>
-      </c>
-      <c r="D472" s="10" t="s">
-        <v>534</v>
-      </c>
-      <c r="E472" s="10" t="s">
-        <v>555</v>
       </c>
       <c r="F472" s="10" t="s">
         <v>3</v>
@@ -18882,13 +18883,13 @@
         <v>36</v>
       </c>
       <c r="C473" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D473" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E473" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F473" s="10" t="s">
         <v>3</v>
@@ -18916,13 +18917,13 @@
         <v>36</v>
       </c>
       <c r="C474" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D474" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E474" s="10" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F474" s="10" t="s">
         <v>3</v>
@@ -18950,13 +18951,13 @@
         <v>36</v>
       </c>
       <c r="C475" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D475" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E475" s="10" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="F475" s="10" t="s">
         <v>3</v>
@@ -18984,13 +18985,13 @@
         <v>36</v>
       </c>
       <c r="C476" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D476" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E476" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="F476" s="10" t="s">
         <v>3</v>
@@ -19018,13 +19019,13 @@
         <v>36</v>
       </c>
       <c r="C477" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D477" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E477" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="F477" s="10" t="s">
         <v>3</v>
@@ -19052,13 +19053,13 @@
         <v>36</v>
       </c>
       <c r="C478" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D478" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E478" s="10" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F478" s="10" t="s">
         <v>3</v>
@@ -19086,13 +19087,13 @@
         <v>36</v>
       </c>
       <c r="C479" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D479" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E479" s="10" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="F479" s="10" t="s">
         <v>3</v>
@@ -19120,13 +19121,13 @@
         <v>36</v>
       </c>
       <c r="C480" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D480" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E480" s="10" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="F480" s="10" t="s">
         <v>3</v>
@@ -19154,13 +19155,13 @@
         <v>36</v>
       </c>
       <c r="C481" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D481" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E481" s="10" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="F481" s="10" t="s">
         <v>3</v>
@@ -19188,13 +19189,13 @@
         <v>36</v>
       </c>
       <c r="C482" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D482" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E482" s="10" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="F482" s="10" t="s">
         <v>3</v>
@@ -19222,13 +19223,13 @@
         <v>36</v>
       </c>
       <c r="C483" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D483" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E483" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="F483" s="10" t="s">
         <v>3</v>
@@ -19256,13 +19257,13 @@
         <v>36</v>
       </c>
       <c r="C484" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D484" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E484" s="10" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F484" s="10" t="s">
         <v>3</v>
@@ -19290,13 +19291,13 @@
         <v>36</v>
       </c>
       <c r="C485" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D485" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E485" s="10" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F485" s="10" t="s">
         <v>3</v>
@@ -19324,13 +19325,13 @@
         <v>36</v>
       </c>
       <c r="C486" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D486" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E486" s="10" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="F486" s="10" t="s">
         <v>3</v>
@@ -19358,13 +19359,13 @@
         <v>36</v>
       </c>
       <c r="C487" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D487" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E487" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="F487" s="10" t="s">
         <v>3</v>
@@ -19392,13 +19393,13 @@
         <v>36</v>
       </c>
       <c r="C488" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D488" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E488" s="10" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="F488" s="10" t="s">
         <v>3</v>
@@ -19426,13 +19427,13 @@
         <v>36</v>
       </c>
       <c r="C489" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D489" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E489" s="10" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F489" s="10" t="s">
         <v>3</v>
@@ -19460,13 +19461,13 @@
         <v>37</v>
       </c>
       <c r="C490" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="D490" s="10" t="s">
+        <v>533</v>
+      </c>
+      <c r="E490" s="10" t="s">
         <v>573</v>
-      </c>
-      <c r="D490" s="10" t="s">
-        <v>534</v>
-      </c>
-      <c r="E490" s="10" t="s">
-        <v>574</v>
       </c>
       <c r="F490" s="10" t="s">
         <v>3</v>
@@ -19494,13 +19495,13 @@
         <v>37</v>
       </c>
       <c r="C491" s="10" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D491" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E491" s="10" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="F491" s="10" t="s">
         <v>3</v>
@@ -19528,13 +19529,13 @@
         <v>37</v>
       </c>
       <c r="C492" s="10" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D492" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E492" s="10" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="F492" s="10" t="s">
         <v>3</v>
@@ -19562,13 +19563,13 @@
         <v>37</v>
       </c>
       <c r="C493" s="10" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D493" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E493" s="10" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="F493" s="10" t="s">
         <v>3</v>
@@ -19596,13 +19597,13 @@
         <v>37</v>
       </c>
       <c r="C494" s="10" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D494" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E494" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="F494" s="10" t="s">
         <v>3</v>
@@ -19630,13 +19631,13 @@
         <v>37</v>
       </c>
       <c r="C495" s="10" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D495" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E495" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="F495" s="10" t="s">
         <v>3</v>
@@ -19664,13 +19665,13 @@
         <v>37</v>
       </c>
       <c r="C496" s="10" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D496" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E496" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="F496" s="10" t="s">
         <v>3</v>
@@ -19887,7 +19888,7 @@
       </c>
       <c r="C5">
         <f>COUNTIFS(Checklist!$B:$B,A5,Checklist!$F:$F,"Chưa làm")</f>
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="D5">
         <f>COUNTIFS(Checklist!$B:$B,A5,Checklist!$F:$F,"Đang làm")</f>
@@ -19895,7 +19896,7 @@
       </c>
       <c r="E5">
         <f>COUNTIFS(Checklist!$B:$B,A5,Checklist!$F:$F,"Hoàn thành")</f>
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="F5">
         <f>COUNTIFS(Checklist!$B:$B,A5,Checklist!$F:$F,"Bị chặn")</f>
@@ -19907,7 +19908,7 @@
       </c>
       <c r="H5" s="6">
         <f t="shared" si="0"/>
-        <v>0.33913043478260868</v>
+        <v>0.45217391304347826</v>
       </c>
     </row>
     <row r="6" spans="1:8">

--- a/CHECKLIST_TRIEN_KHAI_FULL.xlsx
+++ b/CHECKLIST_TRIEN_KHAI_FULL.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ssl_detection_xray_v2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{069139B6-8849-422C-8C83-925C437F16D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37481A0D-976C-4184-A5E8-DCC44049C867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3886" uniqueCount="640">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3887" uniqueCount="666">
   <si>
     <t>CHECKLIST TRIỂN KHAI FULL — SEMI-SUPERVISED OBJECT DETECTION TRÊN X-QUANG PHỔI</t>
   </si>
@@ -629,1120 +629,13 @@
     <t>Số annotation khớp với canonical bbox table.</t>
   </si>
   <si>
-    <t>2E. Fixed Train/Val/Test Split</t>
-  </si>
-  <si>
-    <t>Tạo train/val/test cố định.</t>
-  </si>
-  <si>
-    <t>Stratify theo class nếu khả thi.</t>
-  </si>
-  <si>
-    <t>Giữ phân phối ảnh negative hợp lý.</t>
-  </si>
-  <si>
-    <t>Đảm bảo test set có đủ ảnh No Finding để đo FP per negative image.</t>
-  </si>
-  <si>
-    <t>Kiểm tra số lượng và tỷ lệ No Finding trong train/val/test.</t>
-  </si>
-  <si>
-    <t>Check không trùng image_id giữa train/val/test.</t>
-  </si>
-  <si>
-    <t>Xuất split_lock_manifest.json.</t>
-  </si>
-  <si>
-    <t>data/manifests/split_lock_manifest.json</t>
-  </si>
-  <si>
-    <t>data/manifests/leakage_check_report.json</t>
-  </si>
-  <si>
-    <t>reports/split_negative_distribution.csv</t>
-  </si>
-  <si>
-    <t>data/processed/coco/instances_train.json</t>
-  </si>
-  <si>
-    <t>data/processed/coco/instances_val.json</t>
-  </si>
-  <si>
-    <t>data/processed/coco/instances_test.json</t>
-  </si>
-  <si>
-    <t>Leakage = 0.</t>
-  </si>
-  <si>
-    <t>Test set cố định, không dùng để tune.</t>
-  </si>
-  <si>
-    <t>Mọi experiment dùng cùng test set.</t>
-  </si>
-  <si>
-    <t>Test set chứa đủ ảnh No Finding để tính FP per negative image.</t>
-  </si>
-  <si>
-    <t>Tỷ lệ negative trong train/val/test được báo cáo rõ.</t>
-  </si>
-  <si>
-    <t>2F. Labeled/Unlabeled Split for SSL</t>
-  </si>
-  <si>
-    <t>Tạo labeled split 1%.</t>
-  </si>
-  <si>
-    <t>Tạo labeled split 5%.</t>
-  </si>
-  <si>
-    <t>Tạo labeled split 10%.</t>
-  </si>
-  <si>
-    <t>Tạo labeled split 20%.</t>
-  </si>
-  <si>
-    <t>Nested sampling: 1% ⊂ 5% ⊂ 10% ⊂ 20%.</t>
-  </si>
-  <si>
-    <t>Stratified theo class distribution.</t>
-  </si>
-  <si>
-    <t>Unlabeled = phần còn lại của train.</t>
-  </si>
-  <si>
-    <t>Unlabeled có thể gồm abnormal và No Finding.</t>
-  </si>
-  <si>
-    <t>Ground truth của unlabeled bị cô lập khỏi training SSL.</t>
-  </si>
-  <si>
-    <t>Theo dõi số lượng unlabeled negative images để phân tích pseudo-box sai.</t>
-  </si>
-  <si>
-    <t>data/processed/coco/labeled_splits/instances_labeled_1pct.json</t>
-  </si>
-  <si>
-    <t>data/processed/coco/labeled_splits/instances_labeled_5pct.json</t>
-  </si>
-  <si>
-    <t>data/processed/coco/labeled_splits/instances_labeled_10pct.json</t>
-  </si>
-  <si>
-    <t>data/processed/coco/labeled_splits/instances_labeled_20pct.json</t>
-  </si>
-  <si>
-    <t>data/processed/coco/labeled_splits/instances_unlabeled_1pct.json</t>
-  </si>
-  <si>
-    <t>data/processed/coco/labeled_splits/instances_unlabeled_5pct.json</t>
-  </si>
-  <si>
-    <t>data/processed/coco/labeled_splits/instances_unlabeled_10pct.json</t>
-  </si>
-  <si>
-    <t>data/processed/coco/labeled_splits/instances_unlabeled_20pct.json</t>
-  </si>
-  <si>
-    <t>data/manifests/nested_split_check.json</t>
-  </si>
-  <si>
-    <t>Nested property pass.</t>
-  </si>
-  <si>
-    <t>Không leakage với val/test.</t>
-  </si>
-  <si>
-    <t>Supervised low-label và SSL dùng cùng labeled split.</t>
-  </si>
-  <si>
-    <t>split_seed được lưu trong manifest.</t>
-  </si>
-  <si>
-    <t>2F.1 Seed Protocol: split_seed vs training_seed</t>
-  </si>
-  <si>
-    <t>split_seed dùng để tạo train/val/test và labeled/unlabeled split.</t>
-  </si>
-  <si>
-    <t>training_seed dùng để khởi tạo mô hình, dataloader shuffle, augmentation và training.</t>
-  </si>
-  <si>
-    <t>Supervised vs SSL dùng cùng split_seed để nhìn cùng dữ liệu.</t>
-  </si>
-  <si>
-    <t>Stability dùng nhiều training_seed để đo variance thật.</t>
-  </si>
-  <si>
-    <t>Không khóa cùng training_seed cho mọi run vì sẽ tạo variance giả thấp.</t>
-  </si>
-  <si>
-    <t>Log rõ split_seed, training_seed, rng_state_id cho từng run.</t>
-  </si>
-  <si>
-    <t>data/manifests/seed_manifest.json</t>
-  </si>
-  <si>
-    <t>reports/seed_protocol.md</t>
-  </si>
-  <si>
-    <t>Mỗi experiment log rõ split_seed và training_seed.</t>
-  </si>
-  <si>
-    <t>Stability được đo bằng nhiều training_seed.</t>
-  </si>
-  <si>
-    <t>Không có seed leakage hoặc variance giả do khóa nhầm seed.</t>
-  </si>
-  <si>
-    <t>3A. Pre-training Dataset Diagnostics</t>
-  </si>
-  <si>
-    <t>Vẽ class distribution.</t>
-  </si>
-  <si>
-    <t>Vẽ bbox count theo class.</t>
-  </si>
-  <si>
-    <t>Vẽ bbox size distribution.</t>
-  </si>
-  <si>
-    <t>Vẽ bbox location heatmap.</t>
-  </si>
-  <si>
-    <t>Thống kê rare class và chốt tiêu chí rare class.</t>
-  </si>
-  <si>
-    <t>Thống kê negative images.</t>
-  </si>
-  <si>
-    <t>Thống kê split distribution.</t>
-  </si>
-  <si>
-    <t>Chỉ dùng train cho diagnostics chính, không nhìn test để tune.</t>
-  </si>
-  <si>
-    <t>reports/dataset_analysis_report.md</t>
-  </si>
-  <si>
-    <t>plots/dataset/class_distribution.png</t>
-  </si>
-  <si>
-    <t>plots/dataset/bbox_distribution.png</t>
-  </si>
-  <si>
-    <t>plots/dataset/bbox_location_heatmap.png</t>
-  </si>
-  <si>
-    <t>plots/dataset/negative_image_distribution.png</t>
-  </si>
-  <si>
-    <t>Có báo cáo trước train.</t>
-  </si>
-  <si>
-    <t>Biết lớp nào rare.</t>
-  </si>
-  <si>
-    <t>Biết rủi ro imbalance.</t>
-  </si>
-  <si>
-    <t>Biết bbox nhỏ/vừa/lớn phân bố thế nào.</t>
-  </si>
-  <si>
-    <t>4A.0 Full-label supervised upper bound</t>
-  </si>
-  <si>
-    <t>Chọn detector chính.</t>
-  </si>
-  <si>
-    <t>Train trên 100% labeled train.</t>
-  </si>
-  <si>
-    <t>Select checkpoint theo validation set.</t>
-  </si>
-  <si>
-    <t>Chọn checkpoint tốt nhất theo validation mAP@0.5:0.95.</t>
-  </si>
-  <si>
-    <t>Không chọn checkpoint theo test set.</t>
-  </si>
-  <si>
-    <t>Không thay đổi tiêu chí chọn checkpoint giữa các experiment.</t>
-  </si>
-  <si>
-    <t>Evaluate trên fixed test set.</t>
-  </si>
-  <si>
-    <t>Lưu config, seed, RNG state, checkpoint, log.</t>
-  </si>
-  <si>
-    <t>Metric bắt buộc</t>
-  </si>
-  <si>
-    <t>mAP@0.5:0.95 — metric chính</t>
-  </si>
-  <si>
-    <t>mAP@0.5</t>
-  </si>
-  <si>
-    <t>Class-wise AP</t>
-  </si>
-  <si>
-    <t>Recall</t>
-  </si>
-  <si>
-    <t>FP per image</t>
-  </si>
-  <si>
-    <t>FP per negative image</t>
-  </si>
-  <si>
-    <t>reports/supervised_full_results.csv</t>
-  </si>
-  <si>
-    <t>experiments/exp1_full_label_baseline/</t>
-  </si>
-  <si>
-    <t>models/supervised/full_label/</t>
-  </si>
-  <si>
-    <t>Có upper bound 100%.</t>
-  </si>
-  <si>
-    <t>Kết quả trace được từ config → log → checkpoint → report.</t>
-  </si>
-  <si>
-    <t>Không dùng test để chọn model.</t>
-  </si>
-  <si>
-    <t>FP per negative image được tính trên test set có đủ ảnh No Finding.</t>
-  </si>
-  <si>
-    <t>Checkpoint selection criterion khóa là validation mAP@0.5:0.95.</t>
-  </si>
-  <si>
-    <t>4A.1 Low-label supervised baseline</t>
-  </si>
-  <si>
-    <t>Train 1% labeled.</t>
-  </si>
-  <si>
-    <t>Train 5% labeled.</t>
-  </si>
-  <si>
-    <t>Train 10% labeled.</t>
-  </si>
-  <si>
-    <t>Train 20% labeled.</t>
-  </si>
-  <si>
-    <t>Mỗi mức label chạy 3–5 training_seed.</t>
-  </si>
-  <si>
-    <t>Dùng đúng labeled split đã khóa bằng split_seed.</t>
-  </si>
-  <si>
-    <t>Chọn checkpoint theo validation mAP@0.5:0.95.</t>
-  </si>
-  <si>
-    <t>Evaluate trên cùng fixed test set.</t>
-  </si>
-  <si>
-    <t>Báo cáo mean ± std.</t>
-  </si>
-  <si>
-    <t>Lưu seed number, RNG state và deterministic flags cho từng run.</t>
-  </si>
-  <si>
-    <t>reports/supervised_lowlabel_results.csv</t>
-  </si>
-  <si>
-    <t>experiments/exp2_low_label_baseline/</t>
-  </si>
-  <si>
-    <t>Có baseline đối chứng cho từng mức label.</t>
-  </si>
-  <si>
-    <t>SSL so sánh với baseline dùng cùng labeled split/cùng split_seed.</t>
-  </si>
-  <si>
-    <t>Stability đo qua nhiều training_seed.</t>
-  </si>
-  <si>
-    <t>Nếu variance lớn, ghi rõ trong báo cáo.</t>
-  </si>
-  <si>
-    <t>Checkpoint chọn nhất quán bằng validation mAP@0.5:0.95.</t>
-  </si>
-  <si>
-    <t>4B. Extension: Attention / ViT-Oriented Supervised Analysis</t>
-  </si>
-  <si>
-    <t>Đánh giá feasibility GPU/VRAM/thời gian train cho ViT/Attention.</t>
-  </si>
-  <si>
-    <t>Nếu khả thi: chạy supervised baseline ViT/Attention.</t>
-  </si>
-  <si>
-    <t>So sánh với detector chính trên cùng split/test/metric.</t>
-  </si>
-  <si>
-    <t>Ghi rõ đây là extension, không phải trọng tâm chính.</t>
-  </si>
-  <si>
-    <t>reports/vit_attention_feasibility_report.md</t>
-  </si>
-  <si>
-    <t>reports/attention_supervised_results.csv</t>
-  </si>
-  <si>
-    <t>Có quyết định chạy hoặc không chạy extension dựa trên compute.</t>
-  </si>
-  <si>
-    <t>Extension không làm lệch trọng tâm teacher-student SSOD.</t>
-  </si>
-  <si>
-    <t>5.1A Teacher–Student SSL Pipeline</t>
-  </si>
-  <si>
-    <t>Khởi tạo student từ supervised detector.</t>
-  </si>
-  <si>
-    <t>Khởi tạo teacher.</t>
-  </si>
-  <si>
-    <t>Teacher sinh pseudo-label trên weak augmentation.</t>
-  </si>
-  <si>
-    <t>Student học trên strong augmentation.</t>
-  </si>
-  <si>
-    <t>Teacher cập nhật bằng EMA.</t>
-  </si>
-  <si>
-    <t>Có burn-in supervised trước khi bật SSL.</t>
-  </si>
-  <si>
-    <t>Ghi rõ λ của unlabeled loss.</t>
-  </si>
-  <si>
-    <t>Đồng bộ transform bbox với geometric augmentation.</t>
-  </si>
-  <si>
-    <t>reports/ssl_results.csv</t>
-  </si>
-  <si>
-    <t>experiments/exp3_ssl_detection/</t>
-  </si>
-  <si>
-    <t>models/ssl/</t>
-  </si>
-  <si>
-    <t>Train SSL chạy end-to-end.</t>
-  </si>
-  <si>
-    <t>Có log pseudo-label count.</t>
-  </si>
-  <si>
-    <t>Có log unlabeled loss λ.</t>
-  </si>
-  <si>
-    <t>Không có lỗi box lệch do augmentation.</t>
-  </si>
-  <si>
-    <t>5.1B Pseudo-BBox Generation, NMS &amp; Box Filtering</t>
-  </si>
-  <si>
-    <t>Teacher prediction trên weak image tạo pseudo-label dạng class_id + confidence + bbox xywh.</t>
-  </si>
-  <si>
-    <t>Lọc theo confidence threshold.</t>
-  </si>
-  <si>
-    <t>Áp dụng class-wise threshold nếu cấu hình bật.</t>
-  </si>
-  <si>
-    <t>Áp dụng NMS trước khi nhận pseudo-bbox để giảm box trùng lặp.</t>
-  </si>
-  <si>
-    <t>Áp dụng box quality filters: bbox size, aspect ratio, boundary, area.</t>
-  </si>
-  <si>
-    <t>Giới hạn số pseudo-box tối đa mỗi ảnh nếu cần để tránh nhiễu dày đặc.</t>
-  </si>
-  <si>
-    <t>Lưu pseudo-label gồm image_id, class_id, confidence, bbox xywh, threshold_used, nms_iou.</t>
-  </si>
-  <si>
-    <t>Transform pseudo-bbox đúng từ weak view sang strong view.</t>
-  </si>
-  <si>
-    <t>Visualize một số pseudo-box sau transform để kiểm tra khớp ảnh student.</t>
-  </si>
-  <si>
-    <t>reports/pseudo_label_filter_report.csv</t>
-  </si>
-  <si>
-    <t>reports/pseudo_bbox_generation_report.md</t>
-  </si>
-  <si>
-    <t>plots/error_vis/pseudo_label_failure_cases/</t>
-  </si>
-  <si>
-    <t>Pseudo-label cho detection có đủ class_id, confidence, bbox xywh.</t>
-  </si>
-  <si>
-    <t>NMS được áp dụng trước khi student học pseudo-box.</t>
-  </si>
-  <si>
-    <t>Box transform weak→strong được kiểm tra bằng test và visualization.</t>
-  </si>
-  <si>
-    <t>5.1C Anti-confirmation-bias Safeguards</t>
-  </si>
-  <si>
-    <t>Dùng supervised burn-in trước SSL.</t>
-  </si>
-  <si>
-    <t>Dùng EMA teacher thay vì cập nhật teacher trực tiếp.</t>
-  </si>
-  <si>
-    <t>Không bật pseudo-label nếu teacher chưa đạt ngưỡng tối thiểu trên validation hoặc chưa qua burn-in.</t>
-  </si>
-  <si>
-    <t>Theo dõi pseudo-label quality proxy theo epoch.</t>
-  </si>
-  <si>
-    <t>Theo dõi pseudo-box sai trên ảnh No Finding trong unlabeled set.</t>
-  </si>
-  <si>
-    <t>Theo dõi class-wise pseudo-label count để phát hiện teacher bias.</t>
-  </si>
-  <si>
-    <t>Không chọn threshold chỉ vì mAP tổng tốt nếu rare class bị triệt tiêu.</t>
-  </si>
-  <si>
-    <t>Ghi rõ confirmation bias như rủi ro chính trong report.</t>
-  </si>
-  <si>
-    <t>reports/confirmation_bias_monitoring.md</t>
-  </si>
-  <si>
-    <t>reports/pseudolabel_rareclass_report.csv</t>
-  </si>
-  <si>
-    <t>reports/negative_pseudobox_report.csv</t>
-  </si>
-  <si>
-    <t>Có ít nhất một cơ chế chống confirmation bias ngoài threshold đơn giản.</t>
-  </si>
-  <si>
-    <t>Có báo cáo pseudo-box sai trên No Finding.</t>
-  </si>
-  <si>
-    <t>Có báo cáo rare-class pseudo-label survival rate.</t>
-  </si>
-  <si>
-    <t>5.1D Threshold Strategy: Global, Class-wise, Dynamic</t>
-  </si>
-  <si>
-    <t>Sweep confidence threshold chung từ 0.1 → 0.9.</t>
-  </si>
-  <si>
-    <t>Thử class-wise / dynamic threshold như ablation.</t>
-  </si>
-  <si>
-    <t>Không khóa cứng threshold cụ thể trước khi có validation.</t>
-  </si>
-  <si>
-    <t>Với class hiếm, đánh giá cân bằng giữa pseudo-label coverage và pseudo-label noise.</t>
-  </si>
-  <si>
-    <t>Ghi threshold_used theo từng pseudo-label.</t>
-  </si>
-  <si>
-    <t>Báo cáo pseudo-label count theo class và threshold.</t>
-  </si>
-  <si>
-    <t>reports/threshold_policy.md</t>
-  </si>
-  <si>
-    <t>reports/threshold_sweep_report.csv</t>
-  </si>
-  <si>
-    <t>Threshold cuối được chọn bằng validation/analysis split, không dùng test.</t>
-  </si>
-  <si>
-    <t>Class-wise threshold chỉ được kết luận nếu có ablation.</t>
-  </si>
-  <si>
-    <t>Không dùng ví dụ 0.9/0.6 như protocol cố định nếu chưa có bằng chứng.</t>
-  </si>
-  <si>
-    <t>5.1E Positive/Negative Batch Monitoring</t>
-  </si>
-  <si>
-    <t>Log tỷ lệ positive/negative trong labeled batch.</t>
-  </si>
-  <si>
-    <t>Log tỷ lệ positive/negative trong unlabeled batch nếu metadata cho phép.</t>
-  </si>
-  <si>
-    <t>Không giả định ảnh Normal chiếm đa số; kiểm tra tỷ lệ thật trong split và batch.</t>
-  </si>
-  <si>
-    <t>Theo dõi pseudo-box sinh trên unlabeled negative images.</t>
-  </si>
-  <si>
-    <t>Nếu batch lệch quá mạnh, dùng sampler kiểm soát nhẹ như biện pháp ổn định training, không xem là contribution xử lý imbalance.</t>
-  </si>
-  <si>
-    <t>reports/batch_composition_report.csv</t>
-  </si>
-  <si>
-    <t>reports/unlabeled_negative_monitoring.csv</t>
-  </si>
-  <si>
-    <t>Biết tỷ lệ positive/negative trong training batches.</t>
-  </si>
-  <si>
-    <t>Nếu SSL thất bại, có dữ liệu để kiểm tra batch bias.</t>
-  </si>
-  <si>
-    <t>5.1F Compute / OOM Fallback for SSOD</t>
-  </si>
-  <si>
-    <t>Chạy smoke test SSL trước full training.</t>
-  </si>
-  <si>
-    <t>Chuẩn bị AMP mixed precision.</t>
-  </si>
-  <si>
-    <t>Chuẩn bị gradient accumulation.</t>
-  </si>
-  <si>
-    <t>Giảm batch size khi OOM.</t>
-  </si>
-  <si>
-    <t>Giảm image size có kiểm soát nếu cần và ghi rõ ảnh hưởng.</t>
-  </si>
-  <si>
-    <t>Giảm unlabeled images per batch nếu OOM.</t>
-  </si>
-  <si>
-    <t>Lưu checkpoint/resume để tránh mất tiến trình.</t>
-  </si>
-  <si>
-    <t>Nếu Colab/Kaggle không đủ, chuyển Vast.ai.</t>
-  </si>
-  <si>
-    <t>reports/compute_budget_report.md</t>
-  </si>
-  <si>
-    <t>reports/oom_fallback_log.md</t>
-  </si>
-  <si>
-    <t>Có kế hoạch fallback trước khi chạy SSL tốn GPU.</t>
-  </si>
-  <si>
-    <t>OOM không làm mất checkpoint hoặc thay đổi protocol âm thầm.</t>
-  </si>
-  <si>
-    <t>5.1G SSL Main Experiments</t>
-  </si>
-  <si>
-    <t>Chạy SSL 1%.</t>
-  </si>
-  <si>
-    <t>Chạy SSL 5%.</t>
-  </si>
-  <si>
-    <t>Chạy SSL 10%.</t>
-  </si>
-  <si>
-    <t>Chạy SSL 20%.</t>
-  </si>
-  <si>
-    <t>Mỗi mức chạy 3–5 training_seed.</t>
-  </si>
-  <si>
-    <t>So sánh với supervised baseline cùng labeled split, cùng split_seed, cùng fixed test set.</t>
-  </si>
-  <si>
-    <t>Không hiểu 'cùng seed' là khóa giống toàn bộ training_seed; fair comparison dùng cùng split_seed, stability dùng nhiều training_seed.</t>
-  </si>
-  <si>
-    <t>SSL checkpoint chọn theo validation mAP@0.5:0.95.</t>
-  </si>
-  <si>
-    <t>Tính SSL Gain = mAP@0.5:0.95_SSL - mAP@0.5:0.95_Supervised.</t>
-  </si>
-  <si>
-    <t>reports/ssl_gain_curve.csv</t>
-  </si>
-  <si>
-    <t>plots/results/ssl_gain_curve.png</t>
-  </si>
-  <si>
-    <t>Có SSL gain/loss từng mức label.</t>
-  </si>
-  <si>
-    <t>Có mean ± std.</t>
-  </si>
-  <si>
-    <t>Không kết luận gain nếu gain nhỏ hơn std giữa seed.</t>
-  </si>
-  <si>
-    <t>Metric chọn checkpoint khóa là validation mAP@0.5:0.95.</t>
-  </si>
-  <si>
-    <t>5.2 / 5.3 Optional Extension: Attention / ViT SSL</t>
-  </si>
-  <si>
-    <t>Chỉ chạy nếu compute cho phép.</t>
-  </si>
-  <si>
-    <t>Dùng cùng split, metric, checkpoint criterion.</t>
-  </si>
-  <si>
-    <t>Kiểm tra Attention/ViT có cải thiện SSL gain hoặc stability không.</t>
-  </si>
-  <si>
-    <t>Không xem là đóng góp chính nếu chưa đủ multi-seed.</t>
-  </si>
-  <si>
-    <t>reports/attention_ssl_results.csv</t>
-  </si>
-  <si>
-    <t>reports/attention_ssl_stability_report.csv</t>
-  </si>
-  <si>
-    <t>Có quyết định chạy/không chạy extension dựa trên compute.</t>
-  </si>
-  <si>
-    <t>Extension không làm thay đổi kết luận chính nếu thiếu multi-seed.</t>
-  </si>
-  <si>
-    <t>6A. Threshold sweep</t>
-  </si>
-  <si>
-    <t>Sweep threshold 0.1 → 0.9.</t>
-  </si>
-  <si>
-    <t>Ghi pseudo-label count theo threshold.</t>
-  </si>
-  <si>
-    <t>Ghi pseudo-label count theo class.</t>
-  </si>
-  <si>
-    <t>Ghi rare-class survival rate.</t>
-  </si>
-  <si>
-    <t>Ghi mAP theo threshold.</t>
-  </si>
-  <si>
-    <t>Ghi FP trên negative theo threshold.</t>
-  </si>
-  <si>
-    <t>Threshold tuning chỉ dùng validation hoặc analysis split được quy định trước, không dùng test.</t>
-  </si>
-  <si>
-    <t>Phân tích NMS IoU và max pseudo-box per image nếu có.</t>
-  </si>
-  <si>
-    <t>plots/results/threshold_sweep.png</t>
-  </si>
-  <si>
-    <t>Biết threshold nào tốt nhưng gây bias.</t>
-  </si>
-  <si>
-    <t>Biết threshold nào giữ rare class tốt hơn.</t>
-  </si>
-  <si>
-    <t>Có cơ sở chọn threshold cuối.</t>
-  </si>
-  <si>
-    <t>Test set không bị dùng để chọn threshold.</t>
-  </si>
-  <si>
-    <t>6B. Evaluation chính</t>
-  </si>
-  <si>
-    <t>Evaluate tất cả checkpoint tốt nhất.</t>
-  </si>
-  <si>
-    <t>Tính mAP@0.5:0.95.</t>
-  </si>
-  <si>
-    <t>Tính mAP@0.5.</t>
-  </si>
-  <si>
-    <t>Tính class-wise AP.</t>
-  </si>
-  <si>
-    <t>Tính recall.</t>
-  </si>
-  <si>
-    <t>Tính FP per image.</t>
-  </si>
-  <si>
-    <t>Tính FP per negative image.</t>
-  </si>
-  <si>
-    <t>Tính bbox-size AP nếu có.</t>
-  </si>
-  <si>
-    <t>reports/final_evaluation_results.csv</t>
-  </si>
-  <si>
-    <t>reports/classwise_ap_results.csv</t>
-  </si>
-  <si>
-    <t>reports/negative_fp_report.csv</t>
-  </si>
-  <si>
-    <t>Tất cả mô hình evaluate trên cùng fixed test set.</t>
-  </si>
-  <si>
-    <t>Metric chính là mAP@0.5:0.95.</t>
-  </si>
-  <si>
-    <t>Không dùng metric phụ để thay thế kết luận chính.</t>
-  </si>
-  <si>
-    <t>FP per negative image tính trên test set có đủ No Finding.</t>
-  </si>
-  <si>
-    <t>6C. Error analysis</t>
-  </si>
-  <si>
-    <t>Phân tích false positive trên ảnh No Finding.</t>
-  </si>
-  <si>
-    <t>Phân tích false negative trên ảnh abnormal.</t>
-  </si>
-  <si>
-    <t>Phân tích class nào hay bị nhầm.</t>
-  </si>
-  <si>
-    <t>Phân tích bbox nhỏ có bị bỏ sót không.</t>
-  </si>
-  <si>
-    <t>Visualize TP / FP / FN.</t>
-  </si>
-  <si>
-    <t>Visualize pseudo-label failure cases.</t>
-  </si>
-  <si>
-    <t>Liên hệ lỗi với confirmation bias, threshold, NMS và batch composition.</t>
-  </si>
-  <si>
-    <t>reports/error_analysis_report.md</t>
-  </si>
-  <si>
-    <t>plots/error_vis/true_positive_examples/</t>
-  </si>
-  <si>
-    <t>plots/error_vis/false_positive_negative_images/</t>
-  </si>
-  <si>
-    <t>plots/error_vis/false_negative_abnormal_images/</t>
-  </si>
-  <si>
-    <t>Mỗi kết luận định lượng có ví dụ hình ảnh minh họa.</t>
-  </si>
-  <si>
-    <t>Mỗi lỗi chính có giải thích hoặc hành động.</t>
-  </si>
-  <si>
-    <t>6D. Stability analysis</t>
-  </si>
-  <si>
-    <t>Tổng hợp kết quả theo seed.</t>
-  </si>
-  <si>
-    <t>Phân biệt rõ split_seed và training_seed trong bảng stability.</t>
-  </si>
-  <si>
-    <t>Tính mean ± std.</t>
-  </si>
-  <si>
-    <t>Tính 95% CI nếu đủ seed.</t>
-  </si>
-  <si>
-    <t>Vẽ seed stability plot.</t>
-  </si>
-  <si>
-    <t>So sánh gain với baseline variability.</t>
-  </si>
-  <si>
-    <t>Cảnh báo seed leakage: supervised vs SSL cùng split_seed, nhiều training_seed để đo variance thật.</t>
-  </si>
-  <si>
-    <t>reports/seed_stability_report.csv</t>
-  </si>
-  <si>
-    <t>plots/results/seed_stability.png</t>
-  </si>
-  <si>
-    <t>Biết SSL gain có ổn định không.</t>
-  </si>
-  <si>
-    <t>Nếu gain nhỏ hơn std, ghi rõ không đủ mạnh để kết luận.</t>
-  </si>
-  <si>
-    <t>Không over-claim.</t>
-  </si>
-  <si>
-    <t>Không có variance giả do khóa nhầm training_seed.</t>
-  </si>
-  <si>
-    <t>7A. Generate final reports</t>
-  </si>
-  <si>
-    <t>Tổng hợp dataset report.</t>
-  </si>
-  <si>
-    <t>Tổng hợp supervised baseline.</t>
-  </si>
-  <si>
-    <t>Tổng hợp SSL results.</t>
-  </si>
-  <si>
-    <t>Tổng hợp threshold sweep.</t>
-  </si>
-  <si>
-    <t>Tổng hợp negative FP.</t>
-  </si>
-  <si>
-    <t>Tổng hợp seed stability.</t>
-  </si>
-  <si>
-    <t>Tổng hợp pseudo-bbox/NMS/confirmation-bias findings.</t>
-  </si>
-  <si>
-    <t>Tạo bảng kết quả chính.</t>
-  </si>
-  <si>
-    <t>Tạo hình label efficiency curve.</t>
-  </si>
-  <si>
-    <t>Tạo hình SSL gain curve.</t>
-  </si>
-  <si>
-    <t>reports/final_results_summary.md</t>
-  </si>
-  <si>
-    <t>reports/paper_framing.md</t>
-  </si>
-  <si>
-    <t>plots/results/label_efficiency_curve.png</t>
-  </si>
-  <si>
-    <t>Mọi bảng/hình trong thesis truy vết được tới CSV/log/config.</t>
-  </si>
-  <si>
-    <t>Không có số liệu nhập tay không rõ nguồn.</t>
-  </si>
-  <si>
-    <t>7B. Viết thesis/paper theo STRUCTURE.md</t>
-  </si>
-  <si>
-    <t>Viết Abstract.</t>
-  </si>
-  <si>
-    <t>Viết Introduction.</t>
-  </si>
-  <si>
-    <t>Viết Related Work.</t>
-  </si>
-  <si>
-    <t>Viết Materials and Data Protocol.</t>
-  </si>
-  <si>
-    <t>Viết Methodology.</t>
-  </si>
-  <si>
-    <t>Viết Experiments.</t>
-  </si>
-  <si>
-    <t>Viết Results.</t>
-  </si>
-  <si>
-    <t>Viết Discussion.</t>
-  </si>
-  <si>
-    <t>Viết Conclusion.</t>
-  </si>
-  <si>
-    <t>Viết Appendix.</t>
-  </si>
-  <si>
-    <t>draft/thesis/</t>
-  </si>
-  <si>
-    <t>draft/paper/</t>
-  </si>
-  <si>
-    <t>RQ nào cũng có experiment trả lời.</t>
-  </si>
-  <si>
-    <t>Experiment nào cũng có result.</t>
-  </si>
-  <si>
-    <t>Result nào cũng được discussion giải thích.</t>
-  </si>
-  <si>
-    <t>Không over-claim khi SSL gain yếu hoặc bất ổn.</t>
-  </si>
-  <si>
-    <t>Pre-train Gate</t>
-  </si>
-  <si>
-    <t>Gate</t>
-  </si>
-  <si>
-    <t>COCO master validate thành công.</t>
-  </si>
-  <si>
-    <t>No Finding không nằm trong categories.</t>
-  </si>
-  <si>
-    <t>Ảnh No Finding nằm trong images và không có annotations.</t>
-  </si>
-  <si>
-    <t>Framework không lọc bỏ ảnh empty.</t>
-  </si>
-  <si>
-    <t>Train/val/test leakage = 0.</t>
-  </si>
-  <si>
-    <t>Test set có đủ No Finding để đo FP per negative image.</t>
-  </si>
-  <si>
-    <t>Labeled splits nested đúng.</t>
-  </si>
-  <si>
-    <t>Supervised và SSL dùng cùng labeled split.</t>
-  </si>
-  <si>
-    <t>Supervised vs SSL dùng cùng split_seed.</t>
-  </si>
-  <si>
-    <t>Stability dùng nhiều training_seed.</t>
-  </si>
-  <si>
-    <t>Đã lưu seed number, RNG state và deterministic flags.</t>
-  </si>
-  <si>
-    <t>Test set không dùng để tune.</t>
-  </si>
-  <si>
-    <t>Test set không dùng để chọn checkpoint, threshold hoặc model tốt nhất.</t>
-  </si>
-  <si>
-    <t>Augmentation bbox transform đúng.</t>
-  </si>
-  <si>
-    <t>Pseudo-bbox generation có NMS và box quality filtering.</t>
-  </si>
-  <si>
-    <t>Có burn-in + EMA teacher để giảm confirmation bias.</t>
-  </si>
-  <si>
-    <t>Config seed được lưu.</t>
-  </si>
-  <si>
-    <t>Checkpoint được chọn bằng validation mAP@0.5:0.95.</t>
-  </si>
-  <si>
-    <t>Có kế hoạch OOM fallback trước khi chạy SSOD.</t>
-  </si>
-  <si>
-    <t>Silent Failure Checks</t>
-  </si>
-  <si>
-    <t>No Finding bị đưa nhầm thành detection class.</t>
-  </si>
-  <si>
-    <t>Ảnh empty bị framework loại khỏi dataloader.</t>
-  </si>
-  <si>
-    <t>Bbox format nhầm xyxy thành xywh.</t>
-  </si>
-  <si>
-    <t>Bbox bị lệch sau resize.</t>
-  </si>
-  <si>
-    <t>Bbox bị lệch sau flip/crop/scale.</t>
-  </si>
-  <si>
-    <t>Unlabeled data vô tình dùng ground truth.</t>
-  </si>
-  <si>
-    <t>Test set bị dùng trong threshold tuning.</t>
-  </si>
-  <si>
-    <t>SSL so với supervised nhưng không cùng labeled split.</t>
-  </si>
-  <si>
-    <t>SSL so với supervised nhưng không cùng split_seed.</t>
-  </si>
-  <si>
-    <t>Chỉ chạy 1 seed rồi kết luận gain.</t>
-  </si>
-  <si>
-    <t>Khóa nhầm training_seed giống nhau cho mọi run làm variance giả thấp.</t>
-  </si>
-  <si>
-    <t>Chỉ lưu seed number, không lưu RNG state và deterministic flags.</t>
-  </si>
-  <si>
-    <t>Teacher sinh quá nhiều pseudo-bbox trùng lặp vì thiếu NMS.</t>
-  </si>
-  <si>
-    <t>Pseudo-bbox không transform đúng từ weak sang strong view.</t>
-  </si>
-  <si>
-    <t>Threshold cao làm rare class biến mất.</t>
-  </si>
-  <si>
-    <t>Threshold thấp làm ảnh negative sinh nhiều pseudo-box sai.</t>
-  </si>
-  <si>
-    <t>Checkpoint tốt nhất chọn bằng test thay vì validation.</t>
-  </si>
-  <si>
-    <t>Checkpoint mỗi experiment chọn theo tiêu chí khác nhau.</t>
-  </si>
-  <si>
-    <t>Conclusion Rules</t>
-  </si>
-  <si>
-    <t>SSL gain/loss phải tính bằng mAP@0.5:0.95.</t>
-  </si>
-  <si>
-    <t>SSL gain phải so với supervised baseline cùng labeled split và cùng split_seed.</t>
-  </si>
-  <si>
-    <t>SSL gain phải báo cáo kèm mean ± std theo nhiều training_seed.</t>
-  </si>
-  <si>
-    <t>Nếu SSL gain nhỏ hơn hoặc tương đương std giữa các seed, chỉ nói chưa đủ bằng chứng ổn định.</t>
-  </si>
-  <si>
-    <t>Nếu SSL tăng mAP nhưng FP per negative image tăng mạnh, phải thảo luận trade-off y khoa.</t>
-  </si>
-  <si>
-    <t>Nếu threshold làm rare-class survival rate giảm mạnh, không được chỉ báo cáo mAP tổng.</t>
-  </si>
-  <si>
-    <t>Nếu SSL không giúp, kiểm tra threshold, NMS, confirmation bias, batch composition, OOM/compute simplification trước khi kết luận.</t>
-  </si>
-  <si>
     <t>2D.1A. Image Representation Protocol Decision</t>
   </si>
   <si>
     <t>Khóa vai trò: DICOM là immutable raw medical source; JPG là processed training representation.</t>
+  </si>
+  <si>
+    <t>CLOSED / PASS; GPT review PASS; full conversion not run</t>
   </si>
   <si>
     <t>Khóa vai trò: coco_master.json là annotation master; coco_master_jpg.json là training derivative.</t>
@@ -1791,15 +684,19 @@
     <t>Phase 2D.1A evidence đầy đủ và GPT review PASS; chưa full-convert dataset.</t>
   </si>
   <si>
+    <t>scripts/02D1A_image_representation_protocol.py
+configs/protocol/phase2D1_jpg_representation.yaml
+reports/phase2D1_image_representation_decision.md
+reports/phase2D1_image_representation_decision.json
+tests/test_phase2D1A_protocol_guardrails.py</t>
+  </si>
+  <si>
     <t>2D.1B-Pilot. DICOM-to-JPG Pilot</t>
   </si>
   <si>
     <t>Chọn pilot có abnormal, No Finding, min/max dimensions và metadata DICOM đại diện.</t>
   </si>
   <si>
-    <t>LOCKED until 2D.1A GPT review PASS</t>
-  </si>
-  <si>
     <t>Decode DICOM theo protocol 2D.1A và tạo pre-JPEG uint8 reference.</t>
   </si>
   <si>
@@ -1809,12 +706,6 @@
     <t>Encode/decode pilot với JPEG quality 100.</t>
   </si>
   <si>
-    <t>So sánh pre-JPEG uint8 với decoded JPG bằng file size, MAE, PSNR và SSIM.</t>
-  </si>
-  <si>
-    <t>Thực hiện visual audit, gồm ảnh abnormal và vùng tổn thương có bbox.</t>
-  </si>
-  <si>
     <t>Khóa một final JPEG quality dựa trên pilot evidence và GPT review.</t>
   </si>
   <si>
@@ -1825,9 +716,6 @@
   </si>
   <si>
     <t>Tạo script full DICOM-to-JPG conversion theo protocol và final quality đã khóa.</t>
-  </si>
-  <si>
-    <t>LOCKED until pilot and final JPEG quality decision PASS</t>
   </si>
   <si>
     <t>Tạo đúng 4,894 JPG; missing=0, duplicate image_id=0, decode error=0.</t>
@@ -1948,17 +836,1207 @@
     <t>Stage reviewed evidence, commit/push Phase 2D.1; không commit 4,894 JPG vào ordinary Git.</t>
   </si>
   <si>
-    <t>CLOSED / PASS; GPT review PASS; full conversion not run</t>
-  </si>
-  <si>
-    <t>scripts/02D1A_image_representation_protocol.py
-configs/protocol/phase2D1_jpg_representation.yaml
-reports/phase2D1_image_representation_decision.md
-reports/phase2D1_image_representation_decision.json
-tests/test_phase2D1A_protocol_guardrails.py</t>
-  </si>
-  <si>
-    <t>OPEN / CURRENT; full conversion locked until pilot evidence, final JPEG quality decision and GPT review PASS</t>
+    <t>2E. Fixed Train/Val/Test Split</t>
+  </si>
+  <si>
+    <t>Tạo train/val/test cố định.</t>
+  </si>
+  <si>
+    <t>Stratify theo class nếu khả thi.</t>
+  </si>
+  <si>
+    <t>Giữ phân phối ảnh negative hợp lý.</t>
+  </si>
+  <si>
+    <t>Đảm bảo test set có đủ ảnh No Finding để đo FP per negative image.</t>
+  </si>
+  <si>
+    <t>Kiểm tra số lượng và tỷ lệ No Finding trong train/val/test.</t>
+  </si>
+  <si>
+    <t>Check không trùng image_id giữa train/val/test.</t>
+  </si>
+  <si>
+    <t>Xuất split_lock_manifest.json.</t>
+  </si>
+  <si>
+    <t>data/manifests/split_lock_manifest.json</t>
+  </si>
+  <si>
+    <t>data/manifests/leakage_check_report.json</t>
+  </si>
+  <si>
+    <t>reports/split_negative_distribution.csv</t>
+  </si>
+  <si>
+    <t>data/processed/coco/instances_train.json</t>
+  </si>
+  <si>
+    <t>data/processed/coco/instances_val.json</t>
+  </si>
+  <si>
+    <t>data/processed/coco/instances_test.json</t>
+  </si>
+  <si>
+    <t>Leakage = 0.</t>
+  </si>
+  <si>
+    <t>Test set cố định, không dùng để tune.</t>
+  </si>
+  <si>
+    <t>Mọi experiment dùng cùng test set.</t>
+  </si>
+  <si>
+    <t>Test set chứa đủ ảnh No Finding để tính FP per negative image.</t>
+  </si>
+  <si>
+    <t>Tỷ lệ negative trong train/val/test được báo cáo rõ.</t>
+  </si>
+  <si>
+    <t>2F. Labeled/Unlabeled Split for SSL</t>
+  </si>
+  <si>
+    <t>Tạo labeled split 1%.</t>
+  </si>
+  <si>
+    <t>Tạo labeled split 5%.</t>
+  </si>
+  <si>
+    <t>Tạo labeled split 10%.</t>
+  </si>
+  <si>
+    <t>Tạo labeled split 20%.</t>
+  </si>
+  <si>
+    <t>Nested sampling: 1% ⊂ 5% ⊂ 10% ⊂ 20%.</t>
+  </si>
+  <si>
+    <t>Stratified theo class distribution.</t>
+  </si>
+  <si>
+    <t>Unlabeled = phần còn lại của train.</t>
+  </si>
+  <si>
+    <t>Unlabeled có thể gồm abnormal và No Finding.</t>
+  </si>
+  <si>
+    <t>Ground truth của unlabeled bị cô lập khỏi training SSL.</t>
+  </si>
+  <si>
+    <t>Theo dõi số lượng unlabeled negative images để phân tích pseudo-box sai.</t>
+  </si>
+  <si>
+    <t>data/processed/coco/labeled_splits/instances_labeled_1pct.json</t>
+  </si>
+  <si>
+    <t>data/processed/coco/labeled_splits/instances_labeled_5pct.json</t>
+  </si>
+  <si>
+    <t>data/processed/coco/labeled_splits/instances_labeled_10pct.json</t>
+  </si>
+  <si>
+    <t>data/processed/coco/labeled_splits/instances_labeled_20pct.json</t>
+  </si>
+  <si>
+    <t>data/processed/coco/labeled_splits/instances_unlabeled_1pct.json</t>
+  </si>
+  <si>
+    <t>data/processed/coco/labeled_splits/instances_unlabeled_5pct.json</t>
+  </si>
+  <si>
+    <t>data/processed/coco/labeled_splits/instances_unlabeled_10pct.json</t>
+  </si>
+  <si>
+    <t>data/processed/coco/labeled_splits/instances_unlabeled_20pct.json</t>
+  </si>
+  <si>
+    <t>data/manifests/nested_split_check.json</t>
+  </si>
+  <si>
+    <t>Nested property pass.</t>
+  </si>
+  <si>
+    <t>Không leakage với val/test.</t>
+  </si>
+  <si>
+    <t>Supervised low-label và SSL dùng cùng labeled split.</t>
+  </si>
+  <si>
+    <t>split_seed được lưu trong manifest.</t>
+  </si>
+  <si>
+    <t>2F.1 Seed Protocol: split_seed vs training_seed</t>
+  </si>
+  <si>
+    <t>split_seed dùng để tạo train/val/test và labeled/unlabeled split.</t>
+  </si>
+  <si>
+    <t>training_seed dùng để khởi tạo mô hình, dataloader shuffle, augmentation và training.</t>
+  </si>
+  <si>
+    <t>Supervised vs SSL dùng cùng split_seed để nhìn cùng dữ liệu.</t>
+  </si>
+  <si>
+    <t>Stability dùng nhiều training_seed để đo variance thật.</t>
+  </si>
+  <si>
+    <t>Không khóa cùng training_seed cho mọi run vì sẽ tạo variance giả thấp.</t>
+  </si>
+  <si>
+    <t>Log rõ split_seed, training_seed, rng_state_id cho từng run.</t>
+  </si>
+  <si>
+    <t>data/manifests/seed_manifest.json</t>
+  </si>
+  <si>
+    <t>reports/seed_protocol.md</t>
+  </si>
+  <si>
+    <t>Mỗi experiment log rõ split_seed và training_seed.</t>
+  </si>
+  <si>
+    <t>Stability được đo bằng nhiều training_seed.</t>
+  </si>
+  <si>
+    <t>Không có seed leakage hoặc variance giả do khóa nhầm seed.</t>
+  </si>
+  <si>
+    <t>3A. Pre-training Dataset Diagnostics</t>
+  </si>
+  <si>
+    <t>Vẽ class distribution.</t>
+  </si>
+  <si>
+    <t>Vẽ bbox count theo class.</t>
+  </si>
+  <si>
+    <t>Vẽ bbox size distribution.</t>
+  </si>
+  <si>
+    <t>Vẽ bbox location heatmap.</t>
+  </si>
+  <si>
+    <t>Thống kê rare class và chốt tiêu chí rare class.</t>
+  </si>
+  <si>
+    <t>Thống kê negative images.</t>
+  </si>
+  <si>
+    <t>Thống kê split distribution.</t>
+  </si>
+  <si>
+    <t>Chỉ dùng train cho diagnostics chính, không nhìn test để tune.</t>
+  </si>
+  <si>
+    <t>reports/dataset_analysis_report.md</t>
+  </si>
+  <si>
+    <t>plots/dataset/class_distribution.png</t>
+  </si>
+  <si>
+    <t>plots/dataset/bbox_distribution.png</t>
+  </si>
+  <si>
+    <t>plots/dataset/bbox_location_heatmap.png</t>
+  </si>
+  <si>
+    <t>plots/dataset/negative_image_distribution.png</t>
+  </si>
+  <si>
+    <t>Có báo cáo trước train.</t>
+  </si>
+  <si>
+    <t>Biết lớp nào rare.</t>
+  </si>
+  <si>
+    <t>Biết rủi ro imbalance.</t>
+  </si>
+  <si>
+    <t>Biết bbox nhỏ/vừa/lớn phân bố thế nào.</t>
+  </si>
+  <si>
+    <t>4A.0 Full-label supervised upper bound</t>
+  </si>
+  <si>
+    <t>Chọn detector chính.</t>
+  </si>
+  <si>
+    <t>Train trên 100% labeled train.</t>
+  </si>
+  <si>
+    <t>Select checkpoint theo validation set.</t>
+  </si>
+  <si>
+    <t>Chọn checkpoint tốt nhất theo validation mAP@0.5:0.95.</t>
+  </si>
+  <si>
+    <t>Không chọn checkpoint theo test set.</t>
+  </si>
+  <si>
+    <t>Không thay đổi tiêu chí chọn checkpoint giữa các experiment.</t>
+  </si>
+  <si>
+    <t>Evaluate trên fixed test set.</t>
+  </si>
+  <si>
+    <t>Lưu config, seed, RNG state, checkpoint, log.</t>
+  </si>
+  <si>
+    <t>Metric bắt buộc</t>
+  </si>
+  <si>
+    <t>mAP@0.5:0.95 — metric chính</t>
+  </si>
+  <si>
+    <t>mAP@0.5</t>
+  </si>
+  <si>
+    <t>Class-wise AP</t>
+  </si>
+  <si>
+    <t>Recall</t>
+  </si>
+  <si>
+    <t>FP per image</t>
+  </si>
+  <si>
+    <t>FP per negative image</t>
+  </si>
+  <si>
+    <t>reports/supervised_full_results.csv</t>
+  </si>
+  <si>
+    <t>experiments/exp1_full_label_baseline/</t>
+  </si>
+  <si>
+    <t>models/supervised/full_label/</t>
+  </si>
+  <si>
+    <t>Có upper bound 100%.</t>
+  </si>
+  <si>
+    <t>Kết quả trace được từ config → log → checkpoint → report.</t>
+  </si>
+  <si>
+    <t>Không dùng test để chọn model.</t>
+  </si>
+  <si>
+    <t>FP per negative image được tính trên test set có đủ ảnh No Finding.</t>
+  </si>
+  <si>
+    <t>Checkpoint selection criterion khóa là validation mAP@0.5:0.95.</t>
+  </si>
+  <si>
+    <t>4A.1 Low-label supervised baseline</t>
+  </si>
+  <si>
+    <t>Train 1% labeled.</t>
+  </si>
+  <si>
+    <t>Train 5% labeled.</t>
+  </si>
+  <si>
+    <t>Train 10% labeled.</t>
+  </si>
+  <si>
+    <t>Train 20% labeled.</t>
+  </si>
+  <si>
+    <t>Mỗi mức label chạy 3–5 training_seed.</t>
+  </si>
+  <si>
+    <t>Dùng đúng labeled split đã khóa bằng split_seed.</t>
+  </si>
+  <si>
+    <t>Chọn checkpoint theo validation mAP@0.5:0.95.</t>
+  </si>
+  <si>
+    <t>Evaluate trên cùng fixed test set.</t>
+  </si>
+  <si>
+    <t>Báo cáo mean ± std.</t>
+  </si>
+  <si>
+    <t>Lưu seed number, RNG state và deterministic flags cho từng run.</t>
+  </si>
+  <si>
+    <t>reports/supervised_lowlabel_results.csv</t>
+  </si>
+  <si>
+    <t>experiments/exp2_low_label_baseline/</t>
+  </si>
+  <si>
+    <t>Có baseline đối chứng cho từng mức label.</t>
+  </si>
+  <si>
+    <t>SSL so sánh với baseline dùng cùng labeled split/cùng split_seed.</t>
+  </si>
+  <si>
+    <t>Stability đo qua nhiều training_seed.</t>
+  </si>
+  <si>
+    <t>Nếu variance lớn, ghi rõ trong báo cáo.</t>
+  </si>
+  <si>
+    <t>Checkpoint chọn nhất quán bằng validation mAP@0.5:0.95.</t>
+  </si>
+  <si>
+    <t>4B. Extension: Attention / ViT-Oriented Supervised Analysis</t>
+  </si>
+  <si>
+    <t>Đánh giá feasibility GPU/VRAM/thời gian train cho ViT/Attention.</t>
+  </si>
+  <si>
+    <t>Nếu khả thi: chạy supervised baseline ViT/Attention.</t>
+  </si>
+  <si>
+    <t>So sánh với detector chính trên cùng split/test/metric.</t>
+  </si>
+  <si>
+    <t>Ghi rõ đây là extension, không phải trọng tâm chính.</t>
+  </si>
+  <si>
+    <t>reports/vit_attention_feasibility_report.md</t>
+  </si>
+  <si>
+    <t>reports/attention_supervised_results.csv</t>
+  </si>
+  <si>
+    <t>Có quyết định chạy hoặc không chạy extension dựa trên compute.</t>
+  </si>
+  <si>
+    <t>Extension không làm lệch trọng tâm teacher-student SSOD.</t>
+  </si>
+  <si>
+    <t>5.1A Teacher–Student SSL Pipeline</t>
+  </si>
+  <si>
+    <t>Khởi tạo student từ supervised detector.</t>
+  </si>
+  <si>
+    <t>Khởi tạo teacher.</t>
+  </si>
+  <si>
+    <t>Teacher sinh pseudo-label trên weak augmentation.</t>
+  </si>
+  <si>
+    <t>Student học trên strong augmentation.</t>
+  </si>
+  <si>
+    <t>Teacher cập nhật bằng EMA.</t>
+  </si>
+  <si>
+    <t>Có burn-in supervised trước khi bật SSL.</t>
+  </si>
+  <si>
+    <t>Ghi rõ λ của unlabeled loss.</t>
+  </si>
+  <si>
+    <t>Đồng bộ transform bbox với geometric augmentation.</t>
+  </si>
+  <si>
+    <t>reports/ssl_results.csv</t>
+  </si>
+  <si>
+    <t>experiments/exp3_ssl_detection/</t>
+  </si>
+  <si>
+    <t>models/ssl/</t>
+  </si>
+  <si>
+    <t>Train SSL chạy end-to-end.</t>
+  </si>
+  <si>
+    <t>Có log pseudo-label count.</t>
+  </si>
+  <si>
+    <t>Có log unlabeled loss λ.</t>
+  </si>
+  <si>
+    <t>Không có lỗi box lệch do augmentation.</t>
+  </si>
+  <si>
+    <t>5.1B Pseudo-BBox Generation, NMS &amp; Box Filtering</t>
+  </si>
+  <si>
+    <t>Teacher prediction trên weak image tạo pseudo-label dạng class_id + confidence + bbox xywh.</t>
+  </si>
+  <si>
+    <t>Lọc theo confidence threshold.</t>
+  </si>
+  <si>
+    <t>Áp dụng class-wise threshold nếu cấu hình bật.</t>
+  </si>
+  <si>
+    <t>Áp dụng NMS trước khi nhận pseudo-bbox để giảm box trùng lặp.</t>
+  </si>
+  <si>
+    <t>Áp dụng box quality filters: bbox size, aspect ratio, boundary, area.</t>
+  </si>
+  <si>
+    <t>Giới hạn số pseudo-box tối đa mỗi ảnh nếu cần để tránh nhiễu dày đặc.</t>
+  </si>
+  <si>
+    <t>Lưu pseudo-label gồm image_id, class_id, confidence, bbox xywh, threshold_used, nms_iou.</t>
+  </si>
+  <si>
+    <t>Transform pseudo-bbox đúng từ weak view sang strong view.</t>
+  </si>
+  <si>
+    <t>Visualize một số pseudo-box sau transform để kiểm tra khớp ảnh student.</t>
+  </si>
+  <si>
+    <t>reports/pseudo_label_filter_report.csv</t>
+  </si>
+  <si>
+    <t>reports/pseudo_bbox_generation_report.md</t>
+  </si>
+  <si>
+    <t>plots/error_vis/pseudo_label_failure_cases/</t>
+  </si>
+  <si>
+    <t>Pseudo-label cho detection có đủ class_id, confidence, bbox xywh.</t>
+  </si>
+  <si>
+    <t>NMS được áp dụng trước khi student học pseudo-box.</t>
+  </si>
+  <si>
+    <t>Box transform weak→strong được kiểm tra bằng test và visualization.</t>
+  </si>
+  <si>
+    <t>5.1C Anti-confirmation-bias Safeguards</t>
+  </si>
+  <si>
+    <t>Dùng supervised burn-in trước SSL.</t>
+  </si>
+  <si>
+    <t>Dùng EMA teacher thay vì cập nhật teacher trực tiếp.</t>
+  </si>
+  <si>
+    <t>Không bật pseudo-label nếu teacher chưa đạt ngưỡng tối thiểu trên validation hoặc chưa qua burn-in.</t>
+  </si>
+  <si>
+    <t>Theo dõi pseudo-label quality proxy theo epoch.</t>
+  </si>
+  <si>
+    <t>Theo dõi pseudo-box sai trên ảnh No Finding trong unlabeled set.</t>
+  </si>
+  <si>
+    <t>Theo dõi class-wise pseudo-label count để phát hiện teacher bias.</t>
+  </si>
+  <si>
+    <t>Không chọn threshold chỉ vì mAP tổng tốt nếu rare class bị triệt tiêu.</t>
+  </si>
+  <si>
+    <t>Ghi rõ confirmation bias như rủi ro chính trong report.</t>
+  </si>
+  <si>
+    <t>reports/confirmation_bias_monitoring.md</t>
+  </si>
+  <si>
+    <t>reports/pseudolabel_rareclass_report.csv</t>
+  </si>
+  <si>
+    <t>reports/negative_pseudobox_report.csv</t>
+  </si>
+  <si>
+    <t>Có ít nhất một cơ chế chống confirmation bias ngoài threshold đơn giản.</t>
+  </si>
+  <si>
+    <t>Có báo cáo pseudo-box sai trên No Finding.</t>
+  </si>
+  <si>
+    <t>Có báo cáo rare-class pseudo-label survival rate.</t>
+  </si>
+  <si>
+    <t>5.1D Threshold Strategy: Global, Class-wise, Dynamic</t>
+  </si>
+  <si>
+    <t>Sweep confidence threshold chung từ 0.1 → 0.9.</t>
+  </si>
+  <si>
+    <t>Thử class-wise / dynamic threshold như ablation.</t>
+  </si>
+  <si>
+    <t>Không khóa cứng threshold cụ thể trước khi có validation.</t>
+  </si>
+  <si>
+    <t>Với class hiếm, đánh giá cân bằng giữa pseudo-label coverage và pseudo-label noise.</t>
+  </si>
+  <si>
+    <t>Ghi threshold_used theo từng pseudo-label.</t>
+  </si>
+  <si>
+    <t>Báo cáo pseudo-label count theo class và threshold.</t>
+  </si>
+  <si>
+    <t>reports/threshold_policy.md</t>
+  </si>
+  <si>
+    <t>reports/threshold_sweep_report.csv</t>
+  </si>
+  <si>
+    <t>Threshold cuối được chọn bằng validation/analysis split, không dùng test.</t>
+  </si>
+  <si>
+    <t>Class-wise threshold chỉ được kết luận nếu có ablation.</t>
+  </si>
+  <si>
+    <t>Không dùng ví dụ 0.9/0.6 như protocol cố định nếu chưa có bằng chứng.</t>
+  </si>
+  <si>
+    <t>5.1E Positive/Negative Batch Monitoring</t>
+  </si>
+  <si>
+    <t>Log tỷ lệ positive/negative trong labeled batch.</t>
+  </si>
+  <si>
+    <t>Log tỷ lệ positive/negative trong unlabeled batch nếu metadata cho phép.</t>
+  </si>
+  <si>
+    <t>Không giả định ảnh Normal chiếm đa số; kiểm tra tỷ lệ thật trong split và batch.</t>
+  </si>
+  <si>
+    <t>Theo dõi pseudo-box sinh trên unlabeled negative images.</t>
+  </si>
+  <si>
+    <t>Nếu batch lệch quá mạnh, dùng sampler kiểm soát nhẹ như biện pháp ổn định training, không xem là contribution xử lý imbalance.</t>
+  </si>
+  <si>
+    <t>reports/batch_composition_report.csv</t>
+  </si>
+  <si>
+    <t>reports/unlabeled_negative_monitoring.csv</t>
+  </si>
+  <si>
+    <t>Biết tỷ lệ positive/negative trong training batches.</t>
+  </si>
+  <si>
+    <t>Nếu SSL thất bại, có dữ liệu để kiểm tra batch bias.</t>
+  </si>
+  <si>
+    <t>5.1F Compute / OOM Fallback for SSOD</t>
+  </si>
+  <si>
+    <t>Chạy smoke test SSL trước full training.</t>
+  </si>
+  <si>
+    <t>Chuẩn bị AMP mixed precision.</t>
+  </si>
+  <si>
+    <t>Chuẩn bị gradient accumulation.</t>
+  </si>
+  <si>
+    <t>Giảm batch size khi OOM.</t>
+  </si>
+  <si>
+    <t>Giảm image size có kiểm soát nếu cần và ghi rõ ảnh hưởng.</t>
+  </si>
+  <si>
+    <t>Giảm unlabeled images per batch nếu OOM.</t>
+  </si>
+  <si>
+    <t>Lưu checkpoint/resume để tránh mất tiến trình.</t>
+  </si>
+  <si>
+    <t>Nếu Colab/Kaggle không đủ, chuyển Vast.ai.</t>
+  </si>
+  <si>
+    <t>reports/compute_budget_report.md</t>
+  </si>
+  <si>
+    <t>reports/oom_fallback_log.md</t>
+  </si>
+  <si>
+    <t>Có kế hoạch fallback trước khi chạy SSL tốn GPU.</t>
+  </si>
+  <si>
+    <t>OOM không làm mất checkpoint hoặc thay đổi protocol âm thầm.</t>
+  </si>
+  <si>
+    <t>5.1G SSL Main Experiments</t>
+  </si>
+  <si>
+    <t>Chạy SSL 1%.</t>
+  </si>
+  <si>
+    <t>Chạy SSL 5%.</t>
+  </si>
+  <si>
+    <t>Chạy SSL 10%.</t>
+  </si>
+  <si>
+    <t>Chạy SSL 20%.</t>
+  </si>
+  <si>
+    <t>Mỗi mức chạy 3–5 training_seed.</t>
+  </si>
+  <si>
+    <t>So sánh với supervised baseline cùng labeled split, cùng split_seed, cùng fixed test set.</t>
+  </si>
+  <si>
+    <t>Không hiểu 'cùng seed' là khóa giống toàn bộ training_seed; fair comparison dùng cùng split_seed, stability dùng nhiều training_seed.</t>
+  </si>
+  <si>
+    <t>SSL checkpoint chọn theo validation mAP@0.5:0.95.</t>
+  </si>
+  <si>
+    <t>Tính SSL Gain = mAP@0.5:0.95_SSL - mAP@0.5:0.95_Supervised.</t>
+  </si>
+  <si>
+    <t>reports/ssl_gain_curve.csv</t>
+  </si>
+  <si>
+    <t>plots/results/ssl_gain_curve.png</t>
+  </si>
+  <si>
+    <t>Có SSL gain/loss từng mức label.</t>
+  </si>
+  <si>
+    <t>Có mean ± std.</t>
+  </si>
+  <si>
+    <t>Không kết luận gain nếu gain nhỏ hơn std giữa seed.</t>
+  </si>
+  <si>
+    <t>Metric chọn checkpoint khóa là validation mAP@0.5:0.95.</t>
+  </si>
+  <si>
+    <t>5.2 / 5.3 Optional Extension: Attention / ViT SSL</t>
+  </si>
+  <si>
+    <t>Chỉ chạy nếu compute cho phép.</t>
+  </si>
+  <si>
+    <t>Dùng cùng split, metric, checkpoint criterion.</t>
+  </si>
+  <si>
+    <t>Kiểm tra Attention/ViT có cải thiện SSL gain hoặc stability không.</t>
+  </si>
+  <si>
+    <t>Không xem là đóng góp chính nếu chưa đủ multi-seed.</t>
+  </si>
+  <si>
+    <t>reports/attention_ssl_results.csv</t>
+  </si>
+  <si>
+    <t>reports/attention_ssl_stability_report.csv</t>
+  </si>
+  <si>
+    <t>Có quyết định chạy/không chạy extension dựa trên compute.</t>
+  </si>
+  <si>
+    <t>Extension không làm thay đổi kết luận chính nếu thiếu multi-seed.</t>
+  </si>
+  <si>
+    <t>6A. Threshold sweep</t>
+  </si>
+  <si>
+    <t>Sweep threshold 0.1 → 0.9.</t>
+  </si>
+  <si>
+    <t>Ghi pseudo-label count theo threshold.</t>
+  </si>
+  <si>
+    <t>Ghi pseudo-label count theo class.</t>
+  </si>
+  <si>
+    <t>Ghi rare-class survival rate.</t>
+  </si>
+  <si>
+    <t>Ghi mAP theo threshold.</t>
+  </si>
+  <si>
+    <t>Ghi FP trên negative theo threshold.</t>
+  </si>
+  <si>
+    <t>Threshold tuning chỉ dùng validation hoặc analysis split được quy định trước, không dùng test.</t>
+  </si>
+  <si>
+    <t>Phân tích NMS IoU và max pseudo-box per image nếu có.</t>
+  </si>
+  <si>
+    <t>plots/results/threshold_sweep.png</t>
+  </si>
+  <si>
+    <t>Biết threshold nào tốt nhưng gây bias.</t>
+  </si>
+  <si>
+    <t>Biết threshold nào giữ rare class tốt hơn.</t>
+  </si>
+  <si>
+    <t>Có cơ sở chọn threshold cuối.</t>
+  </si>
+  <si>
+    <t>Test set không bị dùng để chọn threshold.</t>
+  </si>
+  <si>
+    <t>6B. Evaluation chính</t>
+  </si>
+  <si>
+    <t>Evaluate tất cả checkpoint tốt nhất.</t>
+  </si>
+  <si>
+    <t>Tính mAP@0.5:0.95.</t>
+  </si>
+  <si>
+    <t>Tính mAP@0.5.</t>
+  </si>
+  <si>
+    <t>Tính class-wise AP.</t>
+  </si>
+  <si>
+    <t>Tính recall.</t>
+  </si>
+  <si>
+    <t>Tính FP per image.</t>
+  </si>
+  <si>
+    <t>Tính FP per negative image.</t>
+  </si>
+  <si>
+    <t>Tính bbox-size AP nếu có.</t>
+  </si>
+  <si>
+    <t>reports/final_evaluation_results.csv</t>
+  </si>
+  <si>
+    <t>reports/classwise_ap_results.csv</t>
+  </si>
+  <si>
+    <t>reports/negative_fp_report.csv</t>
+  </si>
+  <si>
+    <t>Tất cả mô hình evaluate trên cùng fixed test set.</t>
+  </si>
+  <si>
+    <t>Metric chính là mAP@0.5:0.95.</t>
+  </si>
+  <si>
+    <t>Không dùng metric phụ để thay thế kết luận chính.</t>
+  </si>
+  <si>
+    <t>FP per negative image tính trên test set có đủ No Finding.</t>
+  </si>
+  <si>
+    <t>6C. Error analysis</t>
+  </si>
+  <si>
+    <t>Phân tích false positive trên ảnh No Finding.</t>
+  </si>
+  <si>
+    <t>Phân tích false negative trên ảnh abnormal.</t>
+  </si>
+  <si>
+    <t>Phân tích class nào hay bị nhầm.</t>
+  </si>
+  <si>
+    <t>Phân tích bbox nhỏ có bị bỏ sót không.</t>
+  </si>
+  <si>
+    <t>Visualize TP / FP / FN.</t>
+  </si>
+  <si>
+    <t>Visualize pseudo-label failure cases.</t>
+  </si>
+  <si>
+    <t>Liên hệ lỗi với confirmation bias, threshold, NMS và batch composition.</t>
+  </si>
+  <si>
+    <t>reports/error_analysis_report.md</t>
+  </si>
+  <si>
+    <t>plots/error_vis/true_positive_examples/</t>
+  </si>
+  <si>
+    <t>plots/error_vis/false_positive_negative_images/</t>
+  </si>
+  <si>
+    <t>plots/error_vis/false_negative_abnormal_images/</t>
+  </si>
+  <si>
+    <t>Mỗi kết luận định lượng có ví dụ hình ảnh minh họa.</t>
+  </si>
+  <si>
+    <t>Mỗi lỗi chính có giải thích hoặc hành động.</t>
+  </si>
+  <si>
+    <t>6D. Stability analysis</t>
+  </si>
+  <si>
+    <t>Tổng hợp kết quả theo seed.</t>
+  </si>
+  <si>
+    <t>Phân biệt rõ split_seed và training_seed trong bảng stability.</t>
+  </si>
+  <si>
+    <t>Tính mean ± std.</t>
+  </si>
+  <si>
+    <t>Tính 95% CI nếu đủ seed.</t>
+  </si>
+  <si>
+    <t>Vẽ seed stability plot.</t>
+  </si>
+  <si>
+    <t>So sánh gain với baseline variability.</t>
+  </si>
+  <si>
+    <t>Cảnh báo seed leakage: supervised vs SSL cùng split_seed, nhiều training_seed để đo variance thật.</t>
+  </si>
+  <si>
+    <t>reports/seed_stability_report.csv</t>
+  </si>
+  <si>
+    <t>plots/results/seed_stability.png</t>
+  </si>
+  <si>
+    <t>Biết SSL gain có ổn định không.</t>
+  </si>
+  <si>
+    <t>Nếu gain nhỏ hơn std, ghi rõ không đủ mạnh để kết luận.</t>
+  </si>
+  <si>
+    <t>Không over-claim.</t>
+  </si>
+  <si>
+    <t>Không có variance giả do khóa nhầm training_seed.</t>
+  </si>
+  <si>
+    <t>7A. Generate final reports</t>
+  </si>
+  <si>
+    <t>Tổng hợp dataset report.</t>
+  </si>
+  <si>
+    <t>Tổng hợp supervised baseline.</t>
+  </si>
+  <si>
+    <t>Tổng hợp SSL results.</t>
+  </si>
+  <si>
+    <t>Tổng hợp threshold sweep.</t>
+  </si>
+  <si>
+    <t>Tổng hợp negative FP.</t>
+  </si>
+  <si>
+    <t>Tổng hợp seed stability.</t>
+  </si>
+  <si>
+    <t>Tổng hợp pseudo-bbox/NMS/confirmation-bias findings.</t>
+  </si>
+  <si>
+    <t>Tạo bảng kết quả chính.</t>
+  </si>
+  <si>
+    <t>Tạo hình label efficiency curve.</t>
+  </si>
+  <si>
+    <t>Tạo hình SSL gain curve.</t>
+  </si>
+  <si>
+    <t>reports/final_results_summary.md</t>
+  </si>
+  <si>
+    <t>reports/paper_framing.md</t>
+  </si>
+  <si>
+    <t>plots/results/label_efficiency_curve.png</t>
+  </si>
+  <si>
+    <t>Mọi bảng/hình trong thesis truy vết được tới CSV/log/config.</t>
+  </si>
+  <si>
+    <t>Không có số liệu nhập tay không rõ nguồn.</t>
+  </si>
+  <si>
+    <t>7B. Viết thesis/paper theo STRUCTURE.md</t>
+  </si>
+  <si>
+    <t>Viết Abstract.</t>
+  </si>
+  <si>
+    <t>Viết Introduction.</t>
+  </si>
+  <si>
+    <t>Viết Related Work.</t>
+  </si>
+  <si>
+    <t>Viết Materials and Data Protocol.</t>
+  </si>
+  <si>
+    <t>Viết Methodology.</t>
+  </si>
+  <si>
+    <t>Viết Experiments.</t>
+  </si>
+  <si>
+    <t>Viết Results.</t>
+  </si>
+  <si>
+    <t>Viết Discussion.</t>
+  </si>
+  <si>
+    <t>Viết Conclusion.</t>
+  </si>
+  <si>
+    <t>Viết Appendix.</t>
+  </si>
+  <si>
+    <t>draft/thesis/</t>
+  </si>
+  <si>
+    <t>draft/paper/</t>
+  </si>
+  <si>
+    <t>RQ nào cũng có experiment trả lời.</t>
+  </si>
+  <si>
+    <t>Experiment nào cũng có result.</t>
+  </si>
+  <si>
+    <t>Result nào cũng được discussion giải thích.</t>
+  </si>
+  <si>
+    <t>Không over-claim khi SSL gain yếu hoặc bất ổn.</t>
+  </si>
+  <si>
+    <t>Pre-train Gate</t>
+  </si>
+  <si>
+    <t>Gate</t>
+  </si>
+  <si>
+    <t>COCO master validate thành công.</t>
+  </si>
+  <si>
+    <t>No Finding không nằm trong categories.</t>
+  </si>
+  <si>
+    <t>Ảnh No Finding nằm trong images và không có annotations.</t>
+  </si>
+  <si>
+    <t>Framework không lọc bỏ ảnh empty.</t>
+  </si>
+  <si>
+    <t>Train/val/test leakage = 0.</t>
+  </si>
+  <si>
+    <t>Test set có đủ No Finding để đo FP per negative image.</t>
+  </si>
+  <si>
+    <t>Labeled splits nested đúng.</t>
+  </si>
+  <si>
+    <t>Supervised và SSL dùng cùng labeled split.</t>
+  </si>
+  <si>
+    <t>Supervised vs SSL dùng cùng split_seed.</t>
+  </si>
+  <si>
+    <t>Stability dùng nhiều training_seed.</t>
+  </si>
+  <si>
+    <t>Đã lưu seed number, RNG state và deterministic flags.</t>
+  </si>
+  <si>
+    <t>Test set không dùng để tune.</t>
+  </si>
+  <si>
+    <t>Test set không dùng để chọn checkpoint, threshold hoặc model tốt nhất.</t>
+  </si>
+  <si>
+    <t>Augmentation bbox transform đúng.</t>
+  </si>
+  <si>
+    <t>Pseudo-bbox generation có NMS và box quality filtering.</t>
+  </si>
+  <si>
+    <t>Có burn-in + EMA teacher để giảm confirmation bias.</t>
+  </si>
+  <si>
+    <t>Config seed được lưu.</t>
+  </si>
+  <si>
+    <t>Checkpoint được chọn bằng validation mAP@0.5:0.95.</t>
+  </si>
+  <si>
+    <t>Có kế hoạch OOM fallback trước khi chạy SSOD.</t>
+  </si>
+  <si>
+    <t>Silent Failure Checks</t>
+  </si>
+  <si>
+    <t>No Finding bị đưa nhầm thành detection class.</t>
+  </si>
+  <si>
+    <t>Ảnh empty bị framework loại khỏi dataloader.</t>
+  </si>
+  <si>
+    <t>Bbox format nhầm xyxy thành xywh.</t>
+  </si>
+  <si>
+    <t>Bbox bị lệch sau resize.</t>
+  </si>
+  <si>
+    <t>Bbox bị lệch sau flip/crop/scale.</t>
+  </si>
+  <si>
+    <t>Unlabeled data vô tình dùng ground truth.</t>
+  </si>
+  <si>
+    <t>Test set bị dùng trong threshold tuning.</t>
+  </si>
+  <si>
+    <t>SSL so với supervised nhưng không cùng labeled split.</t>
+  </si>
+  <si>
+    <t>SSL so với supervised nhưng không cùng split_seed.</t>
+  </si>
+  <si>
+    <t>Chỉ chạy 1 seed rồi kết luận gain.</t>
+  </si>
+  <si>
+    <t>Khóa nhầm training_seed giống nhau cho mọi run làm variance giả thấp.</t>
+  </si>
+  <si>
+    <t>Chỉ lưu seed number, không lưu RNG state và deterministic flags.</t>
+  </si>
+  <si>
+    <t>Teacher sinh quá nhiều pseudo-bbox trùng lặp vì thiếu NMS.</t>
+  </si>
+  <si>
+    <t>Pseudo-bbox không transform đúng từ weak sang strong view.</t>
+  </si>
+  <si>
+    <t>Threshold cao làm rare class biến mất.</t>
+  </si>
+  <si>
+    <t>Threshold thấp làm ảnh negative sinh nhiều pseudo-box sai.</t>
+  </si>
+  <si>
+    <t>Checkpoint tốt nhất chọn bằng test thay vì validation.</t>
+  </si>
+  <si>
+    <t>Checkpoint mỗi experiment chọn theo tiêu chí khác nhau.</t>
+  </si>
+  <si>
+    <t>Conclusion Rules</t>
+  </si>
+  <si>
+    <t>SSL gain/loss phải tính bằng mAP@0.5:0.95.</t>
+  </si>
+  <si>
+    <t>SSL gain phải so với supervised baseline cùng labeled split và cùng split_seed.</t>
+  </si>
+  <si>
+    <t>SSL gain phải báo cáo kèm mean ± std theo nhiều training_seed.</t>
+  </si>
+  <si>
+    <t>Nếu SSL gain nhỏ hơn hoặc tương đương std giữa các seed, chỉ nói chưa đủ bằng chứng ổn định.</t>
+  </si>
+  <si>
+    <t>Nếu SSL tăng mAP nhưng FP per negative image tăng mạnh, phải thảo luận trade-off y khoa.</t>
+  </si>
+  <si>
+    <t>Nếu threshold làm rare-class survival rate giảm mạnh, không được chỉ báo cáo mAP tổng.</t>
+  </si>
+  <si>
+    <t>Nếu SSL không giúp, kiểm tra threshold, NMS, confirmation bias, batch composition, OOM/compute simplification trước khi kết luận.</t>
+  </si>
+  <si>
+    <t>CLOSED / PASS; pilot=64 images; No Finding=16; metadata/features coverage=54/54; abnormal class coverage=14/14.</t>
+  </si>
+  <si>
+    <t>reports/phase2D1B_pilot_selection.csv; reports/phase2D1B_pilot_selection_coverage.csv</t>
+  </si>
+  <si>
+    <t>CLOSED / PASS; explicit Pillow backend; pixel decode=64/64; decode errors=0; no silent decoder fallback.</t>
+  </si>
+  <si>
+    <t>reports/phase2D1B_pilot_run_output_pillow.txt; reports/phase2D1B_pilot_environment.json; reports/phase2D1B_pilot_header_inventory.csv; data/processed/image_mapping/phase2D1B_pilot_dicom_to_jpg_mapping.csv</t>
+  </si>
+  <si>
+    <t>CLOSED / PASS; JPEG quality 95 paired encode/decode completed; whole-image and bbox-ROI fidelity evidence complete.</t>
+  </si>
+  <si>
+    <t>reports/phase2D1B_pilot_fidelity_metrics.csv; reports/phase2D1B_pilot_bbox_roi_metrics.csv; data/processed/images_jpg_pilot/q95/</t>
+  </si>
+  <si>
+    <t>CLOSED / PASS; JPEG quality 100 paired encode/decode completed; whole-image and bbox-ROI fidelity evidence complete.</t>
+  </si>
+  <si>
+    <t>reports/phase2D1B_pilot_fidelity_metrics.csv; reports/phase2D1B_pilot_bbox_roi_metrics.csv; data/processed/images_jpg_pilot/q100/</t>
+  </si>
+  <si>
+    <t>So sánh pre-JPEG uint8 với decoded JPG bằng file size, compression ratio, MAE, RMSE, PSNR, SSIM, Max AE, p95/p99 AE và bbox-ROI metrics.</t>
+  </si>
+  <si>
+    <t>q100 wins numerical fidelity. q95 selected as fidelity-storage/I/O trade-off. q95: PSNR=47.2414 dB, SSIM=0.981217, ROI PSNR=47.9413 dB, ROI SSIM=0.996632, projected storage=7.38 GiB. q100: PSNR=58.8577 dB, SSIM=0.998981, ROI PSNR=58.7247 dB, ROI SSIM=0.999820, projected storage=14.41 GiB. q95 reduces projected storage by approximately 48.79%.</t>
+  </si>
+  <si>
+    <t>reports/phase2D1B_pilot_quality_summary.csv; reports/phase2D1B_pilot_quality_pairwise.csv; reports/phase2D1B_pilot_fidelity_metrics.csv; reports/phase2D1B_pilot_bbox_roi_metrics.csv</t>
+  </si>
+  <si>
+    <t>Thực hiện visual audit gồm No Finding, abnormal images, lesion nhỏ, rare class, multi-window, padding, polarity, dimension/bbox extrema và worst-case q95/q100.</t>
+  </si>
+  <si>
+    <t>Visual review complete; no critical polarity inversion, crop, rotation, flip, transpose, geometry deformation or conversion-induced anatomical truncation observed. This is representation-pipeline evidence, not clinical validation.</t>
+  </si>
+  <si>
+    <t>reports/phase2D1B_pilot_visual_audit_manifest.csv; plots/phase2D1B_pilot/contact_sheets/; plots/phase2D1B_pilot/bbox_crops/; plots/phase2D1B_pilot/difference_heatmaps/</t>
+  </si>
+  <si>
+    <t>Final JPEG quality=95 / LOCKED after quantitative, geometry, bbox-ROI, storage and visual review. Full controlled-scope conversion authorized. This is a fidelity-storage/I/O decision and does not claim detector superiority or clinical equivalence.</t>
+  </si>
+  <si>
+    <t>reports/phase2D1B_pilot_decision_template.json; reports/phase2D1B_pilot_quality_summary.csv; reports/phase2D1B_pilot_quality_pairwise.csv</t>
+  </si>
+  <si>
+    <t>Phase 2D.1B-Pilot fidelity and decision evidence package completed. Pilot CLOSED / PASS; final JPEG quality=95. Generated structural validation JSON remains historical pre-review evidence and must not be edited retroactively.</t>
+  </si>
+  <si>
+    <t>reports/phase2D1B_pilot_fidelity_metrics.csv; reports/phase2D1B_pilot_bbox_roi_metrics.csv; reports/phase2D1B_pilot_quality_summary.csv; reports/phase2D1B_pilot_quality_pairwise.csv; reports/phase2D1B_pilot_geometry_validation.csv; reports/phase2D1B_pilot_visual_audit_manifest.csv; reports/phase2D1B_pilot_validation.json; reports/phase2D1B_pilot_validation.md; reports/phase2D1B_pilot_decision_template.json</t>
+  </si>
+  <si>
+    <t>OPEN / NOT STARTED; pilot PASS; final JPEG quality=95; protocol version=1.0.0; full conversion authorized; explicit decoder required; no training.</t>
+  </si>
+  <si>
+    <t>reports/phase2D1B_pilot_decision_template.json</t>
+  </si>
+  <si>
+    <t>NOT STARTED; target exactly 4,894 JPEG quality 95 images; missing=0; duplicate image_id=0; decode errors=0.</t>
+  </si>
+  <si>
+    <t>NOT STARTED; width and height must match DICOM/COCO; resize, crop, rotation, flip and transpose must remain 0.</t>
+  </si>
+  <si>
+    <t>NOT STARTED; bbox_scaling_required must remain false; do not modify, clamp, scale, delete or fuse bbox.</t>
+  </si>
+  <si>
+    <t>NOT STARTED; coco_master_jpg.json is a path-only derivative; only images[].file_name may change from .dicom to .jpg.</t>
+  </si>
+  <si>
+    <t>NOT STARTED; COCO-JPG must preserve images=4,894, annotations=36,096 and categories=14.</t>
+  </si>
+  <si>
+    <t>NOT STARTED; retain abnormal images=4,394, No Finding images=500 and No Finding annotations=0.</t>
+  </si>
+  <si>
+    <t>NOT STARTED; bbox, area, category, annotation ID and traceability mismatches must equal 0.</t>
+  </si>
+  <si>
+    <t>NOT STARTED; full mapping must include DICOM/JPG paths, dimensions, protocol version/hash and source/output hashes.</t>
+  </si>
+  <si>
+    <t>NOT STARTED; create full JPG metadata, bbox validation, No Finding audit and conversion-error evidence.</t>
+  </si>
+  <si>
+    <t>NOT STARTED; create full-conversion validation JSON and Markdown report; do not claim PASS before evidence review.</t>
+  </si>
+  <si>
+    <t>NOT STARTED; full conversion closure requires complete evidence and GPT review PASS. Dataset training and MMDetection loading remain locked.</t>
   </si>
 </sst>
 </file>
@@ -2087,7 +2165,7 @@
         <color rgb="FF166534"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFDCFCE7"/>
         </patternFill>
       </fill>
@@ -2097,7 +2175,7 @@
         <color rgb="FF991B1B"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFEE2E2"/>
         </patternFill>
       </fill>
@@ -2117,7 +2195,7 @@
         <color rgb="FF4B5563"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFE5E7EB"/>
         </patternFill>
       </fill>
@@ -2127,7 +2205,7 @@
         <color rgb="FF991B1B"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFEE2E2"/>
         </patternFill>
       </fill>
@@ -2137,7 +2215,7 @@
         <color rgb="FF166534"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFDCFCE7"/>
         </patternFill>
       </fill>
@@ -2147,7 +2225,7 @@
         <color rgb="FF92400E"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFEF3C7"/>
         </patternFill>
       </fill>
@@ -2446,7 +2524,7 @@
       </c>
       <c r="B5" s="2">
         <f>COUNTIF(Checklist!$F:$F,"Đang làm")</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>7</v>
@@ -2464,7 +2542,7 @@
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Checklist!$F:$F,"Hoàn thành")</f>
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>10</v>
@@ -2500,7 +2578,7 @@
       </c>
       <c r="B8" s="5">
         <f>IFERROR(B6/B3,0)</f>
-        <v>0.27016885553470921</v>
+        <v>0.28517823639774859</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>16</v>
@@ -2673,11 +2751,11 @@
       </c>
       <c r="D15">
         <f>'Phase Summary'!D5</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <f>'Phase Summary'!E5</f>
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="F15">
         <f>'Phase Summary'!F5</f>
@@ -2689,7 +2767,7 @@
       </c>
       <c r="H15" s="6">
         <f>'Phase Summary'!H5</f>
-        <v>0.43137254901960786</v>
+        <v>0.48366013071895425</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -2976,6 +3054,13 @@
       </dataBar>
     </cfRule>
     <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF2563EB"/>
+      </dataBar>
+    </cfRule>
+    <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -7625,7 +7710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:13" ht="21.15" customHeight="1">
+    <row r="136" spans="1:13" ht="16.95" customHeight="1">
       <c r="A136" s="10">
         <v>135</v>
       </c>
@@ -7633,13 +7718,13 @@
         <v>29</v>
       </c>
       <c r="C136" s="10" t="s">
-        <v>571</v>
+        <v>201</v>
       </c>
       <c r="D136" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E136" s="10" t="s">
-        <v>572</v>
+        <v>202</v>
       </c>
       <c r="F136" s="10" t="s">
         <v>9</v>
@@ -7653,7 +7738,7 @@
       <c r="I136" s="10"/>
       <c r="J136" s="10"/>
       <c r="K136" s="10" t="s">
-        <v>637</v>
+        <v>203</v>
       </c>
       <c r="L136" s="10"/>
       <c r="M136" s="10">
@@ -7661,7 +7746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:13" ht="21.15" customHeight="1">
+    <row r="137" spans="1:13" ht="16.95" customHeight="1">
       <c r="A137" s="10">
         <v>136</v>
       </c>
@@ -7669,13 +7754,13 @@
         <v>29</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>571</v>
+        <v>201</v>
       </c>
       <c r="D137" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>573</v>
+        <v>204</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>9</v>
@@ -7689,7 +7774,7 @@
       <c r="I137" s="10"/>
       <c r="J137" s="10"/>
       <c r="K137" s="10" t="s">
-        <v>637</v>
+        <v>203</v>
       </c>
       <c r="L137" s="10"/>
       <c r="M137" s="10">
@@ -7697,7 +7782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:13" ht="21.15" customHeight="1">
+    <row r="138" spans="1:13" ht="16.95" customHeight="1">
       <c r="A138" s="10">
         <v>137</v>
       </c>
@@ -7705,13 +7790,13 @@
         <v>29</v>
       </c>
       <c r="C138" s="10" t="s">
-        <v>571</v>
+        <v>201</v>
       </c>
       <c r="D138" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E138" s="10" t="s">
-        <v>574</v>
+        <v>205</v>
       </c>
       <c r="F138" s="10" t="s">
         <v>9</v>
@@ -7725,7 +7810,7 @@
       <c r="I138" s="10"/>
       <c r="J138" s="10"/>
       <c r="K138" s="10" t="s">
-        <v>637</v>
+        <v>203</v>
       </c>
       <c r="L138" s="10"/>
       <c r="M138" s="10">
@@ -7733,7 +7818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:13" ht="21.15" customHeight="1">
+    <row r="139" spans="1:13" ht="16.95" customHeight="1">
       <c r="A139" s="10">
         <v>138</v>
       </c>
@@ -7741,13 +7826,13 @@
         <v>29</v>
       </c>
       <c r="C139" s="10" t="s">
-        <v>571</v>
+        <v>201</v>
       </c>
       <c r="D139" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>575</v>
+        <v>206</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>9</v>
@@ -7761,7 +7846,7 @@
       <c r="I139" s="10"/>
       <c r="J139" s="10"/>
       <c r="K139" s="10" t="s">
-        <v>637</v>
+        <v>203</v>
       </c>
       <c r="L139" s="10"/>
       <c r="M139" s="10">
@@ -7769,7 +7854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:13" ht="21.15" customHeight="1">
+    <row r="140" spans="1:13" ht="16.95" customHeight="1">
       <c r="A140" s="10">
         <v>139</v>
       </c>
@@ -7777,13 +7862,13 @@
         <v>29</v>
       </c>
       <c r="C140" s="10" t="s">
-        <v>571</v>
+        <v>201</v>
       </c>
       <c r="D140" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E140" s="10" t="s">
-        <v>576</v>
+        <v>207</v>
       </c>
       <c r="F140" s="10" t="s">
         <v>9</v>
@@ -7797,7 +7882,7 @@
       <c r="I140" s="10"/>
       <c r="J140" s="10"/>
       <c r="K140" s="10" t="s">
-        <v>637</v>
+        <v>203</v>
       </c>
       <c r="L140" s="10"/>
       <c r="M140" s="10">
@@ -7805,7 +7890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:13" ht="21.15" customHeight="1">
+    <row r="141" spans="1:13" ht="16.95" customHeight="1">
       <c r="A141" s="10">
         <v>140</v>
       </c>
@@ -7813,13 +7898,13 @@
         <v>29</v>
       </c>
       <c r="C141" s="10" t="s">
-        <v>571</v>
+        <v>201</v>
       </c>
       <c r="D141" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>577</v>
+        <v>208</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>9</v>
@@ -7833,7 +7918,7 @@
       <c r="I141" s="10"/>
       <c r="J141" s="10"/>
       <c r="K141" s="10" t="s">
-        <v>637</v>
+        <v>203</v>
       </c>
       <c r="L141" s="10"/>
       <c r="M141" s="10">
@@ -7841,7 +7926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:13" ht="21.15" customHeight="1">
+    <row r="142" spans="1:13" ht="16.95" customHeight="1">
       <c r="A142" s="10">
         <v>141</v>
       </c>
@@ -7849,13 +7934,13 @@
         <v>29</v>
       </c>
       <c r="C142" s="10" t="s">
-        <v>571</v>
+        <v>201</v>
       </c>
       <c r="D142" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E142" s="10" t="s">
-        <v>578</v>
+        <v>209</v>
       </c>
       <c r="F142" s="10" t="s">
         <v>9</v>
@@ -7869,7 +7954,7 @@
       <c r="I142" s="10"/>
       <c r="J142" s="10"/>
       <c r="K142" s="10" t="s">
-        <v>637</v>
+        <v>203</v>
       </c>
       <c r="L142" s="10"/>
       <c r="M142" s="10">
@@ -7877,7 +7962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:13" ht="21.15" customHeight="1">
+    <row r="143" spans="1:13" ht="16.95" customHeight="1">
       <c r="A143" s="10">
         <v>142</v>
       </c>
@@ -7885,13 +7970,13 @@
         <v>29</v>
       </c>
       <c r="C143" s="10" t="s">
-        <v>571</v>
+        <v>201</v>
       </c>
       <c r="D143" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>579</v>
+        <v>210</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>9</v>
@@ -7905,7 +7990,7 @@
       <c r="I143" s="10"/>
       <c r="J143" s="10"/>
       <c r="K143" s="10" t="s">
-        <v>637</v>
+        <v>203</v>
       </c>
       <c r="L143" s="10"/>
       <c r="M143" s="10">
@@ -7913,7 +7998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:13" ht="21.15" customHeight="1">
+    <row r="144" spans="1:13" ht="16.95" customHeight="1">
       <c r="A144" s="10">
         <v>143</v>
       </c>
@@ -7921,13 +8006,13 @@
         <v>29</v>
       </c>
       <c r="C144" s="10" t="s">
-        <v>571</v>
+        <v>201</v>
       </c>
       <c r="D144" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E144" s="10" t="s">
-        <v>580</v>
+        <v>211</v>
       </c>
       <c r="F144" s="10" t="s">
         <v>9</v>
@@ -7941,7 +8026,7 @@
       <c r="I144" s="10"/>
       <c r="J144" s="10"/>
       <c r="K144" s="10" t="s">
-        <v>637</v>
+        <v>203</v>
       </c>
       <c r="L144" s="10"/>
       <c r="M144" s="10">
@@ -7949,7 +8034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:13" ht="21.15" customHeight="1">
+    <row r="145" spans="1:13" ht="16.95" customHeight="1">
       <c r="A145" s="10">
         <v>144</v>
       </c>
@@ -7957,13 +8042,13 @@
         <v>29</v>
       </c>
       <c r="C145" s="10" t="s">
-        <v>571</v>
+        <v>201</v>
       </c>
       <c r="D145" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>581</v>
+        <v>212</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>9</v>
@@ -7977,7 +8062,7 @@
       <c r="I145" s="10"/>
       <c r="J145" s="10"/>
       <c r="K145" s="10" t="s">
-        <v>637</v>
+        <v>203</v>
       </c>
       <c r="L145" s="10"/>
       <c r="M145" s="10">
@@ -7985,7 +8070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:13" ht="21.15" customHeight="1">
+    <row r="146" spans="1:13" ht="16.95" customHeight="1">
       <c r="A146" s="10">
         <v>145</v>
       </c>
@@ -7993,13 +8078,13 @@
         <v>29</v>
       </c>
       <c r="C146" s="10" t="s">
-        <v>571</v>
+        <v>201</v>
       </c>
       <c r="D146" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E146" s="10" t="s">
-        <v>582</v>
+        <v>213</v>
       </c>
       <c r="F146" s="10" t="s">
         <v>9</v>
@@ -8013,7 +8098,7 @@
       <c r="I146" s="10"/>
       <c r="J146" s="10"/>
       <c r="K146" s="10" t="s">
-        <v>637</v>
+        <v>203</v>
       </c>
       <c r="L146" s="10"/>
       <c r="M146" s="10">
@@ -8021,7 +8106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:13" ht="21.15" customHeight="1">
+    <row r="147" spans="1:13" ht="16.95" customHeight="1">
       <c r="A147" s="10">
         <v>146</v>
       </c>
@@ -8029,13 +8114,13 @@
         <v>29</v>
       </c>
       <c r="C147" s="10" t="s">
-        <v>571</v>
+        <v>201</v>
       </c>
       <c r="D147" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>583</v>
+        <v>214</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>9</v>
@@ -8049,17 +8134,17 @@
       <c r="I147" s="10"/>
       <c r="J147" s="10"/>
       <c r="K147" s="10" t="s">
-        <v>637</v>
+        <v>203</v>
       </c>
       <c r="L147" s="10" t="s">
-        <v>584</v>
+        <v>215</v>
       </c>
       <c r="M147" s="10">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:13" ht="42.15" customHeight="1">
+    <row r="148" spans="1:13" ht="33.75" customHeight="1">
       <c r="A148" s="10">
         <v>147</v>
       </c>
@@ -8067,13 +8152,13 @@
         <v>29</v>
       </c>
       <c r="C148" s="10" t="s">
-        <v>571</v>
+        <v>201</v>
       </c>
       <c r="D148" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E148" s="10" t="s">
-        <v>585</v>
+        <v>216</v>
       </c>
       <c r="F148" s="10" t="s">
         <v>9</v>
@@ -8087,17 +8172,17 @@
       <c r="I148" s="10"/>
       <c r="J148" s="10"/>
       <c r="K148" s="10" t="s">
-        <v>637</v>
+        <v>203</v>
       </c>
       <c r="L148" s="10" t="s">
-        <v>586</v>
+        <v>217</v>
       </c>
       <c r="M148" s="10">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:13" ht="21.15" customHeight="1">
+    <row r="149" spans="1:13" ht="16.95" customHeight="1">
       <c r="A149" s="10">
         <v>148</v>
       </c>
@@ -8105,13 +8190,13 @@
         <v>29</v>
       </c>
       <c r="C149" s="10" t="s">
-        <v>571</v>
+        <v>201</v>
       </c>
       <c r="D149" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>587</v>
+        <v>218</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>9</v>
@@ -8125,17 +8210,17 @@
       <c r="I149" s="10"/>
       <c r="J149" s="10"/>
       <c r="K149" s="10" t="s">
-        <v>637</v>
+        <v>203</v>
       </c>
       <c r="L149" s="10" t="s">
-        <v>638</v>
+        <v>219</v>
       </c>
       <c r="M149" s="10">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:13" ht="21.15" customHeight="1">
+    <row r="150" spans="1:13" ht="52.8" customHeight="1">
       <c r="A150" s="10">
         <v>149</v>
       </c>
@@ -8143,16 +8228,16 @@
         <v>29</v>
       </c>
       <c r="C150" s="10" t="s">
-        <v>588</v>
+        <v>220</v>
       </c>
       <c r="D150" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E150" s="10" t="s">
-        <v>589</v>
+        <v>221</v>
       </c>
       <c r="F150" s="10" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G150" s="10" t="s">
         <v>52</v>
@@ -8163,17 +8248,17 @@
       <c r="I150" s="10"/>
       <c r="J150" s="10"/>
       <c r="K150" s="10" t="s">
-        <v>590</v>
+        <v>635</v>
       </c>
       <c r="L150" s="10" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="M150" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:13" ht="21.15" customHeight="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" ht="95.1" customHeight="1">
       <c r="A151" s="10">
         <v>150</v>
       </c>
@@ -8181,16 +8266,16 @@
         <v>29</v>
       </c>
       <c r="C151" s="10" t="s">
-        <v>588</v>
+        <v>220</v>
       </c>
       <c r="D151" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>591</v>
+        <v>222</v>
       </c>
       <c r="F151" s="10" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G151" s="10" t="s">
         <v>52</v>
@@ -8201,17 +8286,17 @@
       <c r="I151" s="10"/>
       <c r="J151" s="10"/>
       <c r="K151" s="10" t="s">
-        <v>590</v>
+        <v>637</v>
       </c>
       <c r="L151" s="10" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="M151" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:13" ht="21.15" customHeight="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" ht="63.3" customHeight="1">
       <c r="A152" s="10">
         <v>151</v>
       </c>
@@ -8219,16 +8304,16 @@
         <v>29</v>
       </c>
       <c r="C152" s="10" t="s">
-        <v>588</v>
+        <v>220</v>
       </c>
       <c r="D152" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E152" s="10" t="s">
-        <v>592</v>
+        <v>223</v>
       </c>
       <c r="F152" s="10" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G152" s="10" t="s">
         <v>52</v>
@@ -8239,17 +8324,17 @@
       <c r="I152" s="10"/>
       <c r="J152" s="10"/>
       <c r="K152" s="10" t="s">
-        <v>590</v>
+        <v>639</v>
       </c>
       <c r="L152" s="10" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="M152" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:13" ht="21.15" customHeight="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" ht="63.3" customHeight="1">
       <c r="A153" s="10">
         <v>152</v>
       </c>
@@ -8257,16 +8342,16 @@
         <v>29</v>
       </c>
       <c r="C153" s="10" t="s">
-        <v>588</v>
+        <v>220</v>
       </c>
       <c r="D153" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>593</v>
+        <v>224</v>
       </c>
       <c r="F153" s="10" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G153" s="10" t="s">
         <v>52</v>
@@ -8277,17 +8362,17 @@
       <c r="I153" s="10"/>
       <c r="J153" s="10"/>
       <c r="K153" s="10" t="s">
-        <v>590</v>
+        <v>641</v>
       </c>
       <c r="L153" s="10" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="M153" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:13" ht="21.15" customHeight="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" ht="158.4" customHeight="1">
       <c r="A154" s="10">
         <v>153</v>
       </c>
@@ -8295,16 +8380,16 @@
         <v>29</v>
       </c>
       <c r="C154" s="10" t="s">
-        <v>588</v>
+        <v>220</v>
       </c>
       <c r="D154" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E154" s="10" t="s">
-        <v>594</v>
+        <v>643</v>
       </c>
       <c r="F154" s="10" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G154" s="10" t="s">
         <v>52</v>
@@ -8315,17 +8400,17 @@
       <c r="I154" s="10"/>
       <c r="J154" s="10"/>
       <c r="K154" s="10" t="s">
-        <v>590</v>
+        <v>644</v>
       </c>
       <c r="L154" s="10" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="M154" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:13" ht="21.15" customHeight="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" ht="95.1" customHeight="1">
       <c r="A155" s="10">
         <v>154</v>
       </c>
@@ -8333,16 +8418,16 @@
         <v>29</v>
       </c>
       <c r="C155" s="10" t="s">
-        <v>588</v>
+        <v>220</v>
       </c>
       <c r="D155" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>595</v>
+        <v>646</v>
       </c>
       <c r="F155" s="10" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G155" s="10" t="s">
         <v>52</v>
@@ -8353,17 +8438,17 @@
       <c r="I155" s="10"/>
       <c r="J155" s="10"/>
       <c r="K155" s="10" t="s">
-        <v>590</v>
+        <v>647</v>
       </c>
       <c r="L155" s="10" t="s">
-        <v>639</v>
+        <v>648</v>
       </c>
       <c r="M155" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:13" ht="21.15" customHeight="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" ht="95.1" customHeight="1">
       <c r="A156" s="10">
         <v>155</v>
       </c>
@@ -8371,16 +8456,16 @@
         <v>29</v>
       </c>
       <c r="C156" s="10" t="s">
-        <v>588</v>
+        <v>220</v>
       </c>
       <c r="D156" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E156" s="10" t="s">
-        <v>596</v>
+        <v>225</v>
       </c>
       <c r="F156" s="10" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G156" s="10" t="s">
         <v>52</v>
@@ -8391,17 +8476,17 @@
       <c r="I156" s="10"/>
       <c r="J156" s="10"/>
       <c r="K156" s="10" t="s">
-        <v>590</v>
+        <v>649</v>
       </c>
       <c r="L156" s="10" t="s">
-        <v>639</v>
+        <v>650</v>
       </c>
       <c r="M156" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="1:13" ht="42.15" customHeight="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" ht="190.05" customHeight="1">
       <c r="A157" s="10">
         <v>156</v>
       </c>
@@ -8409,16 +8494,16 @@
         <v>29</v>
       </c>
       <c r="C157" s="10" t="s">
-        <v>588</v>
+        <v>220</v>
       </c>
       <c r="D157" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>597</v>
+        <v>226</v>
       </c>
       <c r="F157" s="10" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G157" s="10" t="s">
         <v>64</v>
@@ -8429,17 +8514,17 @@
       <c r="I157" s="10"/>
       <c r="J157" s="10"/>
       <c r="K157" s="10" t="s">
-        <v>590</v>
+        <v>651</v>
       </c>
       <c r="L157" s="10" t="s">
-        <v>639</v>
+        <v>652</v>
       </c>
       <c r="M157" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="1:13" ht="21.15" customHeight="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" ht="52.8" customHeight="1">
       <c r="A158" s="10">
         <v>157</v>
       </c>
@@ -8447,13 +8532,13 @@
         <v>29</v>
       </c>
       <c r="C158" s="10" t="s">
-        <v>598</v>
+        <v>227</v>
       </c>
       <c r="D158" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E158" s="10" t="s">
-        <v>599</v>
+        <v>228</v>
       </c>
       <c r="F158" s="10" t="s">
         <v>3</v>
@@ -8467,15 +8552,17 @@
       <c r="I158" s="10"/>
       <c r="J158" s="10"/>
       <c r="K158" s="10" t="s">
-        <v>600</v>
-      </c>
-      <c r="L158" s="10"/>
+        <v>653</v>
+      </c>
+      <c r="L158" s="10" t="s">
+        <v>654</v>
+      </c>
       <c r="M158" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:13" ht="21.15" customHeight="1">
+    <row r="159" spans="1:13" ht="42.15" customHeight="1">
       <c r="A159" s="10">
         <v>158</v>
       </c>
@@ -8483,13 +8570,13 @@
         <v>29</v>
       </c>
       <c r="C159" s="10" t="s">
-        <v>598</v>
+        <v>227</v>
       </c>
       <c r="D159" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>601</v>
+        <v>229</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>3</v>
@@ -8503,7 +8590,7 @@
       <c r="I159" s="10"/>
       <c r="J159" s="10"/>
       <c r="K159" s="10" t="s">
-        <v>600</v>
+        <v>655</v>
       </c>
       <c r="L159" s="10"/>
       <c r="M159" s="10">
@@ -8511,7 +8598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:13" ht="21.15" customHeight="1">
+    <row r="160" spans="1:13" ht="52.8" customHeight="1">
       <c r="A160" s="10">
         <v>159</v>
       </c>
@@ -8519,13 +8606,13 @@
         <v>29</v>
       </c>
       <c r="C160" s="10" t="s">
-        <v>598</v>
+        <v>227</v>
       </c>
       <c r="D160" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E160" s="10" t="s">
-        <v>602</v>
+        <v>230</v>
       </c>
       <c r="F160" s="10" t="s">
         <v>3</v>
@@ -8539,7 +8626,7 @@
       <c r="I160" s="10"/>
       <c r="J160" s="10"/>
       <c r="K160" s="10" t="s">
-        <v>600</v>
+        <v>656</v>
       </c>
       <c r="L160" s="10"/>
       <c r="M160" s="10">
@@ -8547,7 +8634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:13" ht="21.15" customHeight="1">
+    <row r="161" spans="1:13" ht="52.8" customHeight="1">
       <c r="A161" s="10">
         <v>160</v>
       </c>
@@ -8555,13 +8642,13 @@
         <v>29</v>
       </c>
       <c r="C161" s="10" t="s">
-        <v>598</v>
+        <v>227</v>
       </c>
       <c r="D161" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>603</v>
+        <v>231</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>3</v>
@@ -8575,7 +8662,7 @@
       <c r="I161" s="10"/>
       <c r="J161" s="10"/>
       <c r="K161" s="10" t="s">
-        <v>600</v>
+        <v>657</v>
       </c>
       <c r="L161" s="10"/>
       <c r="M161" s="10">
@@ -8583,7 +8670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:13" ht="21.15" customHeight="1">
+    <row r="162" spans="1:13" ht="52.8" customHeight="1">
       <c r="A162" s="10">
         <v>161</v>
       </c>
@@ -8591,13 +8678,13 @@
         <v>29</v>
       </c>
       <c r="C162" s="10" t="s">
-        <v>598</v>
+        <v>227</v>
       </c>
       <c r="D162" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E162" s="10" t="s">
-        <v>604</v>
+        <v>232</v>
       </c>
       <c r="F162" s="10" t="s">
         <v>3</v>
@@ -8611,17 +8698,17 @@
       <c r="I162" s="10"/>
       <c r="J162" s="10"/>
       <c r="K162" s="10" t="s">
-        <v>600</v>
+        <v>658</v>
       </c>
       <c r="L162" s="10" t="s">
-        <v>605</v>
+        <v>233</v>
       </c>
       <c r="M162" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:13" ht="21.15" customHeight="1">
+    <row r="163" spans="1:13" ht="42.15" customHeight="1">
       <c r="A163" s="10">
         <v>162</v>
       </c>
@@ -8629,13 +8716,13 @@
         <v>29</v>
       </c>
       <c r="C163" s="10" t="s">
-        <v>598</v>
+        <v>227</v>
       </c>
       <c r="D163" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>606</v>
+        <v>234</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>3</v>
@@ -8649,7 +8736,7 @@
       <c r="I163" s="10"/>
       <c r="J163" s="10"/>
       <c r="K163" s="10" t="s">
-        <v>600</v>
+        <v>659</v>
       </c>
       <c r="L163" s="10"/>
       <c r="M163" s="10">
@@ -8657,7 +8744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:13" ht="21.15" customHeight="1">
+    <row r="164" spans="1:13" ht="42.15" customHeight="1">
       <c r="A164" s="10">
         <v>163</v>
       </c>
@@ -8665,13 +8752,13 @@
         <v>29</v>
       </c>
       <c r="C164" s="10" t="s">
-        <v>598</v>
+        <v>227</v>
       </c>
       <c r="D164" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E164" s="10" t="s">
-        <v>607</v>
+        <v>235</v>
       </c>
       <c r="F164" s="10" t="s">
         <v>3</v>
@@ -8685,7 +8772,7 @@
       <c r="I164" s="10"/>
       <c r="J164" s="10"/>
       <c r="K164" s="10" t="s">
-        <v>600</v>
+        <v>660</v>
       </c>
       <c r="L164" s="10"/>
       <c r="M164" s="10">
@@ -8693,7 +8780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:13" ht="21.15" customHeight="1">
+    <row r="165" spans="1:13" ht="42.15" customHeight="1">
       <c r="A165" s="10">
         <v>164</v>
       </c>
@@ -8701,13 +8788,13 @@
         <v>29</v>
       </c>
       <c r="C165" s="10" t="s">
-        <v>598</v>
+        <v>227</v>
       </c>
       <c r="D165" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>608</v>
+        <v>236</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>3</v>
@@ -8721,7 +8808,7 @@
       <c r="I165" s="10"/>
       <c r="J165" s="10"/>
       <c r="K165" s="10" t="s">
-        <v>600</v>
+        <v>661</v>
       </c>
       <c r="L165" s="10"/>
       <c r="M165" s="10">
@@ -8729,7 +8816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:13" ht="21.15" customHeight="1">
+    <row r="166" spans="1:13" ht="52.8" customHeight="1">
       <c r="A166" s="10">
         <v>165</v>
       </c>
@@ -8737,13 +8824,13 @@
         <v>29</v>
       </c>
       <c r="C166" s="10" t="s">
-        <v>598</v>
+        <v>227</v>
       </c>
       <c r="D166" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E166" s="10" t="s">
-        <v>609</v>
+        <v>237</v>
       </c>
       <c r="F166" s="10" t="s">
         <v>3</v>
@@ -8757,10 +8844,10 @@
       <c r="I166" s="10"/>
       <c r="J166" s="10"/>
       <c r="K166" s="10" t="s">
-        <v>600</v>
+        <v>662</v>
       </c>
       <c r="L166" s="10" t="s">
-        <v>610</v>
+        <v>238</v>
       </c>
       <c r="M166" s="10">
         <f t="shared" si="2"/>
@@ -8775,13 +8862,13 @@
         <v>29</v>
       </c>
       <c r="C167" s="10" t="s">
-        <v>598</v>
+        <v>227</v>
       </c>
       <c r="D167" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>611</v>
+        <v>239</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>3</v>
@@ -8795,17 +8882,17 @@
       <c r="I167" s="10"/>
       <c r="J167" s="10"/>
       <c r="K167" s="10" t="s">
-        <v>600</v>
+        <v>663</v>
       </c>
       <c r="L167" s="10" t="s">
-        <v>612</v>
+        <v>240</v>
       </c>
       <c r="M167" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:13" ht="42.15" customHeight="1">
+    <row r="168" spans="1:13" ht="52.8" customHeight="1">
       <c r="A168" s="10">
         <v>167</v>
       </c>
@@ -8813,13 +8900,13 @@
         <v>29</v>
       </c>
       <c r="C168" s="10" t="s">
-        <v>598</v>
+        <v>227</v>
       </c>
       <c r="D168" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E168" s="10" t="s">
-        <v>613</v>
+        <v>241</v>
       </c>
       <c r="F168" s="10" t="s">
         <v>3</v>
@@ -8833,17 +8920,17 @@
       <c r="I168" s="10"/>
       <c r="J168" s="10"/>
       <c r="K168" s="10" t="s">
-        <v>600</v>
+        <v>664</v>
       </c>
       <c r="L168" s="10" t="s">
-        <v>614</v>
+        <v>242</v>
       </c>
       <c r="M168" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:13" ht="21.15" customHeight="1">
+    <row r="169" spans="1:13" ht="63.3" customHeight="1">
       <c r="A169" s="10">
         <v>168</v>
       </c>
@@ -8851,13 +8938,13 @@
         <v>29</v>
       </c>
       <c r="C169" s="10" t="s">
-        <v>598</v>
+        <v>227</v>
       </c>
       <c r="D169" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>615</v>
+        <v>243</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>3</v>
@@ -8871,7 +8958,7 @@
       <c r="I169" s="10"/>
       <c r="J169" s="10"/>
       <c r="K169" s="10" t="s">
-        <v>600</v>
+        <v>665</v>
       </c>
       <c r="L169" s="10"/>
       <c r="M169" s="10">
@@ -8879,7 +8966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:13" ht="42.15" customHeight="1">
+    <row r="170" spans="1:13" ht="33.75" customHeight="1">
       <c r="A170" s="10">
         <v>169</v>
       </c>
@@ -8887,13 +8974,13 @@
         <v>29</v>
       </c>
       <c r="C170" s="10" t="s">
-        <v>616</v>
+        <v>244</v>
       </c>
       <c r="D170" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E170" s="10" t="s">
-        <v>617</v>
+        <v>245</v>
       </c>
       <c r="F170" s="10" t="s">
         <v>3</v>
@@ -8907,17 +8994,17 @@
       <c r="I170" s="10"/>
       <c r="J170" s="10"/>
       <c r="K170" s="10" t="s">
-        <v>618</v>
+        <v>246</v>
       </c>
       <c r="L170" s="10" t="s">
-        <v>619</v>
+        <v>247</v>
       </c>
       <c r="M170" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:13" ht="21.15" customHeight="1">
+    <row r="171" spans="1:13" ht="16.95" customHeight="1">
       <c r="A171" s="10">
         <v>170</v>
       </c>
@@ -8925,13 +9012,13 @@
         <v>29</v>
       </c>
       <c r="C171" s="10" t="s">
-        <v>616</v>
+        <v>244</v>
       </c>
       <c r="D171" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>620</v>
+        <v>248</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>3</v>
@@ -8945,7 +9032,7 @@
       <c r="I171" s="10"/>
       <c r="J171" s="10"/>
       <c r="K171" s="10" t="s">
-        <v>618</v>
+        <v>246</v>
       </c>
       <c r="L171" s="10"/>
       <c r="M171" s="10">
@@ -8953,7 +9040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:13" ht="21.15" customHeight="1">
+    <row r="172" spans="1:13" ht="16.95" customHeight="1">
       <c r="A172" s="10">
         <v>171</v>
       </c>
@@ -8961,13 +9048,13 @@
         <v>29</v>
       </c>
       <c r="C172" s="10" t="s">
-        <v>616</v>
+        <v>244</v>
       </c>
       <c r="D172" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E172" s="10" t="s">
-        <v>621</v>
+        <v>249</v>
       </c>
       <c r="F172" s="10" t="s">
         <v>3</v>
@@ -8981,7 +9068,7 @@
       <c r="I172" s="10"/>
       <c r="J172" s="10"/>
       <c r="K172" s="10" t="s">
-        <v>618</v>
+        <v>246</v>
       </c>
       <c r="L172" s="10"/>
       <c r="M172" s="10">
@@ -8989,7 +9076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:13" ht="21.15" customHeight="1">
+    <row r="173" spans="1:13" ht="16.95" customHeight="1">
       <c r="A173" s="10">
         <v>172</v>
       </c>
@@ -8997,13 +9084,13 @@
         <v>29</v>
       </c>
       <c r="C173" s="10" t="s">
-        <v>616</v>
+        <v>244</v>
       </c>
       <c r="D173" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>622</v>
+        <v>250</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>3</v>
@@ -9017,7 +9104,7 @@
       <c r="I173" s="10"/>
       <c r="J173" s="10"/>
       <c r="K173" s="10" t="s">
-        <v>618</v>
+        <v>246</v>
       </c>
       <c r="L173" s="10"/>
       <c r="M173" s="10">
@@ -9025,7 +9112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:13" ht="21.15" customHeight="1">
+    <row r="174" spans="1:13" ht="16.95" customHeight="1">
       <c r="A174" s="10">
         <v>173</v>
       </c>
@@ -9033,13 +9120,13 @@
         <v>29</v>
       </c>
       <c r="C174" s="10" t="s">
-        <v>616</v>
+        <v>244</v>
       </c>
       <c r="D174" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E174" s="10" t="s">
-        <v>623</v>
+        <v>251</v>
       </c>
       <c r="F174" s="10" t="s">
         <v>3</v>
@@ -9053,7 +9140,7 @@
       <c r="I174" s="10"/>
       <c r="J174" s="10"/>
       <c r="K174" s="10" t="s">
-        <v>618</v>
+        <v>246</v>
       </c>
       <c r="L174" s="10"/>
       <c r="M174" s="10">
@@ -9061,7 +9148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:13" ht="21.15" customHeight="1">
+    <row r="175" spans="1:13" ht="16.95" customHeight="1">
       <c r="A175" s="10">
         <v>174</v>
       </c>
@@ -9069,13 +9156,13 @@
         <v>29</v>
       </c>
       <c r="C175" s="10" t="s">
-        <v>616</v>
+        <v>244</v>
       </c>
       <c r="D175" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>624</v>
+        <v>252</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>3</v>
@@ -9089,7 +9176,7 @@
       <c r="I175" s="10"/>
       <c r="J175" s="10"/>
       <c r="K175" s="10" t="s">
-        <v>618</v>
+        <v>246</v>
       </c>
       <c r="L175" s="10"/>
       <c r="M175" s="10">
@@ -9097,7 +9184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:13" ht="21.15" customHeight="1">
+    <row r="176" spans="1:13" ht="16.95" customHeight="1">
       <c r="A176" s="10">
         <v>175</v>
       </c>
@@ -9105,13 +9192,13 @@
         <v>29</v>
       </c>
       <c r="C176" s="10" t="s">
-        <v>616</v>
+        <v>244</v>
       </c>
       <c r="D176" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E176" s="10" t="s">
-        <v>625</v>
+        <v>253</v>
       </c>
       <c r="F176" s="10" t="s">
         <v>3</v>
@@ -9125,7 +9212,7 @@
       <c r="I176" s="10"/>
       <c r="J176" s="10"/>
       <c r="K176" s="10" t="s">
-        <v>618</v>
+        <v>246</v>
       </c>
       <c r="L176" s="10"/>
       <c r="M176" s="10">
@@ -9133,7 +9220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:13" ht="21.15" customHeight="1">
+    <row r="177" spans="1:13" ht="16.95" customHeight="1">
       <c r="A177" s="10">
         <v>176</v>
       </c>
@@ -9141,13 +9228,13 @@
         <v>29</v>
       </c>
       <c r="C177" s="10" t="s">
-        <v>616</v>
+        <v>244</v>
       </c>
       <c r="D177" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>626</v>
+        <v>254</v>
       </c>
       <c r="F177" s="10" t="s">
         <v>3</v>
@@ -9161,7 +9248,7 @@
       <c r="I177" s="10"/>
       <c r="J177" s="10"/>
       <c r="K177" s="10" t="s">
-        <v>618</v>
+        <v>246</v>
       </c>
       <c r="L177" s="10"/>
       <c r="M177" s="10">
@@ -9169,7 +9256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:13" ht="42.15" customHeight="1">
+    <row r="178" spans="1:13" ht="33.75" customHeight="1">
       <c r="A178" s="10">
         <v>177</v>
       </c>
@@ -9177,13 +9264,13 @@
         <v>29</v>
       </c>
       <c r="C178" s="10" t="s">
-        <v>616</v>
+        <v>244</v>
       </c>
       <c r="D178" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E178" s="10" t="s">
-        <v>627</v>
+        <v>255</v>
       </c>
       <c r="F178" s="10" t="s">
         <v>3</v>
@@ -9197,17 +9284,17 @@
       <c r="I178" s="10"/>
       <c r="J178" s="10"/>
       <c r="K178" s="10" t="s">
-        <v>618</v>
+        <v>246</v>
       </c>
       <c r="L178" s="10" t="s">
-        <v>628</v>
+        <v>256</v>
       </c>
       <c r="M178" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:13" ht="105.6" customHeight="1">
+    <row r="179" spans="1:13" ht="84.45" customHeight="1">
       <c r="A179" s="10">
         <v>178</v>
       </c>
@@ -9215,13 +9302,13 @@
         <v>29</v>
       </c>
       <c r="C179" s="10" t="s">
-        <v>616</v>
+        <v>244</v>
       </c>
       <c r="D179" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>629</v>
+        <v>257</v>
       </c>
       <c r="F179" s="10" t="s">
         <v>3</v>
@@ -9235,17 +9322,17 @@
       <c r="I179" s="10"/>
       <c r="J179" s="10"/>
       <c r="K179" s="10" t="s">
-        <v>618</v>
+        <v>246</v>
       </c>
       <c r="L179" s="10" t="s">
-        <v>630</v>
+        <v>258</v>
       </c>
       <c r="M179" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:13" ht="21.15" customHeight="1">
+    <row r="180" spans="1:13" ht="16.95" customHeight="1">
       <c r="A180" s="10">
         <v>179</v>
       </c>
@@ -9253,13 +9340,13 @@
         <v>29</v>
       </c>
       <c r="C180" s="10" t="s">
-        <v>631</v>
+        <v>259</v>
       </c>
       <c r="D180" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E180" s="10" t="s">
-        <v>632</v>
+        <v>260</v>
       </c>
       <c r="F180" s="10" t="s">
         <v>3</v>
@@ -9273,7 +9360,7 @@
       <c r="I180" s="10"/>
       <c r="J180" s="10"/>
       <c r="K180" s="10" t="s">
-        <v>633</v>
+        <v>261</v>
       </c>
       <c r="L180" s="10"/>
       <c r="M180" s="10">
@@ -9281,7 +9368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:13" ht="21.15" customHeight="1">
+    <row r="181" spans="1:13" ht="16.95" customHeight="1">
       <c r="A181" s="10">
         <v>180</v>
       </c>
@@ -9289,13 +9376,13 @@
         <v>29</v>
       </c>
       <c r="C181" s="10" t="s">
-        <v>631</v>
+        <v>259</v>
       </c>
       <c r="D181" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>634</v>
+        <v>262</v>
       </c>
       <c r="F181" s="10" t="s">
         <v>3</v>
@@ -9309,7 +9396,7 @@
       <c r="I181" s="10"/>
       <c r="J181" s="10"/>
       <c r="K181" s="10" t="s">
-        <v>633</v>
+        <v>261</v>
       </c>
       <c r="L181" s="10"/>
       <c r="M181" s="10">
@@ -9317,7 +9404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:13" ht="21.15" customHeight="1">
+    <row r="182" spans="1:13" ht="16.95" customHeight="1">
       <c r="A182" s="10">
         <v>181</v>
       </c>
@@ -9325,13 +9412,13 @@
         <v>29</v>
       </c>
       <c r="C182" s="10" t="s">
-        <v>631</v>
+        <v>259</v>
       </c>
       <c r="D182" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E182" s="10" t="s">
-        <v>635</v>
+        <v>263</v>
       </c>
       <c r="F182" s="10" t="s">
         <v>3</v>
@@ -9345,7 +9432,7 @@
       <c r="I182" s="10"/>
       <c r="J182" s="10"/>
       <c r="K182" s="10" t="s">
-        <v>633</v>
+        <v>261</v>
       </c>
       <c r="L182" s="10"/>
       <c r="M182" s="10">
@@ -9353,7 +9440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:13" ht="21.15" customHeight="1">
+    <row r="183" spans="1:13" ht="16.95" customHeight="1">
       <c r="A183" s="10">
         <v>182</v>
       </c>
@@ -9361,13 +9448,13 @@
         <v>29</v>
       </c>
       <c r="C183" s="10" t="s">
-        <v>631</v>
+        <v>259</v>
       </c>
       <c r="D183" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>636</v>
+        <v>264</v>
       </c>
       <c r="F183" s="10" t="s">
         <v>3</v>
@@ -9381,7 +9468,7 @@
       <c r="I183" s="10"/>
       <c r="J183" s="10"/>
       <c r="K183" s="10" t="s">
-        <v>633</v>
+        <v>261</v>
       </c>
       <c r="L183" s="10"/>
       <c r="M183" s="10">
@@ -9397,13 +9484,13 @@
         <v>29</v>
       </c>
       <c r="C184" s="10" t="s">
-        <v>201</v>
+        <v>265</v>
       </c>
       <c r="D184" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E184" s="10" t="s">
-        <v>202</v>
+        <v>266</v>
       </c>
       <c r="F184" s="10" t="s">
         <v>3</v>
@@ -9431,13 +9518,13 @@
         <v>29</v>
       </c>
       <c r="C185" s="10" t="s">
-        <v>201</v>
+        <v>265</v>
       </c>
       <c r="D185" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>203</v>
+        <v>267</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>3</v>
@@ -9465,13 +9552,13 @@
         <v>29</v>
       </c>
       <c r="C186" s="10" t="s">
-        <v>201</v>
+        <v>265</v>
       </c>
       <c r="D186" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E186" s="10" t="s">
-        <v>204</v>
+        <v>268</v>
       </c>
       <c r="F186" s="10" t="s">
         <v>3</v>
@@ -9499,13 +9586,13 @@
         <v>29</v>
       </c>
       <c r="C187" s="10" t="s">
-        <v>201</v>
+        <v>265</v>
       </c>
       <c r="D187" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>205</v>
+        <v>269</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>3</v>
@@ -9533,13 +9620,13 @@
         <v>29</v>
       </c>
       <c r="C188" s="10" t="s">
-        <v>201</v>
+        <v>265</v>
       </c>
       <c r="D188" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E188" s="10" t="s">
-        <v>206</v>
+        <v>270</v>
       </c>
       <c r="F188" s="10" t="s">
         <v>3</v>
@@ -9567,13 +9654,13 @@
         <v>29</v>
       </c>
       <c r="C189" s="10" t="s">
-        <v>201</v>
+        <v>265</v>
       </c>
       <c r="D189" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>207</v>
+        <v>271</v>
       </c>
       <c r="F189" s="10" t="s">
         <v>3</v>
@@ -9601,13 +9688,13 @@
         <v>29</v>
       </c>
       <c r="C190" s="10" t="s">
-        <v>201</v>
+        <v>265</v>
       </c>
       <c r="D190" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E190" s="10" t="s">
-        <v>208</v>
+        <v>272</v>
       </c>
       <c r="F190" s="10" t="s">
         <v>3</v>
@@ -9635,13 +9722,13 @@
         <v>29</v>
       </c>
       <c r="C191" s="10" t="s">
-        <v>201</v>
+        <v>265</v>
       </c>
       <c r="D191" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>209</v>
+        <v>273</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>3</v>
@@ -9669,13 +9756,13 @@
         <v>29</v>
       </c>
       <c r="C192" s="10" t="s">
-        <v>201</v>
+        <v>265</v>
       </c>
       <c r="D192" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E192" s="10" t="s">
-        <v>210</v>
+        <v>274</v>
       </c>
       <c r="F192" s="10" t="s">
         <v>3</v>
@@ -9703,13 +9790,13 @@
         <v>29</v>
       </c>
       <c r="C193" s="10" t="s">
-        <v>201</v>
+        <v>265</v>
       </c>
       <c r="D193" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>211</v>
+        <v>275</v>
       </c>
       <c r="F193" s="10" t="s">
         <v>3</v>
@@ -9737,13 +9824,13 @@
         <v>29</v>
       </c>
       <c r="C194" s="10" t="s">
-        <v>201</v>
+        <v>265</v>
       </c>
       <c r="D194" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E194" s="10" t="s">
-        <v>212</v>
+        <v>276</v>
       </c>
       <c r="F194" s="10" t="s">
         <v>3</v>
@@ -9771,13 +9858,13 @@
         <v>29</v>
       </c>
       <c r="C195" s="10" t="s">
-        <v>201</v>
+        <v>265</v>
       </c>
       <c r="D195" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>213</v>
+        <v>277</v>
       </c>
       <c r="F195" s="10" t="s">
         <v>3</v>
@@ -9805,13 +9892,13 @@
         <v>29</v>
       </c>
       <c r="C196" s="10" t="s">
-        <v>201</v>
+        <v>265</v>
       </c>
       <c r="D196" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E196" s="10" t="s">
-        <v>214</v>
+        <v>278</v>
       </c>
       <c r="F196" s="10" t="s">
         <v>3</v>
@@ -9839,13 +9926,13 @@
         <v>29</v>
       </c>
       <c r="C197" s="10" t="s">
-        <v>201</v>
+        <v>265</v>
       </c>
       <c r="D197" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>215</v>
+        <v>279</v>
       </c>
       <c r="F197" s="10" t="s">
         <v>3</v>
@@ -9873,13 +9960,13 @@
         <v>29</v>
       </c>
       <c r="C198" s="10" t="s">
-        <v>201</v>
+        <v>265</v>
       </c>
       <c r="D198" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E198" s="10" t="s">
-        <v>216</v>
+        <v>280</v>
       </c>
       <c r="F198" s="10" t="s">
         <v>3</v>
@@ -9907,13 +9994,13 @@
         <v>29</v>
       </c>
       <c r="C199" s="10" t="s">
-        <v>201</v>
+        <v>265</v>
       </c>
       <c r="D199" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>217</v>
+        <v>281</v>
       </c>
       <c r="F199" s="10" t="s">
         <v>3</v>
@@ -9941,13 +10028,13 @@
         <v>29</v>
       </c>
       <c r="C200" s="10" t="s">
-        <v>201</v>
+        <v>265</v>
       </c>
       <c r="D200" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E200" s="10" t="s">
-        <v>218</v>
+        <v>282</v>
       </c>
       <c r="F200" s="10" t="s">
         <v>3</v>
@@ -9975,13 +10062,13 @@
         <v>29</v>
       </c>
       <c r="C201" s="10" t="s">
-        <v>201</v>
+        <v>265</v>
       </c>
       <c r="D201" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>219</v>
+        <v>283</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>3</v>
@@ -10009,13 +10096,13 @@
         <v>29</v>
       </c>
       <c r="C202" s="10" t="s">
-        <v>220</v>
+        <v>284</v>
       </c>
       <c r="D202" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E202" s="10" t="s">
-        <v>221</v>
+        <v>285</v>
       </c>
       <c r="F202" s="10" t="s">
         <v>3</v>
@@ -10043,13 +10130,13 @@
         <v>29</v>
       </c>
       <c r="C203" s="10" t="s">
-        <v>220</v>
+        <v>284</v>
       </c>
       <c r="D203" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>222</v>
+        <v>286</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>3</v>
@@ -10077,13 +10164,13 @@
         <v>29</v>
       </c>
       <c r="C204" s="10" t="s">
-        <v>220</v>
+        <v>284</v>
       </c>
       <c r="D204" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E204" s="10" t="s">
-        <v>223</v>
+        <v>287</v>
       </c>
       <c r="F204" s="10" t="s">
         <v>3</v>
@@ -10111,13 +10198,13 @@
         <v>29</v>
       </c>
       <c r="C205" s="10" t="s">
-        <v>220</v>
+        <v>284</v>
       </c>
       <c r="D205" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>224</v>
+        <v>288</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>3</v>
@@ -10145,13 +10232,13 @@
         <v>29</v>
       </c>
       <c r="C206" s="10" t="s">
-        <v>220</v>
+        <v>284</v>
       </c>
       <c r="D206" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E206" s="10" t="s">
-        <v>225</v>
+        <v>289</v>
       </c>
       <c r="F206" s="10" t="s">
         <v>3</v>
@@ -10179,13 +10266,13 @@
         <v>29</v>
       </c>
       <c r="C207" s="10" t="s">
-        <v>220</v>
+        <v>284</v>
       </c>
       <c r="D207" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>226</v>
+        <v>290</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>3</v>
@@ -10213,13 +10300,13 @@
         <v>29</v>
       </c>
       <c r="C208" s="10" t="s">
-        <v>220</v>
+        <v>284</v>
       </c>
       <c r="D208" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E208" s="10" t="s">
-        <v>227</v>
+        <v>291</v>
       </c>
       <c r="F208" s="10" t="s">
         <v>3</v>
@@ -10247,13 +10334,13 @@
         <v>29</v>
       </c>
       <c r="C209" s="10" t="s">
-        <v>220</v>
+        <v>284</v>
       </c>
       <c r="D209" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>228</v>
+        <v>292</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>3</v>
@@ -10281,13 +10368,13 @@
         <v>29</v>
       </c>
       <c r="C210" s="10" t="s">
-        <v>220</v>
+        <v>284</v>
       </c>
       <c r="D210" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E210" s="10" t="s">
-        <v>229</v>
+        <v>293</v>
       </c>
       <c r="F210" s="10" t="s">
         <v>3</v>
@@ -10315,13 +10402,13 @@
         <v>29</v>
       </c>
       <c r="C211" s="10" t="s">
-        <v>220</v>
+        <v>284</v>
       </c>
       <c r="D211" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E211" s="10" t="s">
-        <v>230</v>
+        <v>294</v>
       </c>
       <c r="F211" s="10" t="s">
         <v>3</v>
@@ -10349,13 +10436,13 @@
         <v>29</v>
       </c>
       <c r="C212" s="10" t="s">
-        <v>220</v>
+        <v>284</v>
       </c>
       <c r="D212" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E212" s="10" t="s">
-        <v>231</v>
+        <v>295</v>
       </c>
       <c r="F212" s="10" t="s">
         <v>3</v>
@@ -10383,13 +10470,13 @@
         <v>29</v>
       </c>
       <c r="C213" s="10" t="s">
-        <v>220</v>
+        <v>284</v>
       </c>
       <c r="D213" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E213" s="10" t="s">
-        <v>232</v>
+        <v>296</v>
       </c>
       <c r="F213" s="10" t="s">
         <v>3</v>
@@ -10417,13 +10504,13 @@
         <v>29</v>
       </c>
       <c r="C214" s="10" t="s">
-        <v>220</v>
+        <v>284</v>
       </c>
       <c r="D214" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E214" s="10" t="s">
-        <v>233</v>
+        <v>297</v>
       </c>
       <c r="F214" s="10" t="s">
         <v>3</v>
@@ -10451,13 +10538,13 @@
         <v>29</v>
       </c>
       <c r="C215" s="10" t="s">
-        <v>220</v>
+        <v>284</v>
       </c>
       <c r="D215" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E215" s="10" t="s">
-        <v>234</v>
+        <v>298</v>
       </c>
       <c r="F215" s="10" t="s">
         <v>3</v>
@@ -10485,13 +10572,13 @@
         <v>29</v>
       </c>
       <c r="C216" s="10" t="s">
-        <v>220</v>
+        <v>284</v>
       </c>
       <c r="D216" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E216" s="10" t="s">
-        <v>235</v>
+        <v>299</v>
       </c>
       <c r="F216" s="10" t="s">
         <v>3</v>
@@ -10519,13 +10606,13 @@
         <v>29</v>
       </c>
       <c r="C217" s="10" t="s">
-        <v>220</v>
+        <v>284</v>
       </c>
       <c r="D217" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E217" s="10" t="s">
-        <v>236</v>
+        <v>300</v>
       </c>
       <c r="F217" s="10" t="s">
         <v>3</v>
@@ -10553,13 +10640,13 @@
         <v>29</v>
       </c>
       <c r="C218" s="10" t="s">
-        <v>220</v>
+        <v>284</v>
       </c>
       <c r="D218" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E218" s="10" t="s">
-        <v>237</v>
+        <v>301</v>
       </c>
       <c r="F218" s="10" t="s">
         <v>3</v>
@@ -10587,13 +10674,13 @@
         <v>29</v>
       </c>
       <c r="C219" s="10" t="s">
-        <v>220</v>
+        <v>284</v>
       </c>
       <c r="D219" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>238</v>
+        <v>302</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>3</v>
@@ -10621,13 +10708,13 @@
         <v>29</v>
       </c>
       <c r="C220" s="10" t="s">
-        <v>220</v>
+        <v>284</v>
       </c>
       <c r="D220" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E220" s="10" t="s">
-        <v>239</v>
+        <v>303</v>
       </c>
       <c r="F220" s="10" t="s">
         <v>3</v>
@@ -10655,13 +10742,13 @@
         <v>29</v>
       </c>
       <c r="C221" s="10" t="s">
-        <v>220</v>
+        <v>284</v>
       </c>
       <c r="D221" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E221" s="10" t="s">
-        <v>240</v>
+        <v>304</v>
       </c>
       <c r="F221" s="10" t="s">
         <v>3</v>
@@ -10689,13 +10776,13 @@
         <v>29</v>
       </c>
       <c r="C222" s="10" t="s">
-        <v>220</v>
+        <v>284</v>
       </c>
       <c r="D222" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E222" s="10" t="s">
-        <v>241</v>
+        <v>305</v>
       </c>
       <c r="F222" s="10" t="s">
         <v>3</v>
@@ -10723,13 +10810,13 @@
         <v>29</v>
       </c>
       <c r="C223" s="10" t="s">
-        <v>220</v>
+        <v>284</v>
       </c>
       <c r="D223" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E223" s="10" t="s">
-        <v>242</v>
+        <v>306</v>
       </c>
       <c r="F223" s="10" t="s">
         <v>3</v>
@@ -10757,13 +10844,13 @@
         <v>29</v>
       </c>
       <c r="C224" s="10" t="s">
-        <v>220</v>
+        <v>284</v>
       </c>
       <c r="D224" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E224" s="10" t="s">
-        <v>243</v>
+        <v>307</v>
       </c>
       <c r="F224" s="10" t="s">
         <v>3</v>
@@ -10791,13 +10878,13 @@
         <v>29</v>
       </c>
       <c r="C225" s="10" t="s">
-        <v>244</v>
+        <v>308</v>
       </c>
       <c r="D225" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E225" s="10" t="s">
-        <v>245</v>
+        <v>309</v>
       </c>
       <c r="F225" s="10" t="s">
         <v>3</v>
@@ -10825,13 +10912,13 @@
         <v>29</v>
       </c>
       <c r="C226" s="10" t="s">
-        <v>244</v>
+        <v>308</v>
       </c>
       <c r="D226" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E226" s="10" t="s">
-        <v>246</v>
+        <v>310</v>
       </c>
       <c r="F226" s="10" t="s">
         <v>3</v>
@@ -10859,13 +10946,13 @@
         <v>29</v>
       </c>
       <c r="C227" s="10" t="s">
-        <v>244</v>
+        <v>308</v>
       </c>
       <c r="D227" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E227" s="10" t="s">
-        <v>247</v>
+        <v>311</v>
       </c>
       <c r="F227" s="10" t="s">
         <v>3</v>
@@ -10893,13 +10980,13 @@
         <v>29</v>
       </c>
       <c r="C228" s="10" t="s">
-        <v>244</v>
+        <v>308</v>
       </c>
       <c r="D228" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E228" s="10" t="s">
-        <v>248</v>
+        <v>312</v>
       </c>
       <c r="F228" s="10" t="s">
         <v>3</v>
@@ -10927,13 +11014,13 @@
         <v>29</v>
       </c>
       <c r="C229" s="10" t="s">
-        <v>244</v>
+        <v>308</v>
       </c>
       <c r="D229" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E229" s="10" t="s">
-        <v>249</v>
+        <v>313</v>
       </c>
       <c r="F229" s="10" t="s">
         <v>3</v>
@@ -10961,13 +11048,13 @@
         <v>29</v>
       </c>
       <c r="C230" s="10" t="s">
-        <v>244</v>
+        <v>308</v>
       </c>
       <c r="D230" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E230" s="10" t="s">
-        <v>250</v>
+        <v>314</v>
       </c>
       <c r="F230" s="10" t="s">
         <v>3</v>
@@ -10995,13 +11082,13 @@
         <v>29</v>
       </c>
       <c r="C231" s="10" t="s">
-        <v>244</v>
+        <v>308</v>
       </c>
       <c r="D231" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E231" s="10" t="s">
-        <v>251</v>
+        <v>315</v>
       </c>
       <c r="F231" s="10" t="s">
         <v>3</v>
@@ -11029,7 +11116,7 @@
         <v>29</v>
       </c>
       <c r="C232" s="10" t="s">
-        <v>244</v>
+        <v>308</v>
       </c>
       <c r="D232" s="10" t="s">
         <v>78</v>
@@ -11063,13 +11150,13 @@
         <v>29</v>
       </c>
       <c r="C233" s="10" t="s">
-        <v>244</v>
+        <v>308</v>
       </c>
       <c r="D233" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E233" s="10" t="s">
-        <v>252</v>
+        <v>316</v>
       </c>
       <c r="F233" s="10" t="s">
         <v>3</v>
@@ -11097,13 +11184,13 @@
         <v>29</v>
       </c>
       <c r="C234" s="10" t="s">
-        <v>244</v>
+        <v>308</v>
       </c>
       <c r="D234" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E234" s="10" t="s">
-        <v>253</v>
+        <v>317</v>
       </c>
       <c r="F234" s="10" t="s">
         <v>3</v>
@@ -11131,13 +11218,13 @@
         <v>29</v>
       </c>
       <c r="C235" s="10" t="s">
-        <v>244</v>
+        <v>308</v>
       </c>
       <c r="D235" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E235" s="10" t="s">
-        <v>254</v>
+        <v>318</v>
       </c>
       <c r="F235" s="10" t="s">
         <v>3</v>
@@ -11165,13 +11252,13 @@
         <v>29</v>
       </c>
       <c r="C236" s="10" t="s">
-        <v>244</v>
+        <v>308</v>
       </c>
       <c r="D236" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E236" s="10" t="s">
-        <v>255</v>
+        <v>319</v>
       </c>
       <c r="F236" s="10" t="s">
         <v>3</v>
@@ -11199,13 +11286,13 @@
         <v>30</v>
       </c>
       <c r="C237" s="10" t="s">
-        <v>256</v>
+        <v>320</v>
       </c>
       <c r="D237" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E237" s="10" t="s">
-        <v>257</v>
+        <v>321</v>
       </c>
       <c r="F237" s="10" t="s">
         <v>3</v>
@@ -11233,13 +11320,13 @@
         <v>30</v>
       </c>
       <c r="C238" s="10" t="s">
-        <v>256</v>
+        <v>320</v>
       </c>
       <c r="D238" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E238" s="10" t="s">
-        <v>258</v>
+        <v>322</v>
       </c>
       <c r="F238" s="10" t="s">
         <v>3</v>
@@ -11267,13 +11354,13 @@
         <v>30</v>
       </c>
       <c r="C239" s="10" t="s">
-        <v>256</v>
+        <v>320</v>
       </c>
       <c r="D239" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E239" s="10" t="s">
-        <v>259</v>
+        <v>323</v>
       </c>
       <c r="F239" s="10" t="s">
         <v>3</v>
@@ -11301,13 +11388,13 @@
         <v>30</v>
       </c>
       <c r="C240" s="10" t="s">
-        <v>256</v>
+        <v>320</v>
       </c>
       <c r="D240" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E240" s="10" t="s">
-        <v>260</v>
+        <v>324</v>
       </c>
       <c r="F240" s="10" t="s">
         <v>3</v>
@@ -11335,13 +11422,13 @@
         <v>30</v>
       </c>
       <c r="C241" s="10" t="s">
-        <v>256</v>
+        <v>320</v>
       </c>
       <c r="D241" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E241" s="10" t="s">
-        <v>261</v>
+        <v>325</v>
       </c>
       <c r="F241" s="10" t="s">
         <v>3</v>
@@ -11369,13 +11456,13 @@
         <v>30</v>
       </c>
       <c r="C242" s="10" t="s">
-        <v>256</v>
+        <v>320</v>
       </c>
       <c r="D242" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E242" s="10" t="s">
-        <v>262</v>
+        <v>326</v>
       </c>
       <c r="F242" s="10" t="s">
         <v>3</v>
@@ -11403,13 +11490,13 @@
         <v>30</v>
       </c>
       <c r="C243" s="10" t="s">
-        <v>256</v>
+        <v>320</v>
       </c>
       <c r="D243" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E243" s="10" t="s">
-        <v>263</v>
+        <v>327</v>
       </c>
       <c r="F243" s="10" t="s">
         <v>3</v>
@@ -11437,13 +11524,13 @@
         <v>30</v>
       </c>
       <c r="C244" s="10" t="s">
-        <v>256</v>
+        <v>320</v>
       </c>
       <c r="D244" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E244" s="10" t="s">
-        <v>264</v>
+        <v>328</v>
       </c>
       <c r="F244" s="10" t="s">
         <v>3</v>
@@ -11471,13 +11558,13 @@
         <v>30</v>
       </c>
       <c r="C245" s="10" t="s">
-        <v>256</v>
+        <v>320</v>
       </c>
       <c r="D245" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E245" s="10" t="s">
-        <v>265</v>
+        <v>329</v>
       </c>
       <c r="F245" s="10" t="s">
         <v>3</v>
@@ -11505,13 +11592,13 @@
         <v>30</v>
       </c>
       <c r="C246" s="10" t="s">
-        <v>256</v>
+        <v>320</v>
       </c>
       <c r="D246" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E246" s="10" t="s">
-        <v>266</v>
+        <v>330</v>
       </c>
       <c r="F246" s="10" t="s">
         <v>3</v>
@@ -11539,13 +11626,13 @@
         <v>30</v>
       </c>
       <c r="C247" s="10" t="s">
-        <v>256</v>
+        <v>320</v>
       </c>
       <c r="D247" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E247" s="10" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="F247" s="10" t="s">
         <v>3</v>
@@ -11573,13 +11660,13 @@
         <v>30</v>
       </c>
       <c r="C248" s="10" t="s">
-        <v>256</v>
+        <v>320</v>
       </c>
       <c r="D248" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E248" s="10" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="F248" s="10" t="s">
         <v>3</v>
@@ -11607,13 +11694,13 @@
         <v>30</v>
       </c>
       <c r="C249" s="10" t="s">
-        <v>256</v>
+        <v>320</v>
       </c>
       <c r="D249" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E249" s="10" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="F249" s="10" t="s">
         <v>3</v>
@@ -11641,13 +11728,13 @@
         <v>30</v>
       </c>
       <c r="C250" s="10" t="s">
-        <v>256</v>
+        <v>320</v>
       </c>
       <c r="D250" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E250" s="10" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="F250" s="10" t="s">
         <v>3</v>
@@ -11675,13 +11762,13 @@
         <v>30</v>
       </c>
       <c r="C251" s="10" t="s">
-        <v>256</v>
+        <v>320</v>
       </c>
       <c r="D251" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E251" s="10" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="F251" s="10" t="s">
         <v>3</v>
@@ -11709,13 +11796,13 @@
         <v>30</v>
       </c>
       <c r="C252" s="10" t="s">
-        <v>256</v>
+        <v>320</v>
       </c>
       <c r="D252" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E252" s="10" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="F252" s="10" t="s">
         <v>3</v>
@@ -11743,13 +11830,13 @@
         <v>30</v>
       </c>
       <c r="C253" s="10" t="s">
-        <v>256</v>
+        <v>320</v>
       </c>
       <c r="D253" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E253" s="10" t="s">
-        <v>273</v>
+        <v>337</v>
       </c>
       <c r="F253" s="10" t="s">
         <v>3</v>
@@ -11777,13 +11864,13 @@
         <v>31</v>
       </c>
       <c r="C254" s="10" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="D254" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E254" s="10" t="s">
-        <v>275</v>
+        <v>339</v>
       </c>
       <c r="F254" s="10" t="s">
         <v>3</v>
@@ -11811,13 +11898,13 @@
         <v>31</v>
       </c>
       <c r="C255" s="10" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="D255" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E255" s="10" t="s">
-        <v>276</v>
+        <v>340</v>
       </c>
       <c r="F255" s="10" t="s">
         <v>3</v>
@@ -11845,13 +11932,13 @@
         <v>31</v>
       </c>
       <c r="C256" s="10" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="D256" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E256" s="10" t="s">
-        <v>277</v>
+        <v>341</v>
       </c>
       <c r="F256" s="10" t="s">
         <v>3</v>
@@ -11879,13 +11966,13 @@
         <v>31</v>
       </c>
       <c r="C257" s="10" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="D257" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E257" s="10" t="s">
-        <v>278</v>
+        <v>342</v>
       </c>
       <c r="F257" s="10" t="s">
         <v>3</v>
@@ -11913,13 +12000,13 @@
         <v>31</v>
       </c>
       <c r="C258" s="10" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="D258" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E258" s="10" t="s">
-        <v>279</v>
+        <v>343</v>
       </c>
       <c r="F258" s="10" t="s">
         <v>3</v>
@@ -11947,13 +12034,13 @@
         <v>31</v>
       </c>
       <c r="C259" s="10" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="D259" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E259" s="10" t="s">
-        <v>280</v>
+        <v>344</v>
       </c>
       <c r="F259" s="10" t="s">
         <v>3</v>
@@ -11981,13 +12068,13 @@
         <v>31</v>
       </c>
       <c r="C260" s="10" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="D260" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E260" s="10" t="s">
-        <v>281</v>
+        <v>345</v>
       </c>
       <c r="F260" s="10" t="s">
         <v>3</v>
@@ -12015,13 +12102,13 @@
         <v>31</v>
       </c>
       <c r="C261" s="10" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="D261" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E261" s="10" t="s">
-        <v>282</v>
+        <v>346</v>
       </c>
       <c r="F261" s="10" t="s">
         <v>3</v>
@@ -12049,13 +12136,13 @@
         <v>31</v>
       </c>
       <c r="C262" s="10" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="D262" s="10" t="s">
-        <v>283</v>
+        <v>347</v>
       </c>
       <c r="E262" s="10" t="s">
-        <v>284</v>
+        <v>348</v>
       </c>
       <c r="F262" s="10" t="s">
         <v>3</v>
@@ -12083,13 +12170,13 @@
         <v>31</v>
       </c>
       <c r="C263" s="10" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="D263" s="10" t="s">
-        <v>283</v>
+        <v>347</v>
       </c>
       <c r="E263" s="10" t="s">
-        <v>285</v>
+        <v>349</v>
       </c>
       <c r="F263" s="10" t="s">
         <v>3</v>
@@ -12117,13 +12204,13 @@
         <v>31</v>
       </c>
       <c r="C264" s="10" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="D264" s="10" t="s">
-        <v>283</v>
+        <v>347</v>
       </c>
       <c r="E264" s="10" t="s">
-        <v>286</v>
+        <v>350</v>
       </c>
       <c r="F264" s="10" t="s">
         <v>3</v>
@@ -12151,13 +12238,13 @@
         <v>31</v>
       </c>
       <c r="C265" s="10" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="D265" s="10" t="s">
-        <v>283</v>
+        <v>347</v>
       </c>
       <c r="E265" s="10" t="s">
-        <v>287</v>
+        <v>351</v>
       </c>
       <c r="F265" s="10" t="s">
         <v>3</v>
@@ -12185,13 +12272,13 @@
         <v>31</v>
       </c>
       <c r="C266" s="10" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="D266" s="10" t="s">
-        <v>283</v>
+        <v>347</v>
       </c>
       <c r="E266" s="10" t="s">
-        <v>288</v>
+        <v>352</v>
       </c>
       <c r="F266" s="10" t="s">
         <v>3</v>
@@ -12219,13 +12306,13 @@
         <v>31</v>
       </c>
       <c r="C267" s="10" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="D267" s="10" t="s">
-        <v>283</v>
+        <v>347</v>
       </c>
       <c r="E267" s="10" t="s">
-        <v>289</v>
+        <v>353</v>
       </c>
       <c r="F267" s="10" t="s">
         <v>3</v>
@@ -12253,13 +12340,13 @@
         <v>31</v>
       </c>
       <c r="C268" s="10" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="D268" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E268" s="10" t="s">
-        <v>290</v>
+        <v>354</v>
       </c>
       <c r="F268" s="10" t="s">
         <v>3</v>
@@ -12287,13 +12374,13 @@
         <v>31</v>
       </c>
       <c r="C269" s="10" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="D269" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E269" s="10" t="s">
-        <v>291</v>
+        <v>355</v>
       </c>
       <c r="F269" s="10" t="s">
         <v>3</v>
@@ -12321,13 +12408,13 @@
         <v>31</v>
       </c>
       <c r="C270" s="10" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="D270" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E270" s="10" t="s">
-        <v>292</v>
+        <v>356</v>
       </c>
       <c r="F270" s="10" t="s">
         <v>3</v>
@@ -12355,13 +12442,13 @@
         <v>31</v>
       </c>
       <c r="C271" s="10" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="D271" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E271" s="10" t="s">
-        <v>293</v>
+        <v>357</v>
       </c>
       <c r="F271" s="10" t="s">
         <v>3</v>
@@ -12389,13 +12476,13 @@
         <v>31</v>
       </c>
       <c r="C272" s="10" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="D272" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E272" s="10" t="s">
-        <v>294</v>
+        <v>358</v>
       </c>
       <c r="F272" s="10" t="s">
         <v>3</v>
@@ -12423,13 +12510,13 @@
         <v>31</v>
       </c>
       <c r="C273" s="10" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="D273" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E273" s="10" t="s">
-        <v>295</v>
+        <v>359</v>
       </c>
       <c r="F273" s="10" t="s">
         <v>3</v>
@@ -12457,13 +12544,13 @@
         <v>31</v>
       </c>
       <c r="C274" s="10" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="D274" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E274" s="10" t="s">
-        <v>296</v>
+        <v>360</v>
       </c>
       <c r="F274" s="10" t="s">
         <v>3</v>
@@ -12491,13 +12578,13 @@
         <v>31</v>
       </c>
       <c r="C275" s="10" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="D275" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E275" s="10" t="s">
-        <v>297</v>
+        <v>361</v>
       </c>
       <c r="F275" s="10" t="s">
         <v>3</v>
@@ -12525,13 +12612,13 @@
         <v>31</v>
       </c>
       <c r="C276" s="10" t="s">
-        <v>298</v>
+        <v>362</v>
       </c>
       <c r="D276" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E276" s="10" t="s">
-        <v>299</v>
+        <v>363</v>
       </c>
       <c r="F276" s="10" t="s">
         <v>3</v>
@@ -12559,13 +12646,13 @@
         <v>31</v>
       </c>
       <c r="C277" s="10" t="s">
-        <v>298</v>
+        <v>362</v>
       </c>
       <c r="D277" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E277" s="10" t="s">
-        <v>300</v>
+        <v>364</v>
       </c>
       <c r="F277" s="10" t="s">
         <v>3</v>
@@ -12593,13 +12680,13 @@
         <v>31</v>
       </c>
       <c r="C278" s="10" t="s">
-        <v>298</v>
+        <v>362</v>
       </c>
       <c r="D278" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E278" s="10" t="s">
-        <v>301</v>
+        <v>365</v>
       </c>
       <c r="F278" s="10" t="s">
         <v>3</v>
@@ -12627,13 +12714,13 @@
         <v>31</v>
       </c>
       <c r="C279" s="10" t="s">
-        <v>298</v>
+        <v>362</v>
       </c>
       <c r="D279" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E279" s="10" t="s">
-        <v>302</v>
+        <v>366</v>
       </c>
       <c r="F279" s="10" t="s">
         <v>3</v>
@@ -12661,13 +12748,13 @@
         <v>31</v>
       </c>
       <c r="C280" s="10" t="s">
-        <v>298</v>
+        <v>362</v>
       </c>
       <c r="D280" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E280" s="10" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="F280" s="10" t="s">
         <v>3</v>
@@ -12695,13 +12782,13 @@
         <v>31</v>
       </c>
       <c r="C281" s="10" t="s">
-        <v>298</v>
+        <v>362</v>
       </c>
       <c r="D281" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E281" s="10" t="s">
-        <v>304</v>
+        <v>368</v>
       </c>
       <c r="F281" s="10" t="s">
         <v>3</v>
@@ -12729,13 +12816,13 @@
         <v>31</v>
       </c>
       <c r="C282" s="10" t="s">
-        <v>298</v>
+        <v>362</v>
       </c>
       <c r="D282" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E282" s="10" t="s">
-        <v>305</v>
+        <v>369</v>
       </c>
       <c r="F282" s="10" t="s">
         <v>3</v>
@@ -12763,13 +12850,13 @@
         <v>31</v>
       </c>
       <c r="C283" s="10" t="s">
-        <v>298</v>
+        <v>362</v>
       </c>
       <c r="D283" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E283" s="10" t="s">
-        <v>306</v>
+        <v>370</v>
       </c>
       <c r="F283" s="10" t="s">
         <v>3</v>
@@ -12797,13 +12884,13 @@
         <v>31</v>
       </c>
       <c r="C284" s="10" t="s">
-        <v>298</v>
+        <v>362</v>
       </c>
       <c r="D284" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E284" s="10" t="s">
-        <v>307</v>
+        <v>371</v>
       </c>
       <c r="F284" s="10" t="s">
         <v>3</v>
@@ -12831,13 +12918,13 @@
         <v>31</v>
       </c>
       <c r="C285" s="10" t="s">
-        <v>298</v>
+        <v>362</v>
       </c>
       <c r="D285" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E285" s="10" t="s">
-        <v>308</v>
+        <v>372</v>
       </c>
       <c r="F285" s="10" t="s">
         <v>3</v>
@@ -12865,13 +12952,13 @@
         <v>31</v>
       </c>
       <c r="C286" s="10" t="s">
-        <v>298</v>
+        <v>362</v>
       </c>
       <c r="D286" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E286" s="10" t="s">
-        <v>309</v>
+        <v>373</v>
       </c>
       <c r="F286" s="10" t="s">
         <v>3</v>
@@ -12899,13 +12986,13 @@
         <v>31</v>
       </c>
       <c r="C287" s="10" t="s">
-        <v>298</v>
+        <v>362</v>
       </c>
       <c r="D287" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E287" s="10" t="s">
-        <v>310</v>
+        <v>374</v>
       </c>
       <c r="F287" s="10" t="s">
         <v>3</v>
@@ -12933,13 +13020,13 @@
         <v>31</v>
       </c>
       <c r="C288" s="10" t="s">
-        <v>298</v>
+        <v>362</v>
       </c>
       <c r="D288" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E288" s="10" t="s">
-        <v>311</v>
+        <v>375</v>
       </c>
       <c r="F288" s="10" t="s">
         <v>3</v>
@@ -12967,13 +13054,13 @@
         <v>31</v>
       </c>
       <c r="C289" s="10" t="s">
-        <v>298</v>
+        <v>362</v>
       </c>
       <c r="D289" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E289" s="10" t="s">
-        <v>312</v>
+        <v>376</v>
       </c>
       <c r="F289" s="10" t="s">
         <v>3</v>
@@ -13001,13 +13088,13 @@
         <v>31</v>
       </c>
       <c r="C290" s="10" t="s">
-        <v>298</v>
+        <v>362</v>
       </c>
       <c r="D290" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E290" s="10" t="s">
-        <v>313</v>
+        <v>377</v>
       </c>
       <c r="F290" s="10" t="s">
         <v>3</v>
@@ -13035,13 +13122,13 @@
         <v>31</v>
       </c>
       <c r="C291" s="10" t="s">
-        <v>298</v>
+        <v>362</v>
       </c>
       <c r="D291" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E291" s="10" t="s">
-        <v>314</v>
+        <v>378</v>
       </c>
       <c r="F291" s="10" t="s">
         <v>3</v>
@@ -13069,13 +13156,13 @@
         <v>31</v>
       </c>
       <c r="C292" s="10" t="s">
-        <v>298</v>
+        <v>362</v>
       </c>
       <c r="D292" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E292" s="10" t="s">
-        <v>315</v>
+        <v>379</v>
       </c>
       <c r="F292" s="10" t="s">
         <v>3</v>
@@ -13103,13 +13190,13 @@
         <v>31</v>
       </c>
       <c r="C293" s="10" t="s">
-        <v>316</v>
+        <v>380</v>
       </c>
       <c r="D293" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E293" s="10" t="s">
-        <v>317</v>
+        <v>381</v>
       </c>
       <c r="F293" s="10" t="s">
         <v>3</v>
@@ -13137,13 +13224,13 @@
         <v>31</v>
       </c>
       <c r="C294" s="10" t="s">
-        <v>316</v>
+        <v>380</v>
       </c>
       <c r="D294" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E294" s="10" t="s">
-        <v>318</v>
+        <v>382</v>
       </c>
       <c r="F294" s="10" t="s">
         <v>3</v>
@@ -13171,13 +13258,13 @@
         <v>31</v>
       </c>
       <c r="C295" s="10" t="s">
-        <v>316</v>
+        <v>380</v>
       </c>
       <c r="D295" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E295" s="10" t="s">
-        <v>319</v>
+        <v>383</v>
       </c>
       <c r="F295" s="10" t="s">
         <v>3</v>
@@ -13205,13 +13292,13 @@
         <v>31</v>
       </c>
       <c r="C296" s="10" t="s">
-        <v>316</v>
+        <v>380</v>
       </c>
       <c r="D296" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E296" s="10" t="s">
-        <v>320</v>
+        <v>384</v>
       </c>
       <c r="F296" s="10" t="s">
         <v>3</v>
@@ -13239,13 +13326,13 @@
         <v>31</v>
       </c>
       <c r="C297" s="10" t="s">
-        <v>316</v>
+        <v>380</v>
       </c>
       <c r="D297" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E297" s="10" t="s">
-        <v>321</v>
+        <v>385</v>
       </c>
       <c r="F297" s="10" t="s">
         <v>3</v>
@@ -13273,13 +13360,13 @@
         <v>31</v>
       </c>
       <c r="C298" s="10" t="s">
-        <v>316</v>
+        <v>380</v>
       </c>
       <c r="D298" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E298" s="10" t="s">
-        <v>322</v>
+        <v>386</v>
       </c>
       <c r="F298" s="10" t="s">
         <v>3</v>
@@ -13307,13 +13394,13 @@
         <v>31</v>
       </c>
       <c r="C299" s="10" t="s">
-        <v>316</v>
+        <v>380</v>
       </c>
       <c r="D299" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E299" s="10" t="s">
-        <v>323</v>
+        <v>387</v>
       </c>
       <c r="F299" s="10" t="s">
         <v>3</v>
@@ -13341,13 +13428,13 @@
         <v>31</v>
       </c>
       <c r="C300" s="10" t="s">
-        <v>316</v>
+        <v>380</v>
       </c>
       <c r="D300" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E300" s="10" t="s">
-        <v>324</v>
+        <v>388</v>
       </c>
       <c r="F300" s="10" t="s">
         <v>3</v>
@@ -13375,13 +13462,13 @@
         <v>32</v>
       </c>
       <c r="C301" s="10" t="s">
-        <v>325</v>
+        <v>389</v>
       </c>
       <c r="D301" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E301" s="10" t="s">
-        <v>326</v>
+        <v>390</v>
       </c>
       <c r="F301" s="10" t="s">
         <v>3</v>
@@ -13409,13 +13496,13 @@
         <v>32</v>
       </c>
       <c r="C302" s="10" t="s">
-        <v>325</v>
+        <v>389</v>
       </c>
       <c r="D302" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E302" s="10" t="s">
-        <v>327</v>
+        <v>391</v>
       </c>
       <c r="F302" s="10" t="s">
         <v>3</v>
@@ -13443,13 +13530,13 @@
         <v>32</v>
       </c>
       <c r="C303" s="10" t="s">
-        <v>325</v>
+        <v>389</v>
       </c>
       <c r="D303" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E303" s="10" t="s">
-        <v>328</v>
+        <v>392</v>
       </c>
       <c r="F303" s="10" t="s">
         <v>3</v>
@@ -13477,13 +13564,13 @@
         <v>32</v>
       </c>
       <c r="C304" s="10" t="s">
-        <v>325</v>
+        <v>389</v>
       </c>
       <c r="D304" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E304" s="10" t="s">
-        <v>329</v>
+        <v>393</v>
       </c>
       <c r="F304" s="10" t="s">
         <v>3</v>
@@ -13511,13 +13598,13 @@
         <v>32</v>
       </c>
       <c r="C305" s="10" t="s">
-        <v>325</v>
+        <v>389</v>
       </c>
       <c r="D305" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E305" s="10" t="s">
-        <v>330</v>
+        <v>394</v>
       </c>
       <c r="F305" s="10" t="s">
         <v>3</v>
@@ -13545,13 +13632,13 @@
         <v>32</v>
       </c>
       <c r="C306" s="10" t="s">
-        <v>325</v>
+        <v>389</v>
       </c>
       <c r="D306" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E306" s="10" t="s">
-        <v>331</v>
+        <v>395</v>
       </c>
       <c r="F306" s="10" t="s">
         <v>3</v>
@@ -13579,13 +13666,13 @@
         <v>32</v>
       </c>
       <c r="C307" s="10" t="s">
-        <v>325</v>
+        <v>389</v>
       </c>
       <c r="D307" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E307" s="10" t="s">
-        <v>332</v>
+        <v>396</v>
       </c>
       <c r="F307" s="10" t="s">
         <v>3</v>
@@ -13613,13 +13700,13 @@
         <v>32</v>
       </c>
       <c r="C308" s="10" t="s">
-        <v>325</v>
+        <v>389</v>
       </c>
       <c r="D308" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E308" s="10" t="s">
-        <v>333</v>
+        <v>397</v>
       </c>
       <c r="F308" s="10" t="s">
         <v>3</v>
@@ -13647,13 +13734,13 @@
         <v>32</v>
       </c>
       <c r="C309" s="10" t="s">
-        <v>325</v>
+        <v>389</v>
       </c>
       <c r="D309" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E309" s="10" t="s">
-        <v>308</v>
+        <v>372</v>
       </c>
       <c r="F309" s="10" t="s">
         <v>3</v>
@@ -13681,13 +13768,13 @@
         <v>32</v>
       </c>
       <c r="C310" s="10" t="s">
-        <v>325</v>
+        <v>389</v>
       </c>
       <c r="D310" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E310" s="10" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="F310" s="10" t="s">
         <v>3</v>
@@ -13715,13 +13802,13 @@
         <v>32</v>
       </c>
       <c r="C311" s="10" t="s">
-        <v>325</v>
+        <v>389</v>
       </c>
       <c r="D311" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E311" s="10" t="s">
-        <v>335</v>
+        <v>399</v>
       </c>
       <c r="F311" s="10" t="s">
         <v>3</v>
@@ -13749,13 +13836,13 @@
         <v>32</v>
       </c>
       <c r="C312" s="10" t="s">
-        <v>325</v>
+        <v>389</v>
       </c>
       <c r="D312" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E312" s="10" t="s">
-        <v>336</v>
+        <v>400</v>
       </c>
       <c r="F312" s="10" t="s">
         <v>3</v>
@@ -13783,13 +13870,13 @@
         <v>32</v>
       </c>
       <c r="C313" s="10" t="s">
-        <v>325</v>
+        <v>389</v>
       </c>
       <c r="D313" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E313" s="10" t="s">
-        <v>337</v>
+        <v>401</v>
       </c>
       <c r="F313" s="10" t="s">
         <v>3</v>
@@ -13817,13 +13904,13 @@
         <v>32</v>
       </c>
       <c r="C314" s="10" t="s">
-        <v>325</v>
+        <v>389</v>
       </c>
       <c r="D314" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E314" s="10" t="s">
-        <v>338</v>
+        <v>402</v>
       </c>
       <c r="F314" s="10" t="s">
         <v>3</v>
@@ -13851,13 +13938,13 @@
         <v>32</v>
       </c>
       <c r="C315" s="10" t="s">
-        <v>325</v>
+        <v>389</v>
       </c>
       <c r="D315" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E315" s="10" t="s">
-        <v>339</v>
+        <v>403</v>
       </c>
       <c r="F315" s="10" t="s">
         <v>3</v>
@@ -13885,13 +13972,13 @@
         <v>32</v>
       </c>
       <c r="C316" s="10" t="s">
-        <v>325</v>
+        <v>389</v>
       </c>
       <c r="D316" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E316" s="10" t="s">
-        <v>340</v>
+        <v>404</v>
       </c>
       <c r="F316" s="10" t="s">
         <v>3</v>
@@ -13919,13 +14006,13 @@
         <v>32</v>
       </c>
       <c r="C317" s="10" t="s">
-        <v>341</v>
+        <v>405</v>
       </c>
       <c r="D317" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E317" s="10" t="s">
-        <v>342</v>
+        <v>406</v>
       </c>
       <c r="F317" s="10" t="s">
         <v>3</v>
@@ -13953,13 +14040,13 @@
         <v>32</v>
       </c>
       <c r="C318" s="10" t="s">
-        <v>341</v>
+        <v>405</v>
       </c>
       <c r="D318" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E318" s="10" t="s">
-        <v>343</v>
+        <v>407</v>
       </c>
       <c r="F318" s="10" t="s">
         <v>3</v>
@@ -13987,13 +14074,13 @@
         <v>32</v>
       </c>
       <c r="C319" s="10" t="s">
-        <v>341</v>
+        <v>405</v>
       </c>
       <c r="D319" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E319" s="10" t="s">
-        <v>344</v>
+        <v>408</v>
       </c>
       <c r="F319" s="10" t="s">
         <v>3</v>
@@ -14021,13 +14108,13 @@
         <v>32</v>
       </c>
       <c r="C320" s="10" t="s">
-        <v>341</v>
+        <v>405</v>
       </c>
       <c r="D320" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E320" s="10" t="s">
-        <v>345</v>
+        <v>409</v>
       </c>
       <c r="F320" s="10" t="s">
         <v>3</v>
@@ -14055,13 +14142,13 @@
         <v>32</v>
       </c>
       <c r="C321" s="10" t="s">
-        <v>341</v>
+        <v>405</v>
       </c>
       <c r="D321" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E321" s="10" t="s">
-        <v>346</v>
+        <v>410</v>
       </c>
       <c r="F321" s="10" t="s">
         <v>3</v>
@@ -14089,13 +14176,13 @@
         <v>32</v>
       </c>
       <c r="C322" s="10" t="s">
-        <v>341</v>
+        <v>405</v>
       </c>
       <c r="D322" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E322" s="10" t="s">
-        <v>347</v>
+        <v>411</v>
       </c>
       <c r="F322" s="10" t="s">
         <v>3</v>
@@ -14123,13 +14210,13 @@
         <v>32</v>
       </c>
       <c r="C323" s="10" t="s">
-        <v>341</v>
+        <v>405</v>
       </c>
       <c r="D323" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E323" s="10" t="s">
-        <v>348</v>
+        <v>412</v>
       </c>
       <c r="F323" s="10" t="s">
         <v>3</v>
@@ -14157,13 +14244,13 @@
         <v>32</v>
       </c>
       <c r="C324" s="10" t="s">
-        <v>341</v>
+        <v>405</v>
       </c>
       <c r="D324" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E324" s="10" t="s">
-        <v>349</v>
+        <v>413</v>
       </c>
       <c r="F324" s="10" t="s">
         <v>3</v>
@@ -14191,13 +14278,13 @@
         <v>32</v>
       </c>
       <c r="C325" s="10" t="s">
-        <v>341</v>
+        <v>405</v>
       </c>
       <c r="D325" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E325" s="10" t="s">
-        <v>350</v>
+        <v>414</v>
       </c>
       <c r="F325" s="10" t="s">
         <v>3</v>
@@ -14225,13 +14312,13 @@
         <v>32</v>
       </c>
       <c r="C326" s="10" t="s">
-        <v>341</v>
+        <v>405</v>
       </c>
       <c r="D326" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E326" s="10" t="s">
-        <v>351</v>
+        <v>415</v>
       </c>
       <c r="F326" s="10" t="s">
         <v>3</v>
@@ -14259,13 +14346,13 @@
         <v>32</v>
       </c>
       <c r="C327" s="10" t="s">
-        <v>341</v>
+        <v>405</v>
       </c>
       <c r="D327" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E327" s="10" t="s">
-        <v>352</v>
+        <v>416</v>
       </c>
       <c r="F327" s="10" t="s">
         <v>3</v>
@@ -14293,13 +14380,13 @@
         <v>32</v>
       </c>
       <c r="C328" s="10" t="s">
-        <v>341</v>
+        <v>405</v>
       </c>
       <c r="D328" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E328" s="10" t="s">
-        <v>353</v>
+        <v>417</v>
       </c>
       <c r="F328" s="10" t="s">
         <v>3</v>
@@ -14327,13 +14414,13 @@
         <v>32</v>
       </c>
       <c r="C329" s="10" t="s">
-        <v>341</v>
+        <v>405</v>
       </c>
       <c r="D329" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E329" s="10" t="s">
-        <v>354</v>
+        <v>418</v>
       </c>
       <c r="F329" s="10" t="s">
         <v>3</v>
@@ -14361,13 +14448,13 @@
         <v>32</v>
       </c>
       <c r="C330" s="10" t="s">
-        <v>341</v>
+        <v>405</v>
       </c>
       <c r="D330" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E330" s="10" t="s">
-        <v>355</v>
+        <v>419</v>
       </c>
       <c r="F330" s="10" t="s">
         <v>3</v>
@@ -14395,13 +14482,13 @@
         <v>32</v>
       </c>
       <c r="C331" s="10" t="s">
-        <v>341</v>
+        <v>405</v>
       </c>
       <c r="D331" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E331" s="10" t="s">
-        <v>356</v>
+        <v>420</v>
       </c>
       <c r="F331" s="10" t="s">
         <v>3</v>
@@ -14429,13 +14516,13 @@
         <v>32</v>
       </c>
       <c r="C332" s="10" t="s">
-        <v>357</v>
+        <v>421</v>
       </c>
       <c r="D332" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E332" s="10" t="s">
-        <v>358</v>
+        <v>422</v>
       </c>
       <c r="F332" s="10" t="s">
         <v>3</v>
@@ -14463,13 +14550,13 @@
         <v>32</v>
       </c>
       <c r="C333" s="10" t="s">
-        <v>357</v>
+        <v>421</v>
       </c>
       <c r="D333" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E333" s="10" t="s">
-        <v>359</v>
+        <v>423</v>
       </c>
       <c r="F333" s="10" t="s">
         <v>3</v>
@@ -14497,13 +14584,13 @@
         <v>32</v>
       </c>
       <c r="C334" s="10" t="s">
-        <v>357</v>
+        <v>421</v>
       </c>
       <c r="D334" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E334" s="10" t="s">
-        <v>360</v>
+        <v>424</v>
       </c>
       <c r="F334" s="10" t="s">
         <v>3</v>
@@ -14531,13 +14618,13 @@
         <v>32</v>
       </c>
       <c r="C335" s="10" t="s">
-        <v>357</v>
+        <v>421</v>
       </c>
       <c r="D335" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E335" s="10" t="s">
-        <v>361</v>
+        <v>425</v>
       </c>
       <c r="F335" s="10" t="s">
         <v>3</v>
@@ -14565,13 +14652,13 @@
         <v>32</v>
       </c>
       <c r="C336" s="10" t="s">
-        <v>357</v>
+        <v>421</v>
       </c>
       <c r="D336" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E336" s="10" t="s">
-        <v>362</v>
+        <v>426</v>
       </c>
       <c r="F336" s="10" t="s">
         <v>3</v>
@@ -14599,13 +14686,13 @@
         <v>32</v>
       </c>
       <c r="C337" s="10" t="s">
-        <v>357</v>
+        <v>421</v>
       </c>
       <c r="D337" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E337" s="10" t="s">
-        <v>363</v>
+        <v>427</v>
       </c>
       <c r="F337" s="10" t="s">
         <v>3</v>
@@ -14633,13 +14720,13 @@
         <v>32</v>
       </c>
       <c r="C338" s="10" t="s">
-        <v>357</v>
+        <v>421</v>
       </c>
       <c r="D338" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E338" s="10" t="s">
-        <v>364</v>
+        <v>428</v>
       </c>
       <c r="F338" s="10" t="s">
         <v>3</v>
@@ -14667,13 +14754,13 @@
         <v>32</v>
       </c>
       <c r="C339" s="10" t="s">
-        <v>357</v>
+        <v>421</v>
       </c>
       <c r="D339" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E339" s="10" t="s">
-        <v>365</v>
+        <v>429</v>
       </c>
       <c r="F339" s="10" t="s">
         <v>3</v>
@@ -14701,13 +14788,13 @@
         <v>32</v>
       </c>
       <c r="C340" s="10" t="s">
-        <v>357</v>
+        <v>421</v>
       </c>
       <c r="D340" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E340" s="10" t="s">
-        <v>366</v>
+        <v>430</v>
       </c>
       <c r="F340" s="10" t="s">
         <v>3</v>
@@ -14735,13 +14822,13 @@
         <v>32</v>
       </c>
       <c r="C341" s="10" t="s">
-        <v>357</v>
+        <v>421</v>
       </c>
       <c r="D341" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E341" s="10" t="s">
-        <v>367</v>
+        <v>431</v>
       </c>
       <c r="F341" s="10" t="s">
         <v>3</v>
@@ -14769,13 +14856,13 @@
         <v>32</v>
       </c>
       <c r="C342" s="10" t="s">
-        <v>357</v>
+        <v>421</v>
       </c>
       <c r="D342" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E342" s="10" t="s">
-        <v>368</v>
+        <v>432</v>
       </c>
       <c r="F342" s="10" t="s">
         <v>3</v>
@@ -14803,13 +14890,13 @@
         <v>32</v>
       </c>
       <c r="C343" s="10" t="s">
-        <v>357</v>
+        <v>421</v>
       </c>
       <c r="D343" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E343" s="10" t="s">
-        <v>369</v>
+        <v>433</v>
       </c>
       <c r="F343" s="10" t="s">
         <v>3</v>
@@ -14837,13 +14924,13 @@
         <v>32</v>
       </c>
       <c r="C344" s="10" t="s">
-        <v>357</v>
+        <v>421</v>
       </c>
       <c r="D344" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E344" s="10" t="s">
-        <v>370</v>
+        <v>434</v>
       </c>
       <c r="F344" s="10" t="s">
         <v>3</v>
@@ -14871,13 +14958,13 @@
         <v>32</v>
       </c>
       <c r="C345" s="10" t="s">
-        <v>357</v>
+        <v>421</v>
       </c>
       <c r="D345" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E345" s="10" t="s">
-        <v>371</v>
+        <v>435</v>
       </c>
       <c r="F345" s="10" t="s">
         <v>3</v>
@@ -14905,13 +14992,13 @@
         <v>32</v>
       </c>
       <c r="C346" s="10" t="s">
-        <v>372</v>
+        <v>436</v>
       </c>
       <c r="D346" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E346" s="10" t="s">
-        <v>373</v>
+        <v>437</v>
       </c>
       <c r="F346" s="10" t="s">
         <v>3</v>
@@ -14939,13 +15026,13 @@
         <v>32</v>
       </c>
       <c r="C347" s="10" t="s">
-        <v>372</v>
+        <v>436</v>
       </c>
       <c r="D347" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E347" s="10" t="s">
-        <v>374</v>
+        <v>438</v>
       </c>
       <c r="F347" s="10" t="s">
         <v>3</v>
@@ -14973,13 +15060,13 @@
         <v>32</v>
       </c>
       <c r="C348" s="10" t="s">
-        <v>372</v>
+        <v>436</v>
       </c>
       <c r="D348" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E348" s="10" t="s">
-        <v>375</v>
+        <v>439</v>
       </c>
       <c r="F348" s="10" t="s">
         <v>3</v>
@@ -15007,13 +15094,13 @@
         <v>32</v>
       </c>
       <c r="C349" s="10" t="s">
-        <v>372</v>
+        <v>436</v>
       </c>
       <c r="D349" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E349" s="10" t="s">
-        <v>376</v>
+        <v>440</v>
       </c>
       <c r="F349" s="10" t="s">
         <v>3</v>
@@ -15041,13 +15128,13 @@
         <v>32</v>
       </c>
       <c r="C350" s="10" t="s">
-        <v>372</v>
+        <v>436</v>
       </c>
       <c r="D350" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E350" s="10" t="s">
-        <v>377</v>
+        <v>441</v>
       </c>
       <c r="F350" s="10" t="s">
         <v>3</v>
@@ -15075,13 +15162,13 @@
         <v>32</v>
       </c>
       <c r="C351" s="10" t="s">
-        <v>372</v>
+        <v>436</v>
       </c>
       <c r="D351" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E351" s="10" t="s">
-        <v>378</v>
+        <v>442</v>
       </c>
       <c r="F351" s="10" t="s">
         <v>3</v>
@@ -15109,13 +15196,13 @@
         <v>32</v>
       </c>
       <c r="C352" s="10" t="s">
-        <v>372</v>
+        <v>436</v>
       </c>
       <c r="D352" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E352" s="10" t="s">
-        <v>379</v>
+        <v>443</v>
       </c>
       <c r="F352" s="10" t="s">
         <v>3</v>
@@ -15143,13 +15230,13 @@
         <v>32</v>
       </c>
       <c r="C353" s="10" t="s">
-        <v>372</v>
+        <v>436</v>
       </c>
       <c r="D353" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E353" s="10" t="s">
-        <v>380</v>
+        <v>444</v>
       </c>
       <c r="F353" s="10" t="s">
         <v>3</v>
@@ -15177,13 +15264,13 @@
         <v>32</v>
       </c>
       <c r="C354" s="10" t="s">
-        <v>372</v>
+        <v>436</v>
       </c>
       <c r="D354" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E354" s="10" t="s">
-        <v>381</v>
+        <v>445</v>
       </c>
       <c r="F354" s="10" t="s">
         <v>3</v>
@@ -15211,13 +15298,13 @@
         <v>32</v>
       </c>
       <c r="C355" s="10" t="s">
-        <v>372</v>
+        <v>436</v>
       </c>
       <c r="D355" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E355" s="10" t="s">
-        <v>382</v>
+        <v>446</v>
       </c>
       <c r="F355" s="10" t="s">
         <v>3</v>
@@ -15245,13 +15332,13 @@
         <v>32</v>
       </c>
       <c r="C356" s="10" t="s">
-        <v>372</v>
+        <v>436</v>
       </c>
       <c r="D356" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E356" s="10" t="s">
-        <v>383</v>
+        <v>447</v>
       </c>
       <c r="F356" s="10" t="s">
         <v>3</v>
@@ -15279,13 +15366,13 @@
         <v>32</v>
       </c>
       <c r="C357" s="10" t="s">
-        <v>384</v>
+        <v>448</v>
       </c>
       <c r="D357" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E357" s="10" t="s">
-        <v>385</v>
+        <v>449</v>
       </c>
       <c r="F357" s="10" t="s">
         <v>3</v>
@@ -15313,13 +15400,13 @@
         <v>32</v>
       </c>
       <c r="C358" s="10" t="s">
-        <v>384</v>
+        <v>448</v>
       </c>
       <c r="D358" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E358" s="10" t="s">
-        <v>386</v>
+        <v>450</v>
       </c>
       <c r="F358" s="10" t="s">
         <v>3</v>
@@ -15347,13 +15434,13 @@
         <v>32</v>
       </c>
       <c r="C359" s="10" t="s">
-        <v>384</v>
+        <v>448</v>
       </c>
       <c r="D359" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E359" s="10" t="s">
-        <v>387</v>
+        <v>451</v>
       </c>
       <c r="F359" s="10" t="s">
         <v>3</v>
@@ -15381,13 +15468,13 @@
         <v>32</v>
       </c>
       <c r="C360" s="10" t="s">
-        <v>384</v>
+        <v>448</v>
       </c>
       <c r="D360" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E360" s="10" t="s">
-        <v>388</v>
+        <v>452</v>
       </c>
       <c r="F360" s="10" t="s">
         <v>3</v>
@@ -15415,13 +15502,13 @@
         <v>32</v>
       </c>
       <c r="C361" s="10" t="s">
-        <v>384</v>
+        <v>448</v>
       </c>
       <c r="D361" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E361" s="10" t="s">
-        <v>389</v>
+        <v>453</v>
       </c>
       <c r="F361" s="10" t="s">
         <v>3</v>
@@ -15449,13 +15536,13 @@
         <v>32</v>
       </c>
       <c r="C362" s="10" t="s">
-        <v>384</v>
+        <v>448</v>
       </c>
       <c r="D362" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E362" s="10" t="s">
-        <v>390</v>
+        <v>454</v>
       </c>
       <c r="F362" s="10" t="s">
         <v>3</v>
@@ -15483,13 +15570,13 @@
         <v>32</v>
       </c>
       <c r="C363" s="10" t="s">
-        <v>384</v>
+        <v>448</v>
       </c>
       <c r="D363" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E363" s="10" t="s">
-        <v>391</v>
+        <v>455</v>
       </c>
       <c r="F363" s="10" t="s">
         <v>3</v>
@@ -15517,13 +15604,13 @@
         <v>32</v>
       </c>
       <c r="C364" s="10" t="s">
-        <v>384</v>
+        <v>448</v>
       </c>
       <c r="D364" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E364" s="10" t="s">
-        <v>392</v>
+        <v>456</v>
       </c>
       <c r="F364" s="10" t="s">
         <v>3</v>
@@ -15551,13 +15638,13 @@
         <v>32</v>
       </c>
       <c r="C365" s="10" t="s">
-        <v>384</v>
+        <v>448</v>
       </c>
       <c r="D365" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E365" s="10" t="s">
-        <v>393</v>
+        <v>457</v>
       </c>
       <c r="F365" s="10" t="s">
         <v>3</v>
@@ -15585,13 +15672,13 @@
         <v>32</v>
       </c>
       <c r="C366" s="10" t="s">
-        <v>394</v>
+        <v>458</v>
       </c>
       <c r="D366" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E366" s="10" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="F366" s="10" t="s">
         <v>3</v>
@@ -15619,13 +15706,13 @@
         <v>32</v>
       </c>
       <c r="C367" s="10" t="s">
-        <v>394</v>
+        <v>458</v>
       </c>
       <c r="D367" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E367" s="10" t="s">
-        <v>396</v>
+        <v>460</v>
       </c>
       <c r="F367" s="10" t="s">
         <v>3</v>
@@ -15653,13 +15740,13 @@
         <v>32</v>
       </c>
       <c r="C368" s="10" t="s">
-        <v>394</v>
+        <v>458</v>
       </c>
       <c r="D368" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E368" s="10" t="s">
-        <v>397</v>
+        <v>461</v>
       </c>
       <c r="F368" s="10" t="s">
         <v>3</v>
@@ -15687,13 +15774,13 @@
         <v>32</v>
       </c>
       <c r="C369" s="10" t="s">
-        <v>394</v>
+        <v>458</v>
       </c>
       <c r="D369" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E369" s="10" t="s">
-        <v>398</v>
+        <v>462</v>
       </c>
       <c r="F369" s="10" t="s">
         <v>3</v>
@@ -15721,13 +15808,13 @@
         <v>32</v>
       </c>
       <c r="C370" s="10" t="s">
-        <v>394</v>
+        <v>458</v>
       </c>
       <c r="D370" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E370" s="10" t="s">
-        <v>399</v>
+        <v>463</v>
       </c>
       <c r="F370" s="10" t="s">
         <v>3</v>
@@ -15755,13 +15842,13 @@
         <v>32</v>
       </c>
       <c r="C371" s="10" t="s">
-        <v>394</v>
+        <v>458</v>
       </c>
       <c r="D371" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E371" s="10" t="s">
-        <v>400</v>
+        <v>464</v>
       </c>
       <c r="F371" s="10" t="s">
         <v>3</v>
@@ -15789,13 +15876,13 @@
         <v>32</v>
       </c>
       <c r="C372" s="10" t="s">
-        <v>394</v>
+        <v>458</v>
       </c>
       <c r="D372" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E372" s="10" t="s">
-        <v>401</v>
+        <v>465</v>
       </c>
       <c r="F372" s="10" t="s">
         <v>3</v>
@@ -15823,13 +15910,13 @@
         <v>32</v>
       </c>
       <c r="C373" s="10" t="s">
-        <v>394</v>
+        <v>458</v>
       </c>
       <c r="D373" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E373" s="10" t="s">
-        <v>402</v>
+        <v>466</v>
       </c>
       <c r="F373" s="10" t="s">
         <v>3</v>
@@ -15857,13 +15944,13 @@
         <v>32</v>
       </c>
       <c r="C374" s="10" t="s">
-        <v>394</v>
+        <v>458</v>
       </c>
       <c r="D374" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E374" s="10" t="s">
-        <v>403</v>
+        <v>467</v>
       </c>
       <c r="F374" s="10" t="s">
         <v>3</v>
@@ -15891,13 +15978,13 @@
         <v>32</v>
       </c>
       <c r="C375" s="10" t="s">
-        <v>394</v>
+        <v>458</v>
       </c>
       <c r="D375" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E375" s="10" t="s">
-        <v>404</v>
+        <v>468</v>
       </c>
       <c r="F375" s="10" t="s">
         <v>3</v>
@@ -15925,13 +16012,13 @@
         <v>32</v>
       </c>
       <c r="C376" s="10" t="s">
-        <v>394</v>
+        <v>458</v>
       </c>
       <c r="D376" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E376" s="10" t="s">
-        <v>405</v>
+        <v>469</v>
       </c>
       <c r="F376" s="10" t="s">
         <v>3</v>
@@ -15959,13 +16046,13 @@
         <v>32</v>
       </c>
       <c r="C377" s="10" t="s">
-        <v>394</v>
+        <v>458</v>
       </c>
       <c r="D377" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E377" s="10" t="s">
-        <v>406</v>
+        <v>470</v>
       </c>
       <c r="F377" s="10" t="s">
         <v>3</v>
@@ -15993,13 +16080,13 @@
         <v>32</v>
       </c>
       <c r="C378" s="10" t="s">
-        <v>407</v>
+        <v>471</v>
       </c>
       <c r="D378" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E378" s="10" t="s">
-        <v>408</v>
+        <v>472</v>
       </c>
       <c r="F378" s="10" t="s">
         <v>3</v>
@@ -16027,13 +16114,13 @@
         <v>32</v>
       </c>
       <c r="C379" s="10" t="s">
-        <v>407</v>
+        <v>471</v>
       </c>
       <c r="D379" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E379" s="10" t="s">
-        <v>409</v>
+        <v>473</v>
       </c>
       <c r="F379" s="10" t="s">
         <v>3</v>
@@ -16061,13 +16148,13 @@
         <v>32</v>
       </c>
       <c r="C380" s="10" t="s">
-        <v>407</v>
+        <v>471</v>
       </c>
       <c r="D380" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E380" s="10" t="s">
-        <v>410</v>
+        <v>474</v>
       </c>
       <c r="F380" s="10" t="s">
         <v>3</v>
@@ -16095,13 +16182,13 @@
         <v>32</v>
       </c>
       <c r="C381" s="10" t="s">
-        <v>407</v>
+        <v>471</v>
       </c>
       <c r="D381" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E381" s="10" t="s">
-        <v>411</v>
+        <v>475</v>
       </c>
       <c r="F381" s="10" t="s">
         <v>3</v>
@@ -16129,13 +16216,13 @@
         <v>32</v>
       </c>
       <c r="C382" s="10" t="s">
-        <v>407</v>
+        <v>471</v>
       </c>
       <c r="D382" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E382" s="10" t="s">
-        <v>412</v>
+        <v>476</v>
       </c>
       <c r="F382" s="10" t="s">
         <v>3</v>
@@ -16163,13 +16250,13 @@
         <v>32</v>
       </c>
       <c r="C383" s="10" t="s">
-        <v>407</v>
+        <v>471</v>
       </c>
       <c r="D383" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E383" s="10" t="s">
-        <v>413</v>
+        <v>477</v>
       </c>
       <c r="F383" s="10" t="s">
         <v>3</v>
@@ -16197,13 +16284,13 @@
         <v>32</v>
       </c>
       <c r="C384" s="10" t="s">
-        <v>407</v>
+        <v>471</v>
       </c>
       <c r="D384" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E384" s="10" t="s">
-        <v>414</v>
+        <v>478</v>
       </c>
       <c r="F384" s="10" t="s">
         <v>3</v>
@@ -16231,13 +16318,13 @@
         <v>32</v>
       </c>
       <c r="C385" s="10" t="s">
-        <v>407</v>
+        <v>471</v>
       </c>
       <c r="D385" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E385" s="10" t="s">
-        <v>415</v>
+        <v>479</v>
       </c>
       <c r="F385" s="10" t="s">
         <v>3</v>
@@ -16265,13 +16352,13 @@
         <v>32</v>
       </c>
       <c r="C386" s="10" t="s">
-        <v>407</v>
+        <v>471</v>
       </c>
       <c r="D386" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E386" s="10" t="s">
-        <v>416</v>
+        <v>480</v>
       </c>
       <c r="F386" s="10" t="s">
         <v>3</v>
@@ -16299,13 +16386,13 @@
         <v>32</v>
       </c>
       <c r="C387" s="10" t="s">
-        <v>407</v>
+        <v>471</v>
       </c>
       <c r="D387" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E387" s="10" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="F387" s="10" t="s">
         <v>3</v>
@@ -16333,13 +16420,13 @@
         <v>32</v>
       </c>
       <c r="C388" s="10" t="s">
-        <v>407</v>
+        <v>471</v>
       </c>
       <c r="D388" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E388" s="10" t="s">
-        <v>417</v>
+        <v>481</v>
       </c>
       <c r="F388" s="10" t="s">
         <v>3</v>
@@ -16367,13 +16454,13 @@
         <v>32</v>
       </c>
       <c r="C389" s="10" t="s">
-        <v>407</v>
+        <v>471</v>
       </c>
       <c r="D389" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E389" s="10" t="s">
-        <v>418</v>
+        <v>482</v>
       </c>
       <c r="F389" s="10" t="s">
         <v>3</v>
@@ -16401,13 +16488,13 @@
         <v>32</v>
       </c>
       <c r="C390" s="10" t="s">
-        <v>407</v>
+        <v>471</v>
       </c>
       <c r="D390" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E390" s="10" t="s">
-        <v>419</v>
+        <v>483</v>
       </c>
       <c r="F390" s="10" t="s">
         <v>3</v>
@@ -16435,13 +16522,13 @@
         <v>32</v>
       </c>
       <c r="C391" s="10" t="s">
-        <v>407</v>
+        <v>471</v>
       </c>
       <c r="D391" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E391" s="10" t="s">
-        <v>420</v>
+        <v>484</v>
       </c>
       <c r="F391" s="10" t="s">
         <v>3</v>
@@ -16469,13 +16556,13 @@
         <v>32</v>
       </c>
       <c r="C392" s="10" t="s">
-        <v>407</v>
+        <v>471</v>
       </c>
       <c r="D392" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E392" s="10" t="s">
-        <v>421</v>
+        <v>485</v>
       </c>
       <c r="F392" s="10" t="s">
         <v>3</v>
@@ -16503,13 +16590,13 @@
         <v>32</v>
       </c>
       <c r="C393" s="10" t="s">
-        <v>407</v>
+        <v>471</v>
       </c>
       <c r="D393" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E393" s="10" t="s">
-        <v>422</v>
+        <v>486</v>
       </c>
       <c r="F393" s="10" t="s">
         <v>3</v>
@@ -16537,13 +16624,13 @@
         <v>32</v>
       </c>
       <c r="C394" s="10" t="s">
-        <v>423</v>
+        <v>487</v>
       </c>
       <c r="D394" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E394" s="10" t="s">
-        <v>424</v>
+        <v>488</v>
       </c>
       <c r="F394" s="10" t="s">
         <v>3</v>
@@ -16571,13 +16658,13 @@
         <v>32</v>
       </c>
       <c r="C395" s="10" t="s">
-        <v>423</v>
+        <v>487</v>
       </c>
       <c r="D395" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E395" s="10" t="s">
-        <v>425</v>
+        <v>489</v>
       </c>
       <c r="F395" s="10" t="s">
         <v>3</v>
@@ -16605,13 +16692,13 @@
         <v>32</v>
       </c>
       <c r="C396" s="10" t="s">
-        <v>423</v>
+        <v>487</v>
       </c>
       <c r="D396" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E396" s="10" t="s">
-        <v>426</v>
+        <v>490</v>
       </c>
       <c r="F396" s="10" t="s">
         <v>3</v>
@@ -16639,13 +16726,13 @@
         <v>32</v>
       </c>
       <c r="C397" s="10" t="s">
-        <v>423</v>
+        <v>487</v>
       </c>
       <c r="D397" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E397" s="10" t="s">
-        <v>427</v>
+        <v>491</v>
       </c>
       <c r="F397" s="10" t="s">
         <v>3</v>
@@ -16673,13 +16760,13 @@
         <v>32</v>
       </c>
       <c r="C398" s="10" t="s">
-        <v>423</v>
+        <v>487</v>
       </c>
       <c r="D398" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E398" s="10" t="s">
-        <v>428</v>
+        <v>492</v>
       </c>
       <c r="F398" s="10" t="s">
         <v>3</v>
@@ -16707,13 +16794,13 @@
         <v>32</v>
       </c>
       <c r="C399" s="10" t="s">
-        <v>423</v>
+        <v>487</v>
       </c>
       <c r="D399" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E399" s="10" t="s">
-        <v>429</v>
+        <v>493</v>
       </c>
       <c r="F399" s="10" t="s">
         <v>3</v>
@@ -16741,13 +16828,13 @@
         <v>32</v>
       </c>
       <c r="C400" s="10" t="s">
-        <v>423</v>
+        <v>487</v>
       </c>
       <c r="D400" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E400" s="10" t="s">
-        <v>430</v>
+        <v>494</v>
       </c>
       <c r="F400" s="10" t="s">
         <v>3</v>
@@ -16775,13 +16862,13 @@
         <v>32</v>
       </c>
       <c r="C401" s="10" t="s">
-        <v>423</v>
+        <v>487</v>
       </c>
       <c r="D401" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E401" s="10" t="s">
-        <v>431</v>
+        <v>495</v>
       </c>
       <c r="F401" s="10" t="s">
         <v>3</v>
@@ -16809,13 +16896,13 @@
         <v>33</v>
       </c>
       <c r="C402" s="10" t="s">
-        <v>432</v>
+        <v>496</v>
       </c>
       <c r="D402" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E402" s="10" t="s">
-        <v>433</v>
+        <v>497</v>
       </c>
       <c r="F402" s="10" t="s">
         <v>3</v>
@@ -16843,13 +16930,13 @@
         <v>33</v>
       </c>
       <c r="C403" s="10" t="s">
-        <v>432</v>
+        <v>496</v>
       </c>
       <c r="D403" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E403" s="10" t="s">
-        <v>434</v>
+        <v>498</v>
       </c>
       <c r="F403" s="10" t="s">
         <v>3</v>
@@ -16877,13 +16964,13 @@
         <v>33</v>
       </c>
       <c r="C404" s="10" t="s">
-        <v>432</v>
+        <v>496</v>
       </c>
       <c r="D404" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E404" s="10" t="s">
-        <v>435</v>
+        <v>499</v>
       </c>
       <c r="F404" s="10" t="s">
         <v>3</v>
@@ -16911,13 +16998,13 @@
         <v>33</v>
       </c>
       <c r="C405" s="10" t="s">
-        <v>432</v>
+        <v>496</v>
       </c>
       <c r="D405" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E405" s="10" t="s">
-        <v>436</v>
+        <v>500</v>
       </c>
       <c r="F405" s="10" t="s">
         <v>3</v>
@@ -16945,13 +17032,13 @@
         <v>33</v>
       </c>
       <c r="C406" s="10" t="s">
-        <v>432</v>
+        <v>496</v>
       </c>
       <c r="D406" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E406" s="10" t="s">
-        <v>437</v>
+        <v>501</v>
       </c>
       <c r="F406" s="10" t="s">
         <v>3</v>
@@ -16979,13 +17066,13 @@
         <v>33</v>
       </c>
       <c r="C407" s="10" t="s">
-        <v>432</v>
+        <v>496</v>
       </c>
       <c r="D407" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E407" s="10" t="s">
-        <v>438</v>
+        <v>502</v>
       </c>
       <c r="F407" s="10" t="s">
         <v>3</v>
@@ -17013,13 +17100,13 @@
         <v>33</v>
       </c>
       <c r="C408" s="10" t="s">
-        <v>432</v>
+        <v>496</v>
       </c>
       <c r="D408" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E408" s="10" t="s">
-        <v>439</v>
+        <v>503</v>
       </c>
       <c r="F408" s="10" t="s">
         <v>3</v>
@@ -17047,13 +17134,13 @@
         <v>33</v>
       </c>
       <c r="C409" s="10" t="s">
-        <v>432</v>
+        <v>496</v>
       </c>
       <c r="D409" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E409" s="10" t="s">
-        <v>440</v>
+        <v>504</v>
       </c>
       <c r="F409" s="10" t="s">
         <v>3</v>
@@ -17081,13 +17168,13 @@
         <v>33</v>
       </c>
       <c r="C410" s="10" t="s">
-        <v>432</v>
+        <v>496</v>
       </c>
       <c r="D410" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E410" s="10" t="s">
-        <v>380</v>
+        <v>444</v>
       </c>
       <c r="F410" s="10" t="s">
         <v>3</v>
@@ -17115,13 +17202,13 @@
         <v>33</v>
       </c>
       <c r="C411" s="10" t="s">
-        <v>432</v>
+        <v>496</v>
       </c>
       <c r="D411" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E411" s="10" t="s">
-        <v>441</v>
+        <v>505</v>
       </c>
       <c r="F411" s="10" t="s">
         <v>3</v>
@@ -17149,13 +17236,13 @@
         <v>33</v>
       </c>
       <c r="C412" s="10" t="s">
-        <v>432</v>
+        <v>496</v>
       </c>
       <c r="D412" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E412" s="10" t="s">
-        <v>442</v>
+        <v>506</v>
       </c>
       <c r="F412" s="10" t="s">
         <v>3</v>
@@ -17183,13 +17270,13 @@
         <v>33</v>
       </c>
       <c r="C413" s="10" t="s">
-        <v>432</v>
+        <v>496</v>
       </c>
       <c r="D413" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E413" s="10" t="s">
-        <v>443</v>
+        <v>507</v>
       </c>
       <c r="F413" s="10" t="s">
         <v>3</v>
@@ -17217,13 +17304,13 @@
         <v>33</v>
       </c>
       <c r="C414" s="10" t="s">
-        <v>432</v>
+        <v>496</v>
       </c>
       <c r="D414" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E414" s="10" t="s">
-        <v>444</v>
+        <v>508</v>
       </c>
       <c r="F414" s="10" t="s">
         <v>3</v>
@@ -17251,13 +17338,13 @@
         <v>33</v>
       </c>
       <c r="C415" s="10" t="s">
-        <v>432</v>
+        <v>496</v>
       </c>
       <c r="D415" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E415" s="10" t="s">
-        <v>445</v>
+        <v>509</v>
       </c>
       <c r="F415" s="10" t="s">
         <v>3</v>
@@ -17285,13 +17372,13 @@
         <v>33</v>
       </c>
       <c r="C416" s="10" t="s">
-        <v>446</v>
+        <v>510</v>
       </c>
       <c r="D416" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E416" s="10" t="s">
-        <v>447</v>
+        <v>511</v>
       </c>
       <c r="F416" s="10" t="s">
         <v>3</v>
@@ -17319,13 +17406,13 @@
         <v>33</v>
       </c>
       <c r="C417" s="10" t="s">
-        <v>446</v>
+        <v>510</v>
       </c>
       <c r="D417" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E417" s="10" t="s">
-        <v>448</v>
+        <v>512</v>
       </c>
       <c r="F417" s="10" t="s">
         <v>3</v>
@@ -17353,13 +17440,13 @@
         <v>33</v>
       </c>
       <c r="C418" s="10" t="s">
-        <v>446</v>
+        <v>510</v>
       </c>
       <c r="D418" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E418" s="10" t="s">
-        <v>449</v>
+        <v>513</v>
       </c>
       <c r="F418" s="10" t="s">
         <v>3</v>
@@ -17387,13 +17474,13 @@
         <v>33</v>
       </c>
       <c r="C419" s="10" t="s">
-        <v>446</v>
+        <v>510</v>
       </c>
       <c r="D419" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E419" s="10" t="s">
-        <v>450</v>
+        <v>514</v>
       </c>
       <c r="F419" s="10" t="s">
         <v>3</v>
@@ -17421,13 +17508,13 @@
         <v>33</v>
       </c>
       <c r="C420" s="10" t="s">
-        <v>446</v>
+        <v>510</v>
       </c>
       <c r="D420" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E420" s="10" t="s">
-        <v>451</v>
+        <v>515</v>
       </c>
       <c r="F420" s="10" t="s">
         <v>3</v>
@@ -17455,13 +17542,13 @@
         <v>33</v>
       </c>
       <c r="C421" s="10" t="s">
-        <v>446</v>
+        <v>510</v>
       </c>
       <c r="D421" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E421" s="10" t="s">
-        <v>452</v>
+        <v>516</v>
       </c>
       <c r="F421" s="10" t="s">
         <v>3</v>
@@ -17489,13 +17576,13 @@
         <v>33</v>
       </c>
       <c r="C422" s="10" t="s">
-        <v>446</v>
+        <v>510</v>
       </c>
       <c r="D422" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E422" s="10" t="s">
-        <v>453</v>
+        <v>517</v>
       </c>
       <c r="F422" s="10" t="s">
         <v>3</v>
@@ -17523,13 +17610,13 @@
         <v>33</v>
       </c>
       <c r="C423" s="10" t="s">
-        <v>446</v>
+        <v>510</v>
       </c>
       <c r="D423" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E423" s="10" t="s">
-        <v>454</v>
+        <v>518</v>
       </c>
       <c r="F423" s="10" t="s">
         <v>3</v>
@@ -17557,13 +17644,13 @@
         <v>33</v>
       </c>
       <c r="C424" s="10" t="s">
-        <v>446</v>
+        <v>510</v>
       </c>
       <c r="D424" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E424" s="10" t="s">
-        <v>455</v>
+        <v>519</v>
       </c>
       <c r="F424" s="10" t="s">
         <v>3</v>
@@ -17591,13 +17678,13 @@
         <v>33</v>
       </c>
       <c r="C425" s="10" t="s">
-        <v>446</v>
+        <v>510</v>
       </c>
       <c r="D425" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E425" s="10" t="s">
-        <v>456</v>
+        <v>520</v>
       </c>
       <c r="F425" s="10" t="s">
         <v>3</v>
@@ -17625,13 +17712,13 @@
         <v>33</v>
       </c>
       <c r="C426" s="10" t="s">
-        <v>446</v>
+        <v>510</v>
       </c>
       <c r="D426" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E426" s="10" t="s">
-        <v>457</v>
+        <v>521</v>
       </c>
       <c r="F426" s="10" t="s">
         <v>3</v>
@@ -17659,13 +17746,13 @@
         <v>33</v>
       </c>
       <c r="C427" s="10" t="s">
-        <v>446</v>
+        <v>510</v>
       </c>
       <c r="D427" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E427" s="10" t="s">
-        <v>458</v>
+        <v>522</v>
       </c>
       <c r="F427" s="10" t="s">
         <v>3</v>
@@ -17693,13 +17780,13 @@
         <v>33</v>
       </c>
       <c r="C428" s="10" t="s">
-        <v>446</v>
+        <v>510</v>
       </c>
       <c r="D428" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E428" s="10" t="s">
-        <v>459</v>
+        <v>523</v>
       </c>
       <c r="F428" s="10" t="s">
         <v>3</v>
@@ -17727,13 +17814,13 @@
         <v>33</v>
       </c>
       <c r="C429" s="10" t="s">
-        <v>446</v>
+        <v>510</v>
       </c>
       <c r="D429" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E429" s="10" t="s">
-        <v>460</v>
+        <v>524</v>
       </c>
       <c r="F429" s="10" t="s">
         <v>3</v>
@@ -17761,13 +17848,13 @@
         <v>33</v>
       </c>
       <c r="C430" s="10" t="s">
-        <v>446</v>
+        <v>510</v>
       </c>
       <c r="D430" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E430" s="10" t="s">
-        <v>461</v>
+        <v>525</v>
       </c>
       <c r="F430" s="10" t="s">
         <v>3</v>
@@ -17795,13 +17882,13 @@
         <v>33</v>
       </c>
       <c r="C431" s="10" t="s">
-        <v>462</v>
+        <v>526</v>
       </c>
       <c r="D431" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E431" s="10" t="s">
-        <v>463</v>
+        <v>527</v>
       </c>
       <c r="F431" s="10" t="s">
         <v>3</v>
@@ -17829,13 +17916,13 @@
         <v>33</v>
       </c>
       <c r="C432" s="10" t="s">
-        <v>462</v>
+        <v>526</v>
       </c>
       <c r="D432" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E432" s="10" t="s">
-        <v>464</v>
+        <v>528</v>
       </c>
       <c r="F432" s="10" t="s">
         <v>3</v>
@@ -17863,13 +17950,13 @@
         <v>33</v>
       </c>
       <c r="C433" s="10" t="s">
-        <v>462</v>
+        <v>526</v>
       </c>
       <c r="D433" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E433" s="10" t="s">
-        <v>465</v>
+        <v>529</v>
       </c>
       <c r="F433" s="10" t="s">
         <v>3</v>
@@ -17897,13 +17984,13 @@
         <v>33</v>
       </c>
       <c r="C434" s="10" t="s">
-        <v>462</v>
+        <v>526</v>
       </c>
       <c r="D434" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E434" s="10" t="s">
-        <v>466</v>
+        <v>530</v>
       </c>
       <c r="F434" s="10" t="s">
         <v>3</v>
@@ -17931,13 +18018,13 @@
         <v>33</v>
       </c>
       <c r="C435" s="10" t="s">
-        <v>462</v>
+        <v>526</v>
       </c>
       <c r="D435" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E435" s="10" t="s">
-        <v>467</v>
+        <v>531</v>
       </c>
       <c r="F435" s="10" t="s">
         <v>3</v>
@@ -17965,13 +18052,13 @@
         <v>33</v>
       </c>
       <c r="C436" s="10" t="s">
-        <v>462</v>
+        <v>526</v>
       </c>
       <c r="D436" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E436" s="10" t="s">
-        <v>468</v>
+        <v>532</v>
       </c>
       <c r="F436" s="10" t="s">
         <v>3</v>
@@ -17999,13 +18086,13 @@
         <v>33</v>
       </c>
       <c r="C437" s="10" t="s">
-        <v>462</v>
+        <v>526</v>
       </c>
       <c r="D437" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E437" s="10" t="s">
-        <v>469</v>
+        <v>533</v>
       </c>
       <c r="F437" s="10" t="s">
         <v>3</v>
@@ -18033,13 +18120,13 @@
         <v>33</v>
       </c>
       <c r="C438" s="10" t="s">
-        <v>462</v>
+        <v>526</v>
       </c>
       <c r="D438" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E438" s="10" t="s">
-        <v>470</v>
+        <v>534</v>
       </c>
       <c r="F438" s="10" t="s">
         <v>3</v>
@@ -18067,13 +18154,13 @@
         <v>33</v>
       </c>
       <c r="C439" s="10" t="s">
-        <v>462</v>
+        <v>526</v>
       </c>
       <c r="D439" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E439" s="10" t="s">
-        <v>471</v>
+        <v>535</v>
       </c>
       <c r="F439" s="10" t="s">
         <v>3</v>
@@ -18101,13 +18188,13 @@
         <v>33</v>
       </c>
       <c r="C440" s="10" t="s">
-        <v>462</v>
+        <v>526</v>
       </c>
       <c r="D440" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E440" s="10" t="s">
-        <v>472</v>
+        <v>536</v>
       </c>
       <c r="F440" s="10" t="s">
         <v>3</v>
@@ -18135,13 +18222,13 @@
         <v>33</v>
       </c>
       <c r="C441" s="10" t="s">
-        <v>462</v>
+        <v>526</v>
       </c>
       <c r="D441" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E441" s="10" t="s">
-        <v>473</v>
+        <v>537</v>
       </c>
       <c r="F441" s="10" t="s">
         <v>3</v>
@@ -18169,13 +18256,13 @@
         <v>33</v>
       </c>
       <c r="C442" s="10" t="s">
-        <v>462</v>
+        <v>526</v>
       </c>
       <c r="D442" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E442" s="10" t="s">
-        <v>353</v>
+        <v>417</v>
       </c>
       <c r="F442" s="10" t="s">
         <v>3</v>
@@ -18203,13 +18290,13 @@
         <v>33</v>
       </c>
       <c r="C443" s="10" t="s">
-        <v>462</v>
+        <v>526</v>
       </c>
       <c r="D443" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E443" s="10" t="s">
-        <v>474</v>
+        <v>538</v>
       </c>
       <c r="F443" s="10" t="s">
         <v>3</v>
@@ -18237,13 +18324,13 @@
         <v>33</v>
       </c>
       <c r="C444" s="10" t="s">
-        <v>462</v>
+        <v>526</v>
       </c>
       <c r="D444" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E444" s="10" t="s">
-        <v>475</v>
+        <v>539</v>
       </c>
       <c r="F444" s="10" t="s">
         <v>3</v>
@@ -18271,13 +18358,13 @@
         <v>33</v>
       </c>
       <c r="C445" s="10" t="s">
-        <v>476</v>
+        <v>540</v>
       </c>
       <c r="D445" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E445" s="10" t="s">
-        <v>477</v>
+        <v>541</v>
       </c>
       <c r="F445" s="10" t="s">
         <v>3</v>
@@ -18305,13 +18392,13 @@
         <v>33</v>
       </c>
       <c r="C446" s="10" t="s">
-        <v>476</v>
+        <v>540</v>
       </c>
       <c r="D446" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E446" s="10" t="s">
-        <v>478</v>
+        <v>542</v>
       </c>
       <c r="F446" s="10" t="s">
         <v>3</v>
@@ -18339,13 +18426,13 @@
         <v>33</v>
       </c>
       <c r="C447" s="10" t="s">
-        <v>476</v>
+        <v>540</v>
       </c>
       <c r="D447" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E447" s="10" t="s">
-        <v>479</v>
+        <v>543</v>
       </c>
       <c r="F447" s="10" t="s">
         <v>3</v>
@@ -18373,13 +18460,13 @@
         <v>33</v>
       </c>
       <c r="C448" s="10" t="s">
-        <v>476</v>
+        <v>540</v>
       </c>
       <c r="D448" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E448" s="10" t="s">
-        <v>480</v>
+        <v>544</v>
       </c>
       <c r="F448" s="10" t="s">
         <v>3</v>
@@ -18407,13 +18494,13 @@
         <v>33</v>
       </c>
       <c r="C449" s="10" t="s">
-        <v>476</v>
+        <v>540</v>
       </c>
       <c r="D449" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E449" s="10" t="s">
-        <v>481</v>
+        <v>545</v>
       </c>
       <c r="F449" s="10" t="s">
         <v>3</v>
@@ -18441,13 +18528,13 @@
         <v>33</v>
       </c>
       <c r="C450" s="10" t="s">
-        <v>476</v>
+        <v>540</v>
       </c>
       <c r="D450" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E450" s="10" t="s">
-        <v>482</v>
+        <v>546</v>
       </c>
       <c r="F450" s="10" t="s">
         <v>3</v>
@@ -18475,13 +18562,13 @@
         <v>33</v>
       </c>
       <c r="C451" s="10" t="s">
-        <v>476</v>
+        <v>540</v>
       </c>
       <c r="D451" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E451" s="10" t="s">
-        <v>483</v>
+        <v>547</v>
       </c>
       <c r="F451" s="10" t="s">
         <v>3</v>
@@ -18509,13 +18596,13 @@
         <v>33</v>
       </c>
       <c r="C452" s="10" t="s">
-        <v>476</v>
+        <v>540</v>
       </c>
       <c r="D452" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E452" s="10" t="s">
-        <v>484</v>
+        <v>548</v>
       </c>
       <c r="F452" s="10" t="s">
         <v>3</v>
@@ -18543,13 +18630,13 @@
         <v>33</v>
       </c>
       <c r="C453" s="10" t="s">
-        <v>476</v>
+        <v>540</v>
       </c>
       <c r="D453" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E453" s="10" t="s">
-        <v>485</v>
+        <v>549</v>
       </c>
       <c r="F453" s="10" t="s">
         <v>3</v>
@@ -18577,13 +18664,13 @@
         <v>33</v>
       </c>
       <c r="C454" s="10" t="s">
-        <v>476</v>
+        <v>540</v>
       </c>
       <c r="D454" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E454" s="10" t="s">
-        <v>486</v>
+        <v>550</v>
       </c>
       <c r="F454" s="10" t="s">
         <v>3</v>
@@ -18611,13 +18698,13 @@
         <v>33</v>
       </c>
       <c r="C455" s="10" t="s">
-        <v>476</v>
+        <v>540</v>
       </c>
       <c r="D455" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E455" s="10" t="s">
-        <v>487</v>
+        <v>551</v>
       </c>
       <c r="F455" s="10" t="s">
         <v>3</v>
@@ -18645,13 +18732,13 @@
         <v>33</v>
       </c>
       <c r="C456" s="10" t="s">
-        <v>476</v>
+        <v>540</v>
       </c>
       <c r="D456" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E456" s="10" t="s">
-        <v>488</v>
+        <v>552</v>
       </c>
       <c r="F456" s="10" t="s">
         <v>3</v>
@@ -18679,13 +18766,13 @@
         <v>33</v>
       </c>
       <c r="C457" s="10" t="s">
-        <v>476</v>
+        <v>540</v>
       </c>
       <c r="D457" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E457" s="10" t="s">
-        <v>489</v>
+        <v>553</v>
       </c>
       <c r="F457" s="10" t="s">
         <v>3</v>
@@ -18713,13 +18800,13 @@
         <v>34</v>
       </c>
       <c r="C458" s="10" t="s">
-        <v>490</v>
+        <v>554</v>
       </c>
       <c r="D458" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E458" s="10" t="s">
-        <v>491</v>
+        <v>555</v>
       </c>
       <c r="F458" s="10" t="s">
         <v>3</v>
@@ -18747,13 +18834,13 @@
         <v>34</v>
       </c>
       <c r="C459" s="10" t="s">
-        <v>490</v>
+        <v>554</v>
       </c>
       <c r="D459" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E459" s="10" t="s">
-        <v>492</v>
+        <v>556</v>
       </c>
       <c r="F459" s="10" t="s">
         <v>3</v>
@@ -18781,13 +18868,13 @@
         <v>34</v>
       </c>
       <c r="C460" s="10" t="s">
-        <v>490</v>
+        <v>554</v>
       </c>
       <c r="D460" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E460" s="10" t="s">
-        <v>493</v>
+        <v>557</v>
       </c>
       <c r="F460" s="10" t="s">
         <v>3</v>
@@ -18815,13 +18902,13 @@
         <v>34</v>
       </c>
       <c r="C461" s="10" t="s">
-        <v>490</v>
+        <v>554</v>
       </c>
       <c r="D461" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E461" s="10" t="s">
-        <v>494</v>
+        <v>558</v>
       </c>
       <c r="F461" s="10" t="s">
         <v>3</v>
@@ -18849,13 +18936,13 @@
         <v>34</v>
       </c>
       <c r="C462" s="10" t="s">
-        <v>490</v>
+        <v>554</v>
       </c>
       <c r="D462" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E462" s="10" t="s">
-        <v>495</v>
+        <v>559</v>
       </c>
       <c r="F462" s="10" t="s">
         <v>3</v>
@@ -18883,13 +18970,13 @@
         <v>34</v>
       </c>
       <c r="C463" s="10" t="s">
-        <v>490</v>
+        <v>554</v>
       </c>
       <c r="D463" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E463" s="10" t="s">
-        <v>496</v>
+        <v>560</v>
       </c>
       <c r="F463" s="10" t="s">
         <v>3</v>
@@ -18917,13 +19004,13 @@
         <v>34</v>
       </c>
       <c r="C464" s="10" t="s">
-        <v>490</v>
+        <v>554</v>
       </c>
       <c r="D464" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E464" s="10" t="s">
-        <v>497</v>
+        <v>561</v>
       </c>
       <c r="F464" s="10" t="s">
         <v>3</v>
@@ -18951,13 +19038,13 @@
         <v>34</v>
       </c>
       <c r="C465" s="10" t="s">
-        <v>490</v>
+        <v>554</v>
       </c>
       <c r="D465" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E465" s="10" t="s">
-        <v>498</v>
+        <v>562</v>
       </c>
       <c r="F465" s="10" t="s">
         <v>3</v>
@@ -18985,13 +19072,13 @@
         <v>34</v>
       </c>
       <c r="C466" s="10" t="s">
-        <v>490</v>
+        <v>554</v>
       </c>
       <c r="D466" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E466" s="10" t="s">
-        <v>499</v>
+        <v>563</v>
       </c>
       <c r="F466" s="10" t="s">
         <v>3</v>
@@ -19019,13 +19106,13 @@
         <v>34</v>
       </c>
       <c r="C467" s="10" t="s">
-        <v>490</v>
+        <v>554</v>
       </c>
       <c r="D467" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E467" s="10" t="s">
-        <v>500</v>
+        <v>564</v>
       </c>
       <c r="F467" s="10" t="s">
         <v>3</v>
@@ -19053,13 +19140,13 @@
         <v>34</v>
       </c>
       <c r="C468" s="10" t="s">
-        <v>490</v>
+        <v>554</v>
       </c>
       <c r="D468" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E468" s="10" t="s">
-        <v>501</v>
+        <v>565</v>
       </c>
       <c r="F468" s="10" t="s">
         <v>3</v>
@@ -19087,13 +19174,13 @@
         <v>34</v>
       </c>
       <c r="C469" s="10" t="s">
-        <v>490</v>
+        <v>554</v>
       </c>
       <c r="D469" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E469" s="10" t="s">
-        <v>502</v>
+        <v>566</v>
       </c>
       <c r="F469" s="10" t="s">
         <v>3</v>
@@ -19121,13 +19208,13 @@
         <v>34</v>
       </c>
       <c r="C470" s="10" t="s">
-        <v>490</v>
+        <v>554</v>
       </c>
       <c r="D470" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E470" s="10" t="s">
-        <v>503</v>
+        <v>567</v>
       </c>
       <c r="F470" s="10" t="s">
         <v>3</v>
@@ -19155,13 +19242,13 @@
         <v>34</v>
       </c>
       <c r="C471" s="10" t="s">
-        <v>490</v>
+        <v>554</v>
       </c>
       <c r="D471" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E471" s="10" t="s">
-        <v>418</v>
+        <v>482</v>
       </c>
       <c r="F471" s="10" t="s">
         <v>3</v>
@@ -19189,13 +19276,13 @@
         <v>34</v>
       </c>
       <c r="C472" s="10" t="s">
-        <v>490</v>
+        <v>554</v>
       </c>
       <c r="D472" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E472" s="10" t="s">
-        <v>504</v>
+        <v>568</v>
       </c>
       <c r="F472" s="10" t="s">
         <v>3</v>
@@ -19223,13 +19310,13 @@
         <v>34</v>
       </c>
       <c r="C473" s="10" t="s">
-        <v>490</v>
+        <v>554</v>
       </c>
       <c r="D473" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E473" s="10" t="s">
-        <v>505</v>
+        <v>569</v>
       </c>
       <c r="F473" s="10" t="s">
         <v>3</v>
@@ -19257,13 +19344,13 @@
         <v>34</v>
       </c>
       <c r="C474" s="10" t="s">
-        <v>506</v>
+        <v>570</v>
       </c>
       <c r="D474" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E474" s="10" t="s">
-        <v>507</v>
+        <v>571</v>
       </c>
       <c r="F474" s="10" t="s">
         <v>3</v>
@@ -19291,13 +19378,13 @@
         <v>34</v>
       </c>
       <c r="C475" s="10" t="s">
-        <v>506</v>
+        <v>570</v>
       </c>
       <c r="D475" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E475" s="10" t="s">
-        <v>508</v>
+        <v>572</v>
       </c>
       <c r="F475" s="10" t="s">
         <v>3</v>
@@ -19325,13 +19412,13 @@
         <v>34</v>
       </c>
       <c r="C476" s="10" t="s">
-        <v>506</v>
+        <v>570</v>
       </c>
       <c r="D476" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E476" s="10" t="s">
-        <v>509</v>
+        <v>573</v>
       </c>
       <c r="F476" s="10" t="s">
         <v>3</v>
@@ -19359,13 +19446,13 @@
         <v>34</v>
       </c>
       <c r="C477" s="10" t="s">
-        <v>506</v>
+        <v>570</v>
       </c>
       <c r="D477" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E477" s="10" t="s">
-        <v>510</v>
+        <v>574</v>
       </c>
       <c r="F477" s="10" t="s">
         <v>3</v>
@@ -19393,13 +19480,13 @@
         <v>34</v>
       </c>
       <c r="C478" s="10" t="s">
-        <v>506</v>
+        <v>570</v>
       </c>
       <c r="D478" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E478" s="10" t="s">
-        <v>511</v>
+        <v>575</v>
       </c>
       <c r="F478" s="10" t="s">
         <v>3</v>
@@ -19427,13 +19514,13 @@
         <v>34</v>
       </c>
       <c r="C479" s="10" t="s">
-        <v>506</v>
+        <v>570</v>
       </c>
       <c r="D479" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E479" s="10" t="s">
-        <v>512</v>
+        <v>576</v>
       </c>
       <c r="F479" s="10" t="s">
         <v>3</v>
@@ -19461,13 +19548,13 @@
         <v>34</v>
       </c>
       <c r="C480" s="10" t="s">
-        <v>506</v>
+        <v>570</v>
       </c>
       <c r="D480" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E480" s="10" t="s">
-        <v>513</v>
+        <v>577</v>
       </c>
       <c r="F480" s="10" t="s">
         <v>3</v>
@@ -19495,13 +19582,13 @@
         <v>34</v>
       </c>
       <c r="C481" s="10" t="s">
-        <v>506</v>
+        <v>570</v>
       </c>
       <c r="D481" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E481" s="10" t="s">
-        <v>514</v>
+        <v>578</v>
       </c>
       <c r="F481" s="10" t="s">
         <v>3</v>
@@ -19529,13 +19616,13 @@
         <v>34</v>
       </c>
       <c r="C482" s="10" t="s">
-        <v>506</v>
+        <v>570</v>
       </c>
       <c r="D482" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E482" s="10" t="s">
-        <v>515</v>
+        <v>579</v>
       </c>
       <c r="F482" s="10" t="s">
         <v>3</v>
@@ -19563,13 +19650,13 @@
         <v>34</v>
       </c>
       <c r="C483" s="10" t="s">
-        <v>506</v>
+        <v>570</v>
       </c>
       <c r="D483" s="10" t="s">
         <v>62</v>
       </c>
       <c r="E483" s="10" t="s">
-        <v>516</v>
+        <v>580</v>
       </c>
       <c r="F483" s="10" t="s">
         <v>3</v>
@@ -19597,13 +19684,13 @@
         <v>34</v>
       </c>
       <c r="C484" s="10" t="s">
-        <v>506</v>
+        <v>570</v>
       </c>
       <c r="D484" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E484" s="10" t="s">
-        <v>517</v>
+        <v>581</v>
       </c>
       <c r="F484" s="10" t="s">
         <v>3</v>
@@ -19631,13 +19718,13 @@
         <v>34</v>
       </c>
       <c r="C485" s="10" t="s">
-        <v>506</v>
+        <v>570</v>
       </c>
       <c r="D485" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E485" s="10" t="s">
-        <v>518</v>
+        <v>582</v>
       </c>
       <c r="F485" s="10" t="s">
         <v>3</v>
@@ -19665,13 +19752,13 @@
         <v>34</v>
       </c>
       <c r="C486" s="10" t="s">
-        <v>506</v>
+        <v>570</v>
       </c>
       <c r="D486" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E486" s="10" t="s">
-        <v>519</v>
+        <v>583</v>
       </c>
       <c r="F486" s="10" t="s">
         <v>3</v>
@@ -19699,13 +19786,13 @@
         <v>34</v>
       </c>
       <c r="C487" s="10" t="s">
-        <v>506</v>
+        <v>570</v>
       </c>
       <c r="D487" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E487" s="10" t="s">
-        <v>520</v>
+        <v>584</v>
       </c>
       <c r="F487" s="10" t="s">
         <v>3</v>
@@ -19733,13 +19820,13 @@
         <v>34</v>
       </c>
       <c r="C488" s="10" t="s">
-        <v>506</v>
+        <v>570</v>
       </c>
       <c r="D488" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E488" s="10" t="s">
-        <v>521</v>
+        <v>585</v>
       </c>
       <c r="F488" s="10" t="s">
         <v>3</v>
@@ -19767,13 +19854,13 @@
         <v>34</v>
       </c>
       <c r="C489" s="10" t="s">
-        <v>506</v>
+        <v>570</v>
       </c>
       <c r="D489" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E489" s="10" t="s">
-        <v>522</v>
+        <v>586</v>
       </c>
       <c r="F489" s="10" t="s">
         <v>3</v>
@@ -19801,13 +19888,13 @@
         <v>35</v>
       </c>
       <c r="C490" s="10" t="s">
-        <v>523</v>
+        <v>587</v>
       </c>
       <c r="D490" s="10" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E490" s="10" t="s">
-        <v>525</v>
+        <v>589</v>
       </c>
       <c r="F490" s="10" t="s">
         <v>3</v>
@@ -19835,13 +19922,13 @@
         <v>35</v>
       </c>
       <c r="C491" s="10" t="s">
-        <v>523</v>
+        <v>587</v>
       </c>
       <c r="D491" s="10" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E491" s="10" t="s">
-        <v>526</v>
+        <v>590</v>
       </c>
       <c r="F491" s="10" t="s">
         <v>3</v>
@@ -19869,13 +19956,13 @@
         <v>35</v>
       </c>
       <c r="C492" s="10" t="s">
-        <v>523</v>
+        <v>587</v>
       </c>
       <c r="D492" s="10" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E492" s="10" t="s">
-        <v>527</v>
+        <v>591</v>
       </c>
       <c r="F492" s="10" t="s">
         <v>3</v>
@@ -19903,13 +19990,13 @@
         <v>35</v>
       </c>
       <c r="C493" s="10" t="s">
-        <v>523</v>
+        <v>587</v>
       </c>
       <c r="D493" s="10" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E493" s="10" t="s">
-        <v>528</v>
+        <v>592</v>
       </c>
       <c r="F493" s="10" t="s">
         <v>3</v>
@@ -19937,13 +20024,13 @@
         <v>35</v>
       </c>
       <c r="C494" s="10" t="s">
-        <v>523</v>
+        <v>587</v>
       </c>
       <c r="D494" s="10" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E494" s="10" t="s">
-        <v>529</v>
+        <v>593</v>
       </c>
       <c r="F494" s="10" t="s">
         <v>3</v>
@@ -19971,13 +20058,13 @@
         <v>35</v>
       </c>
       <c r="C495" s="10" t="s">
-        <v>523</v>
+        <v>587</v>
       </c>
       <c r="D495" s="10" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E495" s="10" t="s">
-        <v>530</v>
+        <v>594</v>
       </c>
       <c r="F495" s="10" t="s">
         <v>3</v>
@@ -20005,13 +20092,13 @@
         <v>35</v>
       </c>
       <c r="C496" s="10" t="s">
-        <v>523</v>
+        <v>587</v>
       </c>
       <c r="D496" s="10" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E496" s="10" t="s">
-        <v>531</v>
+        <v>595</v>
       </c>
       <c r="F496" s="10" t="s">
         <v>3</v>
@@ -20039,13 +20126,13 @@
         <v>35</v>
       </c>
       <c r="C497" t="s">
-        <v>523</v>
+        <v>587</v>
       </c>
       <c r="D497" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E497" t="s">
-        <v>532</v>
+        <v>596</v>
       </c>
       <c r="F497" t="s">
         <v>3</v>
@@ -20073,13 +20160,13 @@
         <v>35</v>
       </c>
       <c r="C498" t="s">
-        <v>523</v>
+        <v>587</v>
       </c>
       <c r="D498" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E498" t="s">
-        <v>533</v>
+        <v>597</v>
       </c>
       <c r="F498" t="s">
         <v>3</v>
@@ -20107,13 +20194,13 @@
         <v>35</v>
       </c>
       <c r="C499" t="s">
-        <v>523</v>
+        <v>587</v>
       </c>
       <c r="D499" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E499" t="s">
-        <v>534</v>
+        <v>598</v>
       </c>
       <c r="F499" t="s">
         <v>3</v>
@@ -20141,13 +20228,13 @@
         <v>35</v>
       </c>
       <c r="C500" t="s">
-        <v>523</v>
+        <v>587</v>
       </c>
       <c r="D500" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E500" t="s">
-        <v>535</v>
+        <v>599</v>
       </c>
       <c r="F500" t="s">
         <v>3</v>
@@ -20175,13 +20262,13 @@
         <v>35</v>
       </c>
       <c r="C501" t="s">
-        <v>523</v>
+        <v>587</v>
       </c>
       <c r="D501" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E501" t="s">
-        <v>536</v>
+        <v>600</v>
       </c>
       <c r="F501" t="s">
         <v>3</v>
@@ -20209,13 +20296,13 @@
         <v>35</v>
       </c>
       <c r="C502" t="s">
-        <v>523</v>
+        <v>587</v>
       </c>
       <c r="D502" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E502" t="s">
-        <v>537</v>
+        <v>601</v>
       </c>
       <c r="F502" t="s">
         <v>3</v>
@@ -20243,13 +20330,13 @@
         <v>35</v>
       </c>
       <c r="C503" t="s">
-        <v>523</v>
+        <v>587</v>
       </c>
       <c r="D503" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E503" t="s">
-        <v>538</v>
+        <v>602</v>
       </c>
       <c r="F503" t="s">
         <v>3</v>
@@ -20277,13 +20364,13 @@
         <v>35</v>
       </c>
       <c r="C504" t="s">
-        <v>523</v>
+        <v>587</v>
       </c>
       <c r="D504" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E504" t="s">
-        <v>539</v>
+        <v>603</v>
       </c>
       <c r="F504" t="s">
         <v>3</v>
@@ -20311,13 +20398,13 @@
         <v>35</v>
       </c>
       <c r="C505" t="s">
-        <v>523</v>
+        <v>587</v>
       </c>
       <c r="D505" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E505" t="s">
-        <v>540</v>
+        <v>604</v>
       </c>
       <c r="F505" t="s">
         <v>3</v>
@@ -20345,13 +20432,13 @@
         <v>35</v>
       </c>
       <c r="C506" t="s">
-        <v>523</v>
+        <v>587</v>
       </c>
       <c r="D506" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E506" t="s">
-        <v>541</v>
+        <v>605</v>
       </c>
       <c r="F506" t="s">
         <v>3</v>
@@ -20379,10 +20466,10 @@
         <v>35</v>
       </c>
       <c r="C507" t="s">
-        <v>523</v>
+        <v>587</v>
       </c>
       <c r="D507" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E507" t="s">
         <v>17</v>
@@ -20413,13 +20500,13 @@
         <v>35</v>
       </c>
       <c r="C508" t="s">
-        <v>523</v>
+        <v>587</v>
       </c>
       <c r="D508" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E508" t="s">
-        <v>542</v>
+        <v>606</v>
       </c>
       <c r="F508" t="s">
         <v>3</v>
@@ -20447,13 +20534,13 @@
         <v>35</v>
       </c>
       <c r="C509" t="s">
-        <v>523</v>
+        <v>587</v>
       </c>
       <c r="D509" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E509" t="s">
-        <v>543</v>
+        <v>607</v>
       </c>
       <c r="F509" t="s">
         <v>3</v>
@@ -20481,13 +20568,13 @@
         <v>36</v>
       </c>
       <c r="C510" t="s">
-        <v>544</v>
+        <v>608</v>
       </c>
       <c r="D510" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E510" t="s">
-        <v>545</v>
+        <v>609</v>
       </c>
       <c r="F510" t="s">
         <v>3</v>
@@ -20515,13 +20602,13 @@
         <v>36</v>
       </c>
       <c r="C511" t="s">
-        <v>544</v>
+        <v>608</v>
       </c>
       <c r="D511" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E511" t="s">
-        <v>546</v>
+        <v>610</v>
       </c>
       <c r="F511" t="s">
         <v>3</v>
@@ -20549,13 +20636,13 @@
         <v>36</v>
       </c>
       <c r="C512" t="s">
-        <v>544</v>
+        <v>608</v>
       </c>
       <c r="D512" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E512" t="s">
-        <v>547</v>
+        <v>611</v>
       </c>
       <c r="F512" t="s">
         <v>3</v>
@@ -20583,13 +20670,13 @@
         <v>36</v>
       </c>
       <c r="C513" t="s">
-        <v>544</v>
+        <v>608</v>
       </c>
       <c r="D513" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E513" t="s">
-        <v>548</v>
+        <v>612</v>
       </c>
       <c r="F513" t="s">
         <v>3</v>
@@ -20617,13 +20704,13 @@
         <v>36</v>
       </c>
       <c r="C514" t="s">
-        <v>544</v>
+        <v>608</v>
       </c>
       <c r="D514" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E514" t="s">
-        <v>549</v>
+        <v>613</v>
       </c>
       <c r="F514" t="s">
         <v>3</v>
@@ -20651,13 +20738,13 @@
         <v>36</v>
       </c>
       <c r="C515" t="s">
-        <v>544</v>
+        <v>608</v>
       </c>
       <c r="D515" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E515" t="s">
-        <v>550</v>
+        <v>614</v>
       </c>
       <c r="F515" t="s">
         <v>3</v>
@@ -20685,13 +20772,13 @@
         <v>36</v>
       </c>
       <c r="C516" t="s">
-        <v>544</v>
+        <v>608</v>
       </c>
       <c r="D516" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E516" t="s">
-        <v>551</v>
+        <v>615</v>
       </c>
       <c r="F516" t="s">
         <v>3</v>
@@ -20719,13 +20806,13 @@
         <v>36</v>
       </c>
       <c r="C517" t="s">
-        <v>544</v>
+        <v>608</v>
       </c>
       <c r="D517" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E517" t="s">
-        <v>552</v>
+        <v>616</v>
       </c>
       <c r="F517" t="s">
         <v>3</v>
@@ -20753,13 +20840,13 @@
         <v>36</v>
       </c>
       <c r="C518" t="s">
-        <v>544</v>
+        <v>608</v>
       </c>
       <c r="D518" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E518" t="s">
-        <v>553</v>
+        <v>617</v>
       </c>
       <c r="F518" t="s">
         <v>3</v>
@@ -20787,13 +20874,13 @@
         <v>36</v>
       </c>
       <c r="C519" t="s">
-        <v>544</v>
+        <v>608</v>
       </c>
       <c r="D519" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E519" t="s">
-        <v>554</v>
+        <v>618</v>
       </c>
       <c r="F519" t="s">
         <v>3</v>
@@ -20821,13 +20908,13 @@
         <v>36</v>
       </c>
       <c r="C520" t="s">
-        <v>544</v>
+        <v>608</v>
       </c>
       <c r="D520" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E520" t="s">
-        <v>555</v>
+        <v>619</v>
       </c>
       <c r="F520" t="s">
         <v>3</v>
@@ -20855,13 +20942,13 @@
         <v>36</v>
       </c>
       <c r="C521" t="s">
-        <v>544</v>
+        <v>608</v>
       </c>
       <c r="D521" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E521" t="s">
-        <v>556</v>
+        <v>620</v>
       </c>
       <c r="F521" t="s">
         <v>3</v>
@@ -20889,13 +20976,13 @@
         <v>36</v>
       </c>
       <c r="C522" t="s">
-        <v>544</v>
+        <v>608</v>
       </c>
       <c r="D522" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E522" t="s">
-        <v>557</v>
+        <v>621</v>
       </c>
       <c r="F522" t="s">
         <v>3</v>
@@ -20923,13 +21010,13 @@
         <v>36</v>
       </c>
       <c r="C523" t="s">
-        <v>544</v>
+        <v>608</v>
       </c>
       <c r="D523" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E523" t="s">
-        <v>558</v>
+        <v>622</v>
       </c>
       <c r="F523" t="s">
         <v>3</v>
@@ -20957,13 +21044,13 @@
         <v>36</v>
       </c>
       <c r="C524" t="s">
-        <v>544</v>
+        <v>608</v>
       </c>
       <c r="D524" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E524" t="s">
-        <v>559</v>
+        <v>623</v>
       </c>
       <c r="F524" t="s">
         <v>3</v>
@@ -20991,13 +21078,13 @@
         <v>36</v>
       </c>
       <c r="C525" t="s">
-        <v>544</v>
+        <v>608</v>
       </c>
       <c r="D525" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E525" t="s">
-        <v>560</v>
+        <v>624</v>
       </c>
       <c r="F525" t="s">
         <v>3</v>
@@ -21025,13 +21112,13 @@
         <v>36</v>
       </c>
       <c r="C526" t="s">
-        <v>544</v>
+        <v>608</v>
       </c>
       <c r="D526" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E526" t="s">
-        <v>561</v>
+        <v>625</v>
       </c>
       <c r="F526" t="s">
         <v>3</v>
@@ -21059,13 +21146,13 @@
         <v>36</v>
       </c>
       <c r="C527" t="s">
-        <v>544</v>
+        <v>608</v>
       </c>
       <c r="D527" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E527" t="s">
-        <v>562</v>
+        <v>626</v>
       </c>
       <c r="F527" t="s">
         <v>3</v>
@@ -21093,13 +21180,13 @@
         <v>37</v>
       </c>
       <c r="C528" t="s">
-        <v>563</v>
+        <v>627</v>
       </c>
       <c r="D528" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E528" t="s">
-        <v>564</v>
+        <v>628</v>
       </c>
       <c r="F528" t="s">
         <v>3</v>
@@ -21127,13 +21214,13 @@
         <v>37</v>
       </c>
       <c r="C529" t="s">
-        <v>563</v>
+        <v>627</v>
       </c>
       <c r="D529" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E529" t="s">
-        <v>565</v>
+        <v>629</v>
       </c>
       <c r="F529" t="s">
         <v>3</v>
@@ -21161,13 +21248,13 @@
         <v>37</v>
       </c>
       <c r="C530" t="s">
-        <v>563</v>
+        <v>627</v>
       </c>
       <c r="D530" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E530" t="s">
-        <v>566</v>
+        <v>630</v>
       </c>
       <c r="F530" t="s">
         <v>3</v>
@@ -21195,13 +21282,13 @@
         <v>37</v>
       </c>
       <c r="C531" t="s">
-        <v>563</v>
+        <v>627</v>
       </c>
       <c r="D531" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E531" t="s">
-        <v>567</v>
+        <v>631</v>
       </c>
       <c r="F531" t="s">
         <v>3</v>
@@ -21229,13 +21316,13 @@
         <v>37</v>
       </c>
       <c r="C532" t="s">
-        <v>563</v>
+        <v>627</v>
       </c>
       <c r="D532" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E532" t="s">
-        <v>568</v>
+        <v>632</v>
       </c>
       <c r="F532" t="s">
         <v>3</v>
@@ -21263,13 +21350,13 @@
         <v>37</v>
       </c>
       <c r="C533" t="s">
-        <v>563</v>
+        <v>627</v>
       </c>
       <c r="D533" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E533" t="s">
-        <v>569</v>
+        <v>633</v>
       </c>
       <c r="F533" t="s">
         <v>3</v>
@@ -21297,13 +21384,13 @@
         <v>37</v>
       </c>
       <c r="C534" t="s">
-        <v>563</v>
+        <v>627</v>
       </c>
       <c r="D534" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="E534" t="s">
-        <v>570</v>
+        <v>634</v>
       </c>
       <c r="F534" t="s">
         <v>3</v>
@@ -26795,11 +26882,11 @@
       </c>
       <c r="D5">
         <f>COUNTIFS(Checklist!$B:$B,A5,Checklist!$F:$F,"Đang làm")</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <f>COUNTIFS(Checklist!$B:$B,A5,Checklist!$F:$F,"Hoàn thành")</f>
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="F5">
         <f>COUNTIFS(Checklist!$B:$B,A5,Checklist!$F:$F,"Bị chặn")</f>
@@ -26811,7 +26898,7 @@
       </c>
       <c r="H5" s="6">
         <f t="shared" si="0"/>
-        <v>0.43137254901960786</v>
+        <v>0.48366013071895425</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -27095,6 +27182,13 @@
       </dataBar>
     </cfRule>
     <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF2563EB"/>
+      </dataBar>
+    </cfRule>
+    <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>

--- a/CHECKLIST_TRIEN_KHAI_FULL.xlsx
+++ b/CHECKLIST_TRIEN_KHAI_FULL.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rd803bee6e9cf4002"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="Rf488c25af4514b13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase Summary" sheetId="3" r:id="Rd961bc86c1f34ab8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="4" r:id="Rb52d4bd7b7094233"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R0778639ab7ac45c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="Ra4983f8a6c4e481e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase Summary" sheetId="3" r:id="R3f1b907f723043dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="4" r:id="R834fa94213014256"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -799,10 +799,6 @@
     <x:t xml:space="preserve">Cài/pin Colab environment và ghi Python, PyTorch, CUDA, MMEngine, MMCV, MMDetection, pycocotools.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">reports/phase2D1_mmdet_environment_versions.txt
-reports/phase2D1_mmdet_pip_freeze.txt</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">MMDetection import PASS; COCO-JPG parse và dataset build PASS.</x:t>
   </x:si>
   <x:si>
@@ -827,27 +823,13 @@
     <x:t xml:space="preserve">Tạo MMDetection config và loading-validation script.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">configs/dataset/mmdet_coco_jpg_loading.py
-scripts/02D1C_mmdet_loading_validation.py</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Tạo loading, empty-image, sample và dataloader audit reports; GPT review PASS.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">reports/phase2D1_mmdet_loading_check.md
-reports/phase2D1_mmdet_loading_check.json
-reports/phase2D1_empty_image_retention_audit.csv
-reports/phase2D1_sample_loading_audit.csv
-reports/phase2D1_dataloader_iteration_audit.csv</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">2D.1D. Evidence Consolidation, GPT Review &amp; Closure</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Tải Colab evidence về local và kiểm tra file/hash.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">LOCKED until 2D.1C PASS</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Cập nhật PROJECT_CONTEXT.md, PHASE_HANDOFF.md, research_log.md và checklist sau PASS.</x:t>
@@ -2418,7 +2400,7 @@
       </x:c>
       <x:c r="B4" s="2" t="n">
         <x:f>COUNTIF(Checklist!$F:$F,"Chưa làm")</x:f>
-        <x:v>367</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="D4" s="3" t="s">
         <x:v>4</x:v>
@@ -2436,7 +2418,7 @@
       </x:c>
       <x:c r="B5" s="2" t="n">
         <x:f>COUNTIF(Checklist!$F:$F,"Đang làm")</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="3" t="s">
         <x:v>7</x:v>
@@ -2454,7 +2436,7 @@
       </x:c>
       <x:c r="B6" s="2" t="n">
         <x:f>COUNTIF(Checklist!$F:$F,"Hoàn thành")</x:f>
-        <x:v>164</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="D6" s="3" t="s">
         <x:v>10</x:v>
@@ -2490,7 +2472,7 @@
       </x:c>
       <x:c r="B8" s="5" t="n">
         <x:f>IFERROR(B6/B3,0)</x:f>
-        <x:v>0.3076923076923077</x:v>
+        <x:v>0.3302063789868668</x:v>
       </x:c>
       <x:c r="D8" s="3" t="s">
         <x:v>16</x:v>
@@ -2659,15 +2641,15 @@
       </x:c>
       <x:c r="C15" t="n">
         <x:f>'Phase Summary'!C5</x:f>
-        <x:v>67</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D15" t="n">
         <x:f>'Phase Summary'!D5</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E15" t="n">
         <x:f>'Phase Summary'!E5</x:f>
-        <x:v>86</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F15" t="n">
         <x:f>'Phase Summary'!F5</x:f>
@@ -2679,7 +2661,7 @@
       </x:c>
       <x:c r="H15" s="6" t="n">
         <x:f>'Phase Summary'!H5</x:f>
-        <x:v>0.5620915032679739</x:v>
+        <x:v>0.6405228758169934</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -8875,7 +8857,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="169" ht="63.29999923706055" customHeight="1">
+    <x:row r="169" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A169" s="10">
         <x:v>168</x:v>
       </x:c>
@@ -8903,7 +8885,7 @@
       <x:c r="I169" s="10"/>
       <x:c r="J169" s="10"/>
       <x:c r="K169" s="10" t="str">
-        <x:v>CLOSED / PASS; full conversion and validation GPT/researcher review PASS; JPG representation and COCO-JPG derivative ready. MMDetection loading, empty-image retention, dataset training readiness and training authorization remain false.</x:v>
+        <x:v>CLOSED / PASS at Phase 2D.1B-Full closure; JPG representation and COCO-JPG derivative ready. At that historical point MMDetection loading, empty-image retention and dataset training readiness were unresolved. Resolution update (2026-07-30): Phase 2D.1C full pipeline audit CLOSED / PASS; dataset_training_ready=true; training_authorized=false.</x:v>
       </x:c>
       <x:c r="L169" s="10" t="str">
         <x:v>reports/phase2D1B_full_validation.md
@@ -8915,7 +8897,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="170" ht="33.75" customHeight="1">
+    <x:row r="170" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A170" s="10">
         <x:v>169</x:v>
       </x:c>
@@ -8931,8 +8913,8 @@
       <x:c r="E170" s="10" t="s">
         <x:v>259</x:v>
       </x:c>
-      <x:c r="F170" s="10" t="s">
-        <x:v>3</x:v>
+      <x:c r="F170" s="10" t="str">
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="G170" s="10" t="s">
         <x:v>52</x:v>
@@ -8943,17 +8925,18 @@
       <x:c r="I170" s="10"/>
       <x:c r="J170" s="10"/>
       <x:c r="K170" s="10" t="str">
-        <x:v>NOT STARTED / NEXT; unlocked after Phase 2D.1B-Full CLOSED / PASS; Google Colab; no training.</x:v>
-      </x:c>
-      <x:c r="L170" s="10" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="M170" s="10">
+        <x:v>CLOSED / PASS; pinned Colab MMDetection 3.3.0 environment initialized successfully. Runtime/dependency evidence is recorded in the loading report; this phase performs validation only, not training.</x:v>
+      </x:c>
+      <x:c r="L170" s="10" t="str">
+        <x:v>reports/phase2D1C_mmdet_dataset_loading_report.json
+reports/phase2D1C_mmdet_dataset_loading_report.md</x:v>
+      </x:c>
+      <x:c r="M170" s="10" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="171" ht="16.950000762939453" customHeight="1">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" ht="66" hidden="0" customHeight="1">
       <x:c r="A171" s="10">
         <x:v>170</x:v>
       </x:c>
@@ -8967,10 +8950,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="E171" s="10" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="F171" s="10" t="s">
-        <x:v>3</x:v>
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="F171" s="10" t="str">
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="G171" s="10" t="s">
         <x:v>52</x:v>
@@ -8981,15 +8964,18 @@
       <x:c r="I171" s="10"/>
       <x:c r="J171" s="10"/>
       <x:c r="K171" s="10" t="str">
-        <x:v>NOT STARTED / NEXT; unlocked after Phase 2D.1B-Full CLOSED / PASS; Google Colab; no training.</x:v>
-      </x:c>
-      <x:c r="L171" s="10"/>
-      <x:c r="M171" s="10">
+        <x:v>CLOSED / PASS; MMDetection import, COCO-JPG parsing and dataset construction succeeded; full audit completed with errors=0.</x:v>
+      </x:c>
+      <x:c r="L171" s="10" t="str">
+        <x:v>reports/phase2D1C_mmdet_dataset_loading_report.json
+reports/phase2D1C_mmdet_dataset_loading_report.md</x:v>
+      </x:c>
+      <x:c r="M171" s="10" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="172" ht="16.950000762939453" customHeight="1">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A172" s="10">
         <x:v>171</x:v>
       </x:c>
@@ -9003,10 +8989,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="E172" s="10" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="F172" s="10" t="s">
-        <x:v>3</x:v>
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="F172" s="10" t="str">
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="G172" s="10" t="s">
         <x:v>52</x:v>
@@ -9017,15 +9003,18 @@
       <x:c r="I172" s="10"/>
       <x:c r="J172" s="10"/>
       <x:c r="K172" s="10" t="str">
-        <x:v>NOT STARTED / NEXT; unlocked after Phase 2D.1B-Full CLOSED / PASS; Google Colab; no training.</x:v>
-      </x:c>
-      <x:c r="L172" s="10"/>
-      <x:c r="M172" s="10">
+        <x:v>CLOSED / PASS; dataset.full_init() succeeded and filter_empty_gt=False retained len(dataset)=4,894.</x:v>
+      </x:c>
+      <x:c r="L172" s="10" t="str">
+        <x:v>reports/phase2D1C_mmdet_dataset_loading_report.json
+reports/phase2D1C_mmdet_dataset_image_audit.csv</x:v>
+      </x:c>
+      <x:c r="M172" s="10" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="173" ht="16.950000762939453" customHeight="1">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A173" s="10">
         <x:v>172</x:v>
       </x:c>
@@ -9039,10 +9028,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="E173" s="10" t="s">
-        <x:v>263</x:v>
-      </x:c>
-      <x:c r="F173" s="10" t="s">
-        <x:v>3</x:v>
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="F173" s="10" t="str">
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="G173" s="10" t="s">
         <x:v>52</x:v>
@@ -9053,15 +9042,18 @@
       <x:c r="I173" s="10"/>
       <x:c r="J173" s="10"/>
       <x:c r="K173" s="10" t="str">
-        <x:v>NOT STARTED / NEXT; unlocked after Phase 2D.1B-Full CLOSED / PASS; Google Colab; no training.</x:v>
-      </x:c>
-      <x:c r="L173" s="10"/>
-      <x:c r="M173" s="10">
+        <x:v>CLOSED / PASS; retained abnormal images=4,394/4,394 and No Finding zero-GT images=500/500.</x:v>
+      </x:c>
+      <x:c r="L173" s="10" t="str">
+        <x:v>reports/phase2D1C_mmdet_dataset_image_audit.csv
+reports/phase2D1C_mmdet_dataset_loading_report.json</x:v>
+      </x:c>
+      <x:c r="M173" s="10" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="174" ht="16.950000762939453" customHeight="1">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A174" s="10">
         <x:v>173</x:v>
       </x:c>
@@ -9075,10 +9067,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="E174" s="10" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="F174" s="10" t="s">
-        <x:v>3</x:v>
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="F174" s="10" t="str">
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="G174" s="10" t="s">
         <x:v>52</x:v>
@@ -9089,15 +9081,18 @@
       <x:c r="I174" s="10"/>
       <x:c r="J174" s="10"/>
       <x:c r="K174" s="10" t="str">
-        <x:v>NOT STARTED / NEXT; unlocked after Phase 2D.1B-Full CLOSED / PASS; Google Colab; no training.</x:v>
-      </x:c>
-      <x:c r="L174" s="10"/>
-      <x:c r="M174" s="10">
+        <x:v>CLOSED / PASS; empty-GT samples=500; unexpected empty abnormal=0; annotated No Finding=0; errors=0.</x:v>
+      </x:c>
+      <x:c r="L174" s="10" t="str">
+        <x:v>reports/phase2D1C_mmdet_dataset_image_audit.csv
+reports/phase2D1C_mmdet_dataset_errors.csv</x:v>
+      </x:c>
+      <x:c r="M174" s="10" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="175" ht="16.950000762939453" customHeight="1">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" ht="66" hidden="0" customHeight="1">
       <x:c r="A175" s="10">
         <x:v>174</x:v>
       </x:c>
@@ -9111,10 +9106,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="E175" s="10" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="F175" s="10" t="s">
-        <x:v>3</x:v>
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="F175" s="10" t="str">
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="G175" s="10" t="s">
         <x:v>52</x:v>
@@ -9125,15 +9120,18 @@
       <x:c r="I175" s="10"/>
       <x:c r="J175" s="10"/>
       <x:c r="K175" s="10" t="str">
-        <x:v>NOT STARTED / NEXT; unlocked after Phase 2D.1B-Full CLOSED / PASS; Google Colab; no training.</x:v>
-      </x:c>
-      <x:c r="L175" s="10"/>
-      <x:c r="M175" s="10">
+        <x:v>CLOSED / PASS; filter_empty_gt=False retained 4,894/4,894. Control check with filter_empty_gt=True excluded exactly the 500 zero-GT images.</x:v>
+      </x:c>
+      <x:c r="L175" s="10" t="str">
+        <x:v>configs/validation/phase2D1C_mmdet_dataset_loading.py
+reports/phase2D1C_mmdet_dataset_loading_report.json</x:v>
+      </x:c>
+      <x:c r="M175" s="10" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="176" ht="16.950000762939453" customHeight="1">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" ht="66" hidden="0" customHeight="1">
       <x:c r="A176" s="10">
         <x:v>175</x:v>
       </x:c>
@@ -9147,10 +9145,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="E176" s="10" t="s">
-        <x:v>266</x:v>
-      </x:c>
-      <x:c r="F176" s="10" t="s">
-        <x:v>3</x:v>
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="F176" s="10" t="str">
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="G176" s="10" t="s">
         <x:v>52</x:v>
@@ -9161,15 +9159,18 @@
       <x:c r="I176" s="10"/>
       <x:c r="J176" s="10"/>
       <x:c r="K176" s="10" t="str">
-        <x:v>NOT STARTED / NEXT; unlocked after Phase 2D.1B-Full CLOSED / PASS; Google Colab; no training.</x:v>
-      </x:c>
-      <x:c r="L176" s="10"/>
-      <x:c r="M176" s="10">
+        <x:v>CLOSED / PASS; abnormal and No Finding samples loaded with valid image tensors, bbox and label structures; full bbox/label audit valid for 4,894/4,894.</x:v>
+      </x:c>
+      <x:c r="L176" s="10" t="str">
+        <x:v>reports/phase2D1C_mmdet_dataset_image_audit.csv
+reports/phase2D1C_mmdet_dataset_loading_report.json</x:v>
+      </x:c>
+      <x:c r="M176" s="10" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="177" ht="16.950000762939453" customHeight="1">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" ht="66" hidden="0" customHeight="1">
       <x:c r="A177" s="10">
         <x:v>176</x:v>
       </x:c>
@@ -9183,10 +9184,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="E177" s="10" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="F177" s="10" t="s">
-        <x:v>3</x:v>
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="F177" s="10" t="str">
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="G177" s="10" t="s">
         <x:v>52</x:v>
@@ -9197,15 +9198,18 @@
       <x:c r="I177" s="10"/>
       <x:c r="J177" s="10"/>
       <x:c r="K177" s="10" t="str">
-        <x:v>NOT STARTED / NEXT; unlocked after Phase 2D.1B-Full CLOSED / PASS; Google Colab; no training.</x:v>
-      </x:c>
-      <x:c r="L177" s="10"/>
-      <x:c r="M177" s="10">
+        <x:v>CLOSED / PASS; standard and forced empty-GT dataloader batches passed, including multi-worker loading; all required dataset-loading checks passed.</x:v>
+      </x:c>
+      <x:c r="L177" s="10" t="str">
+        <x:v>reports/phase2D1C_mmdet_dataset_loading_report.json
+reports/phase2D1C_mmdet_dataset_loading_report.md</x:v>
+      </x:c>
+      <x:c r="M177" s="10" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="178" ht="33.75" customHeight="1">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A178" s="10">
         <x:v>177</x:v>
       </x:c>
@@ -9219,10 +9223,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="E178" s="10" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="F178" s="10" t="s">
-        <x:v>3</x:v>
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="F178" s="10" t="str">
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="G178" s="10" t="s">
         <x:v>64</x:v>
@@ -9233,17 +9237,19 @@
       <x:c r="I178" s="10"/>
       <x:c r="J178" s="10"/>
       <x:c r="K178" s="10" t="str">
-        <x:v>NOT STARTED / NEXT; unlocked after Phase 2D.1B-Full CLOSED / PASS; Google Colab; no training.</x:v>
-      </x:c>
-      <x:c r="L178" s="10" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="M178" s="10">
+        <x:v>CLOSED / PASS; final validation config, executable audit script and guardrail test suite created. Regression/unit tests: 35 passed.</x:v>
+      </x:c>
+      <x:c r="L178" s="10" t="str">
+        <x:v>configs/validation/phase2D1C_mmdet_dataset_loading.py
+scripts/02D1C_validate_mmdet_dataset_loading.py
+tests/test_phase2D1C_mmdet_dataset_loading_guardrails.py</x:v>
+      </x:c>
+      <x:c r="M178" s="10" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="179" ht="84.44999694824219" customHeight="1">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A179" s="10">
         <x:v>178</x:v>
       </x:c>
@@ -9257,10 +9263,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="E179" s="10" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="F179" s="10" t="s">
-        <x:v>3</x:v>
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="F179" s="10" t="str">
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="G179" s="10" t="s">
         <x:v>64</x:v>
@@ -9271,17 +9277,20 @@
       <x:c r="I179" s="10"/>
       <x:c r="J179" s="10"/>
       <x:c r="K179" s="10" t="str">
-        <x:v>NOT STARTED / NEXT; unlocked after Phase 2D.1B-Full CLOSED / PASS; Google Colab; no training.</x:v>
-      </x:c>
-      <x:c r="L179" s="10" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="M179" s="10">
+        <x:v>CLOSED / PASS; full pipeline audit reviewed: 4,894/4,894 images, bbox/label validation PASS, errors=0, 35 tests passed. dataset_training_ready=true; training_authorized=false.</x:v>
+      </x:c>
+      <x:c r="L179" s="10" t="str">
+        <x:v>reports/phase2D1C_mmdet_dataset_errors.csv
+reports/phase2D1C_mmdet_dataset_image_audit.csv
+reports/phase2D1C_mmdet_dataset_loading_report.json
+reports/phase2D1C_mmdet_dataset_loading_report.md</x:v>
+      </x:c>
+      <x:c r="M179" s="10" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="180" ht="16.950000762939453" customHeight="1">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A180" s="10">
         <x:v>179</x:v>
       </x:c>
@@ -9289,16 +9298,16 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C180" s="10" t="s">
-        <x:v>272</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="D180" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E180" s="10" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="F180" s="10" t="s">
-        <x:v>3</x:v>
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="F180" s="10" t="str">
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="G180" s="10" t="s">
         <x:v>52</x:v>
@@ -9308,16 +9317,21 @@
       </x:c>
       <x:c r="I180" s="10"/>
       <x:c r="J180" s="10"/>
-      <x:c r="K180" s="10" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="L180" s="10"/>
-      <x:c r="M180" s="10">
+      <x:c r="K180" s="10" t="str">
+        <x:v>COMPLETED; Colab evidence transferred to local project and the four final report SHA-256 hashes rechecked unchanged.</x:v>
+      </x:c>
+      <x:c r="L180" s="10" t="str">
+        <x:v>reports/phase2D1C_mmdet_dataset_errors.csv
+reports/phase2D1C_mmdet_dataset_image_audit.csv
+reports/phase2D1C_mmdet_dataset_loading_report.json
+reports/phase2D1C_mmdet_dataset_loading_report.md</x:v>
+      </x:c>
+      <x:c r="M180" s="10" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="181" ht="16.950000762939453" customHeight="1">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A181" s="10">
         <x:v>180</x:v>
       </x:c>
@@ -9325,16 +9339,16 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C181" s="10" t="s">
-        <x:v>272</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="D181" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E181" s="10" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="F181" s="10" t="s">
-        <x:v>3</x:v>
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="F181" s="10" t="str">
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="G181" s="10" t="s">
         <x:v>52</x:v>
@@ -9344,16 +9358,22 @@
       </x:c>
       <x:c r="I181" s="10"/>
       <x:c r="J181" s="10"/>
-      <x:c r="K181" s="10" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="L181" s="10"/>
-      <x:c r="M181" s="10">
+      <x:c r="K181" s="10" t="str">
+        <x:v>COMPLETED; PHASE_HANDOFF.md, PROJECT_CONTEXT.md, research_log.md, README.md and CHECKLIST_TRIEN_KHAI_FULL.xlsx updated consistently after Phase 2D.1C PASS.</x:v>
+      </x:c>
+      <x:c r="L181" s="10" t="str">
+        <x:v>PHASE_HANDOFF.md
+PROJECT_CONTEXT.md
+research_log.md
+README.md
+CHECKLIST_TRIEN_KHAI_FULL.xlsx</x:v>
+      </x:c>
+      <x:c r="M181" s="10" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="182" ht="16.950000762939453" customHeight="1">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A182" s="10">
         <x:v>181</x:v>
       </x:c>
@@ -9361,16 +9381,16 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C182" s="10" t="s">
-        <x:v>272</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="D182" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E182" s="10" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="F182" s="10" t="s">
-        <x:v>3</x:v>
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="F182" s="10" t="str">
+        <x:v>Đang làm</x:v>
       </x:c>
       <x:c r="G182" s="10" t="s">
         <x:v>52</x:v>
@@ -9380,16 +9400,22 @@
       </x:c>
       <x:c r="I182" s="10"/>
       <x:c r="J182" s="10"/>
-      <x:c r="K182" s="10" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="L182" s="10"/>
-      <x:c r="M182" s="10">
+      <x:c r="K182" s="10" t="str">
+        <x:v>OPEN / CURRENT; final Phase 2D.1 closure review is in progress. Dataset is training-ready, but training remains unauthorized until this gate is closed.</x:v>
+      </x:c>
+      <x:c r="L182" s="10" t="str">
+        <x:v>PHASE_HANDOFF.md
+PROJECT_CONTEXT.md
+research_log.md
+README.md
+CHECKLIST_TRIEN_KHAI_FULL.xlsx</x:v>
+      </x:c>
+      <x:c r="M182" s="10" t="n">
         <x:f t="shared" si="2"/>
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="183" ht="16.950000762939453" customHeight="1">
+    <x:row r="183" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A183" s="10">
         <x:v>182</x:v>
       </x:c>
@@ -9397,16 +9423,16 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C183" s="10" t="s">
-        <x:v>272</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="D183" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E183" s="10" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="F183" s="10" t="s">
-        <x:v>3</x:v>
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="F183" s="10" t="str">
+        <x:v>Chưa làm</x:v>
       </x:c>
       <x:c r="G183" s="10" t="s">
         <x:v>52</x:v>
@@ -9416,11 +9442,11 @@
       </x:c>
       <x:c r="I183" s="10"/>
       <x:c r="J183" s="10"/>
-      <x:c r="K183" s="10" t="s">
-        <x:v>274</x:v>
+      <x:c r="K183" s="10" t="str">
+        <x:v>UNLOCKED / PENDING; stage reviewed evidence and updated project documents, inspect the complete staged diff, then commit/push. Do not commit the 4,894 JPG files to ordinary Git.</x:v>
       </x:c>
       <x:c r="L183" s="10"/>
-      <x:c r="M183" s="10">
+      <x:c r="M183" s="10" t="n">
         <x:f t="shared" si="2"/>
         <x:v>0</x:v>
       </x:c>
@@ -9433,13 +9459,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C184" s="10" t="s">
-        <x:v>278</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="D184" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E184" s="10" t="s">
-        <x:v>279</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="F184" s="10" t="s">
         <x:v>3</x:v>
@@ -9467,13 +9493,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C185" s="10" t="s">
-        <x:v>278</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="D185" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E185" s="10" t="s">
-        <x:v>280</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="F185" s="10" t="s">
         <x:v>3</x:v>
@@ -9501,13 +9527,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C186" s="10" t="s">
-        <x:v>278</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="D186" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E186" s="10" t="s">
-        <x:v>281</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="F186" s="10" t="s">
         <x:v>3</x:v>
@@ -9535,13 +9561,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C187" s="10" t="s">
-        <x:v>278</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="D187" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E187" s="10" t="s">
-        <x:v>282</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="F187" s="10" t="s">
         <x:v>3</x:v>
@@ -9569,13 +9595,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C188" s="10" t="s">
-        <x:v>278</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="D188" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E188" s="10" t="s">
-        <x:v>283</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="F188" s="10" t="s">
         <x:v>3</x:v>
@@ -9603,13 +9629,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C189" s="10" t="s">
-        <x:v>278</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="D189" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E189" s="10" t="s">
-        <x:v>284</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="F189" s="10" t="s">
         <x:v>3</x:v>
@@ -9637,13 +9663,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C190" s="10" t="s">
-        <x:v>278</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="D190" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E190" s="10" t="s">
-        <x:v>285</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="F190" s="10" t="s">
         <x:v>3</x:v>
@@ -9671,13 +9697,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C191" s="10" t="s">
-        <x:v>278</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="D191" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E191" s="10" t="s">
-        <x:v>286</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="F191" s="10" t="s">
         <x:v>3</x:v>
@@ -9705,13 +9731,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C192" s="10" t="s">
-        <x:v>278</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="D192" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E192" s="10" t="s">
-        <x:v>287</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="F192" s="10" t="s">
         <x:v>3</x:v>
@@ -9739,13 +9765,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C193" s="10" t="s">
-        <x:v>278</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="D193" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E193" s="10" t="s">
-        <x:v>288</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="F193" s="10" t="s">
         <x:v>3</x:v>
@@ -9773,13 +9799,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C194" s="10" t="s">
-        <x:v>278</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="D194" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E194" s="10" t="s">
-        <x:v>289</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="F194" s="10" t="s">
         <x:v>3</x:v>
@@ -9807,13 +9833,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C195" s="10" t="s">
-        <x:v>278</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="D195" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E195" s="10" t="s">
-        <x:v>290</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="F195" s="10" t="s">
         <x:v>3</x:v>
@@ -9841,13 +9867,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C196" s="10" t="s">
-        <x:v>278</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="D196" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E196" s="10" t="s">
-        <x:v>291</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="F196" s="10" t="s">
         <x:v>3</x:v>
@@ -9875,13 +9901,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C197" s="10" t="s">
-        <x:v>278</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="D197" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E197" s="10" t="s">
-        <x:v>292</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="F197" s="10" t="s">
         <x:v>3</x:v>
@@ -9909,13 +9935,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C198" s="10" t="s">
-        <x:v>278</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="D198" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E198" s="10" t="s">
-        <x:v>293</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="F198" s="10" t="s">
         <x:v>3</x:v>
@@ -9943,13 +9969,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C199" s="10" t="s">
-        <x:v>278</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="D199" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E199" s="10" t="s">
-        <x:v>294</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="F199" s="10" t="s">
         <x:v>3</x:v>
@@ -9977,13 +10003,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C200" s="10" t="s">
-        <x:v>278</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="D200" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E200" s="10" t="s">
-        <x:v>295</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="F200" s="10" t="s">
         <x:v>3</x:v>
@@ -10011,13 +10037,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C201" s="10" t="s">
-        <x:v>278</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="D201" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E201" s="10" t="s">
-        <x:v>296</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="F201" s="10" t="s">
         <x:v>3</x:v>
@@ -10045,13 +10071,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C202" s="10" t="s">
-        <x:v>297</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="D202" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E202" s="10" t="s">
-        <x:v>298</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="F202" s="10" t="s">
         <x:v>3</x:v>
@@ -10079,13 +10105,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C203" s="10" t="s">
-        <x:v>297</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="D203" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E203" s="10" t="s">
-        <x:v>299</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="F203" s="10" t="s">
         <x:v>3</x:v>
@@ -10113,13 +10139,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C204" s="10" t="s">
-        <x:v>297</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="D204" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E204" s="10" t="s">
-        <x:v>300</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="F204" s="10" t="s">
         <x:v>3</x:v>
@@ -10147,13 +10173,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C205" s="10" t="s">
-        <x:v>297</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="D205" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E205" s="10" t="s">
-        <x:v>301</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="F205" s="10" t="s">
         <x:v>3</x:v>
@@ -10181,13 +10207,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C206" s="10" t="s">
-        <x:v>297</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="D206" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E206" s="10" t="s">
-        <x:v>302</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="F206" s="10" t="s">
         <x:v>3</x:v>
@@ -10215,13 +10241,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C207" s="10" t="s">
-        <x:v>297</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="D207" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E207" s="10" t="s">
-        <x:v>303</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="F207" s="10" t="s">
         <x:v>3</x:v>
@@ -10249,13 +10275,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C208" s="10" t="s">
-        <x:v>297</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="D208" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E208" s="10" t="s">
-        <x:v>304</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="F208" s="10" t="s">
         <x:v>3</x:v>
@@ -10283,13 +10309,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C209" s="10" t="s">
-        <x:v>297</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="D209" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E209" s="10" t="s">
-        <x:v>305</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="F209" s="10" t="s">
         <x:v>3</x:v>
@@ -10317,13 +10343,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C210" s="10" t="s">
-        <x:v>297</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="D210" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E210" s="10" t="s">
-        <x:v>306</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="F210" s="10" t="s">
         <x:v>3</x:v>
@@ -10351,13 +10377,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C211" s="10" t="s">
-        <x:v>297</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="D211" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E211" s="10" t="s">
-        <x:v>307</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F211" s="10" t="s">
         <x:v>3</x:v>
@@ -10385,13 +10411,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C212" s="10" t="s">
-        <x:v>297</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="D212" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E212" s="10" t="s">
-        <x:v>308</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="F212" s="10" t="s">
         <x:v>3</x:v>
@@ -10419,13 +10445,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C213" s="10" t="s">
-        <x:v>297</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="D213" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E213" s="10" t="s">
-        <x:v>309</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="F213" s="10" t="s">
         <x:v>3</x:v>
@@ -10453,13 +10479,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C214" s="10" t="s">
-        <x:v>297</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="D214" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E214" s="10" t="s">
-        <x:v>310</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="F214" s="10" t="s">
         <x:v>3</x:v>
@@ -10487,13 +10513,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C215" s="10" t="s">
-        <x:v>297</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="D215" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E215" s="10" t="s">
-        <x:v>311</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="F215" s="10" t="s">
         <x:v>3</x:v>
@@ -10521,13 +10547,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C216" s="10" t="s">
-        <x:v>297</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="D216" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E216" s="10" t="s">
-        <x:v>312</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="F216" s="10" t="s">
         <x:v>3</x:v>
@@ -10555,13 +10581,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C217" s="10" t="s">
-        <x:v>297</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="D217" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E217" s="10" t="s">
-        <x:v>313</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="F217" s="10" t="s">
         <x:v>3</x:v>
@@ -10589,13 +10615,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C218" s="10" t="s">
-        <x:v>297</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="D218" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E218" s="10" t="s">
-        <x:v>314</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="F218" s="10" t="s">
         <x:v>3</x:v>
@@ -10623,13 +10649,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C219" s="10" t="s">
-        <x:v>297</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="D219" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E219" s="10" t="s">
-        <x:v>315</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="F219" s="10" t="s">
         <x:v>3</x:v>
@@ -10657,13 +10683,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C220" s="10" t="s">
-        <x:v>297</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="D220" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E220" s="10" t="s">
-        <x:v>316</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="F220" s="10" t="s">
         <x:v>3</x:v>
@@ -10691,13 +10717,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C221" s="10" t="s">
-        <x:v>297</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="D221" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E221" s="10" t="s">
-        <x:v>317</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="F221" s="10" t="s">
         <x:v>3</x:v>
@@ -10725,13 +10751,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C222" s="10" t="s">
-        <x:v>297</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="D222" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E222" s="10" t="s">
-        <x:v>318</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="F222" s="10" t="s">
         <x:v>3</x:v>
@@ -10759,13 +10785,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C223" s="10" t="s">
-        <x:v>297</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="D223" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E223" s="10" t="s">
-        <x:v>319</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="F223" s="10" t="s">
         <x:v>3</x:v>
@@ -10793,13 +10819,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C224" s="10" t="s">
-        <x:v>297</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="D224" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E224" s="10" t="s">
-        <x:v>320</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="F224" s="10" t="s">
         <x:v>3</x:v>
@@ -10827,13 +10853,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C225" s="10" t="s">
-        <x:v>321</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="D225" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E225" s="10" t="s">
-        <x:v>322</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="F225" s="10" t="s">
         <x:v>3</x:v>
@@ -10861,13 +10887,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C226" s="10" t="s">
-        <x:v>321</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="D226" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E226" s="10" t="s">
-        <x:v>323</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="F226" s="10" t="s">
         <x:v>3</x:v>
@@ -10895,13 +10921,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C227" s="10" t="s">
-        <x:v>321</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="D227" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E227" s="10" t="s">
-        <x:v>324</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="F227" s="10" t="s">
         <x:v>3</x:v>
@@ -10929,13 +10955,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C228" s="10" t="s">
-        <x:v>321</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="D228" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E228" s="10" t="s">
-        <x:v>325</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="F228" s="10" t="s">
         <x:v>3</x:v>
@@ -10963,13 +10989,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C229" s="10" t="s">
-        <x:v>321</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="D229" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E229" s="10" t="s">
-        <x:v>326</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="F229" s="10" t="s">
         <x:v>3</x:v>
@@ -10997,13 +11023,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C230" s="10" t="s">
-        <x:v>321</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="D230" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E230" s="10" t="s">
-        <x:v>327</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="F230" s="10" t="s">
         <x:v>3</x:v>
@@ -11031,13 +11057,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C231" s="10" t="s">
-        <x:v>321</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="D231" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E231" s="10" t="s">
-        <x:v>328</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="F231" s="10" t="s">
         <x:v>3</x:v>
@@ -11065,7 +11091,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C232" s="10" t="s">
-        <x:v>321</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="D232" s="10" t="s">
         <x:v>78</x:v>
@@ -11099,13 +11125,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C233" s="10" t="s">
-        <x:v>321</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="D233" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E233" s="10" t="s">
-        <x:v>329</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="F233" s="10" t="s">
         <x:v>3</x:v>
@@ -11133,13 +11159,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C234" s="10" t="s">
-        <x:v>321</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="D234" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E234" s="10" t="s">
-        <x:v>330</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="F234" s="10" t="s">
         <x:v>3</x:v>
@@ -11167,13 +11193,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C235" s="10" t="s">
-        <x:v>321</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="D235" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E235" s="10" t="s">
-        <x:v>331</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="F235" s="10" t="s">
         <x:v>3</x:v>
@@ -11201,13 +11227,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C236" s="10" t="s">
-        <x:v>321</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="D236" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E236" s="10" t="s">
-        <x:v>332</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="F236" s="10" t="s">
         <x:v>3</x:v>
@@ -11235,13 +11261,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C237" s="10" t="s">
-        <x:v>333</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="D237" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E237" s="10" t="s">
-        <x:v>334</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="F237" s="10" t="s">
         <x:v>3</x:v>
@@ -11269,13 +11295,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C238" s="10" t="s">
-        <x:v>333</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="D238" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E238" s="10" t="s">
-        <x:v>335</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="F238" s="10" t="s">
         <x:v>3</x:v>
@@ -11303,13 +11329,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C239" s="10" t="s">
-        <x:v>333</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="D239" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E239" s="10" t="s">
-        <x:v>336</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="F239" s="10" t="s">
         <x:v>3</x:v>
@@ -11337,13 +11363,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C240" s="10" t="s">
-        <x:v>333</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="D240" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E240" s="10" t="s">
-        <x:v>337</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="F240" s="10" t="s">
         <x:v>3</x:v>
@@ -11371,13 +11397,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C241" s="10" t="s">
-        <x:v>333</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="D241" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E241" s="10" t="s">
-        <x:v>338</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="F241" s="10" t="s">
         <x:v>3</x:v>
@@ -11405,13 +11431,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C242" s="10" t="s">
-        <x:v>333</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="D242" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E242" s="10" t="s">
-        <x:v>339</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="F242" s="10" t="s">
         <x:v>3</x:v>
@@ -11439,13 +11465,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C243" s="10" t="s">
-        <x:v>333</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="D243" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E243" s="10" t="s">
-        <x:v>340</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="F243" s="10" t="s">
         <x:v>3</x:v>
@@ -11473,13 +11499,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C244" s="10" t="s">
-        <x:v>333</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="D244" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E244" s="10" t="s">
-        <x:v>341</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="F244" s="10" t="s">
         <x:v>3</x:v>
@@ -11507,13 +11533,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C245" s="10" t="s">
-        <x:v>333</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="D245" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E245" s="10" t="s">
-        <x:v>342</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="F245" s="10" t="s">
         <x:v>3</x:v>
@@ -11541,13 +11567,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C246" s="10" t="s">
-        <x:v>333</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="D246" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E246" s="10" t="s">
-        <x:v>343</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="F246" s="10" t="s">
         <x:v>3</x:v>
@@ -11575,13 +11601,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C247" s="10" t="s">
-        <x:v>333</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="D247" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E247" s="10" t="s">
-        <x:v>344</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="F247" s="10" t="s">
         <x:v>3</x:v>
@@ -11609,13 +11635,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C248" s="10" t="s">
-        <x:v>333</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="D248" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E248" s="10" t="s">
-        <x:v>345</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="F248" s="10" t="s">
         <x:v>3</x:v>
@@ -11643,13 +11669,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C249" s="10" t="s">
-        <x:v>333</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="D249" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E249" s="10" t="s">
-        <x:v>346</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="F249" s="10" t="s">
         <x:v>3</x:v>
@@ -11677,13 +11703,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C250" s="10" t="s">
-        <x:v>333</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="D250" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E250" s="10" t="s">
-        <x:v>347</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="F250" s="10" t="s">
         <x:v>3</x:v>
@@ -11711,13 +11737,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C251" s="10" t="s">
-        <x:v>333</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="D251" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E251" s="10" t="s">
-        <x:v>348</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="F251" s="10" t="s">
         <x:v>3</x:v>
@@ -11745,13 +11771,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C252" s="10" t="s">
-        <x:v>333</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="D252" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E252" s="10" t="s">
-        <x:v>349</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="F252" s="10" t="s">
         <x:v>3</x:v>
@@ -11779,13 +11805,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C253" s="10" t="s">
-        <x:v>333</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="D253" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E253" s="10" t="s">
-        <x:v>350</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="F253" s="10" t="s">
         <x:v>3</x:v>
@@ -11813,13 +11839,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C254" s="10" t="s">
-        <x:v>351</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="D254" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E254" s="10" t="s">
-        <x:v>352</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="F254" s="10" t="s">
         <x:v>3</x:v>
@@ -11847,13 +11873,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C255" s="10" t="s">
-        <x:v>351</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="D255" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E255" s="10" t="s">
-        <x:v>353</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F255" s="10" t="s">
         <x:v>3</x:v>
@@ -11881,13 +11907,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C256" s="10" t="s">
-        <x:v>351</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="D256" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E256" s="10" t="s">
-        <x:v>354</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="F256" s="10" t="s">
         <x:v>3</x:v>
@@ -11915,13 +11941,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C257" s="10" t="s">
-        <x:v>351</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="D257" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E257" s="10" t="s">
-        <x:v>355</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="F257" s="10" t="s">
         <x:v>3</x:v>
@@ -11949,13 +11975,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C258" s="10" t="s">
-        <x:v>351</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="D258" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E258" s="10" t="s">
-        <x:v>356</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="F258" s="10" t="s">
         <x:v>3</x:v>
@@ -11983,13 +12009,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C259" s="10" t="s">
-        <x:v>351</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="D259" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E259" s="10" t="s">
-        <x:v>357</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="F259" s="10" t="s">
         <x:v>3</x:v>
@@ -12017,13 +12043,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C260" s="10" t="s">
-        <x:v>351</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="D260" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E260" s="10" t="s">
-        <x:v>358</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="F260" s="10" t="s">
         <x:v>3</x:v>
@@ -12051,13 +12077,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C261" s="10" t="s">
-        <x:v>351</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="D261" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E261" s="10" t="s">
-        <x:v>359</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="F261" s="10" t="s">
         <x:v>3</x:v>
@@ -12085,13 +12111,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C262" s="10" t="s">
-        <x:v>351</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="D262" s="10" t="s">
-        <x:v>360</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="E262" s="10" t="s">
-        <x:v>361</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="F262" s="10" t="s">
         <x:v>3</x:v>
@@ -12119,13 +12145,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C263" s="10" t="s">
-        <x:v>351</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="D263" s="10" t="s">
-        <x:v>360</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="E263" s="10" t="s">
-        <x:v>362</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="F263" s="10" t="s">
         <x:v>3</x:v>
@@ -12153,13 +12179,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C264" s="10" t="s">
-        <x:v>351</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="D264" s="10" t="s">
-        <x:v>360</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="E264" s="10" t="s">
-        <x:v>363</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="F264" s="10" t="s">
         <x:v>3</x:v>
@@ -12187,13 +12213,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C265" s="10" t="s">
-        <x:v>351</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="D265" s="10" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="E265" s="10" t="s">
         <x:v>360</x:v>
-      </x:c>
-      <x:c r="E265" s="10" t="s">
-        <x:v>364</x:v>
       </x:c>
       <x:c r="F265" s="10" t="s">
         <x:v>3</x:v>
@@ -12221,13 +12247,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C266" s="10" t="s">
-        <x:v>351</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="D266" s="10" t="s">
-        <x:v>360</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="E266" s="10" t="s">
-        <x:v>365</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="F266" s="10" t="s">
         <x:v>3</x:v>
@@ -12255,13 +12281,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C267" s="10" t="s">
-        <x:v>351</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="D267" s="10" t="s">
-        <x:v>360</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="E267" s="10" t="s">
-        <x:v>366</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="F267" s="10" t="s">
         <x:v>3</x:v>
@@ -12289,13 +12315,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C268" s="10" t="s">
-        <x:v>351</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="D268" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E268" s="10" t="s">
-        <x:v>367</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="F268" s="10" t="s">
         <x:v>3</x:v>
@@ -12323,13 +12349,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C269" s="10" t="s">
-        <x:v>351</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="D269" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E269" s="10" t="s">
-        <x:v>368</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="F269" s="10" t="s">
         <x:v>3</x:v>
@@ -12357,13 +12383,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C270" s="10" t="s">
-        <x:v>351</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="D270" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E270" s="10" t="s">
-        <x:v>369</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="F270" s="10" t="s">
         <x:v>3</x:v>
@@ -12391,13 +12417,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C271" s="10" t="s">
-        <x:v>351</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="D271" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E271" s="10" t="s">
-        <x:v>370</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="F271" s="10" t="s">
         <x:v>3</x:v>
@@ -12425,13 +12451,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C272" s="10" t="s">
-        <x:v>351</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="D272" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E272" s="10" t="s">
-        <x:v>371</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="F272" s="10" t="s">
         <x:v>3</x:v>
@@ -12459,13 +12485,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C273" s="10" t="s">
-        <x:v>351</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="D273" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E273" s="10" t="s">
-        <x:v>372</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="F273" s="10" t="s">
         <x:v>3</x:v>
@@ -12493,13 +12519,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C274" s="10" t="s">
-        <x:v>351</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="D274" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E274" s="10" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="F274" s="10" t="s">
         <x:v>3</x:v>
@@ -12527,13 +12553,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C275" s="10" t="s">
-        <x:v>351</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="D275" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E275" s="10" t="s">
-        <x:v>374</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="F275" s="10" t="s">
         <x:v>3</x:v>
@@ -12561,13 +12587,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C276" s="10" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="D276" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E276" s="10" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="F276" s="10" t="s">
         <x:v>3</x:v>
@@ -12595,13 +12621,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C277" s="10" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="D277" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E277" s="10" t="s">
-        <x:v>377</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="F277" s="10" t="s">
         <x:v>3</x:v>
@@ -12629,13 +12655,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C278" s="10" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="D278" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E278" s="10" t="s">
-        <x:v>378</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="F278" s="10" t="s">
         <x:v>3</x:v>
@@ -12663,13 +12689,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C279" s="10" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="D279" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E279" s="10" t="s">
-        <x:v>379</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="F279" s="10" t="s">
         <x:v>3</x:v>
@@ -12697,13 +12723,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C280" s="10" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="D280" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E280" s="10" t="s">
-        <x:v>380</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="F280" s="10" t="s">
         <x:v>3</x:v>
@@ -12731,13 +12757,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C281" s="10" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="D281" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E281" s="10" t="s">
-        <x:v>381</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="F281" s="10" t="s">
         <x:v>3</x:v>
@@ -12765,13 +12791,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C282" s="10" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="D282" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E282" s="10" t="s">
-        <x:v>382</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="F282" s="10" t="s">
         <x:v>3</x:v>
@@ -12799,13 +12825,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C283" s="10" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="D283" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E283" s="10" t="s">
-        <x:v>383</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="F283" s="10" t="s">
         <x:v>3</x:v>
@@ -12833,13 +12859,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C284" s="10" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="D284" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E284" s="10" t="s">
-        <x:v>384</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="F284" s="10" t="s">
         <x:v>3</x:v>
@@ -12867,13 +12893,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C285" s="10" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="D285" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E285" s="10" t="s">
-        <x:v>385</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="F285" s="10" t="s">
         <x:v>3</x:v>
@@ -12901,13 +12927,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C286" s="10" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="D286" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E286" s="10" t="s">
-        <x:v>386</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="F286" s="10" t="s">
         <x:v>3</x:v>
@@ -12935,13 +12961,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C287" s="10" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="D287" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E287" s="10" t="s">
-        <x:v>387</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="F287" s="10" t="s">
         <x:v>3</x:v>
@@ -12969,13 +12995,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C288" s="10" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="D288" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E288" s="10" t="s">
-        <x:v>388</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="F288" s="10" t="s">
         <x:v>3</x:v>
@@ -13003,13 +13029,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C289" s="10" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="D289" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E289" s="10" t="s">
-        <x:v>389</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="F289" s="10" t="s">
         <x:v>3</x:v>
@@ -13037,13 +13063,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C290" s="10" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="D290" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E290" s="10" t="s">
-        <x:v>390</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="F290" s="10" t="s">
         <x:v>3</x:v>
@@ -13071,13 +13097,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C291" s="10" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="D291" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E291" s="10" t="s">
-        <x:v>391</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="F291" s="10" t="s">
         <x:v>3</x:v>
@@ -13105,13 +13131,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C292" s="10" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="D292" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E292" s="10" t="s">
-        <x:v>392</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="F292" s="10" t="s">
         <x:v>3</x:v>
@@ -13139,13 +13165,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C293" s="10" t="s">
-        <x:v>393</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="D293" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E293" s="10" t="s">
-        <x:v>394</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="F293" s="10" t="s">
         <x:v>3</x:v>
@@ -13173,13 +13199,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C294" s="10" t="s">
-        <x:v>393</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="D294" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E294" s="10" t="s">
-        <x:v>395</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="F294" s="10" t="s">
         <x:v>3</x:v>
@@ -13207,13 +13233,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C295" s="10" t="s">
-        <x:v>393</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="D295" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E295" s="10" t="s">
-        <x:v>396</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="F295" s="10" t="s">
         <x:v>3</x:v>
@@ -13241,13 +13267,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C296" s="10" t="s">
-        <x:v>393</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="D296" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E296" s="10" t="s">
-        <x:v>397</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="F296" s="10" t="s">
         <x:v>3</x:v>
@@ -13275,13 +13301,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C297" s="10" t="s">
-        <x:v>393</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="D297" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E297" s="10" t="s">
-        <x:v>398</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="F297" s="10" t="s">
         <x:v>3</x:v>
@@ -13309,13 +13335,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C298" s="10" t="s">
-        <x:v>393</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="D298" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E298" s="10" t="s">
-        <x:v>399</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="F298" s="10" t="s">
         <x:v>3</x:v>
@@ -13343,13 +13369,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C299" s="10" t="s">
-        <x:v>393</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="D299" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E299" s="10" t="s">
-        <x:v>400</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="F299" s="10" t="s">
         <x:v>3</x:v>
@@ -13377,13 +13403,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C300" s="10" t="s">
-        <x:v>393</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="D300" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E300" s="10" t="s">
-        <x:v>401</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="F300" s="10" t="s">
         <x:v>3</x:v>
@@ -13411,13 +13437,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C301" s="10" t="s">
-        <x:v>402</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="D301" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E301" s="10" t="s">
-        <x:v>403</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="F301" s="10" t="s">
         <x:v>3</x:v>
@@ -13445,13 +13471,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C302" s="10" t="s">
-        <x:v>402</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="D302" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E302" s="10" t="s">
-        <x:v>404</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="F302" s="10" t="s">
         <x:v>3</x:v>
@@ -13479,13 +13505,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C303" s="10" t="s">
-        <x:v>402</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="D303" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E303" s="10" t="s">
-        <x:v>405</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="F303" s="10" t="s">
         <x:v>3</x:v>
@@ -13513,13 +13539,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C304" s="10" t="s">
-        <x:v>402</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="D304" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E304" s="10" t="s">
-        <x:v>406</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="F304" s="10" t="s">
         <x:v>3</x:v>
@@ -13547,13 +13573,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C305" s="10" t="s">
-        <x:v>402</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="D305" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E305" s="10" t="s">
-        <x:v>407</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="F305" s="10" t="s">
         <x:v>3</x:v>
@@ -13581,13 +13607,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C306" s="10" t="s">
-        <x:v>402</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="D306" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E306" s="10" t="s">
-        <x:v>408</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="F306" s="10" t="s">
         <x:v>3</x:v>
@@ -13615,13 +13641,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C307" s="10" t="s">
-        <x:v>402</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="D307" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E307" s="10" t="s">
-        <x:v>409</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="F307" s="10" t="s">
         <x:v>3</x:v>
@@ -13649,13 +13675,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C308" s="10" t="s">
-        <x:v>402</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="D308" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E308" s="10" t="s">
-        <x:v>410</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="F308" s="10" t="s">
         <x:v>3</x:v>
@@ -13683,13 +13709,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C309" s="10" t="s">
-        <x:v>402</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="D309" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E309" s="10" t="s">
-        <x:v>385</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="F309" s="10" t="s">
         <x:v>3</x:v>
@@ -13717,13 +13743,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C310" s="10" t="s">
-        <x:v>402</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="D310" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E310" s="10" t="s">
-        <x:v>411</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="F310" s="10" t="s">
         <x:v>3</x:v>
@@ -13751,13 +13777,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C311" s="10" t="s">
-        <x:v>402</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="D311" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E311" s="10" t="s">
-        <x:v>412</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="F311" s="10" t="s">
         <x:v>3</x:v>
@@ -13785,13 +13811,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C312" s="10" t="s">
-        <x:v>402</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="D312" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E312" s="10" t="s">
-        <x:v>413</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="F312" s="10" t="s">
         <x:v>3</x:v>
@@ -13819,13 +13845,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C313" s="10" t="s">
-        <x:v>402</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="D313" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E313" s="10" t="s">
-        <x:v>414</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="F313" s="10" t="s">
         <x:v>3</x:v>
@@ -13853,13 +13879,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C314" s="10" t="s">
-        <x:v>402</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="D314" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E314" s="10" t="s">
-        <x:v>415</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="F314" s="10" t="s">
         <x:v>3</x:v>
@@ -13887,13 +13913,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C315" s="10" t="s">
-        <x:v>402</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="D315" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E315" s="10" t="s">
-        <x:v>416</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="F315" s="10" t="s">
         <x:v>3</x:v>
@@ -13921,13 +13947,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C316" s="10" t="s">
-        <x:v>402</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="D316" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E316" s="10" t="s">
-        <x:v>417</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="F316" s="10" t="s">
         <x:v>3</x:v>
@@ -13955,13 +13981,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C317" s="10" t="s">
-        <x:v>418</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="D317" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E317" s="10" t="s">
-        <x:v>419</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="F317" s="10" t="s">
         <x:v>3</x:v>
@@ -13989,13 +14015,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C318" s="10" t="s">
-        <x:v>418</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="D318" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E318" s="10" t="s">
-        <x:v>420</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="F318" s="10" t="s">
         <x:v>3</x:v>
@@ -14023,13 +14049,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C319" s="10" t="s">
-        <x:v>418</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="D319" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E319" s="10" t="s">
-        <x:v>421</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="F319" s="10" t="s">
         <x:v>3</x:v>
@@ -14057,13 +14083,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C320" s="10" t="s">
-        <x:v>418</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="D320" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E320" s="10" t="s">
-        <x:v>422</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="F320" s="10" t="s">
         <x:v>3</x:v>
@@ -14091,13 +14117,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C321" s="10" t="s">
-        <x:v>418</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="D321" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E321" s="10" t="s">
-        <x:v>423</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="F321" s="10" t="s">
         <x:v>3</x:v>
@@ -14125,13 +14151,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C322" s="10" t="s">
-        <x:v>418</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="D322" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E322" s="10" t="s">
-        <x:v>424</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="F322" s="10" t="s">
         <x:v>3</x:v>
@@ -14159,13 +14185,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C323" s="10" t="s">
-        <x:v>418</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="D323" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E323" s="10" t="s">
-        <x:v>425</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="F323" s="10" t="s">
         <x:v>3</x:v>
@@ -14193,13 +14219,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C324" s="10" t="s">
-        <x:v>418</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="D324" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E324" s="10" t="s">
-        <x:v>426</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="F324" s="10" t="s">
         <x:v>3</x:v>
@@ -14227,13 +14253,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C325" s="10" t="s">
-        <x:v>418</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="D325" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E325" s="10" t="s">
-        <x:v>427</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="F325" s="10" t="s">
         <x:v>3</x:v>
@@ -14261,13 +14287,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C326" s="10" t="s">
-        <x:v>418</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="D326" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E326" s="10" t="s">
-        <x:v>428</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="F326" s="10" t="s">
         <x:v>3</x:v>
@@ -14295,13 +14321,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C327" s="10" t="s">
-        <x:v>418</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="D327" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E327" s="10" t="s">
-        <x:v>429</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="F327" s="10" t="s">
         <x:v>3</x:v>
@@ -14329,13 +14355,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C328" s="10" t="s">
-        <x:v>418</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="D328" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E328" s="10" t="s">
-        <x:v>430</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="F328" s="10" t="s">
         <x:v>3</x:v>
@@ -14363,13 +14389,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C329" s="10" t="s">
-        <x:v>418</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="D329" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E329" s="10" t="s">
-        <x:v>431</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="F329" s="10" t="s">
         <x:v>3</x:v>
@@ -14397,13 +14423,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C330" s="10" t="s">
-        <x:v>418</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="D330" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E330" s="10" t="s">
-        <x:v>432</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="F330" s="10" t="s">
         <x:v>3</x:v>
@@ -14431,13 +14457,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C331" s="10" t="s">
-        <x:v>418</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="D331" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E331" s="10" t="s">
-        <x:v>433</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="F331" s="10" t="s">
         <x:v>3</x:v>
@@ -14465,13 +14491,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C332" s="10" t="s">
-        <x:v>434</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="D332" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E332" s="10" t="s">
-        <x:v>435</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="F332" s="10" t="s">
         <x:v>3</x:v>
@@ -14499,13 +14525,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C333" s="10" t="s">
-        <x:v>434</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="D333" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E333" s="10" t="s">
-        <x:v>436</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="F333" s="10" t="s">
         <x:v>3</x:v>
@@ -14533,13 +14559,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C334" s="10" t="s">
-        <x:v>434</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="D334" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E334" s="10" t="s">
-        <x:v>437</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="F334" s="10" t="s">
         <x:v>3</x:v>
@@ -14567,13 +14593,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C335" s="10" t="s">
-        <x:v>434</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="D335" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E335" s="10" t="s">
-        <x:v>438</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="F335" s="10" t="s">
         <x:v>3</x:v>
@@ -14601,13 +14627,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C336" s="10" t="s">
-        <x:v>434</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="D336" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E336" s="10" t="s">
-        <x:v>439</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="F336" s="10" t="s">
         <x:v>3</x:v>
@@ -14635,13 +14661,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C337" s="10" t="s">
-        <x:v>434</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="D337" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E337" s="10" t="s">
-        <x:v>440</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="F337" s="10" t="s">
         <x:v>3</x:v>
@@ -14669,13 +14695,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C338" s="10" t="s">
-        <x:v>434</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="D338" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E338" s="10" t="s">
-        <x:v>441</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="F338" s="10" t="s">
         <x:v>3</x:v>
@@ -14703,13 +14729,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C339" s="10" t="s">
-        <x:v>434</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="D339" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E339" s="10" t="s">
-        <x:v>442</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="F339" s="10" t="s">
         <x:v>3</x:v>
@@ -14737,13 +14763,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C340" s="10" t="s">
-        <x:v>434</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="D340" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E340" s="10" t="s">
-        <x:v>443</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="F340" s="10" t="s">
         <x:v>3</x:v>
@@ -14771,13 +14797,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C341" s="10" t="s">
-        <x:v>434</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="D341" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E341" s="10" t="s">
-        <x:v>444</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="F341" s="10" t="s">
         <x:v>3</x:v>
@@ -14805,13 +14831,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C342" s="10" t="s">
-        <x:v>434</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="D342" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E342" s="10" t="s">
-        <x:v>445</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="F342" s="10" t="s">
         <x:v>3</x:v>
@@ -14839,13 +14865,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C343" s="10" t="s">
-        <x:v>434</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="D343" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E343" s="10" t="s">
-        <x:v>446</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="F343" s="10" t="s">
         <x:v>3</x:v>
@@ -14873,13 +14899,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C344" s="10" t="s">
-        <x:v>434</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="D344" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E344" s="10" t="s">
-        <x:v>447</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="F344" s="10" t="s">
         <x:v>3</x:v>
@@ -14907,13 +14933,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C345" s="10" t="s">
-        <x:v>434</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="D345" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E345" s="10" t="s">
-        <x:v>448</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="F345" s="10" t="s">
         <x:v>3</x:v>
@@ -14941,13 +14967,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C346" s="10" t="s">
-        <x:v>449</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="D346" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E346" s="10" t="s">
-        <x:v>450</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="F346" s="10" t="s">
         <x:v>3</x:v>
@@ -14975,13 +15001,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C347" s="10" t="s">
-        <x:v>449</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="D347" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E347" s="10" t="s">
-        <x:v>451</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="F347" s="10" t="s">
         <x:v>3</x:v>
@@ -15009,13 +15035,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C348" s="10" t="s">
-        <x:v>449</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="D348" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E348" s="10" t="s">
-        <x:v>452</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="F348" s="10" t="s">
         <x:v>3</x:v>
@@ -15043,13 +15069,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C349" s="10" t="s">
-        <x:v>449</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="D349" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E349" s="10" t="s">
-        <x:v>453</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="F349" s="10" t="s">
         <x:v>3</x:v>
@@ -15077,13 +15103,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C350" s="10" t="s">
-        <x:v>449</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="D350" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E350" s="10" t="s">
-        <x:v>454</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="F350" s="10" t="s">
         <x:v>3</x:v>
@@ -15111,13 +15137,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C351" s="10" t="s">
-        <x:v>449</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="D351" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E351" s="10" t="s">
-        <x:v>455</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="F351" s="10" t="s">
         <x:v>3</x:v>
@@ -15145,13 +15171,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C352" s="10" t="s">
-        <x:v>449</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="D352" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E352" s="10" t="s">
-        <x:v>456</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="F352" s="10" t="s">
         <x:v>3</x:v>
@@ -15179,13 +15205,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C353" s="10" t="s">
-        <x:v>449</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="D353" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E353" s="10" t="s">
-        <x:v>457</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="F353" s="10" t="s">
         <x:v>3</x:v>
@@ -15213,13 +15239,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C354" s="10" t="s">
-        <x:v>449</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="D354" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E354" s="10" t="s">
-        <x:v>458</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="F354" s="10" t="s">
         <x:v>3</x:v>
@@ -15247,13 +15273,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C355" s="10" t="s">
-        <x:v>449</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="D355" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E355" s="10" t="s">
-        <x:v>459</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="F355" s="10" t="s">
         <x:v>3</x:v>
@@ -15281,13 +15307,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C356" s="10" t="s">
-        <x:v>449</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="D356" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E356" s="10" t="s">
-        <x:v>460</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="F356" s="10" t="s">
         <x:v>3</x:v>
@@ -15315,13 +15341,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C357" s="10" t="s">
-        <x:v>461</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="D357" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E357" s="10" t="s">
-        <x:v>462</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="F357" s="10" t="s">
         <x:v>3</x:v>
@@ -15349,13 +15375,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C358" s="10" t="s">
-        <x:v>461</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="D358" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E358" s="10" t="s">
-        <x:v>463</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F358" s="10" t="s">
         <x:v>3</x:v>
@@ -15383,13 +15409,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C359" s="10" t="s">
-        <x:v>461</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="D359" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E359" s="10" t="s">
-        <x:v>464</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="F359" s="10" t="s">
         <x:v>3</x:v>
@@ -15417,13 +15443,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C360" s="10" t="s">
-        <x:v>461</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="D360" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E360" s="10" t="s">
-        <x:v>465</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="F360" s="10" t="s">
         <x:v>3</x:v>
@@ -15451,13 +15477,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C361" s="10" t="s">
-        <x:v>461</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="D361" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E361" s="10" t="s">
-        <x:v>466</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="F361" s="10" t="s">
         <x:v>3</x:v>
@@ -15485,13 +15511,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C362" s="10" t="s">
-        <x:v>461</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="D362" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E362" s="10" t="s">
-        <x:v>467</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="F362" s="10" t="s">
         <x:v>3</x:v>
@@ -15519,13 +15545,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C363" s="10" t="s">
-        <x:v>461</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="D363" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E363" s="10" t="s">
-        <x:v>468</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="F363" s="10" t="s">
         <x:v>3</x:v>
@@ -15553,13 +15579,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C364" s="10" t="s">
-        <x:v>461</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="D364" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E364" s="10" t="s">
-        <x:v>469</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="F364" s="10" t="s">
         <x:v>3</x:v>
@@ -15587,13 +15613,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C365" s="10" t="s">
-        <x:v>461</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="D365" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E365" s="10" t="s">
-        <x:v>470</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="F365" s="10" t="s">
         <x:v>3</x:v>
@@ -15621,13 +15647,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C366" s="10" t="s">
-        <x:v>471</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="D366" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E366" s="10" t="s">
-        <x:v>472</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="F366" s="10" t="s">
         <x:v>3</x:v>
@@ -15655,13 +15681,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C367" s="10" t="s">
-        <x:v>471</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="D367" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E367" s="10" t="s">
-        <x:v>473</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="F367" s="10" t="s">
         <x:v>3</x:v>
@@ -15689,13 +15715,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C368" s="10" t="s">
-        <x:v>471</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="D368" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E368" s="10" t="s">
-        <x:v>474</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="F368" s="10" t="s">
         <x:v>3</x:v>
@@ -15723,13 +15749,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C369" s="10" t="s">
-        <x:v>471</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="D369" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E369" s="10" t="s">
-        <x:v>475</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="F369" s="10" t="s">
         <x:v>3</x:v>
@@ -15757,13 +15783,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C370" s="10" t="s">
-        <x:v>471</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="D370" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E370" s="10" t="s">
-        <x:v>476</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="F370" s="10" t="s">
         <x:v>3</x:v>
@@ -15791,13 +15817,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C371" s="10" t="s">
-        <x:v>471</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="D371" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E371" s="10" t="s">
-        <x:v>477</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="F371" s="10" t="s">
         <x:v>3</x:v>
@@ -15825,13 +15851,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C372" s="10" t="s">
-        <x:v>471</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="D372" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E372" s="10" t="s">
-        <x:v>478</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="F372" s="10" t="s">
         <x:v>3</x:v>
@@ -15859,13 +15885,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C373" s="10" t="s">
-        <x:v>471</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="D373" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E373" s="10" t="s">
-        <x:v>479</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="F373" s="10" t="s">
         <x:v>3</x:v>
@@ -15893,13 +15919,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C374" s="10" t="s">
-        <x:v>471</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="D374" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E374" s="10" t="s">
-        <x:v>480</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="F374" s="10" t="s">
         <x:v>3</x:v>
@@ -15927,13 +15953,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C375" s="10" t="s">
-        <x:v>471</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="D375" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E375" s="10" t="s">
-        <x:v>481</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="F375" s="10" t="s">
         <x:v>3</x:v>
@@ -15961,13 +15987,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C376" s="10" t="s">
-        <x:v>471</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="D376" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E376" s="10" t="s">
-        <x:v>482</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="F376" s="10" t="s">
         <x:v>3</x:v>
@@ -15995,13 +16021,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C377" s="10" t="s">
-        <x:v>471</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="D377" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E377" s="10" t="s">
-        <x:v>483</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="F377" s="10" t="s">
         <x:v>3</x:v>
@@ -16029,13 +16055,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C378" s="10" t="s">
-        <x:v>484</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="D378" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E378" s="10" t="s">
-        <x:v>485</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="F378" s="10" t="s">
         <x:v>3</x:v>
@@ -16063,13 +16089,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C379" s="10" t="s">
-        <x:v>484</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="D379" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E379" s="10" t="s">
-        <x:v>486</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="F379" s="10" t="s">
         <x:v>3</x:v>
@@ -16097,13 +16123,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C380" s="10" t="s">
-        <x:v>484</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="D380" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E380" s="10" t="s">
-        <x:v>487</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="F380" s="10" t="s">
         <x:v>3</x:v>
@@ -16131,13 +16157,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C381" s="10" t="s">
-        <x:v>484</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="D381" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E381" s="10" t="s">
-        <x:v>488</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="F381" s="10" t="s">
         <x:v>3</x:v>
@@ -16165,13 +16191,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C382" s="10" t="s">
-        <x:v>484</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="D382" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E382" s="10" t="s">
-        <x:v>489</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="F382" s="10" t="s">
         <x:v>3</x:v>
@@ -16199,13 +16225,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C383" s="10" t="s">
-        <x:v>484</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="D383" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E383" s="10" t="s">
-        <x:v>490</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="F383" s="10" t="s">
         <x:v>3</x:v>
@@ -16233,13 +16259,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C384" s="10" t="s">
-        <x:v>484</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="D384" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E384" s="10" t="s">
-        <x:v>491</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="F384" s="10" t="s">
         <x:v>3</x:v>
@@ -16267,13 +16293,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C385" s="10" t="s">
-        <x:v>484</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="D385" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E385" s="10" t="s">
-        <x:v>492</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="F385" s="10" t="s">
         <x:v>3</x:v>
@@ -16301,13 +16327,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C386" s="10" t="s">
-        <x:v>484</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="D386" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E386" s="10" t="s">
-        <x:v>493</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="F386" s="10" t="s">
         <x:v>3</x:v>
@@ -16335,13 +16361,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C387" s="10" t="s">
-        <x:v>484</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="D387" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E387" s="10" t="s">
-        <x:v>411</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="F387" s="10" t="s">
         <x:v>3</x:v>
@@ -16369,13 +16395,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C388" s="10" t="s">
-        <x:v>484</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="D388" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E388" s="10" t="s">
-        <x:v>494</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="F388" s="10" t="s">
         <x:v>3</x:v>
@@ -16403,13 +16429,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C389" s="10" t="s">
-        <x:v>484</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="D389" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E389" s="10" t="s">
-        <x:v>495</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="F389" s="10" t="s">
         <x:v>3</x:v>
@@ -16437,13 +16463,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C390" s="10" t="s">
-        <x:v>484</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="D390" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E390" s="10" t="s">
-        <x:v>496</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="F390" s="10" t="s">
         <x:v>3</x:v>
@@ -16471,13 +16497,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C391" s="10" t="s">
-        <x:v>484</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="D391" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E391" s="10" t="s">
-        <x:v>497</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="F391" s="10" t="s">
         <x:v>3</x:v>
@@ -16505,13 +16531,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C392" s="10" t="s">
-        <x:v>484</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="D392" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E392" s="10" t="s">
-        <x:v>498</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="F392" s="10" t="s">
         <x:v>3</x:v>
@@ -16539,13 +16565,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C393" s="10" t="s">
-        <x:v>484</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="D393" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E393" s="10" t="s">
-        <x:v>499</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="F393" s="10" t="s">
         <x:v>3</x:v>
@@ -16573,13 +16599,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C394" s="10" t="s">
-        <x:v>500</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="D394" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E394" s="10" t="s">
-        <x:v>501</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="F394" s="10" t="s">
         <x:v>3</x:v>
@@ -16607,13 +16633,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C395" s="10" t="s">
-        <x:v>500</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="D395" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E395" s="10" t="s">
-        <x:v>502</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="F395" s="10" t="s">
         <x:v>3</x:v>
@@ -16641,13 +16667,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C396" s="10" t="s">
-        <x:v>500</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="D396" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E396" s="10" t="s">
-        <x:v>503</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="F396" s="10" t="s">
         <x:v>3</x:v>
@@ -16675,13 +16701,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C397" s="10" t="s">
-        <x:v>500</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="D397" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E397" s="10" t="s">
-        <x:v>504</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="F397" s="10" t="s">
         <x:v>3</x:v>
@@ -16709,13 +16735,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C398" s="10" t="s">
-        <x:v>500</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="D398" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E398" s="10" t="s">
-        <x:v>505</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="F398" s="10" t="s">
         <x:v>3</x:v>
@@ -16743,13 +16769,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C399" s="10" t="s">
-        <x:v>500</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="D399" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E399" s="10" t="s">
-        <x:v>506</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="F399" s="10" t="s">
         <x:v>3</x:v>
@@ -16777,13 +16803,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C400" s="10" t="s">
-        <x:v>500</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="D400" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E400" s="10" t="s">
-        <x:v>507</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="F400" s="10" t="s">
         <x:v>3</x:v>
@@ -16811,13 +16837,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C401" s="10" t="s">
-        <x:v>500</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="D401" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E401" s="10" t="s">
-        <x:v>508</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="F401" s="10" t="s">
         <x:v>3</x:v>
@@ -16845,13 +16871,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C402" s="10" t="s">
-        <x:v>509</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="D402" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E402" s="10" t="s">
-        <x:v>510</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="F402" s="10" t="s">
         <x:v>3</x:v>
@@ -16879,13 +16905,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C403" s="10" t="s">
-        <x:v>509</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="D403" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E403" s="10" t="s">
-        <x:v>511</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="F403" s="10" t="s">
         <x:v>3</x:v>
@@ -16913,13 +16939,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C404" s="10" t="s">
-        <x:v>509</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="D404" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E404" s="10" t="s">
-        <x:v>512</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="F404" s="10" t="s">
         <x:v>3</x:v>
@@ -16947,13 +16973,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C405" s="10" t="s">
-        <x:v>509</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="D405" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E405" s="10" t="s">
-        <x:v>513</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="F405" s="10" t="s">
         <x:v>3</x:v>
@@ -16981,13 +17007,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C406" s="10" t="s">
-        <x:v>509</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="D406" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E406" s="10" t="s">
-        <x:v>514</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="F406" s="10" t="s">
         <x:v>3</x:v>
@@ -17015,13 +17041,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C407" s="10" t="s">
-        <x:v>509</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="D407" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E407" s="10" t="s">
-        <x:v>515</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="F407" s="10" t="s">
         <x:v>3</x:v>
@@ -17049,13 +17075,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C408" s="10" t="s">
-        <x:v>509</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="D408" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E408" s="10" t="s">
-        <x:v>516</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="F408" s="10" t="s">
         <x:v>3</x:v>
@@ -17083,13 +17109,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C409" s="10" t="s">
-        <x:v>509</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="D409" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E409" s="10" t="s">
-        <x:v>517</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="F409" s="10" t="s">
         <x:v>3</x:v>
@@ -17117,13 +17143,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C410" s="10" t="s">
-        <x:v>509</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="D410" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E410" s="10" t="s">
-        <x:v>457</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="F410" s="10" t="s">
         <x:v>3</x:v>
@@ -17151,13 +17177,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C411" s="10" t="s">
-        <x:v>509</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="D411" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E411" s="10" t="s">
-        <x:v>518</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="F411" s="10" t="s">
         <x:v>3</x:v>
@@ -17185,13 +17211,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C412" s="10" t="s">
-        <x:v>509</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="D412" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E412" s="10" t="s">
-        <x:v>519</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="F412" s="10" t="s">
         <x:v>3</x:v>
@@ -17219,13 +17245,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C413" s="10" t="s">
-        <x:v>509</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="D413" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E413" s="10" t="s">
-        <x:v>520</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="F413" s="10" t="s">
         <x:v>3</x:v>
@@ -17253,13 +17279,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C414" s="10" t="s">
-        <x:v>509</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="D414" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E414" s="10" t="s">
-        <x:v>521</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="F414" s="10" t="s">
         <x:v>3</x:v>
@@ -17287,13 +17313,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C415" s="10" t="s">
-        <x:v>509</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="D415" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E415" s="10" t="s">
-        <x:v>522</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="F415" s="10" t="s">
         <x:v>3</x:v>
@@ -17321,13 +17347,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C416" s="10" t="s">
-        <x:v>523</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="D416" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E416" s="10" t="s">
-        <x:v>524</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="F416" s="10" t="s">
         <x:v>3</x:v>
@@ -17355,13 +17381,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C417" s="10" t="s">
-        <x:v>523</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="D417" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E417" s="10" t="s">
-        <x:v>525</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="F417" s="10" t="s">
         <x:v>3</x:v>
@@ -17389,13 +17415,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C418" s="10" t="s">
-        <x:v>523</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="D418" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E418" s="10" t="s">
-        <x:v>526</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="F418" s="10" t="s">
         <x:v>3</x:v>
@@ -17423,13 +17449,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C419" s="10" t="s">
-        <x:v>523</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="D419" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E419" s="10" t="s">
-        <x:v>527</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="F419" s="10" t="s">
         <x:v>3</x:v>
@@ -17457,13 +17483,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C420" s="10" t="s">
-        <x:v>523</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="D420" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E420" s="10" t="s">
-        <x:v>528</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="F420" s="10" t="s">
         <x:v>3</x:v>
@@ -17491,13 +17517,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C421" s="10" t="s">
-        <x:v>523</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="D421" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E421" s="10" t="s">
-        <x:v>529</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="F421" s="10" t="s">
         <x:v>3</x:v>
@@ -17525,13 +17551,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C422" s="10" t="s">
-        <x:v>523</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="D422" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E422" s="10" t="s">
-        <x:v>530</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="F422" s="10" t="s">
         <x:v>3</x:v>
@@ -17559,13 +17585,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C423" s="10" t="s">
-        <x:v>523</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="D423" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E423" s="10" t="s">
-        <x:v>531</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="F423" s="10" t="s">
         <x:v>3</x:v>
@@ -17593,13 +17619,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C424" s="10" t="s">
-        <x:v>523</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="D424" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E424" s="10" t="s">
-        <x:v>532</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="F424" s="10" t="s">
         <x:v>3</x:v>
@@ -17627,13 +17653,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C425" s="10" t="s">
-        <x:v>523</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="D425" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E425" s="10" t="s">
-        <x:v>533</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="F425" s="10" t="s">
         <x:v>3</x:v>
@@ -17661,13 +17687,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C426" s="10" t="s">
-        <x:v>523</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="D426" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E426" s="10" t="s">
-        <x:v>534</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="F426" s="10" t="s">
         <x:v>3</x:v>
@@ -17695,13 +17721,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C427" s="10" t="s">
-        <x:v>523</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="D427" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E427" s="10" t="s">
-        <x:v>535</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="F427" s="10" t="s">
         <x:v>3</x:v>
@@ -17729,13 +17755,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C428" s="10" t="s">
-        <x:v>523</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="D428" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E428" s="10" t="s">
-        <x:v>536</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="F428" s="10" t="s">
         <x:v>3</x:v>
@@ -17763,13 +17789,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C429" s="10" t="s">
-        <x:v>523</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="D429" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E429" s="10" t="s">
-        <x:v>537</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="F429" s="10" t="s">
         <x:v>3</x:v>
@@ -17797,13 +17823,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C430" s="10" t="s">
-        <x:v>523</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="D430" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E430" s="10" t="s">
-        <x:v>538</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="F430" s="10" t="s">
         <x:v>3</x:v>
@@ -17831,13 +17857,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C431" s="10" t="s">
-        <x:v>539</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="D431" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E431" s="10" t="s">
-        <x:v>540</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="F431" s="10" t="s">
         <x:v>3</x:v>
@@ -17865,13 +17891,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C432" s="10" t="s">
-        <x:v>539</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="D432" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E432" s="10" t="s">
-        <x:v>541</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="F432" s="10" t="s">
         <x:v>3</x:v>
@@ -17899,13 +17925,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C433" s="10" t="s">
-        <x:v>539</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="D433" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E433" s="10" t="s">
-        <x:v>542</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="F433" s="10" t="s">
         <x:v>3</x:v>
@@ -17933,13 +17959,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C434" s="10" t="s">
-        <x:v>539</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="D434" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E434" s="10" t="s">
-        <x:v>543</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="F434" s="10" t="s">
         <x:v>3</x:v>
@@ -17967,13 +17993,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C435" s="10" t="s">
-        <x:v>539</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="D435" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E435" s="10" t="s">
-        <x:v>544</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="F435" s="10" t="s">
         <x:v>3</x:v>
@@ -18001,13 +18027,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C436" s="10" t="s">
-        <x:v>539</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="D436" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E436" s="10" t="s">
-        <x:v>545</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="F436" s="10" t="s">
         <x:v>3</x:v>
@@ -18035,13 +18061,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C437" s="10" t="s">
-        <x:v>539</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="D437" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E437" s="10" t="s">
-        <x:v>546</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="F437" s="10" t="s">
         <x:v>3</x:v>
@@ -18069,13 +18095,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C438" s="10" t="s">
-        <x:v>539</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="D438" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E438" s="10" t="s">
-        <x:v>547</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="F438" s="10" t="s">
         <x:v>3</x:v>
@@ -18103,13 +18129,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C439" s="10" t="s">
-        <x:v>539</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="D439" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E439" s="10" t="s">
-        <x:v>548</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="F439" s="10" t="s">
         <x:v>3</x:v>
@@ -18137,13 +18163,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C440" s="10" t="s">
-        <x:v>539</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="D440" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E440" s="10" t="s">
-        <x:v>549</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="F440" s="10" t="s">
         <x:v>3</x:v>
@@ -18171,13 +18197,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C441" s="10" t="s">
-        <x:v>539</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="D441" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E441" s="10" t="s">
-        <x:v>550</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="F441" s="10" t="s">
         <x:v>3</x:v>
@@ -18205,13 +18231,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C442" s="10" t="s">
-        <x:v>539</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="D442" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E442" s="10" t="s">
-        <x:v>430</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="F442" s="10" t="s">
         <x:v>3</x:v>
@@ -18239,13 +18265,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C443" s="10" t="s">
-        <x:v>539</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="D443" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E443" s="10" t="s">
-        <x:v>551</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="F443" s="10" t="s">
         <x:v>3</x:v>
@@ -18273,13 +18299,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C444" s="10" t="s">
-        <x:v>539</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="D444" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E444" s="10" t="s">
-        <x:v>552</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="F444" s="10" t="s">
         <x:v>3</x:v>
@@ -18307,13 +18333,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C445" s="10" t="s">
-        <x:v>553</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="D445" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E445" s="10" t="s">
-        <x:v>554</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="F445" s="10" t="s">
         <x:v>3</x:v>
@@ -18341,13 +18367,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C446" s="10" t="s">
-        <x:v>553</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="D446" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E446" s="10" t="s">
-        <x:v>555</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="F446" s="10" t="s">
         <x:v>3</x:v>
@@ -18375,13 +18401,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C447" s="10" t="s">
-        <x:v>553</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="D447" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E447" s="10" t="s">
-        <x:v>556</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="F447" s="10" t="s">
         <x:v>3</x:v>
@@ -18409,13 +18435,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C448" s="10" t="s">
-        <x:v>553</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="D448" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E448" s="10" t="s">
-        <x:v>557</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="F448" s="10" t="s">
         <x:v>3</x:v>
@@ -18443,13 +18469,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C449" s="10" t="s">
-        <x:v>553</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="D449" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E449" s="10" t="s">
-        <x:v>558</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="F449" s="10" t="s">
         <x:v>3</x:v>
@@ -18477,13 +18503,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C450" s="10" t="s">
-        <x:v>553</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="D450" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E450" s="10" t="s">
-        <x:v>559</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="F450" s="10" t="s">
         <x:v>3</x:v>
@@ -18511,13 +18537,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C451" s="10" t="s">
-        <x:v>553</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="D451" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E451" s="10" t="s">
-        <x:v>560</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="F451" s="10" t="s">
         <x:v>3</x:v>
@@ -18545,13 +18571,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C452" s="10" t="s">
-        <x:v>553</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="D452" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E452" s="10" t="s">
-        <x:v>561</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="F452" s="10" t="s">
         <x:v>3</x:v>
@@ -18579,13 +18605,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C453" s="10" t="s">
-        <x:v>553</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="D453" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E453" s="10" t="s">
-        <x:v>562</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="F453" s="10" t="s">
         <x:v>3</x:v>
@@ -18613,13 +18639,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C454" s="10" t="s">
-        <x:v>553</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="D454" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E454" s="10" t="s">
-        <x:v>563</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="F454" s="10" t="s">
         <x:v>3</x:v>
@@ -18647,13 +18673,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C455" s="10" t="s">
-        <x:v>553</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="D455" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E455" s="10" t="s">
-        <x:v>564</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="F455" s="10" t="s">
         <x:v>3</x:v>
@@ -18681,13 +18707,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C456" s="10" t="s">
-        <x:v>553</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="D456" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E456" s="10" t="s">
-        <x:v>565</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="F456" s="10" t="s">
         <x:v>3</x:v>
@@ -18715,13 +18741,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C457" s="10" t="s">
-        <x:v>553</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="D457" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E457" s="10" t="s">
-        <x:v>566</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="F457" s="10" t="s">
         <x:v>3</x:v>
@@ -18749,13 +18775,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C458" s="10" t="s">
-        <x:v>567</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="D458" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E458" s="10" t="s">
-        <x:v>568</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="F458" s="10" t="s">
         <x:v>3</x:v>
@@ -18783,13 +18809,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C459" s="10" t="s">
-        <x:v>567</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="D459" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E459" s="10" t="s">
-        <x:v>569</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="F459" s="10" t="s">
         <x:v>3</x:v>
@@ -18817,13 +18843,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C460" s="10" t="s">
-        <x:v>567</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="D460" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E460" s="10" t="s">
-        <x:v>570</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="F460" s="10" t="s">
         <x:v>3</x:v>
@@ -18851,13 +18877,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C461" s="10" t="s">
-        <x:v>567</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="D461" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E461" s="10" t="s">
-        <x:v>571</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="F461" s="10" t="s">
         <x:v>3</x:v>
@@ -18885,13 +18911,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C462" s="10" t="s">
-        <x:v>567</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="D462" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E462" s="10" t="s">
-        <x:v>572</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="F462" s="10" t="s">
         <x:v>3</x:v>
@@ -18919,13 +18945,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C463" s="10" t="s">
-        <x:v>567</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="D463" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E463" s="10" t="s">
-        <x:v>573</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="F463" s="10" t="s">
         <x:v>3</x:v>
@@ -18953,13 +18979,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C464" s="10" t="s">
-        <x:v>567</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="D464" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E464" s="10" t="s">
-        <x:v>574</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="F464" s="10" t="s">
         <x:v>3</x:v>
@@ -18987,13 +19013,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C465" s="10" t="s">
-        <x:v>567</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="D465" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E465" s="10" t="s">
-        <x:v>575</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="F465" s="10" t="s">
         <x:v>3</x:v>
@@ -19021,13 +19047,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C466" s="10" t="s">
-        <x:v>567</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="D466" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E466" s="10" t="s">
-        <x:v>576</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="F466" s="10" t="s">
         <x:v>3</x:v>
@@ -19055,13 +19081,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C467" s="10" t="s">
-        <x:v>567</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="D467" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E467" s="10" t="s">
-        <x:v>577</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="F467" s="10" t="s">
         <x:v>3</x:v>
@@ -19089,13 +19115,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C468" s="10" t="s">
-        <x:v>567</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="D468" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E468" s="10" t="s">
-        <x:v>578</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="F468" s="10" t="s">
         <x:v>3</x:v>
@@ -19123,13 +19149,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C469" s="10" t="s">
-        <x:v>567</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="D469" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E469" s="10" t="s">
-        <x:v>579</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="F469" s="10" t="s">
         <x:v>3</x:v>
@@ -19157,13 +19183,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C470" s="10" t="s">
-        <x:v>567</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="D470" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E470" s="10" t="s">
-        <x:v>580</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="F470" s="10" t="s">
         <x:v>3</x:v>
@@ -19191,13 +19217,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C471" s="10" t="s">
-        <x:v>567</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="D471" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E471" s="10" t="s">
-        <x:v>495</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="F471" s="10" t="s">
         <x:v>3</x:v>
@@ -19225,13 +19251,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C472" s="10" t="s">
-        <x:v>567</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="D472" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E472" s="10" t="s">
-        <x:v>581</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="F472" s="10" t="s">
         <x:v>3</x:v>
@@ -19259,13 +19285,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C473" s="10" t="s">
-        <x:v>567</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="D473" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E473" s="10" t="s">
-        <x:v>582</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="F473" s="10" t="s">
         <x:v>3</x:v>
@@ -19293,13 +19319,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C474" s="10" t="s">
-        <x:v>583</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="D474" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E474" s="10" t="s">
-        <x:v>584</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="F474" s="10" t="s">
         <x:v>3</x:v>
@@ -19327,13 +19353,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C475" s="10" t="s">
-        <x:v>583</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="D475" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E475" s="10" t="s">
-        <x:v>585</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="F475" s="10" t="s">
         <x:v>3</x:v>
@@ -19361,13 +19387,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C476" s="10" t="s">
-        <x:v>583</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="D476" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E476" s="10" t="s">
-        <x:v>586</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="F476" s="10" t="s">
         <x:v>3</x:v>
@@ -19395,13 +19421,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C477" s="10" t="s">
-        <x:v>583</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="D477" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E477" s="10" t="s">
-        <x:v>587</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="F477" s="10" t="s">
         <x:v>3</x:v>
@@ -19429,13 +19455,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C478" s="10" t="s">
-        <x:v>583</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="D478" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E478" s="10" t="s">
-        <x:v>588</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="F478" s="10" t="s">
         <x:v>3</x:v>
@@ -19463,13 +19489,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C479" s="10" t="s">
-        <x:v>583</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="D479" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E479" s="10" t="s">
-        <x:v>589</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="F479" s="10" t="s">
         <x:v>3</x:v>
@@ -19497,13 +19523,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C480" s="10" t="s">
-        <x:v>583</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="D480" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E480" s="10" t="s">
-        <x:v>590</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="F480" s="10" t="s">
         <x:v>3</x:v>
@@ -19531,13 +19557,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C481" s="10" t="s">
-        <x:v>583</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="D481" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E481" s="10" t="s">
-        <x:v>591</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="F481" s="10" t="s">
         <x:v>3</x:v>
@@ -19565,13 +19591,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C482" s="10" t="s">
-        <x:v>583</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="D482" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E482" s="10" t="s">
-        <x:v>592</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="F482" s="10" t="s">
         <x:v>3</x:v>
@@ -19599,13 +19625,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C483" s="10" t="s">
-        <x:v>583</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="D483" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E483" s="10" t="s">
-        <x:v>593</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="F483" s="10" t="s">
         <x:v>3</x:v>
@@ -19633,13 +19659,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C484" s="10" t="s">
-        <x:v>583</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="D484" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E484" s="10" t="s">
-        <x:v>594</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="F484" s="10" t="s">
         <x:v>3</x:v>
@@ -19667,13 +19693,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C485" s="10" t="s">
-        <x:v>583</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="D485" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E485" s="10" t="s">
-        <x:v>595</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="F485" s="10" t="s">
         <x:v>3</x:v>
@@ -19701,13 +19727,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C486" s="10" t="s">
-        <x:v>583</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="D486" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E486" s="10" t="s">
-        <x:v>596</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="F486" s="10" t="s">
         <x:v>3</x:v>
@@ -19735,13 +19761,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C487" s="10" t="s">
-        <x:v>583</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="D487" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E487" s="10" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="F487" s="10" t="s">
         <x:v>3</x:v>
@@ -19769,13 +19795,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C488" s="10" t="s">
-        <x:v>583</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="D488" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E488" s="10" t="s">
-        <x:v>598</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="F488" s="10" t="s">
         <x:v>3</x:v>
@@ -19803,13 +19829,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C489" s="10" t="s">
-        <x:v>583</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="D489" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E489" s="10" t="s">
-        <x:v>599</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="F489" s="10" t="s">
         <x:v>3</x:v>
@@ -19837,13 +19863,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C490" s="10" t="s">
-        <x:v>600</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="D490" s="10" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E490" s="10" t="s">
-        <x:v>602</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="F490" s="10" t="s">
         <x:v>3</x:v>
@@ -19871,13 +19897,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C491" s="10" t="s">
-        <x:v>600</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="D491" s="10" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E491" s="10" t="s">
-        <x:v>603</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="F491" s="10" t="s">
         <x:v>3</x:v>
@@ -19905,13 +19931,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C492" s="10" t="s">
+        <x:v>596</x:v>
+      </x:c>
+      <x:c r="D492" s="10" t="s">
+        <x:v>597</x:v>
+      </x:c>
+      <x:c r="E492" s="10" t="s">
         <x:v>600</x:v>
-      </x:c>
-      <x:c r="D492" s="10" t="s">
-        <x:v>601</x:v>
-      </x:c>
-      <x:c r="E492" s="10" t="s">
-        <x:v>604</x:v>
       </x:c>
       <x:c r="F492" s="10" t="s">
         <x:v>3</x:v>
@@ -19939,13 +19965,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C493" s="10" t="s">
-        <x:v>600</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="D493" s="10" t="s">
+        <x:v>597</x:v>
+      </x:c>
+      <x:c r="E493" s="10" t="s">
         <x:v>601</x:v>
-      </x:c>
-      <x:c r="E493" s="10" t="s">
-        <x:v>605</x:v>
       </x:c>
       <x:c r="F493" s="10" t="s">
         <x:v>3</x:v>
@@ -19973,13 +19999,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C494" s="10" t="s">
-        <x:v>600</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="D494" s="10" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E494" s="10" t="s">
-        <x:v>606</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="F494" s="10" t="s">
         <x:v>3</x:v>
@@ -20007,13 +20033,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C495" s="10" t="s">
-        <x:v>600</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="D495" s="10" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E495" s="10" t="s">
-        <x:v>607</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="F495" s="10" t="s">
         <x:v>3</x:v>
@@ -20041,13 +20067,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C496" s="10" t="s">
-        <x:v>600</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="D496" s="10" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E496" s="10" t="s">
-        <x:v>608</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="F496" s="10" t="s">
         <x:v>3</x:v>
@@ -20075,13 +20101,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C497" t="s">
-        <x:v>600</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="D497" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E497" t="s">
-        <x:v>609</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="F497" t="s">
         <x:v>3</x:v>
@@ -20109,13 +20135,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C498" t="s">
-        <x:v>600</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="D498" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E498" t="s">
-        <x:v>610</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="F498" t="s">
         <x:v>3</x:v>
@@ -20143,13 +20169,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C499" t="s">
-        <x:v>600</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="D499" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E499" t="s">
-        <x:v>611</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="F499" t="s">
         <x:v>3</x:v>
@@ -20177,13 +20203,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C500" t="s">
-        <x:v>600</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="D500" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E500" t="s">
-        <x:v>612</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="F500" t="s">
         <x:v>3</x:v>
@@ -20211,13 +20237,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C501" t="s">
-        <x:v>600</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="D501" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E501" t="s">
-        <x:v>613</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="F501" t="s">
         <x:v>3</x:v>
@@ -20245,13 +20271,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C502" t="s">
-        <x:v>600</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="D502" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E502" t="s">
-        <x:v>614</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="F502" t="s">
         <x:v>3</x:v>
@@ -20279,13 +20305,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C503" t="s">
-        <x:v>600</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="D503" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E503" t="s">
-        <x:v>615</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="F503" t="s">
         <x:v>3</x:v>
@@ -20313,13 +20339,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C504" t="s">
-        <x:v>600</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="D504" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E504" t="s">
-        <x:v>616</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="F504" t="s">
         <x:v>3</x:v>
@@ -20347,13 +20373,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C505" t="s">
-        <x:v>600</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="D505" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E505" t="s">
-        <x:v>617</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="F505" t="s">
         <x:v>3</x:v>
@@ -20381,13 +20407,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C506" t="s">
-        <x:v>600</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="D506" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E506" t="s">
-        <x:v>618</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="F506" t="s">
         <x:v>3</x:v>
@@ -20415,10 +20441,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C507" t="s">
-        <x:v>600</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="D507" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E507" t="s">
         <x:v>17</x:v>
@@ -20449,13 +20475,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C508" t="s">
-        <x:v>600</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="D508" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E508" t="s">
-        <x:v>619</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="F508" t="s">
         <x:v>3</x:v>
@@ -20483,13 +20509,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C509" t="s">
-        <x:v>600</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="D509" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E509" t="s">
-        <x:v>620</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="F509" t="s">
         <x:v>3</x:v>
@@ -20517,13 +20543,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C510" t="s">
-        <x:v>621</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="D510" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E510" t="s">
-        <x:v>622</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="F510" t="s">
         <x:v>3</x:v>
@@ -20551,13 +20577,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C511" t="s">
-        <x:v>621</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="D511" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E511" t="s">
-        <x:v>623</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="F511" t="s">
         <x:v>3</x:v>
@@ -20585,13 +20611,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C512" t="s">
-        <x:v>621</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="D512" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E512" t="s">
-        <x:v>624</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="F512" t="s">
         <x:v>3</x:v>
@@ -20619,13 +20645,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C513" t="s">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="D513" t="s">
+        <x:v>597</x:v>
+      </x:c>
+      <x:c r="E513" t="s">
         <x:v>621</x:v>
-      </x:c>
-      <x:c r="D513" t="s">
-        <x:v>601</x:v>
-      </x:c>
-      <x:c r="E513" t="s">
-        <x:v>625</x:v>
       </x:c>
       <x:c r="F513" t="s">
         <x:v>3</x:v>
@@ -20653,13 +20679,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C514" t="s">
-        <x:v>621</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="D514" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E514" t="s">
-        <x:v>626</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="F514" t="s">
         <x:v>3</x:v>
@@ -20687,13 +20713,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C515" t="s">
-        <x:v>621</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="D515" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E515" t="s">
-        <x:v>627</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="F515" t="s">
         <x:v>3</x:v>
@@ -20721,13 +20747,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C516" t="s">
-        <x:v>621</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="D516" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E516" t="s">
-        <x:v>628</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="F516" t="s">
         <x:v>3</x:v>
@@ -20755,13 +20781,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C517" t="s">
-        <x:v>621</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="D517" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E517" t="s">
-        <x:v>629</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="F517" t="s">
         <x:v>3</x:v>
@@ -20789,13 +20815,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C518" t="s">
-        <x:v>621</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="D518" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E518" t="s">
-        <x:v>630</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="F518" t="s">
         <x:v>3</x:v>
@@ -20823,13 +20849,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C519" t="s">
-        <x:v>621</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="D519" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E519" t="s">
-        <x:v>631</x:v>
+        <x:v>627</x:v>
       </x:c>
       <x:c r="F519" t="s">
         <x:v>3</x:v>
@@ -20857,13 +20883,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C520" t="s">
-        <x:v>621</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="D520" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E520" t="s">
-        <x:v>632</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="F520" t="s">
         <x:v>3</x:v>
@@ -20891,13 +20917,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C521" t="s">
-        <x:v>621</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="D521" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E521" t="s">
-        <x:v>633</x:v>
+        <x:v>629</x:v>
       </x:c>
       <x:c r="F521" t="s">
         <x:v>3</x:v>
@@ -20925,13 +20951,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C522" t="s">
-        <x:v>621</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="D522" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E522" t="s">
-        <x:v>634</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="F522" t="s">
         <x:v>3</x:v>
@@ -20959,13 +20985,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C523" t="s">
-        <x:v>621</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="D523" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E523" t="s">
-        <x:v>635</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="F523" t="s">
         <x:v>3</x:v>
@@ -20993,13 +21019,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C524" t="s">
-        <x:v>621</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="D524" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E524" t="s">
-        <x:v>636</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="F524" t="s">
         <x:v>3</x:v>
@@ -21027,13 +21053,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C525" t="s">
-        <x:v>621</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="D525" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E525" t="s">
-        <x:v>637</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="F525" t="s">
         <x:v>3</x:v>
@@ -21061,13 +21087,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C526" t="s">
-        <x:v>621</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="D526" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E526" t="s">
-        <x:v>638</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="F526" t="s">
         <x:v>3</x:v>
@@ -21095,13 +21121,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C527" t="s">
-        <x:v>621</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="D527" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E527" t="s">
-        <x:v>639</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="F527" t="s">
         <x:v>3</x:v>
@@ -21129,13 +21155,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C528" t="s">
-        <x:v>640</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="D528" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E528" t="s">
-        <x:v>641</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="F528" t="s">
         <x:v>3</x:v>
@@ -21163,13 +21189,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C529" t="s">
-        <x:v>640</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="D529" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E529" t="s">
-        <x:v>642</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="F529" t="s">
         <x:v>3</x:v>
@@ -21197,13 +21223,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C530" t="s">
-        <x:v>640</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="D530" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E530" t="s">
-        <x:v>643</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="F530" t="s">
         <x:v>3</x:v>
@@ -21231,13 +21257,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C531" t="s">
+        <x:v>636</x:v>
+      </x:c>
+      <x:c r="D531" t="s">
+        <x:v>597</x:v>
+      </x:c>
+      <x:c r="E531" t="s">
         <x:v>640</x:v>
-      </x:c>
-      <x:c r="D531" t="s">
-        <x:v>601</x:v>
-      </x:c>
-      <x:c r="E531" t="s">
-        <x:v>644</x:v>
       </x:c>
       <x:c r="F531" t="s">
         <x:v>3</x:v>
@@ -21265,13 +21291,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C532" t="s">
-        <x:v>640</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="D532" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E532" t="s">
-        <x:v>645</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="F532" t="s">
         <x:v>3</x:v>
@@ -21299,13 +21325,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C533" t="s">
-        <x:v>640</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="D533" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E533" t="s">
-        <x:v>646</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="F533" t="s">
         <x:v>3</x:v>
@@ -21333,13 +21359,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C534" t="s">
-        <x:v>640</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="D534" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E534" t="s">
-        <x:v>647</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="F534" t="s">
         <x:v>3</x:v>
@@ -26678,7 +26704,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a7a8663ebfe4066"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8efaa7a29eb54f79"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26826,15 +26852,15 @@
       </x:c>
       <x:c r="C5" t="n">
         <x:f>COUNTIFS(Checklist!$B:$B,A5,Checklist!$F:$F,"Chưa làm")</x:f>
-        <x:v>67</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D5" t="n">
         <x:f>COUNTIFS(Checklist!$B:$B,A5,Checklist!$F:$F,"Đang làm")</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E5" t="n">
         <x:f>COUNTIFS(Checklist!$B:$B,A5,Checklist!$F:$F,"Hoàn thành")</x:f>
-        <x:v>86</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F5" t="n">
         <x:f>COUNTIFS(Checklist!$B:$B,A5,Checklist!$F:$F,"Bị chặn")</x:f>
@@ -26846,7 +26872,7 @@
       </x:c>
       <x:c r="H5" s="6" t="n">
         <x:f t="shared" si="0">IFERROR(E5/B5,0)</x:f>
-        <x:v>0.5620915032679739</x:v>
+        <x:v>0.6405228758169934</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -27151,7 +27177,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e323ceb459c402e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1674582428814b2e"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">

--- a/CHECKLIST_TRIEN_KHAI_FULL.xlsx
+++ b/CHECKLIST_TRIEN_KHAI_FULL.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R0778639ab7ac45c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="Ra4983f8a6c4e481e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase Summary" sheetId="3" r:id="R3f1b907f723043dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="4" r:id="R834fa94213014256"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Ree558dcd69b74fc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="Rd8f59b92cb734ab7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase Summary" sheetId="3" r:id="R47e5eb15c5b2429e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="4" r:id="Re0dff43412244138"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -817,9 +817,6 @@
     <x:t xml:space="preserve">Abnormal sample load đúng bbox/labels; No Finding load với bbox (0,4), labels (0,).</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Dataloader smoke test num_workers=0 và num_workers&gt;0 PASS; all image IDs seen=4,894.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Tạo MMDetection config và loading-validation script.</x:t>
   </x:si>
   <x:si>
@@ -830,15 +827,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Tải Colab evidence về local và kiểm tra file/hash.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Cập nhật PROJECT_CONTEXT.md, PHASE_HANDOFF.md, research_log.md và checklist sau PASS.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">GPT final review Phase 2D.1 PASS; readiness flags cập nhật đúng, training vẫn locked.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Stage reviewed evidence, commit/push Phase 2D.1; không commit 4,894 JPG vào ordinary Git.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">2E. Fixed Train/Val/Test Split</x:t>
@@ -2400,7 +2388,7 @@
       </x:c>
       <x:c r="B4" s="2" t="n">
         <x:f>COUNTIF(Checklist!$F:$F,"Chưa làm")</x:f>
-        <x:v>354</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="D4" s="3" t="s">
         <x:v>4</x:v>
@@ -2418,7 +2406,7 @@
       </x:c>
       <x:c r="B5" s="2" t="n">
         <x:f>COUNTIF(Checklist!$F:$F,"Đang làm")</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="3" t="s">
         <x:v>7</x:v>
@@ -2436,7 +2424,7 @@
       </x:c>
       <x:c r="B6" s="2" t="n">
         <x:f>COUNTIF(Checklist!$F:$F,"Hoàn thành")</x:f>
-        <x:v>176</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="D6" s="3" t="s">
         <x:v>10</x:v>
@@ -2472,7 +2460,7 @@
       </x:c>
       <x:c r="B8" s="5" t="n">
         <x:f>IFERROR(B6/B3,0)</x:f>
-        <x:v>0.3302063789868668</x:v>
+        <x:v>0.3339587242026266</x:v>
       </x:c>
       <x:c r="D8" s="3" t="s">
         <x:v>16</x:v>
@@ -2641,15 +2629,15 @@
       </x:c>
       <x:c r="C15" t="n">
         <x:f>'Phase Summary'!C5</x:f>
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D15" t="n">
         <x:f>'Phase Summary'!D5</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E15" t="n">
         <x:f>'Phase Summary'!E5</x:f>
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F15" t="n">
         <x:f>'Phase Summary'!F5</x:f>
@@ -2661,7 +2649,7 @@
       </x:c>
       <x:c r="H15" s="6" t="n">
         <x:f>'Phase Summary'!H5</x:f>
-        <x:v>0.6405228758169934</x:v>
+        <x:v>0.6535947712418301</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -8454,9 +8442,9 @@
 reports/phase2D1B_full_preflight.json
 reports/phase2D1B_full_preflight.md</x:v>
       </x:c>
-      <x:c r="M158" s="10">
+      <x:c r="M158" s="10" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="42.150001525878906" customHeight="1">
@@ -8494,9 +8482,9 @@
 reports/phase2D1B_full_validation.md
 reports/phase2D1B_full_errors.csv</x:v>
       </x:c>
-      <x:c r="M159" s="10">
+      <x:c r="M159" s="10" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="52.79999923706055" customHeight="1">
@@ -8533,9 +8521,9 @@
         <x:v>reports/phase2D1B_full_metadata_audit.csv
 reports/phase2D1B_full_validation.json</x:v>
       </x:c>
-      <x:c r="M160" s="10">
+      <x:c r="M160" s="10" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="52.79999923706055" customHeight="1">
@@ -8572,9 +8560,9 @@
         <x:v>reports/phase2D1B_full_bbox_audit.csv
 reports/phase2D1B_full_validation.json</x:v>
       </x:c>
-      <x:c r="M161" s="10">
+      <x:c r="M161" s="10" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="52.79999923706055" customHeight="1">
@@ -8611,9 +8599,9 @@
         <x:v>data/processed/coco/coco_master_jpg.json
 reports/phase2D1B_full_validation.json</x:v>
       </x:c>
-      <x:c r="M162" s="10">
+      <x:c r="M162" s="10" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="42.150001525878906" customHeight="1">
@@ -8650,9 +8638,9 @@
         <x:v>data/processed/coco/coco_master_jpg.json
 reports/phase2D1B_full_validation.json</x:v>
       </x:c>
-      <x:c r="M163" s="10">
+      <x:c r="M163" s="10" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="42.150001525878906" customHeight="1">
@@ -8689,9 +8677,9 @@
         <x:v>reports/phase2D1B_full_no_finding_audit.csv
 reports/phase2D1B_full_validation.json</x:v>
       </x:c>
-      <x:c r="M164" s="10">
+      <x:c r="M164" s="10" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="42.150001525878906" customHeight="1">
@@ -8729,9 +8717,9 @@
 reports/phase2D1B_full_mapping.csv
 reports/phase2D1B_full_validation.json</x:v>
       </x:c>
-      <x:c r="M165" s="10">
+      <x:c r="M165" s="10" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="52.79999923706055" customHeight="1">
@@ -8768,9 +8756,9 @@
         <x:v>reports/phase2D1B_full_mapping.csv
 reports/phase2D1B_full_mapping.jsonl</x:v>
       </x:c>
-      <x:c r="M166" s="10">
+      <x:c r="M166" s="10" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="167" ht="84.44999694824219" customHeight="1">
@@ -8809,9 +8797,9 @@
 reports/phase2D1B_full_no_finding_audit.csv
 reports/phase2D1B_full_errors.csv</x:v>
       </x:c>
-      <x:c r="M167" s="10">
+      <x:c r="M167" s="10" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="52.79999923706055" customHeight="1">
@@ -8852,9 +8840,9 @@
 reports/phase2D1B_full_promotion.json
 reports/phase2D1B_full_cleanup_audit.json</x:v>
       </x:c>
-      <x:c r="M168" s="10">
+      <x:c r="M168" s="10" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="171.60000610351562" hidden="0" customHeight="1">
@@ -8892,9 +8880,9 @@
 reports/phase2D1B_full_promotion.json
 reports/phase2D1B_full_cleanup_audit.json</x:v>
       </x:c>
-      <x:c r="M169" s="10">
+      <x:c r="M169" s="10" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="92.4000015258789" hidden="0" customHeight="1">
@@ -9183,8 +9171,8 @@
       <x:c r="D177" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="E177" s="10" t="s">
-        <x:v>266</x:v>
+      <x:c r="E177" s="10" t="str">
+        <x:v>Dataloader smoke test với num_workers=0 PASS cho standard batch và forced empty-GT batch.</x:v>
       </x:c>
       <x:c r="F177" s="10" t="str">
         <x:v>Hoàn thành</x:v>
@@ -9198,7 +9186,7 @@
       <x:c r="I177" s="10"/>
       <x:c r="J177" s="10"/>
       <x:c r="K177" s="10" t="str">
-        <x:v>CLOSED / PASS; standard and forced empty-GT dataloader batches passed, including multi-worker loading; all required dataset-loading checks passed.</x:v>
+        <x:v>CLOSED / PASS; dataloader smoke tests used num_workers=0. Standard and forced empty-GT batches passed. Multi-worker loading was not validated in Phase 2D.1C.</x:v>
       </x:c>
       <x:c r="L177" s="10" t="str">
         <x:v>reports/phase2D1C_mmdet_dataset_loading_report.json
@@ -9223,7 +9211,7 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="E178" s="10" t="s">
-        <x:v>267</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="F178" s="10" t="str">
         <x:v>Hoàn thành</x:v>
@@ -9263,7 +9251,7 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="E179" s="10" t="s">
-        <x:v>268</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="F179" s="10" t="str">
         <x:v>Hoàn thành</x:v>
@@ -9298,13 +9286,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C180" s="10" t="s">
-        <x:v>269</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="D180" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E180" s="10" t="s">
-        <x:v>270</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="F180" s="10" t="str">
         <x:v>Hoàn thành</x:v>
@@ -9339,13 +9327,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C181" s="10" t="s">
-        <x:v>269</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="D181" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="E181" s="10" t="s">
-        <x:v>271</x:v>
+      <x:c r="E181" s="10" t="str">
+        <x:v>Cập nhật đồng bộ PROJECT_CONTEXT.md, PHASE_HANDOFF.md, research_log.md, README.md, checklist và protocol YAML theo Phase 2D.1D evidence review.</x:v>
       </x:c>
       <x:c r="F181" s="10" t="str">
         <x:v>Hoàn thành</x:v>
@@ -9359,14 +9347,15 @@
       <x:c r="I181" s="10"/>
       <x:c r="J181" s="10"/>
       <x:c r="K181" s="10" t="str">
-        <x:v>COMPLETED; PHASE_HANDOFF.md, PROJECT_CONTEXT.md, research_log.md, README.md and CHECKLIST_TRIEN_KHAI_FULL.xlsx updated consistently after Phase 2D.1C PASS.</x:v>
+        <x:v>COMPLETED; six project documents/protocol files synchronized. Cross-file documentation consistency review: PASS.</x:v>
       </x:c>
       <x:c r="L181" s="10" t="str">
         <x:v>PHASE_HANDOFF.md
 PROJECT_CONTEXT.md
 research_log.md
 README.md
-CHECKLIST_TRIEN_KHAI_FULL.xlsx</x:v>
+CHECKLIST_TRIEN_KHAI_FULL.xlsx
+configs/protocol/phase2D1_jpg_representation.yaml</x:v>
       </x:c>
       <x:c r="M181" s="10" t="n">
         <x:f t="shared" si="2"/>
@@ -9381,16 +9370,16 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C182" s="10" t="s">
-        <x:v>269</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="D182" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="E182" s="10" t="s">
-        <x:v>272</x:v>
+      <x:c r="E182" s="10" t="str">
+        <x:v>Hoàn tất GPT final review Phase 2D.1; xác nhận readiness flags và giữ training locked.</x:v>
       </x:c>
       <x:c r="F182" s="10" t="str">
-        <x:v>Đang làm</x:v>
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="G182" s="10" t="s">
         <x:v>52</x:v>
@@ -9401,7 +9390,7 @@
       <x:c r="I182" s="10"/>
       <x:c r="J182" s="10"/>
       <x:c r="K182" s="10" t="str">
-        <x:v>OPEN / CURRENT; final Phase 2D.1 closure review is in progress. Dataset is training-ready, but training remains unauthorized until this gate is closed.</x:v>
+        <x:v>CLOSED / PASS; technical evidence inventory and documentation consistency review completed. Phase 2D.1D and Phase 2D.1 are CLOSED / PASS. dataset_training_ready=true; training_authorized=false.</x:v>
       </x:c>
       <x:c r="L182" s="10" t="str">
         <x:v>PHASE_HANDOFF.md
@@ -9412,7 +9401,7 @@
       </x:c>
       <x:c r="M182" s="10" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="183" ht="79.19999694824219" hidden="0" customHeight="1">
@@ -9423,16 +9412,16 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C183" s="10" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="D183" s="10" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="E183" s="10" t="s">
-        <x:v>273</x:v>
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="D183" s="10" t="str">
+        <x:v>Output</x:v>
+      </x:c>
+      <x:c r="E183" s="10" t="str">
+        <x:v>Khóa Phase 2D.1D closure package và chính sách Git: dùng một commit riêng, không amend các commit đã khóa.</x:v>
       </x:c>
       <x:c r="F183" s="10" t="str">
-        <x:v>Chưa làm</x:v>
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="G183" s="10" t="s">
         <x:v>52</x:v>
@@ -9443,12 +9432,19 @@
       <x:c r="I183" s="10"/>
       <x:c r="J183" s="10"/>
       <x:c r="K183" s="10" t="str">
-        <x:v>UNLOCKED / PENDING; stage reviewed evidence and updated project documents, inspect the complete staged diff, then commit/push. Do not commit the 4,894 JPG files to ordinary Git.</x:v>
-      </x:c>
-      <x:c r="L183" s="10"/>
+        <x:v>COMPLETED; synchronized closure package is ready for one dedicated Phase 2D.1D commit. The resulting commit hash is read from Git history and is not written back into the same closure package. Do not commit 4,894 JPG files.</x:v>
+      </x:c>
+      <x:c r="L183" s="10" t="str">
+        <x:v>PHASE_HANDOFF.md
+PROJECT_CONTEXT.md
+research_log.md
+README.md
+CHECKLIST_TRIEN_KHAI_FULL.xlsx
+configs/protocol/phase2D1_jpg_representation.yaml</x:v>
+      </x:c>
       <x:c r="M183" s="10" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="184" ht="27.600000381469727">
@@ -9459,13 +9455,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C184" s="10" t="s">
-        <x:v>274</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="D184" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E184" s="10" t="s">
-        <x:v>275</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="F184" s="10" t="s">
         <x:v>3</x:v>
@@ -9493,13 +9489,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C185" s="10" t="s">
-        <x:v>274</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="D185" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E185" s="10" t="s">
-        <x:v>276</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="F185" s="10" t="s">
         <x:v>3</x:v>
@@ -9527,13 +9523,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C186" s="10" t="s">
-        <x:v>274</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="D186" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E186" s="10" t="s">
-        <x:v>277</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="F186" s="10" t="s">
         <x:v>3</x:v>
@@ -9561,13 +9557,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C187" s="10" t="s">
-        <x:v>274</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="D187" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E187" s="10" t="s">
-        <x:v>278</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="F187" s="10" t="s">
         <x:v>3</x:v>
@@ -9595,13 +9591,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C188" s="10" t="s">
-        <x:v>274</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="D188" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E188" s="10" t="s">
-        <x:v>279</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="F188" s="10" t="s">
         <x:v>3</x:v>
@@ -9629,13 +9625,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C189" s="10" t="s">
-        <x:v>274</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="D189" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E189" s="10" t="s">
-        <x:v>280</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="F189" s="10" t="s">
         <x:v>3</x:v>
@@ -9663,13 +9659,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C190" s="10" t="s">
-        <x:v>274</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="D190" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E190" s="10" t="s">
-        <x:v>281</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="F190" s="10" t="s">
         <x:v>3</x:v>
@@ -9697,13 +9693,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C191" s="10" t="s">
-        <x:v>274</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="D191" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E191" s="10" t="s">
-        <x:v>282</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="F191" s="10" t="s">
         <x:v>3</x:v>
@@ -9731,13 +9727,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C192" s="10" t="s">
-        <x:v>274</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="D192" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E192" s="10" t="s">
-        <x:v>283</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="F192" s="10" t="s">
         <x:v>3</x:v>
@@ -9765,13 +9761,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C193" s="10" t="s">
-        <x:v>274</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="D193" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E193" s="10" t="s">
-        <x:v>284</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="F193" s="10" t="s">
         <x:v>3</x:v>
@@ -9799,13 +9795,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C194" s="10" t="s">
-        <x:v>274</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="D194" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E194" s="10" t="s">
-        <x:v>285</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="F194" s="10" t="s">
         <x:v>3</x:v>
@@ -9833,13 +9829,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C195" s="10" t="s">
-        <x:v>274</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="D195" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E195" s="10" t="s">
-        <x:v>286</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="F195" s="10" t="s">
         <x:v>3</x:v>
@@ -9867,13 +9863,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C196" s="10" t="s">
-        <x:v>274</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="D196" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E196" s="10" t="s">
-        <x:v>287</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="F196" s="10" t="s">
         <x:v>3</x:v>
@@ -9901,13 +9897,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C197" s="10" t="s">
-        <x:v>274</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="D197" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E197" s="10" t="s">
-        <x:v>288</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="F197" s="10" t="s">
         <x:v>3</x:v>
@@ -9935,13 +9931,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C198" s="10" t="s">
-        <x:v>274</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="D198" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E198" s="10" t="s">
-        <x:v>289</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="F198" s="10" t="s">
         <x:v>3</x:v>
@@ -9969,13 +9965,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C199" s="10" t="s">
-        <x:v>274</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="D199" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E199" s="10" t="s">
-        <x:v>290</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="F199" s="10" t="s">
         <x:v>3</x:v>
@@ -10003,13 +9999,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C200" s="10" t="s">
-        <x:v>274</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="D200" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E200" s="10" t="s">
-        <x:v>291</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="F200" s="10" t="s">
         <x:v>3</x:v>
@@ -10037,13 +10033,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C201" s="10" t="s">
-        <x:v>274</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="D201" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E201" s="10" t="s">
-        <x:v>292</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="F201" s="10" t="s">
         <x:v>3</x:v>
@@ -10071,13 +10067,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C202" s="10" t="s">
-        <x:v>293</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D202" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E202" s="10" t="s">
-        <x:v>294</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="F202" s="10" t="s">
         <x:v>3</x:v>
@@ -10105,13 +10101,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C203" s="10" t="s">
-        <x:v>293</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D203" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E203" s="10" t="s">
-        <x:v>295</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="F203" s="10" t="s">
         <x:v>3</x:v>
@@ -10139,13 +10135,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C204" s="10" t="s">
-        <x:v>293</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D204" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E204" s="10" t="s">
-        <x:v>296</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="F204" s="10" t="s">
         <x:v>3</x:v>
@@ -10173,13 +10169,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C205" s="10" t="s">
-        <x:v>293</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D205" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E205" s="10" t="s">
-        <x:v>297</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="F205" s="10" t="s">
         <x:v>3</x:v>
@@ -10207,13 +10203,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C206" s="10" t="s">
-        <x:v>293</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D206" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E206" s="10" t="s">
-        <x:v>298</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="F206" s="10" t="s">
         <x:v>3</x:v>
@@ -10241,13 +10237,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C207" s="10" t="s">
-        <x:v>293</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D207" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E207" s="10" t="s">
-        <x:v>299</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="F207" s="10" t="s">
         <x:v>3</x:v>
@@ -10275,13 +10271,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C208" s="10" t="s">
-        <x:v>293</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D208" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E208" s="10" t="s">
-        <x:v>300</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="F208" s="10" t="s">
         <x:v>3</x:v>
@@ -10309,13 +10305,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C209" s="10" t="s">
-        <x:v>293</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D209" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E209" s="10" t="s">
-        <x:v>301</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="F209" s="10" t="s">
         <x:v>3</x:v>
@@ -10343,13 +10339,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C210" s="10" t="s">
-        <x:v>293</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D210" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E210" s="10" t="s">
-        <x:v>302</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="F210" s="10" t="s">
         <x:v>3</x:v>
@@ -10377,13 +10373,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C211" s="10" t="s">
-        <x:v>293</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D211" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E211" s="10" t="s">
-        <x:v>303</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="F211" s="10" t="s">
         <x:v>3</x:v>
@@ -10411,13 +10407,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C212" s="10" t="s">
-        <x:v>293</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D212" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E212" s="10" t="s">
-        <x:v>304</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="F212" s="10" t="s">
         <x:v>3</x:v>
@@ -10445,13 +10441,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C213" s="10" t="s">
-        <x:v>293</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D213" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E213" s="10" t="s">
-        <x:v>305</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="F213" s="10" t="s">
         <x:v>3</x:v>
@@ -10479,13 +10475,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C214" s="10" t="s">
-        <x:v>293</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D214" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E214" s="10" t="s">
-        <x:v>306</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="F214" s="10" t="s">
         <x:v>3</x:v>
@@ -10513,13 +10509,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C215" s="10" t="s">
-        <x:v>293</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D215" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E215" s="10" t="s">
-        <x:v>307</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F215" s="10" t="s">
         <x:v>3</x:v>
@@ -10547,13 +10543,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C216" s="10" t="s">
-        <x:v>293</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D216" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E216" s="10" t="s">
-        <x:v>308</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="F216" s="10" t="s">
         <x:v>3</x:v>
@@ -10581,13 +10577,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C217" s="10" t="s">
-        <x:v>293</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D217" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E217" s="10" t="s">
-        <x:v>309</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="F217" s="10" t="s">
         <x:v>3</x:v>
@@ -10615,13 +10611,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C218" s="10" t="s">
-        <x:v>293</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D218" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E218" s="10" t="s">
-        <x:v>310</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="F218" s="10" t="s">
         <x:v>3</x:v>
@@ -10649,13 +10645,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C219" s="10" t="s">
-        <x:v>293</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D219" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E219" s="10" t="s">
-        <x:v>311</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="F219" s="10" t="s">
         <x:v>3</x:v>
@@ -10683,13 +10679,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C220" s="10" t="s">
-        <x:v>293</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D220" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E220" s="10" t="s">
-        <x:v>312</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="F220" s="10" t="s">
         <x:v>3</x:v>
@@ -10717,13 +10713,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C221" s="10" t="s">
-        <x:v>293</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D221" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E221" s="10" t="s">
-        <x:v>313</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="F221" s="10" t="s">
         <x:v>3</x:v>
@@ -10751,13 +10747,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C222" s="10" t="s">
-        <x:v>293</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D222" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E222" s="10" t="s">
-        <x:v>314</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="F222" s="10" t="s">
         <x:v>3</x:v>
@@ -10785,13 +10781,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C223" s="10" t="s">
-        <x:v>293</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D223" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E223" s="10" t="s">
-        <x:v>315</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="F223" s="10" t="s">
         <x:v>3</x:v>
@@ -10819,13 +10815,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C224" s="10" t="s">
-        <x:v>293</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D224" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E224" s="10" t="s">
-        <x:v>316</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="F224" s="10" t="s">
         <x:v>3</x:v>
@@ -10853,13 +10849,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C225" s="10" t="s">
-        <x:v>317</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="D225" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E225" s="10" t="s">
-        <x:v>318</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="F225" s="10" t="s">
         <x:v>3</x:v>
@@ -10887,13 +10883,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C226" s="10" t="s">
-        <x:v>317</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="D226" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E226" s="10" t="s">
-        <x:v>319</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="F226" s="10" t="s">
         <x:v>3</x:v>
@@ -10921,13 +10917,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C227" s="10" t="s">
-        <x:v>317</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="D227" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E227" s="10" t="s">
-        <x:v>320</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="F227" s="10" t="s">
         <x:v>3</x:v>
@@ -10955,13 +10951,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C228" s="10" t="s">
-        <x:v>317</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="D228" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E228" s="10" t="s">
-        <x:v>321</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="F228" s="10" t="s">
         <x:v>3</x:v>
@@ -10989,13 +10985,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C229" s="10" t="s">
-        <x:v>317</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="D229" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E229" s="10" t="s">
-        <x:v>322</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="F229" s="10" t="s">
         <x:v>3</x:v>
@@ -11023,13 +11019,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C230" s="10" t="s">
-        <x:v>317</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="D230" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E230" s="10" t="s">
-        <x:v>323</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="F230" s="10" t="s">
         <x:v>3</x:v>
@@ -11057,13 +11053,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C231" s="10" t="s">
-        <x:v>317</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="D231" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E231" s="10" t="s">
-        <x:v>324</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="F231" s="10" t="s">
         <x:v>3</x:v>
@@ -11091,7 +11087,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C232" s="10" t="s">
-        <x:v>317</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="D232" s="10" t="s">
         <x:v>78</x:v>
@@ -11125,13 +11121,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C233" s="10" t="s">
-        <x:v>317</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="D233" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E233" s="10" t="s">
-        <x:v>325</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="F233" s="10" t="s">
         <x:v>3</x:v>
@@ -11159,13 +11155,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C234" s="10" t="s">
-        <x:v>317</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="D234" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E234" s="10" t="s">
-        <x:v>326</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="F234" s="10" t="s">
         <x:v>3</x:v>
@@ -11193,13 +11189,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C235" s="10" t="s">
-        <x:v>317</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="D235" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E235" s="10" t="s">
-        <x:v>327</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="F235" s="10" t="s">
         <x:v>3</x:v>
@@ -11227,13 +11223,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C236" s="10" t="s">
-        <x:v>317</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="D236" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E236" s="10" t="s">
-        <x:v>328</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="F236" s="10" t="s">
         <x:v>3</x:v>
@@ -11261,13 +11257,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C237" s="10" t="s">
-        <x:v>329</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="D237" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E237" s="10" t="s">
-        <x:v>330</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="F237" s="10" t="s">
         <x:v>3</x:v>
@@ -11295,13 +11291,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C238" s="10" t="s">
-        <x:v>329</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="D238" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E238" s="10" t="s">
-        <x:v>331</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="F238" s="10" t="s">
         <x:v>3</x:v>
@@ -11329,13 +11325,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C239" s="10" t="s">
-        <x:v>329</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="D239" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E239" s="10" t="s">
-        <x:v>332</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="F239" s="10" t="s">
         <x:v>3</x:v>
@@ -11363,13 +11359,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C240" s="10" t="s">
-        <x:v>329</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="D240" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E240" s="10" t="s">
-        <x:v>333</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="F240" s="10" t="s">
         <x:v>3</x:v>
@@ -11397,13 +11393,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C241" s="10" t="s">
-        <x:v>329</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="D241" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E241" s="10" t="s">
-        <x:v>334</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="F241" s="10" t="s">
         <x:v>3</x:v>
@@ -11431,13 +11427,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C242" s="10" t="s">
-        <x:v>329</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="D242" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E242" s="10" t="s">
-        <x:v>335</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="F242" s="10" t="s">
         <x:v>3</x:v>
@@ -11465,13 +11461,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C243" s="10" t="s">
-        <x:v>329</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="D243" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E243" s="10" t="s">
-        <x:v>336</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="F243" s="10" t="s">
         <x:v>3</x:v>
@@ -11499,13 +11495,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C244" s="10" t="s">
-        <x:v>329</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="D244" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E244" s="10" t="s">
-        <x:v>337</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="F244" s="10" t="s">
         <x:v>3</x:v>
@@ -11533,13 +11529,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C245" s="10" t="s">
-        <x:v>329</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="D245" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E245" s="10" t="s">
-        <x:v>338</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="F245" s="10" t="s">
         <x:v>3</x:v>
@@ -11567,13 +11563,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C246" s="10" t="s">
-        <x:v>329</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="D246" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E246" s="10" t="s">
-        <x:v>339</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="F246" s="10" t="s">
         <x:v>3</x:v>
@@ -11601,13 +11597,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C247" s="10" t="s">
-        <x:v>329</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="D247" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E247" s="10" t="s">
-        <x:v>340</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="F247" s="10" t="s">
         <x:v>3</x:v>
@@ -11635,13 +11631,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C248" s="10" t="s">
-        <x:v>329</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="D248" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E248" s="10" t="s">
-        <x:v>341</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="F248" s="10" t="s">
         <x:v>3</x:v>
@@ -11669,13 +11665,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C249" s="10" t="s">
-        <x:v>329</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="D249" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E249" s="10" t="s">
-        <x:v>342</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="F249" s="10" t="s">
         <x:v>3</x:v>
@@ -11703,13 +11699,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C250" s="10" t="s">
-        <x:v>329</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="D250" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E250" s="10" t="s">
-        <x:v>343</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="F250" s="10" t="s">
         <x:v>3</x:v>
@@ -11737,13 +11733,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C251" s="10" t="s">
-        <x:v>329</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="D251" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E251" s="10" t="s">
-        <x:v>344</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="F251" s="10" t="s">
         <x:v>3</x:v>
@@ -11771,13 +11767,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C252" s="10" t="s">
-        <x:v>329</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="D252" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E252" s="10" t="s">
-        <x:v>345</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="F252" s="10" t="s">
         <x:v>3</x:v>
@@ -11805,13 +11801,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C253" s="10" t="s">
-        <x:v>329</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="D253" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E253" s="10" t="s">
-        <x:v>346</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="F253" s="10" t="s">
         <x:v>3</x:v>
@@ -11839,13 +11835,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C254" s="10" t="s">
-        <x:v>347</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D254" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E254" s="10" t="s">
-        <x:v>348</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="F254" s="10" t="s">
         <x:v>3</x:v>
@@ -11873,13 +11869,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C255" s="10" t="s">
-        <x:v>347</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D255" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E255" s="10" t="s">
-        <x:v>349</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="F255" s="10" t="s">
         <x:v>3</x:v>
@@ -11907,13 +11903,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C256" s="10" t="s">
-        <x:v>347</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D256" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E256" s="10" t="s">
-        <x:v>350</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="F256" s="10" t="s">
         <x:v>3</x:v>
@@ -11941,13 +11937,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C257" s="10" t="s">
-        <x:v>347</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D257" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E257" s="10" t="s">
-        <x:v>351</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="F257" s="10" t="s">
         <x:v>3</x:v>
@@ -11975,13 +11971,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C258" s="10" t="s">
-        <x:v>347</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D258" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E258" s="10" t="s">
-        <x:v>352</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="F258" s="10" t="s">
         <x:v>3</x:v>
@@ -12009,13 +12005,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C259" s="10" t="s">
-        <x:v>347</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D259" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E259" s="10" t="s">
-        <x:v>353</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F259" s="10" t="s">
         <x:v>3</x:v>
@@ -12043,13 +12039,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C260" s="10" t="s">
-        <x:v>347</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D260" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E260" s="10" t="s">
-        <x:v>354</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="F260" s="10" t="s">
         <x:v>3</x:v>
@@ -12077,13 +12073,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C261" s="10" t="s">
-        <x:v>347</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D261" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E261" s="10" t="s">
-        <x:v>355</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="F261" s="10" t="s">
         <x:v>3</x:v>
@@ -12111,13 +12107,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C262" s="10" t="s">
-        <x:v>347</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D262" s="10" t="s">
-        <x:v>356</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E262" s="10" t="s">
-        <x:v>357</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="F262" s="10" t="s">
         <x:v>3</x:v>
@@ -12145,13 +12141,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C263" s="10" t="s">
-        <x:v>347</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D263" s="10" t="s">
-        <x:v>356</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E263" s="10" t="s">
-        <x:v>358</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="F263" s="10" t="s">
         <x:v>3</x:v>
@@ -12179,13 +12175,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C264" s="10" t="s">
-        <x:v>347</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D264" s="10" t="s">
-        <x:v>356</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E264" s="10" t="s">
-        <x:v>359</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="F264" s="10" t="s">
         <x:v>3</x:v>
@@ -12213,13 +12209,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C265" s="10" t="s">
-        <x:v>347</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D265" s="10" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="E265" s="10" t="s">
         <x:v>356</x:v>
-      </x:c>
-      <x:c r="E265" s="10" t="s">
-        <x:v>360</x:v>
       </x:c>
       <x:c r="F265" s="10" t="s">
         <x:v>3</x:v>
@@ -12247,13 +12243,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C266" s="10" t="s">
-        <x:v>347</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D266" s="10" t="s">
-        <x:v>356</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E266" s="10" t="s">
-        <x:v>361</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="F266" s="10" t="s">
         <x:v>3</x:v>
@@ -12281,13 +12277,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C267" s="10" t="s">
-        <x:v>347</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D267" s="10" t="s">
-        <x:v>356</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E267" s="10" t="s">
-        <x:v>362</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="F267" s="10" t="s">
         <x:v>3</x:v>
@@ -12315,13 +12311,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C268" s="10" t="s">
-        <x:v>347</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D268" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E268" s="10" t="s">
-        <x:v>363</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="F268" s="10" t="s">
         <x:v>3</x:v>
@@ -12349,13 +12345,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C269" s="10" t="s">
-        <x:v>347</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D269" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E269" s="10" t="s">
-        <x:v>364</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="F269" s="10" t="s">
         <x:v>3</x:v>
@@ -12383,13 +12379,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C270" s="10" t="s">
-        <x:v>347</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D270" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E270" s="10" t="s">
-        <x:v>365</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="F270" s="10" t="s">
         <x:v>3</x:v>
@@ -12417,13 +12413,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C271" s="10" t="s">
-        <x:v>347</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D271" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E271" s="10" t="s">
-        <x:v>366</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="F271" s="10" t="s">
         <x:v>3</x:v>
@@ -12451,13 +12447,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C272" s="10" t="s">
-        <x:v>347</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D272" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E272" s="10" t="s">
-        <x:v>367</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="F272" s="10" t="s">
         <x:v>3</x:v>
@@ -12485,13 +12481,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C273" s="10" t="s">
-        <x:v>347</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D273" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E273" s="10" t="s">
-        <x:v>368</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="F273" s="10" t="s">
         <x:v>3</x:v>
@@ -12519,13 +12515,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C274" s="10" t="s">
-        <x:v>347</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D274" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E274" s="10" t="s">
-        <x:v>369</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="F274" s="10" t="s">
         <x:v>3</x:v>
@@ -12553,13 +12549,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C275" s="10" t="s">
-        <x:v>347</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D275" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E275" s="10" t="s">
-        <x:v>370</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="F275" s="10" t="s">
         <x:v>3</x:v>
@@ -12587,13 +12583,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C276" s="10" t="s">
-        <x:v>371</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="D276" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E276" s="10" t="s">
-        <x:v>372</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="F276" s="10" t="s">
         <x:v>3</x:v>
@@ -12621,13 +12617,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C277" s="10" t="s">
-        <x:v>371</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="D277" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E277" s="10" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="F277" s="10" t="s">
         <x:v>3</x:v>
@@ -12655,13 +12651,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C278" s="10" t="s">
-        <x:v>371</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="D278" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E278" s="10" t="s">
-        <x:v>374</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="F278" s="10" t="s">
         <x:v>3</x:v>
@@ -12689,13 +12685,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C279" s="10" t="s">
-        <x:v>371</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="D279" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E279" s="10" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="F279" s="10" t="s">
         <x:v>3</x:v>
@@ -12723,13 +12719,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C280" s="10" t="s">
-        <x:v>371</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="D280" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E280" s="10" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="F280" s="10" t="s">
         <x:v>3</x:v>
@@ -12757,13 +12753,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C281" s="10" t="s">
-        <x:v>371</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="D281" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E281" s="10" t="s">
-        <x:v>377</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="F281" s="10" t="s">
         <x:v>3</x:v>
@@ -12791,13 +12787,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C282" s="10" t="s">
-        <x:v>371</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="D282" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E282" s="10" t="s">
-        <x:v>378</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="F282" s="10" t="s">
         <x:v>3</x:v>
@@ -12825,13 +12821,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C283" s="10" t="s">
-        <x:v>371</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="D283" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E283" s="10" t="s">
-        <x:v>379</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="F283" s="10" t="s">
         <x:v>3</x:v>
@@ -12859,13 +12855,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C284" s="10" t="s">
-        <x:v>371</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="D284" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E284" s="10" t="s">
-        <x:v>380</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="F284" s="10" t="s">
         <x:v>3</x:v>
@@ -12893,13 +12889,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C285" s="10" t="s">
-        <x:v>371</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="D285" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E285" s="10" t="s">
-        <x:v>381</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="F285" s="10" t="s">
         <x:v>3</x:v>
@@ -12927,13 +12923,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C286" s="10" t="s">
-        <x:v>371</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="D286" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E286" s="10" t="s">
-        <x:v>382</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="F286" s="10" t="s">
         <x:v>3</x:v>
@@ -12961,13 +12957,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C287" s="10" t="s">
-        <x:v>371</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="D287" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E287" s="10" t="s">
-        <x:v>383</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="F287" s="10" t="s">
         <x:v>3</x:v>
@@ -12995,13 +12991,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C288" s="10" t="s">
-        <x:v>371</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="D288" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E288" s="10" t="s">
-        <x:v>384</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="F288" s="10" t="s">
         <x:v>3</x:v>
@@ -13029,13 +13025,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C289" s="10" t="s">
-        <x:v>371</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="D289" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E289" s="10" t="s">
-        <x:v>385</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="F289" s="10" t="s">
         <x:v>3</x:v>
@@ -13063,13 +13059,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C290" s="10" t="s">
-        <x:v>371</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="D290" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E290" s="10" t="s">
-        <x:v>386</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="F290" s="10" t="s">
         <x:v>3</x:v>
@@ -13097,13 +13093,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C291" s="10" t="s">
-        <x:v>371</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="D291" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E291" s="10" t="s">
-        <x:v>387</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="F291" s="10" t="s">
         <x:v>3</x:v>
@@ -13131,13 +13127,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C292" s="10" t="s">
-        <x:v>371</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="D292" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E292" s="10" t="s">
-        <x:v>388</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="F292" s="10" t="s">
         <x:v>3</x:v>
@@ -13165,13 +13161,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C293" s="10" t="s">
-        <x:v>389</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="D293" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E293" s="10" t="s">
-        <x:v>390</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="F293" s="10" t="s">
         <x:v>3</x:v>
@@ -13199,13 +13195,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C294" s="10" t="s">
-        <x:v>389</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="D294" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E294" s="10" t="s">
-        <x:v>391</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="F294" s="10" t="s">
         <x:v>3</x:v>
@@ -13233,13 +13229,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C295" s="10" t="s">
-        <x:v>389</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="D295" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E295" s="10" t="s">
-        <x:v>392</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="F295" s="10" t="s">
         <x:v>3</x:v>
@@ -13267,13 +13263,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C296" s="10" t="s">
-        <x:v>389</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="D296" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E296" s="10" t="s">
-        <x:v>393</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="F296" s="10" t="s">
         <x:v>3</x:v>
@@ -13301,13 +13297,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C297" s="10" t="s">
-        <x:v>389</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="D297" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E297" s="10" t="s">
-        <x:v>394</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="F297" s="10" t="s">
         <x:v>3</x:v>
@@ -13335,13 +13331,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C298" s="10" t="s">
-        <x:v>389</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="D298" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E298" s="10" t="s">
-        <x:v>395</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="F298" s="10" t="s">
         <x:v>3</x:v>
@@ -13369,13 +13365,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C299" s="10" t="s">
-        <x:v>389</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="D299" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E299" s="10" t="s">
-        <x:v>396</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="F299" s="10" t="s">
         <x:v>3</x:v>
@@ -13403,13 +13399,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C300" s="10" t="s">
-        <x:v>389</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="D300" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E300" s="10" t="s">
-        <x:v>397</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="F300" s="10" t="s">
         <x:v>3</x:v>
@@ -13437,13 +13433,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C301" s="10" t="s">
-        <x:v>398</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="D301" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E301" s="10" t="s">
-        <x:v>399</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="F301" s="10" t="s">
         <x:v>3</x:v>
@@ -13471,13 +13467,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C302" s="10" t="s">
-        <x:v>398</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="D302" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E302" s="10" t="s">
-        <x:v>400</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="F302" s="10" t="s">
         <x:v>3</x:v>
@@ -13505,13 +13501,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C303" s="10" t="s">
-        <x:v>398</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="D303" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E303" s="10" t="s">
-        <x:v>401</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="F303" s="10" t="s">
         <x:v>3</x:v>
@@ -13539,13 +13535,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C304" s="10" t="s">
-        <x:v>398</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="D304" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E304" s="10" t="s">
-        <x:v>402</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="F304" s="10" t="s">
         <x:v>3</x:v>
@@ -13573,13 +13569,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C305" s="10" t="s">
-        <x:v>398</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="D305" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E305" s="10" t="s">
-        <x:v>403</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="F305" s="10" t="s">
         <x:v>3</x:v>
@@ -13607,13 +13603,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C306" s="10" t="s">
-        <x:v>398</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="D306" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E306" s="10" t="s">
-        <x:v>404</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="F306" s="10" t="s">
         <x:v>3</x:v>
@@ -13641,13 +13637,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C307" s="10" t="s">
-        <x:v>398</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="D307" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E307" s="10" t="s">
-        <x:v>405</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="F307" s="10" t="s">
         <x:v>3</x:v>
@@ -13675,13 +13671,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C308" s="10" t="s">
-        <x:v>398</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="D308" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E308" s="10" t="s">
-        <x:v>406</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="F308" s="10" t="s">
         <x:v>3</x:v>
@@ -13709,13 +13705,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C309" s="10" t="s">
-        <x:v>398</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="D309" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E309" s="10" t="s">
-        <x:v>381</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="F309" s="10" t="s">
         <x:v>3</x:v>
@@ -13743,13 +13739,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C310" s="10" t="s">
-        <x:v>398</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="D310" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E310" s="10" t="s">
-        <x:v>407</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="F310" s="10" t="s">
         <x:v>3</x:v>
@@ -13777,13 +13773,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C311" s="10" t="s">
-        <x:v>398</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="D311" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E311" s="10" t="s">
-        <x:v>408</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="F311" s="10" t="s">
         <x:v>3</x:v>
@@ -13811,13 +13807,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C312" s="10" t="s">
-        <x:v>398</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="D312" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E312" s="10" t="s">
-        <x:v>409</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="F312" s="10" t="s">
         <x:v>3</x:v>
@@ -13845,13 +13841,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C313" s="10" t="s">
-        <x:v>398</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="D313" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E313" s="10" t="s">
-        <x:v>410</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="F313" s="10" t="s">
         <x:v>3</x:v>
@@ -13879,13 +13875,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C314" s="10" t="s">
-        <x:v>398</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="D314" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E314" s="10" t="s">
-        <x:v>411</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="F314" s="10" t="s">
         <x:v>3</x:v>
@@ -13913,13 +13909,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C315" s="10" t="s">
-        <x:v>398</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="D315" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E315" s="10" t="s">
-        <x:v>412</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="F315" s="10" t="s">
         <x:v>3</x:v>
@@ -13947,13 +13943,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C316" s="10" t="s">
-        <x:v>398</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="D316" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E316" s="10" t="s">
-        <x:v>413</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="F316" s="10" t="s">
         <x:v>3</x:v>
@@ -13981,13 +13977,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C317" s="10" t="s">
-        <x:v>414</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="D317" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E317" s="10" t="s">
-        <x:v>415</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="F317" s="10" t="s">
         <x:v>3</x:v>
@@ -14015,13 +14011,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C318" s="10" t="s">
-        <x:v>414</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="D318" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E318" s="10" t="s">
-        <x:v>416</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="F318" s="10" t="s">
         <x:v>3</x:v>
@@ -14049,13 +14045,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C319" s="10" t="s">
-        <x:v>414</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="D319" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E319" s="10" t="s">
-        <x:v>417</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="F319" s="10" t="s">
         <x:v>3</x:v>
@@ -14083,13 +14079,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C320" s="10" t="s">
-        <x:v>414</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="D320" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E320" s="10" t="s">
-        <x:v>418</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="F320" s="10" t="s">
         <x:v>3</x:v>
@@ -14117,13 +14113,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C321" s="10" t="s">
-        <x:v>414</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="D321" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E321" s="10" t="s">
-        <x:v>419</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="F321" s="10" t="s">
         <x:v>3</x:v>
@@ -14151,13 +14147,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C322" s="10" t="s">
-        <x:v>414</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="D322" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E322" s="10" t="s">
-        <x:v>420</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="F322" s="10" t="s">
         <x:v>3</x:v>
@@ -14185,13 +14181,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C323" s="10" t="s">
-        <x:v>414</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="D323" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E323" s="10" t="s">
-        <x:v>421</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="F323" s="10" t="s">
         <x:v>3</x:v>
@@ -14219,13 +14215,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C324" s="10" t="s">
-        <x:v>414</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="D324" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E324" s="10" t="s">
-        <x:v>422</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="F324" s="10" t="s">
         <x:v>3</x:v>
@@ -14253,13 +14249,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C325" s="10" t="s">
-        <x:v>414</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="D325" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E325" s="10" t="s">
-        <x:v>423</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="F325" s="10" t="s">
         <x:v>3</x:v>
@@ -14287,13 +14283,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C326" s="10" t="s">
-        <x:v>414</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="D326" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E326" s="10" t="s">
-        <x:v>424</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="F326" s="10" t="s">
         <x:v>3</x:v>
@@ -14321,13 +14317,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C327" s="10" t="s">
-        <x:v>414</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="D327" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E327" s="10" t="s">
-        <x:v>425</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="F327" s="10" t="s">
         <x:v>3</x:v>
@@ -14355,13 +14351,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C328" s="10" t="s">
-        <x:v>414</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="D328" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E328" s="10" t="s">
-        <x:v>426</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="F328" s="10" t="s">
         <x:v>3</x:v>
@@ -14389,13 +14385,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C329" s="10" t="s">
-        <x:v>414</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="D329" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E329" s="10" t="s">
-        <x:v>427</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="F329" s="10" t="s">
         <x:v>3</x:v>
@@ -14423,13 +14419,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C330" s="10" t="s">
-        <x:v>414</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="D330" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E330" s="10" t="s">
-        <x:v>428</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="F330" s="10" t="s">
         <x:v>3</x:v>
@@ -14457,13 +14453,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C331" s="10" t="s">
-        <x:v>414</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="D331" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E331" s="10" t="s">
-        <x:v>429</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="F331" s="10" t="s">
         <x:v>3</x:v>
@@ -14491,13 +14487,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C332" s="10" t="s">
-        <x:v>430</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="D332" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E332" s="10" t="s">
-        <x:v>431</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="F332" s="10" t="s">
         <x:v>3</x:v>
@@ -14525,13 +14521,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C333" s="10" t="s">
-        <x:v>430</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="D333" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E333" s="10" t="s">
-        <x:v>432</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="F333" s="10" t="s">
         <x:v>3</x:v>
@@ -14559,13 +14555,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C334" s="10" t="s">
-        <x:v>430</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="D334" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E334" s="10" t="s">
-        <x:v>433</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="F334" s="10" t="s">
         <x:v>3</x:v>
@@ -14593,13 +14589,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C335" s="10" t="s">
-        <x:v>430</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="D335" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E335" s="10" t="s">
-        <x:v>434</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="F335" s="10" t="s">
         <x:v>3</x:v>
@@ -14627,13 +14623,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C336" s="10" t="s">
-        <x:v>430</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="D336" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E336" s="10" t="s">
-        <x:v>435</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="F336" s="10" t="s">
         <x:v>3</x:v>
@@ -14661,13 +14657,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C337" s="10" t="s">
-        <x:v>430</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="D337" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E337" s="10" t="s">
-        <x:v>436</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="F337" s="10" t="s">
         <x:v>3</x:v>
@@ -14695,13 +14691,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C338" s="10" t="s">
-        <x:v>430</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="D338" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E338" s="10" t="s">
-        <x:v>437</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="F338" s="10" t="s">
         <x:v>3</x:v>
@@ -14729,13 +14725,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C339" s="10" t="s">
-        <x:v>430</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="D339" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E339" s="10" t="s">
-        <x:v>438</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="F339" s="10" t="s">
         <x:v>3</x:v>
@@ -14763,13 +14759,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C340" s="10" t="s">
-        <x:v>430</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="D340" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E340" s="10" t="s">
-        <x:v>439</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="F340" s="10" t="s">
         <x:v>3</x:v>
@@ -14797,13 +14793,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C341" s="10" t="s">
-        <x:v>430</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="D341" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E341" s="10" t="s">
-        <x:v>440</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="F341" s="10" t="s">
         <x:v>3</x:v>
@@ -14831,13 +14827,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C342" s="10" t="s">
-        <x:v>430</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="D342" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E342" s="10" t="s">
-        <x:v>441</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="F342" s="10" t="s">
         <x:v>3</x:v>
@@ -14865,13 +14861,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C343" s="10" t="s">
-        <x:v>430</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="D343" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E343" s="10" t="s">
-        <x:v>442</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="F343" s="10" t="s">
         <x:v>3</x:v>
@@ -14899,13 +14895,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C344" s="10" t="s">
-        <x:v>430</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="D344" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E344" s="10" t="s">
-        <x:v>443</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="F344" s="10" t="s">
         <x:v>3</x:v>
@@ -14933,13 +14929,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C345" s="10" t="s">
-        <x:v>430</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="D345" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E345" s="10" t="s">
-        <x:v>444</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="F345" s="10" t="s">
         <x:v>3</x:v>
@@ -14967,13 +14963,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C346" s="10" t="s">
-        <x:v>445</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="D346" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E346" s="10" t="s">
-        <x:v>446</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="F346" s="10" t="s">
         <x:v>3</x:v>
@@ -15001,13 +14997,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C347" s="10" t="s">
-        <x:v>445</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="D347" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E347" s="10" t="s">
-        <x:v>447</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="F347" s="10" t="s">
         <x:v>3</x:v>
@@ -15035,13 +15031,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C348" s="10" t="s">
-        <x:v>445</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="D348" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E348" s="10" t="s">
-        <x:v>448</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="F348" s="10" t="s">
         <x:v>3</x:v>
@@ -15069,13 +15065,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C349" s="10" t="s">
-        <x:v>445</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="D349" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E349" s="10" t="s">
-        <x:v>449</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="F349" s="10" t="s">
         <x:v>3</x:v>
@@ -15103,13 +15099,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C350" s="10" t="s">
-        <x:v>445</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="D350" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E350" s="10" t="s">
-        <x:v>450</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="F350" s="10" t="s">
         <x:v>3</x:v>
@@ -15137,13 +15133,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C351" s="10" t="s">
-        <x:v>445</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="D351" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E351" s="10" t="s">
-        <x:v>451</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="F351" s="10" t="s">
         <x:v>3</x:v>
@@ -15171,13 +15167,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C352" s="10" t="s">
-        <x:v>445</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="D352" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E352" s="10" t="s">
-        <x:v>452</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="F352" s="10" t="s">
         <x:v>3</x:v>
@@ -15205,13 +15201,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C353" s="10" t="s">
-        <x:v>445</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="D353" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E353" s="10" t="s">
-        <x:v>453</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="F353" s="10" t="s">
         <x:v>3</x:v>
@@ -15239,13 +15235,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C354" s="10" t="s">
-        <x:v>445</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="D354" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E354" s="10" t="s">
-        <x:v>454</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="F354" s="10" t="s">
         <x:v>3</x:v>
@@ -15273,13 +15269,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C355" s="10" t="s">
-        <x:v>445</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="D355" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E355" s="10" t="s">
-        <x:v>455</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="F355" s="10" t="s">
         <x:v>3</x:v>
@@ -15307,13 +15303,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C356" s="10" t="s">
-        <x:v>445</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="D356" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E356" s="10" t="s">
-        <x:v>456</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="F356" s="10" t="s">
         <x:v>3</x:v>
@@ -15341,13 +15337,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C357" s="10" t="s">
-        <x:v>457</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="D357" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E357" s="10" t="s">
-        <x:v>458</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="F357" s="10" t="s">
         <x:v>3</x:v>
@@ -15375,13 +15371,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C358" s="10" t="s">
-        <x:v>457</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="D358" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E358" s="10" t="s">
-        <x:v>459</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="F358" s="10" t="s">
         <x:v>3</x:v>
@@ -15409,13 +15405,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C359" s="10" t="s">
-        <x:v>457</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="D359" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E359" s="10" t="s">
-        <x:v>460</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="F359" s="10" t="s">
         <x:v>3</x:v>
@@ -15443,13 +15439,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C360" s="10" t="s">
-        <x:v>457</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="D360" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E360" s="10" t="s">
-        <x:v>461</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="F360" s="10" t="s">
         <x:v>3</x:v>
@@ -15477,13 +15473,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C361" s="10" t="s">
-        <x:v>457</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="D361" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E361" s="10" t="s">
-        <x:v>462</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="F361" s="10" t="s">
         <x:v>3</x:v>
@@ -15511,13 +15507,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C362" s="10" t="s">
-        <x:v>457</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="D362" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E362" s="10" t="s">
-        <x:v>463</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F362" s="10" t="s">
         <x:v>3</x:v>
@@ -15545,13 +15541,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C363" s="10" t="s">
-        <x:v>457</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="D363" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E363" s="10" t="s">
-        <x:v>464</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="F363" s="10" t="s">
         <x:v>3</x:v>
@@ -15579,13 +15575,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C364" s="10" t="s">
-        <x:v>457</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="D364" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E364" s="10" t="s">
-        <x:v>465</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="F364" s="10" t="s">
         <x:v>3</x:v>
@@ -15613,13 +15609,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C365" s="10" t="s">
-        <x:v>457</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="D365" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E365" s="10" t="s">
-        <x:v>466</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="F365" s="10" t="s">
         <x:v>3</x:v>
@@ -15647,13 +15643,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C366" s="10" t="s">
-        <x:v>467</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="D366" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E366" s="10" t="s">
-        <x:v>468</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="F366" s="10" t="s">
         <x:v>3</x:v>
@@ -15681,13 +15677,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C367" s="10" t="s">
-        <x:v>467</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="D367" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E367" s="10" t="s">
-        <x:v>469</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="F367" s="10" t="s">
         <x:v>3</x:v>
@@ -15715,13 +15711,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C368" s="10" t="s">
-        <x:v>467</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="D368" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E368" s="10" t="s">
-        <x:v>470</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="F368" s="10" t="s">
         <x:v>3</x:v>
@@ -15749,13 +15745,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C369" s="10" t="s">
-        <x:v>467</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="D369" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E369" s="10" t="s">
-        <x:v>471</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="F369" s="10" t="s">
         <x:v>3</x:v>
@@ -15783,13 +15779,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C370" s="10" t="s">
-        <x:v>467</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="D370" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E370" s="10" t="s">
-        <x:v>472</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="F370" s="10" t="s">
         <x:v>3</x:v>
@@ -15817,13 +15813,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C371" s="10" t="s">
-        <x:v>467</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="D371" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E371" s="10" t="s">
-        <x:v>473</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="F371" s="10" t="s">
         <x:v>3</x:v>
@@ -15851,13 +15847,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C372" s="10" t="s">
-        <x:v>467</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="D372" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E372" s="10" t="s">
-        <x:v>474</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="F372" s="10" t="s">
         <x:v>3</x:v>
@@ -15885,13 +15881,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C373" s="10" t="s">
-        <x:v>467</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="D373" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E373" s="10" t="s">
-        <x:v>475</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="F373" s="10" t="s">
         <x:v>3</x:v>
@@ -15919,13 +15915,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C374" s="10" t="s">
-        <x:v>467</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="D374" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E374" s="10" t="s">
-        <x:v>476</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="F374" s="10" t="s">
         <x:v>3</x:v>
@@ -15953,13 +15949,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C375" s="10" t="s">
-        <x:v>467</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="D375" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E375" s="10" t="s">
-        <x:v>477</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="F375" s="10" t="s">
         <x:v>3</x:v>
@@ -15987,13 +15983,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C376" s="10" t="s">
-        <x:v>467</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="D376" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E376" s="10" t="s">
-        <x:v>478</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="F376" s="10" t="s">
         <x:v>3</x:v>
@@ -16021,13 +16017,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C377" s="10" t="s">
-        <x:v>467</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="D377" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E377" s="10" t="s">
-        <x:v>479</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="F377" s="10" t="s">
         <x:v>3</x:v>
@@ -16055,13 +16051,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C378" s="10" t="s">
-        <x:v>480</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="D378" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E378" s="10" t="s">
-        <x:v>481</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="F378" s="10" t="s">
         <x:v>3</x:v>
@@ -16089,13 +16085,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C379" s="10" t="s">
-        <x:v>480</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="D379" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E379" s="10" t="s">
-        <x:v>482</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="F379" s="10" t="s">
         <x:v>3</x:v>
@@ -16123,13 +16119,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C380" s="10" t="s">
-        <x:v>480</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="D380" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E380" s="10" t="s">
-        <x:v>483</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="F380" s="10" t="s">
         <x:v>3</x:v>
@@ -16157,13 +16153,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C381" s="10" t="s">
-        <x:v>480</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="D381" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E381" s="10" t="s">
-        <x:v>484</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="F381" s="10" t="s">
         <x:v>3</x:v>
@@ -16191,13 +16187,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C382" s="10" t="s">
-        <x:v>480</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="D382" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E382" s="10" t="s">
-        <x:v>485</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="F382" s="10" t="s">
         <x:v>3</x:v>
@@ -16225,13 +16221,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C383" s="10" t="s">
-        <x:v>480</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="D383" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E383" s="10" t="s">
-        <x:v>486</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="F383" s="10" t="s">
         <x:v>3</x:v>
@@ -16259,13 +16255,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C384" s="10" t="s">
-        <x:v>480</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="D384" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E384" s="10" t="s">
-        <x:v>487</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="F384" s="10" t="s">
         <x:v>3</x:v>
@@ -16293,13 +16289,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C385" s="10" t="s">
-        <x:v>480</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="D385" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E385" s="10" t="s">
-        <x:v>488</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="F385" s="10" t="s">
         <x:v>3</x:v>
@@ -16327,13 +16323,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C386" s="10" t="s">
-        <x:v>480</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="D386" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E386" s="10" t="s">
-        <x:v>489</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="F386" s="10" t="s">
         <x:v>3</x:v>
@@ -16361,13 +16357,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C387" s="10" t="s">
-        <x:v>480</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="D387" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E387" s="10" t="s">
-        <x:v>407</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="F387" s="10" t="s">
         <x:v>3</x:v>
@@ -16395,13 +16391,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C388" s="10" t="s">
-        <x:v>480</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="D388" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E388" s="10" t="s">
-        <x:v>490</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="F388" s="10" t="s">
         <x:v>3</x:v>
@@ -16429,13 +16425,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C389" s="10" t="s">
-        <x:v>480</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="D389" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E389" s="10" t="s">
-        <x:v>491</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="F389" s="10" t="s">
         <x:v>3</x:v>
@@ -16463,13 +16459,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C390" s="10" t="s">
-        <x:v>480</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="D390" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E390" s="10" t="s">
-        <x:v>492</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="F390" s="10" t="s">
         <x:v>3</x:v>
@@ -16497,13 +16493,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C391" s="10" t="s">
-        <x:v>480</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="D391" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E391" s="10" t="s">
-        <x:v>493</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="F391" s="10" t="s">
         <x:v>3</x:v>
@@ -16531,13 +16527,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C392" s="10" t="s">
-        <x:v>480</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="D392" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E392" s="10" t="s">
-        <x:v>494</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="F392" s="10" t="s">
         <x:v>3</x:v>
@@ -16565,13 +16561,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C393" s="10" t="s">
-        <x:v>480</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="D393" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E393" s="10" t="s">
-        <x:v>495</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="F393" s="10" t="s">
         <x:v>3</x:v>
@@ -16599,13 +16595,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C394" s="10" t="s">
-        <x:v>496</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="D394" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E394" s="10" t="s">
-        <x:v>497</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="F394" s="10" t="s">
         <x:v>3</x:v>
@@ -16633,13 +16629,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C395" s="10" t="s">
-        <x:v>496</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="D395" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E395" s="10" t="s">
-        <x:v>498</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="F395" s="10" t="s">
         <x:v>3</x:v>
@@ -16667,13 +16663,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C396" s="10" t="s">
-        <x:v>496</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="D396" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E396" s="10" t="s">
-        <x:v>499</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="F396" s="10" t="s">
         <x:v>3</x:v>
@@ -16701,13 +16697,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C397" s="10" t="s">
-        <x:v>496</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="D397" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E397" s="10" t="s">
-        <x:v>500</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="F397" s="10" t="s">
         <x:v>3</x:v>
@@ -16735,13 +16731,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C398" s="10" t="s">
-        <x:v>496</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="D398" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E398" s="10" t="s">
-        <x:v>501</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="F398" s="10" t="s">
         <x:v>3</x:v>
@@ -16769,13 +16765,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C399" s="10" t="s">
-        <x:v>496</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="D399" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E399" s="10" t="s">
-        <x:v>502</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="F399" s="10" t="s">
         <x:v>3</x:v>
@@ -16803,13 +16799,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C400" s="10" t="s">
-        <x:v>496</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="D400" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E400" s="10" t="s">
-        <x:v>503</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="F400" s="10" t="s">
         <x:v>3</x:v>
@@ -16837,13 +16833,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C401" s="10" t="s">
-        <x:v>496</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="D401" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E401" s="10" t="s">
-        <x:v>504</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="F401" s="10" t="s">
         <x:v>3</x:v>
@@ -16871,13 +16867,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C402" s="10" t="s">
-        <x:v>505</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="D402" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E402" s="10" t="s">
-        <x:v>506</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="F402" s="10" t="s">
         <x:v>3</x:v>
@@ -16905,13 +16901,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C403" s="10" t="s">
-        <x:v>505</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="D403" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E403" s="10" t="s">
-        <x:v>507</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="F403" s="10" t="s">
         <x:v>3</x:v>
@@ -16939,13 +16935,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C404" s="10" t="s">
-        <x:v>505</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="D404" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E404" s="10" t="s">
-        <x:v>508</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="F404" s="10" t="s">
         <x:v>3</x:v>
@@ -16973,13 +16969,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C405" s="10" t="s">
-        <x:v>505</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="D405" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E405" s="10" t="s">
-        <x:v>509</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="F405" s="10" t="s">
         <x:v>3</x:v>
@@ -17007,13 +17003,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C406" s="10" t="s">
-        <x:v>505</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="D406" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E406" s="10" t="s">
-        <x:v>510</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="F406" s="10" t="s">
         <x:v>3</x:v>
@@ -17041,13 +17037,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C407" s="10" t="s">
-        <x:v>505</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="D407" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E407" s="10" t="s">
-        <x:v>511</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="F407" s="10" t="s">
         <x:v>3</x:v>
@@ -17075,13 +17071,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C408" s="10" t="s">
-        <x:v>505</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="D408" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E408" s="10" t="s">
-        <x:v>512</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="F408" s="10" t="s">
         <x:v>3</x:v>
@@ -17109,13 +17105,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C409" s="10" t="s">
-        <x:v>505</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="D409" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E409" s="10" t="s">
-        <x:v>513</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="F409" s="10" t="s">
         <x:v>3</x:v>
@@ -17143,13 +17139,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C410" s="10" t="s">
-        <x:v>505</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="D410" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E410" s="10" t="s">
-        <x:v>453</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="F410" s="10" t="s">
         <x:v>3</x:v>
@@ -17177,13 +17173,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C411" s="10" t="s">
-        <x:v>505</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="D411" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E411" s="10" t="s">
-        <x:v>514</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="F411" s="10" t="s">
         <x:v>3</x:v>
@@ -17211,13 +17207,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C412" s="10" t="s">
-        <x:v>505</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="D412" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E412" s="10" t="s">
-        <x:v>515</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="F412" s="10" t="s">
         <x:v>3</x:v>
@@ -17245,13 +17241,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C413" s="10" t="s">
-        <x:v>505</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="D413" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E413" s="10" t="s">
-        <x:v>516</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="F413" s="10" t="s">
         <x:v>3</x:v>
@@ -17279,13 +17275,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C414" s="10" t="s">
-        <x:v>505</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="D414" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E414" s="10" t="s">
-        <x:v>517</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="F414" s="10" t="s">
         <x:v>3</x:v>
@@ -17313,13 +17309,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C415" s="10" t="s">
-        <x:v>505</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="D415" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E415" s="10" t="s">
-        <x:v>518</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="F415" s="10" t="s">
         <x:v>3</x:v>
@@ -17347,13 +17343,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C416" s="10" t="s">
-        <x:v>519</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="D416" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E416" s="10" t="s">
-        <x:v>520</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="F416" s="10" t="s">
         <x:v>3</x:v>
@@ -17381,13 +17377,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C417" s="10" t="s">
-        <x:v>519</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="D417" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E417" s="10" t="s">
-        <x:v>521</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="F417" s="10" t="s">
         <x:v>3</x:v>
@@ -17415,13 +17411,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C418" s="10" t="s">
-        <x:v>519</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="D418" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E418" s="10" t="s">
-        <x:v>522</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="F418" s="10" t="s">
         <x:v>3</x:v>
@@ -17449,13 +17445,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C419" s="10" t="s">
-        <x:v>519</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="D419" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E419" s="10" t="s">
-        <x:v>523</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="F419" s="10" t="s">
         <x:v>3</x:v>
@@ -17483,13 +17479,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C420" s="10" t="s">
-        <x:v>519</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="D420" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E420" s="10" t="s">
-        <x:v>524</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="F420" s="10" t="s">
         <x:v>3</x:v>
@@ -17517,13 +17513,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C421" s="10" t="s">
-        <x:v>519</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="D421" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E421" s="10" t="s">
-        <x:v>525</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="F421" s="10" t="s">
         <x:v>3</x:v>
@@ -17551,13 +17547,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C422" s="10" t="s">
-        <x:v>519</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="D422" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E422" s="10" t="s">
-        <x:v>526</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="F422" s="10" t="s">
         <x:v>3</x:v>
@@ -17585,13 +17581,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C423" s="10" t="s">
-        <x:v>519</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="D423" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E423" s="10" t="s">
-        <x:v>527</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="F423" s="10" t="s">
         <x:v>3</x:v>
@@ -17619,13 +17615,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C424" s="10" t="s">
-        <x:v>519</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="D424" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E424" s="10" t="s">
-        <x:v>528</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="F424" s="10" t="s">
         <x:v>3</x:v>
@@ -17653,13 +17649,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C425" s="10" t="s">
-        <x:v>519</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="D425" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E425" s="10" t="s">
-        <x:v>529</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="F425" s="10" t="s">
         <x:v>3</x:v>
@@ -17687,13 +17683,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C426" s="10" t="s">
-        <x:v>519</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="D426" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E426" s="10" t="s">
-        <x:v>530</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="F426" s="10" t="s">
         <x:v>3</x:v>
@@ -17721,13 +17717,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C427" s="10" t="s">
-        <x:v>519</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="D427" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E427" s="10" t="s">
-        <x:v>531</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="F427" s="10" t="s">
         <x:v>3</x:v>
@@ -17755,13 +17751,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C428" s="10" t="s">
-        <x:v>519</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="D428" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E428" s="10" t="s">
-        <x:v>532</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="F428" s="10" t="s">
         <x:v>3</x:v>
@@ -17789,13 +17785,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C429" s="10" t="s">
-        <x:v>519</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="D429" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E429" s="10" t="s">
-        <x:v>533</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="F429" s="10" t="s">
         <x:v>3</x:v>
@@ -17823,13 +17819,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C430" s="10" t="s">
-        <x:v>519</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="D430" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E430" s="10" t="s">
-        <x:v>534</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="F430" s="10" t="s">
         <x:v>3</x:v>
@@ -17857,13 +17853,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C431" s="10" t="s">
-        <x:v>535</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="D431" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E431" s="10" t="s">
-        <x:v>536</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="F431" s="10" t="s">
         <x:v>3</x:v>
@@ -17891,13 +17887,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C432" s="10" t="s">
-        <x:v>535</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="D432" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E432" s="10" t="s">
-        <x:v>537</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="F432" s="10" t="s">
         <x:v>3</x:v>
@@ -17925,13 +17921,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C433" s="10" t="s">
-        <x:v>535</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="D433" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E433" s="10" t="s">
-        <x:v>538</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="F433" s="10" t="s">
         <x:v>3</x:v>
@@ -17959,13 +17955,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C434" s="10" t="s">
-        <x:v>535</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="D434" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E434" s="10" t="s">
-        <x:v>539</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="F434" s="10" t="s">
         <x:v>3</x:v>
@@ -17993,13 +17989,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C435" s="10" t="s">
-        <x:v>535</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="D435" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E435" s="10" t="s">
-        <x:v>540</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="F435" s="10" t="s">
         <x:v>3</x:v>
@@ -18027,13 +18023,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C436" s="10" t="s">
-        <x:v>535</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="D436" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E436" s="10" t="s">
-        <x:v>541</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="F436" s="10" t="s">
         <x:v>3</x:v>
@@ -18061,13 +18057,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C437" s="10" t="s">
-        <x:v>535</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="D437" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E437" s="10" t="s">
-        <x:v>542</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="F437" s="10" t="s">
         <x:v>3</x:v>
@@ -18095,13 +18091,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C438" s="10" t="s">
-        <x:v>535</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="D438" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E438" s="10" t="s">
-        <x:v>543</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="F438" s="10" t="s">
         <x:v>3</x:v>
@@ -18129,13 +18125,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C439" s="10" t="s">
-        <x:v>535</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="D439" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E439" s="10" t="s">
-        <x:v>544</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="F439" s="10" t="s">
         <x:v>3</x:v>
@@ -18163,13 +18159,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C440" s="10" t="s">
-        <x:v>535</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="D440" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E440" s="10" t="s">
-        <x:v>545</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="F440" s="10" t="s">
         <x:v>3</x:v>
@@ -18197,13 +18193,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C441" s="10" t="s">
-        <x:v>535</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="D441" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E441" s="10" t="s">
-        <x:v>546</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="F441" s="10" t="s">
         <x:v>3</x:v>
@@ -18231,13 +18227,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C442" s="10" t="s">
-        <x:v>535</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="D442" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E442" s="10" t="s">
-        <x:v>426</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="F442" s="10" t="s">
         <x:v>3</x:v>
@@ -18265,13 +18261,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C443" s="10" t="s">
-        <x:v>535</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="D443" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E443" s="10" t="s">
-        <x:v>547</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="F443" s="10" t="s">
         <x:v>3</x:v>
@@ -18299,13 +18295,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C444" s="10" t="s">
-        <x:v>535</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="D444" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E444" s="10" t="s">
-        <x:v>548</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="F444" s="10" t="s">
         <x:v>3</x:v>
@@ -18333,13 +18329,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C445" s="10" t="s">
-        <x:v>549</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="D445" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E445" s="10" t="s">
-        <x:v>550</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="F445" s="10" t="s">
         <x:v>3</x:v>
@@ -18367,13 +18363,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C446" s="10" t="s">
-        <x:v>549</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="D446" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E446" s="10" t="s">
-        <x:v>551</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="F446" s="10" t="s">
         <x:v>3</x:v>
@@ -18401,13 +18397,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C447" s="10" t="s">
-        <x:v>549</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="D447" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E447" s="10" t="s">
-        <x:v>552</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="F447" s="10" t="s">
         <x:v>3</x:v>
@@ -18435,13 +18431,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C448" s="10" t="s">
-        <x:v>549</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="D448" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E448" s="10" t="s">
-        <x:v>553</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="F448" s="10" t="s">
         <x:v>3</x:v>
@@ -18469,13 +18465,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C449" s="10" t="s">
-        <x:v>549</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="D449" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E449" s="10" t="s">
-        <x:v>554</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="F449" s="10" t="s">
         <x:v>3</x:v>
@@ -18503,13 +18499,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C450" s="10" t="s">
-        <x:v>549</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="D450" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E450" s="10" t="s">
-        <x:v>555</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="F450" s="10" t="s">
         <x:v>3</x:v>
@@ -18537,13 +18533,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C451" s="10" t="s">
-        <x:v>549</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="D451" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E451" s="10" t="s">
-        <x:v>556</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="F451" s="10" t="s">
         <x:v>3</x:v>
@@ -18571,13 +18567,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C452" s="10" t="s">
-        <x:v>549</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="D452" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E452" s="10" t="s">
-        <x:v>557</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="F452" s="10" t="s">
         <x:v>3</x:v>
@@ -18605,13 +18601,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C453" s="10" t="s">
-        <x:v>549</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="D453" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E453" s="10" t="s">
-        <x:v>558</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="F453" s="10" t="s">
         <x:v>3</x:v>
@@ -18639,13 +18635,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C454" s="10" t="s">
-        <x:v>549</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="D454" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E454" s="10" t="s">
-        <x:v>559</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="F454" s="10" t="s">
         <x:v>3</x:v>
@@ -18673,13 +18669,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C455" s="10" t="s">
-        <x:v>549</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="D455" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E455" s="10" t="s">
-        <x:v>560</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="F455" s="10" t="s">
         <x:v>3</x:v>
@@ -18707,13 +18703,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C456" s="10" t="s">
-        <x:v>549</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="D456" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E456" s="10" t="s">
-        <x:v>561</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="F456" s="10" t="s">
         <x:v>3</x:v>
@@ -18741,13 +18737,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C457" s="10" t="s">
-        <x:v>549</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="D457" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E457" s="10" t="s">
-        <x:v>562</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="F457" s="10" t="s">
         <x:v>3</x:v>
@@ -18775,13 +18771,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C458" s="10" t="s">
-        <x:v>563</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="D458" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E458" s="10" t="s">
-        <x:v>564</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="F458" s="10" t="s">
         <x:v>3</x:v>
@@ -18809,13 +18805,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C459" s="10" t="s">
-        <x:v>563</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="D459" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E459" s="10" t="s">
-        <x:v>565</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="F459" s="10" t="s">
         <x:v>3</x:v>
@@ -18843,13 +18839,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C460" s="10" t="s">
-        <x:v>563</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="D460" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E460" s="10" t="s">
-        <x:v>566</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="F460" s="10" t="s">
         <x:v>3</x:v>
@@ -18877,13 +18873,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C461" s="10" t="s">
-        <x:v>563</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="D461" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E461" s="10" t="s">
-        <x:v>567</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="F461" s="10" t="s">
         <x:v>3</x:v>
@@ -18911,13 +18907,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C462" s="10" t="s">
-        <x:v>563</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="D462" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E462" s="10" t="s">
-        <x:v>568</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="F462" s="10" t="s">
         <x:v>3</x:v>
@@ -18945,13 +18941,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C463" s="10" t="s">
-        <x:v>563</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="D463" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E463" s="10" t="s">
-        <x:v>569</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="F463" s="10" t="s">
         <x:v>3</x:v>
@@ -18979,13 +18975,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C464" s="10" t="s">
-        <x:v>563</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="D464" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E464" s="10" t="s">
-        <x:v>570</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="F464" s="10" t="s">
         <x:v>3</x:v>
@@ -19013,13 +19009,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C465" s="10" t="s">
-        <x:v>563</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="D465" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E465" s="10" t="s">
-        <x:v>571</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="F465" s="10" t="s">
         <x:v>3</x:v>
@@ -19047,13 +19043,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C466" s="10" t="s">
-        <x:v>563</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="D466" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E466" s="10" t="s">
-        <x:v>572</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="F466" s="10" t="s">
         <x:v>3</x:v>
@@ -19081,13 +19077,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C467" s="10" t="s">
-        <x:v>563</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="D467" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E467" s="10" t="s">
-        <x:v>573</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="F467" s="10" t="s">
         <x:v>3</x:v>
@@ -19115,13 +19111,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C468" s="10" t="s">
-        <x:v>563</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="D468" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E468" s="10" t="s">
-        <x:v>574</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="F468" s="10" t="s">
         <x:v>3</x:v>
@@ -19149,13 +19145,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C469" s="10" t="s">
-        <x:v>563</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="D469" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E469" s="10" t="s">
-        <x:v>575</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="F469" s="10" t="s">
         <x:v>3</x:v>
@@ -19183,13 +19179,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C470" s="10" t="s">
-        <x:v>563</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="D470" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E470" s="10" t="s">
-        <x:v>576</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="F470" s="10" t="s">
         <x:v>3</x:v>
@@ -19217,13 +19213,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C471" s="10" t="s">
-        <x:v>563</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="D471" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E471" s="10" t="s">
-        <x:v>491</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="F471" s="10" t="s">
         <x:v>3</x:v>
@@ -19251,13 +19247,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C472" s="10" t="s">
-        <x:v>563</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="D472" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E472" s="10" t="s">
-        <x:v>577</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="F472" s="10" t="s">
         <x:v>3</x:v>
@@ -19285,13 +19281,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C473" s="10" t="s">
-        <x:v>563</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="D473" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E473" s="10" t="s">
-        <x:v>578</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="F473" s="10" t="s">
         <x:v>3</x:v>
@@ -19319,13 +19315,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C474" s="10" t="s">
-        <x:v>579</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="D474" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E474" s="10" t="s">
-        <x:v>580</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="F474" s="10" t="s">
         <x:v>3</x:v>
@@ -19353,13 +19349,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C475" s="10" t="s">
-        <x:v>579</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="D475" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E475" s="10" t="s">
-        <x:v>581</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="F475" s="10" t="s">
         <x:v>3</x:v>
@@ -19387,13 +19383,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C476" s="10" t="s">
-        <x:v>579</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="D476" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E476" s="10" t="s">
-        <x:v>582</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="F476" s="10" t="s">
         <x:v>3</x:v>
@@ -19421,13 +19417,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C477" s="10" t="s">
-        <x:v>579</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="D477" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E477" s="10" t="s">
-        <x:v>583</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="F477" s="10" t="s">
         <x:v>3</x:v>
@@ -19455,13 +19451,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C478" s="10" t="s">
-        <x:v>579</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="D478" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E478" s="10" t="s">
-        <x:v>584</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="F478" s="10" t="s">
         <x:v>3</x:v>
@@ -19489,13 +19485,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C479" s="10" t="s">
-        <x:v>579</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="D479" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E479" s="10" t="s">
-        <x:v>585</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="F479" s="10" t="s">
         <x:v>3</x:v>
@@ -19523,13 +19519,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C480" s="10" t="s">
-        <x:v>579</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="D480" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E480" s="10" t="s">
-        <x:v>586</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="F480" s="10" t="s">
         <x:v>3</x:v>
@@ -19557,13 +19553,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C481" s="10" t="s">
-        <x:v>579</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="D481" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E481" s="10" t="s">
-        <x:v>587</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="F481" s="10" t="s">
         <x:v>3</x:v>
@@ -19591,13 +19587,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C482" s="10" t="s">
-        <x:v>579</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="D482" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E482" s="10" t="s">
-        <x:v>588</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="F482" s="10" t="s">
         <x:v>3</x:v>
@@ -19625,13 +19621,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C483" s="10" t="s">
-        <x:v>579</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="D483" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E483" s="10" t="s">
-        <x:v>589</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="F483" s="10" t="s">
         <x:v>3</x:v>
@@ -19659,13 +19655,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C484" s="10" t="s">
-        <x:v>579</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="D484" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E484" s="10" t="s">
-        <x:v>590</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="F484" s="10" t="s">
         <x:v>3</x:v>
@@ -19693,13 +19689,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C485" s="10" t="s">
-        <x:v>579</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="D485" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E485" s="10" t="s">
-        <x:v>591</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="F485" s="10" t="s">
         <x:v>3</x:v>
@@ -19727,13 +19723,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C486" s="10" t="s">
-        <x:v>579</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="D486" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E486" s="10" t="s">
-        <x:v>592</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="F486" s="10" t="s">
         <x:v>3</x:v>
@@ -19761,13 +19757,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C487" s="10" t="s">
-        <x:v>579</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="D487" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E487" s="10" t="s">
-        <x:v>593</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="F487" s="10" t="s">
         <x:v>3</x:v>
@@ -19795,13 +19791,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C488" s="10" t="s">
-        <x:v>579</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="D488" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E488" s="10" t="s">
-        <x:v>594</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="F488" s="10" t="s">
         <x:v>3</x:v>
@@ -19829,13 +19825,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C489" s="10" t="s">
-        <x:v>579</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="D489" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E489" s="10" t="s">
-        <x:v>595</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="F489" s="10" t="s">
         <x:v>3</x:v>
@@ -19863,13 +19859,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C490" s="10" t="s">
-        <x:v>596</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="D490" s="10" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E490" s="10" t="s">
-        <x:v>598</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="F490" s="10" t="s">
         <x:v>3</x:v>
@@ -19897,13 +19893,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C491" s="10" t="s">
-        <x:v>596</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="D491" s="10" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E491" s="10" t="s">
-        <x:v>599</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="F491" s="10" t="s">
         <x:v>3</x:v>
@@ -19931,13 +19927,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C492" s="10" t="s">
+        <x:v>592</x:v>
+      </x:c>
+      <x:c r="D492" s="10" t="s">
+        <x:v>593</x:v>
+      </x:c>
+      <x:c r="E492" s="10" t="s">
         <x:v>596</x:v>
-      </x:c>
-      <x:c r="D492" s="10" t="s">
-        <x:v>597</x:v>
-      </x:c>
-      <x:c r="E492" s="10" t="s">
-        <x:v>600</x:v>
       </x:c>
       <x:c r="F492" s="10" t="s">
         <x:v>3</x:v>
@@ -19965,13 +19961,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C493" s="10" t="s">
-        <x:v>596</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="D493" s="10" t="s">
+        <x:v>593</x:v>
+      </x:c>
+      <x:c r="E493" s="10" t="s">
         <x:v>597</x:v>
-      </x:c>
-      <x:c r="E493" s="10" t="s">
-        <x:v>601</x:v>
       </x:c>
       <x:c r="F493" s="10" t="s">
         <x:v>3</x:v>
@@ -19999,13 +19995,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C494" s="10" t="s">
-        <x:v>596</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="D494" s="10" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E494" s="10" t="s">
-        <x:v>602</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="F494" s="10" t="s">
         <x:v>3</x:v>
@@ -20033,13 +20029,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C495" s="10" t="s">
-        <x:v>596</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="D495" s="10" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E495" s="10" t="s">
-        <x:v>603</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="F495" s="10" t="s">
         <x:v>3</x:v>
@@ -20067,13 +20063,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C496" s="10" t="s">
-        <x:v>596</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="D496" s="10" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E496" s="10" t="s">
-        <x:v>604</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="F496" s="10" t="s">
         <x:v>3</x:v>
@@ -20101,13 +20097,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C497" t="s">
-        <x:v>596</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="D497" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E497" t="s">
-        <x:v>605</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="F497" t="s">
         <x:v>3</x:v>
@@ -20135,13 +20131,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C498" t="s">
-        <x:v>596</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="D498" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E498" t="s">
-        <x:v>606</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="F498" t="s">
         <x:v>3</x:v>
@@ -20169,13 +20165,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C499" t="s">
-        <x:v>596</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="D499" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E499" t="s">
-        <x:v>607</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="F499" t="s">
         <x:v>3</x:v>
@@ -20203,13 +20199,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C500" t="s">
-        <x:v>596</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="D500" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E500" t="s">
-        <x:v>608</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="F500" t="s">
         <x:v>3</x:v>
@@ -20237,13 +20233,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C501" t="s">
-        <x:v>596</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="D501" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E501" t="s">
-        <x:v>609</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="F501" t="s">
         <x:v>3</x:v>
@@ -20271,13 +20267,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C502" t="s">
-        <x:v>596</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="D502" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E502" t="s">
-        <x:v>610</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="F502" t="s">
         <x:v>3</x:v>
@@ -20305,13 +20301,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C503" t="s">
-        <x:v>596</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="D503" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E503" t="s">
-        <x:v>611</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="F503" t="s">
         <x:v>3</x:v>
@@ -20339,13 +20335,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C504" t="s">
-        <x:v>596</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="D504" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E504" t="s">
-        <x:v>612</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="F504" t="s">
         <x:v>3</x:v>
@@ -20373,13 +20369,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C505" t="s">
-        <x:v>596</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="D505" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E505" t="s">
-        <x:v>613</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="F505" t="s">
         <x:v>3</x:v>
@@ -20407,13 +20403,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C506" t="s">
-        <x:v>596</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="D506" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E506" t="s">
-        <x:v>614</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="F506" t="s">
         <x:v>3</x:v>
@@ -20441,10 +20437,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C507" t="s">
-        <x:v>596</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="D507" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E507" t="s">
         <x:v>17</x:v>
@@ -20475,13 +20471,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C508" t="s">
-        <x:v>596</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="D508" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E508" t="s">
-        <x:v>615</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="F508" t="s">
         <x:v>3</x:v>
@@ -20509,13 +20505,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C509" t="s">
-        <x:v>596</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="D509" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E509" t="s">
-        <x:v>616</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="F509" t="s">
         <x:v>3</x:v>
@@ -20543,13 +20539,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C510" t="s">
-        <x:v>617</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="D510" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E510" t="s">
-        <x:v>618</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="F510" t="s">
         <x:v>3</x:v>
@@ -20577,13 +20573,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C511" t="s">
-        <x:v>617</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="D511" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E511" t="s">
-        <x:v>619</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="F511" t="s">
         <x:v>3</x:v>
@@ -20611,13 +20607,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C512" t="s">
-        <x:v>617</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="D512" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E512" t="s">
-        <x:v>620</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="F512" t="s">
         <x:v>3</x:v>
@@ -20645,13 +20641,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C513" t="s">
+        <x:v>613</x:v>
+      </x:c>
+      <x:c r="D513" t="s">
+        <x:v>593</x:v>
+      </x:c>
+      <x:c r="E513" t="s">
         <x:v>617</x:v>
-      </x:c>
-      <x:c r="D513" t="s">
-        <x:v>597</x:v>
-      </x:c>
-      <x:c r="E513" t="s">
-        <x:v>621</x:v>
       </x:c>
       <x:c r="F513" t="s">
         <x:v>3</x:v>
@@ -20679,13 +20675,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C514" t="s">
-        <x:v>617</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="D514" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E514" t="s">
-        <x:v>622</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="F514" t="s">
         <x:v>3</x:v>
@@ -20713,13 +20709,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C515" t="s">
-        <x:v>617</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="D515" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E515" t="s">
-        <x:v>623</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="F515" t="s">
         <x:v>3</x:v>
@@ -20747,13 +20743,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C516" t="s">
-        <x:v>617</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="D516" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E516" t="s">
-        <x:v>624</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="F516" t="s">
         <x:v>3</x:v>
@@ -20781,13 +20777,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C517" t="s">
-        <x:v>617</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="D517" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E517" t="s">
-        <x:v>625</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="F517" t="s">
         <x:v>3</x:v>
@@ -20815,13 +20811,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C518" t="s">
-        <x:v>617</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="D518" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E518" t="s">
-        <x:v>626</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="F518" t="s">
         <x:v>3</x:v>
@@ -20849,13 +20845,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C519" t="s">
-        <x:v>617</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="D519" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E519" t="s">
-        <x:v>627</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="F519" t="s">
         <x:v>3</x:v>
@@ -20883,13 +20879,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C520" t="s">
-        <x:v>617</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="D520" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E520" t="s">
-        <x:v>628</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="F520" t="s">
         <x:v>3</x:v>
@@ -20917,13 +20913,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C521" t="s">
-        <x:v>617</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="D521" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E521" t="s">
-        <x:v>629</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="F521" t="s">
         <x:v>3</x:v>
@@ -20951,13 +20947,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C522" t="s">
-        <x:v>617</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="D522" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E522" t="s">
-        <x:v>630</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="F522" t="s">
         <x:v>3</x:v>
@@ -20985,13 +20981,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C523" t="s">
-        <x:v>617</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="D523" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E523" t="s">
-        <x:v>631</x:v>
+        <x:v>627</x:v>
       </x:c>
       <x:c r="F523" t="s">
         <x:v>3</x:v>
@@ -21019,13 +21015,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C524" t="s">
-        <x:v>617</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="D524" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E524" t="s">
-        <x:v>632</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="F524" t="s">
         <x:v>3</x:v>
@@ -21053,13 +21049,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C525" t="s">
-        <x:v>617</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="D525" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E525" t="s">
-        <x:v>633</x:v>
+        <x:v>629</x:v>
       </x:c>
       <x:c r="F525" t="s">
         <x:v>3</x:v>
@@ -21087,13 +21083,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C526" t="s">
-        <x:v>617</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="D526" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E526" t="s">
-        <x:v>634</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="F526" t="s">
         <x:v>3</x:v>
@@ -21121,13 +21117,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C527" t="s">
-        <x:v>617</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="D527" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E527" t="s">
-        <x:v>635</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="F527" t="s">
         <x:v>3</x:v>
@@ -21155,13 +21151,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C528" t="s">
-        <x:v>636</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="D528" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E528" t="s">
-        <x:v>637</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="F528" t="s">
         <x:v>3</x:v>
@@ -21189,13 +21185,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C529" t="s">
-        <x:v>636</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="D529" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E529" t="s">
-        <x:v>638</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="F529" t="s">
         <x:v>3</x:v>
@@ -21223,13 +21219,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C530" t="s">
-        <x:v>636</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="D530" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E530" t="s">
-        <x:v>639</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="F530" t="s">
         <x:v>3</x:v>
@@ -21257,13 +21253,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C531" t="s">
+        <x:v>632</x:v>
+      </x:c>
+      <x:c r="D531" t="s">
+        <x:v>593</x:v>
+      </x:c>
+      <x:c r="E531" t="s">
         <x:v>636</x:v>
-      </x:c>
-      <x:c r="D531" t="s">
-        <x:v>597</x:v>
-      </x:c>
-      <x:c r="E531" t="s">
-        <x:v>640</x:v>
       </x:c>
       <x:c r="F531" t="s">
         <x:v>3</x:v>
@@ -21291,13 +21287,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C532" t="s">
-        <x:v>636</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="D532" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E532" t="s">
-        <x:v>641</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="F532" t="s">
         <x:v>3</x:v>
@@ -21325,13 +21321,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C533" t="s">
-        <x:v>636</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="D533" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E533" t="s">
-        <x:v>642</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="F533" t="s">
         <x:v>3</x:v>
@@ -21359,13 +21355,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C534" t="s">
-        <x:v>636</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="D534" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E534" t="s">
-        <x:v>643</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="F534" t="s">
         <x:v>3</x:v>
@@ -26704,7 +26700,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8efaa7a29eb54f79"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8bc80fb34b924b1b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26852,15 +26848,15 @@
       </x:c>
       <x:c r="C5" t="n">
         <x:f>COUNTIFS(Checklist!$B:$B,A5,Checklist!$F:$F,"Chưa làm")</x:f>
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D5" t="n">
         <x:f>COUNTIFS(Checklist!$B:$B,A5,Checklist!$F:$F,"Đang làm")</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E5" t="n">
         <x:f>COUNTIFS(Checklist!$B:$B,A5,Checklist!$F:$F,"Hoàn thành")</x:f>
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F5" t="n">
         <x:f>COUNTIFS(Checklist!$B:$B,A5,Checklist!$F:$F,"Bị chặn")</x:f>
@@ -26872,7 +26868,7 @@
       </x:c>
       <x:c r="H5" s="6" t="n">
         <x:f t="shared" si="0">IFERROR(E5/B5,0)</x:f>
-        <x:v>0.6405228758169934</x:v>
+        <x:v>0.6535947712418301</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -27177,7 +27173,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1674582428814b2e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43692765fc344e4f"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">

--- a/CHECKLIST_TRIEN_KHAI_FULL.xlsx
+++ b/CHECKLIST_TRIEN_KHAI_FULL.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Ree558dcd69b74fc7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="Rd8f59b92cb734ab7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase Summary" sheetId="3" r:id="R47e5eb15c5b2429e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="4" r:id="Re0dff43412244138"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R967e2ae453124166"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="R5d48acdfe5564534"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase Summary" sheetId="3" r:id="Raadb3434e1854135"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="4" r:id="R371b7327354648a0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -869,15 +869,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">data/processed/coco/instances_test.json</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Leakage = 0.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Test set cố định, không dùng để tune.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Mọi experiment dùng cùng test set.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Test set chứa đủ ảnh No Finding để tính FP per negative image.</x:t>
@@ -2388,7 +2379,7 @@
       </x:c>
       <x:c r="B4" s="2" t="n">
         <x:f>COUNTIF(Checklist!$F:$F,"Chưa làm")</x:f>
-        <x:v>353</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="D4" s="3" t="s">
         <x:v>4</x:v>
@@ -2424,7 +2415,7 @@
       </x:c>
       <x:c r="B6" s="2" t="n">
         <x:f>COUNTIF(Checklist!$F:$F,"Hoàn thành")</x:f>
-        <x:v>178</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="D6" s="3" t="s">
         <x:v>10</x:v>
@@ -2460,7 +2451,7 @@
       </x:c>
       <x:c r="B8" s="5" t="n">
         <x:f>IFERROR(B6/B3,0)</x:f>
-        <x:v>0.3339587242026266</x:v>
+        <x:v>0.3677298311444653</x:v>
       </x:c>
       <x:c r="D8" s="3" t="s">
         <x:v>16</x:v>
@@ -2629,7 +2620,7 @@
       </x:c>
       <x:c r="C15" t="n">
         <x:f>'Phase Summary'!C5</x:f>
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D15" t="n">
         <x:f>'Phase Summary'!D5</x:f>
@@ -2637,7 +2628,7 @@
       </x:c>
       <x:c r="E15" t="n">
         <x:f>'Phase Summary'!E5</x:f>
-        <x:v>100</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="F15" t="n">
         <x:f>'Phase Summary'!F5</x:f>
@@ -2649,7 +2640,7 @@
       </x:c>
       <x:c r="H15" s="6" t="n">
         <x:f>'Phase Summary'!H5</x:f>
-        <x:v>0.6535947712418301</x:v>
+        <x:v>0.7712418300653595</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -9463,8 +9454,8 @@
       <x:c r="E184" s="10" t="s">
         <x:v>271</x:v>
       </x:c>
-      <x:c r="F184" s="10" t="s">
-        <x:v>3</x:v>
+      <x:c r="F184" s="10" t="str">
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="G184" s="10" t="s">
         <x:v>52</x:v>
@@ -9474,11 +9465,18 @@
       </x:c>
       <x:c r="I184" s="10"/>
       <x:c r="J184" s="10"/>
-      <x:c r="K184" s="10"/>
-      <x:c r="L184" s="10"/>
-      <x:c r="M184" s="10">
-        <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
+      <x:c r="K184" s="10" t="str">
+        <x:v>CLOSED / PASS; fixed split 70/15/15 đã được tạo từ COCO master: train/val/test = 3,426/734/734 ảnh; annotations = 25,260/5,399/5,437.</x:v>
+      </x:c>
+      <x:c r="L184" s="10" t="str">
+        <x:v>scripts/02E_build_fixed_split.py
+02E_build_fixed_split_output.txt
+reports/02E_build_fixed_split_validation_report.json
+reports/02E_build_fixed_split_log.json</x:v>
+      </x:c>
+      <x:c r="M184" s="10" t="n">
+        <x:f t="shared" si="2">IF(F184="Hoàn thành",1,0)</x:f>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="185" ht="27.600000381469727">
@@ -9497,8 +9495,8 @@
       <x:c r="E185" s="10" t="s">
         <x:v>272</x:v>
       </x:c>
-      <x:c r="F185" s="10" t="s">
-        <x:v>3</x:v>
+      <x:c r="F185" s="10" t="str">
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="G185" s="10" t="s">
         <x:v>64</x:v>
@@ -9508,11 +9506,16 @@
       </x:c>
       <x:c r="I185" s="10"/>
       <x:c r="J185" s="10"/>
-      <x:c r="K185" s="10"/>
-      <x:c r="L185" s="10"/>
-      <x:c r="M185" s="10">
-        <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
+      <x:c r="K185" s="10" t="str">
+        <x:v>PASS; dùng candidate split class-aware/constrained đã khóa từ R2. Cả train/val/test giữ đủ 14 categories; không tuyên bố cân bằng lớp tuyệt đối.</x:v>
+      </x:c>
+      <x:c r="L185" s="10" t="str">
+        <x:v>data/manifests/split_lock_manifest.json
+reports/02E_build_fixed_split_validation_report.json</x:v>
+      </x:c>
+      <x:c r="M185" s="10" t="n">
+        <x:f t="shared" si="2">IF(F185="Hoàn thành",1,0)</x:f>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="186" ht="27.600000381469727">
@@ -9531,8 +9534,8 @@
       <x:c r="E186" s="10" t="s">
         <x:v>273</x:v>
       </x:c>
-      <x:c r="F186" s="10" t="s">
-        <x:v>3</x:v>
+      <x:c r="F186" s="10" t="str">
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="G186" s="10" t="s">
         <x:v>64</x:v>
@@ -9542,11 +9545,16 @@
       </x:c>
       <x:c r="I186" s="10"/>
       <x:c r="J186" s="10"/>
-      <x:c r="K186" s="10"/>
-      <x:c r="L186" s="10"/>
-      <x:c r="M186" s="10">
-        <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
+      <x:c r="K186" s="10" t="str">
+        <x:v>PASS; No Finding được phân bổ 350/75/75, tương ứng 10.216%/10.218%/10.218%.</x:v>
+      </x:c>
+      <x:c r="L186" s="10" t="str">
+        <x:v>reports/split_negative_distribution.csv
+data/manifests/fixed_split_manifest.csv</x:v>
+      </x:c>
+      <x:c r="M186" s="10" t="n">
+        <x:f t="shared" si="2">IF(F186="Hoàn thành",1,0)</x:f>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="187" ht="27.600000381469727">
@@ -9565,8 +9573,8 @@
       <x:c r="E187" s="10" t="s">
         <x:v>274</x:v>
       </x:c>
-      <x:c r="F187" s="10" t="s">
-        <x:v>3</x:v>
+      <x:c r="F187" s="10" t="str">
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="G187" s="10" t="s">
         <x:v>52</x:v>
@@ -9576,11 +9584,16 @@
       </x:c>
       <x:c r="I187" s="10"/>
       <x:c r="J187" s="10"/>
-      <x:c r="K187" s="10"/>
-      <x:c r="L187" s="10"/>
-      <x:c r="M187" s="10">
-        <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
+      <x:c r="K187" s="10" t="str">
+        <x:v>PASS; test có 75 ảnh No Finding (zero-GT), cho phép tính FP per negative image. Cỡ mẫu cho phép tính chỉ số nhưng không mặc nhiên bảo đảm CI hẹp.</x:v>
+      </x:c>
+      <x:c r="L187" s="10" t="str">
+        <x:v>data/processed/coco/instances_test.json
+reports/split_negative_distribution.csv</x:v>
+      </x:c>
+      <x:c r="M187" s="10" t="n">
+        <x:f t="shared" si="2">IF(F187="Hoàn thành",1,0)</x:f>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="188" ht="27.600000381469727">
@@ -9599,8 +9612,8 @@
       <x:c r="E188" s="10" t="s">
         <x:v>275</x:v>
       </x:c>
-      <x:c r="F188" s="10" t="s">
-        <x:v>3</x:v>
+      <x:c r="F188" s="10" t="str">
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="G188" s="10" t="s">
         <x:v>52</x:v>
@@ -9610,11 +9623,16 @@
       </x:c>
       <x:c r="I188" s="10"/>
       <x:c r="J188" s="10"/>
-      <x:c r="K188" s="10"/>
-      <x:c r="L188" s="10"/>
-      <x:c r="M188" s="10">
-        <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
+      <x:c r="K188" s="10" t="str">
+        <x:v>PASS; số lượng và tỷ lệ No Finding đã được báo cáo cho cả train/val/test: 350/3,426; 75/734; 75/734.</x:v>
+      </x:c>
+      <x:c r="L188" s="10" t="str">
+        <x:v>reports/split_negative_distribution.csv
+reports/02E_build_fixed_split_validation_report.json</x:v>
+      </x:c>
+      <x:c r="M188" s="10" t="n">
+        <x:f t="shared" si="2">IF(F188="Hoàn thành",1,0)</x:f>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="27.600000381469727">
@@ -9633,8 +9651,8 @@
       <x:c r="E189" s="10" t="s">
         <x:v>276</x:v>
       </x:c>
-      <x:c r="F189" s="10" t="s">
-        <x:v>3</x:v>
+      <x:c r="F189" s="10" t="str">
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="G189" s="10" t="s">
         <x:v>52</x:v>
@@ -9644,11 +9662,16 @@
       </x:c>
       <x:c r="I189" s="10"/>
       <x:c r="J189" s="10"/>
-      <x:c r="K189" s="10"/>
-      <x:c r="L189" s="10"/>
-      <x:c r="M189" s="10">
-        <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
+      <x:c r="K189" s="10" t="str">
+        <x:v>PASS; overlap image_id: train-val=0, train-test=0, val-test=0; union=4,894/4,894.</x:v>
+      </x:c>
+      <x:c r="L189" s="10" t="str">
+        <x:v>data/manifests/leakage_check_report.json
+reports/02E_build_fixed_split_validation_report.json</x:v>
+      </x:c>
+      <x:c r="M189" s="10" t="n">
+        <x:f t="shared" si="2">IF(F189="Hoàn thành",1,0)</x:f>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="190" ht="27.600000381469727">
@@ -9667,8 +9690,8 @@
       <x:c r="E190" s="10" t="s">
         <x:v>277</x:v>
       </x:c>
-      <x:c r="F190" s="10" t="s">
-        <x:v>3</x:v>
+      <x:c r="F190" s="10" t="str">
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="G190" s="10" t="s">
         <x:v>64</x:v>
@@ -9678,11 +9701,16 @@
       </x:c>
       <x:c r="I190" s="10"/>
       <x:c r="J190" s="10"/>
-      <x:c r="K190" s="10"/>
-      <x:c r="L190" s="10"/>
-      <x:c r="M190" s="10">
-        <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
+      <x:c r="K190" s="10" t="str">
+        <x:v>COMPLETED; split lock manifest đã xuất và khóa SHA-256 image-ID cho từng tập.</x:v>
+      </x:c>
+      <x:c r="L190" s="10" t="str">
+        <x:v>data/manifests/split_lock_manifest.json
+scripts/02E_build_fixed_split.py</x:v>
+      </x:c>
+      <x:c r="M190" s="10" t="n">
+        <x:f t="shared" si="2">IF(F190="Hoàn thành",1,0)</x:f>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="191" ht="27.600000381469727">
@@ -9701,8 +9729,8 @@
       <x:c r="E191" s="10" t="s">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="F191" s="10" t="s">
-        <x:v>3</x:v>
+      <x:c r="F191" s="10" t="str">
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="G191" s="10" t="s">
         <x:v>64</x:v>
@@ -9712,11 +9740,15 @@
       </x:c>
       <x:c r="I191" s="10"/>
       <x:c r="J191" s="10"/>
-      <x:c r="K191" s="10"/>
-      <x:c r="L191" s="10"/>
-      <x:c r="M191" s="10">
-        <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
+      <x:c r="K191" s="10" t="str">
+        <x:v>OUTPUT VERIFIED; manifest ghi split policy, counts và ba SHA-256 image-ID đã khóa.</x:v>
+      </x:c>
+      <x:c r="L191" s="10" t="str">
+        <x:v>data/manifests/split_lock_manifest.json</x:v>
+      </x:c>
+      <x:c r="M191" s="10" t="n">
+        <x:f t="shared" si="2">IF(F191="Hoàn thành",1,0)</x:f>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="192" ht="27.600000381469727">
@@ -9735,8 +9767,8 @@
       <x:c r="E192" s="10" t="s">
         <x:v>279</x:v>
       </x:c>
-      <x:c r="F192" s="10" t="s">
-        <x:v>3</x:v>
+      <x:c r="F192" s="10" t="str">
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="G192" s="10" t="s">
         <x:v>64</x:v>
@@ -9746,11 +9778,16 @@
       </x:c>
       <x:c r="I192" s="10"/>
       <x:c r="J192" s="10"/>
-      <x:c r="K192" s="10"/>
-      <x:c r="L192" s="10"/>
-      <x:c r="M192" s="10">
-        <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
+      <x:c r="K192" s="10" t="str">
+        <x:v>OUTPUT VERIFIED; leakage cấp image_id và annotation bằng 0. Patient-level NOT ASSESSABLE vì PatientID/các định danh nhóm đã bị loại bỏ khi de-identification.</x:v>
+      </x:c>
+      <x:c r="L192" s="10" t="str">
+        <x:v>data/manifests/leakage_check_report.json
+reports/02E_build_fixed_split_validation_report.json</x:v>
+      </x:c>
+      <x:c r="M192" s="10" t="n">
+        <x:f t="shared" si="2">IF(F192="Hoàn thành",1,0)</x:f>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="193" ht="27.600000381469727">
@@ -9769,8 +9806,8 @@
       <x:c r="E193" s="10" t="s">
         <x:v>280</x:v>
       </x:c>
-      <x:c r="F193" s="10" t="s">
-        <x:v>3</x:v>
+      <x:c r="F193" s="10" t="str">
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="G193" s="10" t="s">
         <x:v>64</x:v>
@@ -9780,11 +9817,15 @@
       </x:c>
       <x:c r="I193" s="10"/>
       <x:c r="J193" s="10"/>
-      <x:c r="K193" s="10"/>
-      <x:c r="L193" s="10"/>
-      <x:c r="M193" s="10">
-        <x:f t="shared" si="2"/>
-        <x:v>0</x:v>
+      <x:c r="K193" s="10" t="str">
+        <x:v>OUTPUT VERIFIED; báo cáo negative distribution chứa counts và tỷ lệ train/val/test.</x:v>
+      </x:c>
+      <x:c r="L193" s="10" t="str">
+        <x:v>reports/split_negative_distribution.csv</x:v>
+      </x:c>
+      <x:c r="M193" s="10" t="n">
+        <x:f t="shared" si="2">IF(F193="Hoàn thành",1,0)</x:f>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="194" ht="27.600000381469727">
@@ -9803,8 +9844,8 @@
       <x:c r="E194" s="10" t="s">
         <x:v>281</x:v>
       </x:c>
-      <x:c r="F194" s="10" t="s">
-        <x:v>3</x:v>
+      <x:c r="F194" s="10" t="str">
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="G194" s="10" t="s">
         <x:v>64</x:v>
@@ -9814,11 +9855,16 @@
       </x:c>
       <x:c r="I194" s="10"/>
       <x:c r="J194" s="10"/>
-      <x:c r="K194" s="10"/>
-      <x:c r="L194" s="10"/>
+      <x:c r="K194" s="10" t="str">
+        <x:v>OUTPUT VERIFIED; train COCO: 3,426 images, 25,260 annotations, 350 zero-GT; SHA-256 JSON locked.</x:v>
+      </x:c>
+      <x:c r="L194" s="10" t="str">
+        <x:v>data/processed/coco/instances_train.json
+reports/02E_build_fixed_split_validation_report.json</x:v>
+      </x:c>
       <x:c r="M194" s="10" t="n">
         <x:f t="shared" ref="M194:M257" si="3">IF(F194="Hoàn thành",1,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="195" ht="27.600000381469727">
@@ -9837,8 +9883,8 @@
       <x:c r="E195" s="10" t="s">
         <x:v>282</x:v>
       </x:c>
-      <x:c r="F195" s="10" t="s">
-        <x:v>3</x:v>
+      <x:c r="F195" s="10" t="str">
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="G195" s="10" t="s">
         <x:v>64</x:v>
@@ -9848,11 +9894,16 @@
       </x:c>
       <x:c r="I195" s="10"/>
       <x:c r="J195" s="10"/>
-      <x:c r="K195" s="10"/>
-      <x:c r="L195" s="10"/>
-      <x:c r="M195" s="10">
-        <x:f t="shared" si="3"/>
-        <x:v>0</x:v>
+      <x:c r="K195" s="10" t="str">
+        <x:v>OUTPUT VERIFIED; validation COCO: 734 images, 5,399 annotations, 75 zero-GT; SHA-256 JSON locked.</x:v>
+      </x:c>
+      <x:c r="L195" s="10" t="str">
+        <x:v>data/processed/coco/instances_val.json
+reports/02E_build_fixed_split_validation_report.json</x:v>
+      </x:c>
+      <x:c r="M195" s="10" t="n">
+        <x:f t="shared" si="3">IF(F195="Hoàn thành",1,0)</x:f>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="196" ht="27.600000381469727">
@@ -9871,8 +9922,8 @@
       <x:c r="E196" s="10" t="s">
         <x:v>283</x:v>
       </x:c>
-      <x:c r="F196" s="10" t="s">
-        <x:v>3</x:v>
+      <x:c r="F196" s="10" t="str">
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="G196" s="10" t="s">
         <x:v>64</x:v>
@@ -9882,11 +9933,16 @@
       </x:c>
       <x:c r="I196" s="10"/>
       <x:c r="J196" s="10"/>
-      <x:c r="K196" s="10"/>
-      <x:c r="L196" s="10"/>
-      <x:c r="M196" s="10">
-        <x:f t="shared" si="3"/>
-        <x:v>0</x:v>
+      <x:c r="K196" s="10" t="str">
+        <x:v>OUTPUT VERIFIED; test COCO: 734 images, 5,437 annotations, 75 zero-GT; SHA-256 JSON locked.</x:v>
+      </x:c>
+      <x:c r="L196" s="10" t="str">
+        <x:v>data/processed/coco/instances_test.json
+reports/02E_build_fixed_split_validation_report.json</x:v>
+      </x:c>
+      <x:c r="M196" s="10" t="n">
+        <x:f t="shared" si="3">IF(F196="Hoàn thành",1,0)</x:f>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="197" ht="27.600000381469727">
@@ -9902,11 +9958,11 @@
       <x:c r="D197" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="E197" s="10" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="F197" s="10" t="s">
-        <x:v>3</x:v>
+      <x:c r="E197" s="10" t="str">
+        <x:v>Xác nhận leakage = 0 ở cấp image_id và annotation; ghi rõ patient-level không thể đánh giá do de-identification.</x:v>
+      </x:c>
+      <x:c r="F197" s="10" t="str">
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="G197" s="10" t="s">
         <x:v>52</x:v>
@@ -9916,11 +9972,17 @@
       </x:c>
       <x:c r="I197" s="10"/>
       <x:c r="J197" s="10"/>
-      <x:c r="K197" s="10"/>
-      <x:c r="L197" s="10"/>
-      <x:c r="M197" s="10">
-        <x:f t="shared" si="3"/>
-        <x:v>0</x:v>
+      <x:c r="K197" s="10" t="str">
+        <x:v>PASS trong phạm vi kiểm chứng: image-level và annotation-level leakage = 0. Patient-level leakage không thể đánh giá do không còn khóa bệnh nhân/study trong dữ liệu công bố.</x:v>
+      </x:c>
+      <x:c r="L197" s="10" t="str">
+        <x:v>data/manifests/leakage_check_report.json
+PROJECT_CONTEXT.md
+PHASE_HANDOFF.md</x:v>
+      </x:c>
+      <x:c r="M197" s="10" t="n">
+        <x:f t="shared" si="3">IF(F197="Hoàn thành",1,0)</x:f>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="198" ht="27.600000381469727">
@@ -9936,11 +9998,11 @@
       <x:c r="D198" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="E198" s="10" t="s">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="F198" s="10" t="s">
-        <x:v>3</x:v>
+      <x:c r="E198" s="10" t="str">
+        <x:v>Khóa test set cố định và chính sách không dùng test để tuning/model selection.</x:v>
+      </x:c>
+      <x:c r="F198" s="10" t="str">
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="G198" s="10" t="s">
         <x:v>52</x:v>
@@ -9950,11 +10012,17 @@
       </x:c>
       <x:c r="I198" s="10"/>
       <x:c r="J198" s="10"/>
-      <x:c r="K198" s="10"/>
-      <x:c r="L198" s="10"/>
-      <x:c r="M198" s="10">
-        <x:f t="shared" si="3"/>
-        <x:v>0</x:v>
+      <x:c r="K198" s="10" t="str">
+        <x:v>POLICY LOCKED; test JSON/checksum cố định; cấm dùng test cho checkpoint selection, threshold selection, early stopping, hyperparameter tuning hoặc ablation decisions.</x:v>
+      </x:c>
+      <x:c r="L198" s="10" t="str">
+        <x:v>data/manifests/split_lock_manifest.json
+PROJECT_CONTEXT.md
+PHASE_HANDOFF.md</x:v>
+      </x:c>
+      <x:c r="M198" s="10" t="n">
+        <x:f t="shared" si="3">IF(F198="Hoàn thành",1,0)</x:f>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="27.600000381469727">
@@ -9970,11 +10038,11 @@
       <x:c r="D199" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="E199" s="10" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="F199" s="10" t="s">
-        <x:v>3</x:v>
+      <x:c r="E199" s="10" t="str">
+        <x:v>Khóa chính sách mọi experiment phải dùng cùng fixed test set và xác minh bằng config/log khi chạy.</x:v>
+      </x:c>
+      <x:c r="F199" s="10" t="str">
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="G199" s="10" t="s">
         <x:v>52</x:v>
@@ -9984,11 +10052,17 @@
       </x:c>
       <x:c r="I199" s="10"/>
       <x:c r="J199" s="10"/>
-      <x:c r="K199" s="10"/>
-      <x:c r="L199" s="10"/>
-      <x:c r="M199" s="10">
-        <x:f t="shared" si="3"/>
-        <x:v>0</x:v>
+      <x:c r="K199" s="10" t="str">
+        <x:v>POLICY LOCKED / TO VERIFY PER RUN; mọi experiment phải tham chiếu cùng instances_test.json và checksum; tuân thủ sẽ được audit từ config/log từng experiment.</x:v>
+      </x:c>
+      <x:c r="L199" s="10" t="str">
+        <x:v>data/manifests/split_lock_manifest.json
+PROJECT_CONTEXT.md
+PHASE_HANDOFF.md</x:v>
+      </x:c>
+      <x:c r="M199" s="10" t="n">
+        <x:f t="shared" si="3">IF(F199="Hoàn thành",1,0)</x:f>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="27.600000381469727">
@@ -10005,10 +10079,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="E200" s="10" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="F200" s="10" t="s">
-        <x:v>3</x:v>
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="F200" s="10" t="str">
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="G200" s="10" t="s">
         <x:v>52</x:v>
@@ -10018,11 +10092,16 @@
       </x:c>
       <x:c r="I200" s="10"/>
       <x:c r="J200" s="10"/>
-      <x:c r="K200" s="10"/>
-      <x:c r="L200" s="10"/>
-      <x:c r="M200" s="10">
-        <x:f t="shared" si="3"/>
-        <x:v>0</x:v>
+      <x:c r="K200" s="10" t="str">
+        <x:v>PASS; test có 75 No Finding/zero-GT, đủ điều kiện tính FP per negative image = tổng FP trên ảnh âm tính / 75.</x:v>
+      </x:c>
+      <x:c r="L200" s="10" t="str">
+        <x:v>data/processed/coco/instances_test.json
+reports/split_negative_distribution.csv</x:v>
+      </x:c>
+      <x:c r="M200" s="10" t="n">
+        <x:f t="shared" si="3">IF(F200="Hoàn thành",1,0)</x:f>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="201" ht="27.600000381469727">
@@ -10039,10 +10118,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="E201" s="10" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="F201" s="10" t="s">
-        <x:v>3</x:v>
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="F201" s="10" t="str">
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="G201" s="10" t="s">
         <x:v>52</x:v>
@@ -10052,11 +10131,16 @@
       </x:c>
       <x:c r="I201" s="10"/>
       <x:c r="J201" s="10"/>
-      <x:c r="K201" s="10"/>
-      <x:c r="L201" s="10"/>
-      <x:c r="M201" s="10">
-        <x:f t="shared" si="3"/>
-        <x:v>0</x:v>
+      <x:c r="K201" s="10" t="str">
+        <x:v>PASS; train 350/3,426 (10.216%); val 75/734 (10.218%); test 75/734 (10.218%).</x:v>
+      </x:c>
+      <x:c r="L201" s="10" t="str">
+        <x:v>reports/split_negative_distribution.csv
+reports/02E_build_fixed_split_validation_report.json</x:v>
+      </x:c>
+      <x:c r="M201" s="10" t="n">
+        <x:f t="shared" si="3">IF(F201="Hoàn thành",1,0)</x:f>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="27.600000381469727">
@@ -10067,13 +10151,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C202" s="10" t="s">
-        <x:v>289</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D202" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E202" s="10" t="s">
-        <x:v>290</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="F202" s="10" t="s">
         <x:v>3</x:v>
@@ -10101,13 +10185,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C203" s="10" t="s">
-        <x:v>289</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D203" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E203" s="10" t="s">
-        <x:v>291</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="F203" s="10" t="s">
         <x:v>3</x:v>
@@ -10135,13 +10219,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C204" s="10" t="s">
-        <x:v>289</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D204" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E204" s="10" t="s">
-        <x:v>292</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="F204" s="10" t="s">
         <x:v>3</x:v>
@@ -10169,13 +10253,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C205" s="10" t="s">
-        <x:v>289</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D205" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E205" s="10" t="s">
-        <x:v>293</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="F205" s="10" t="s">
         <x:v>3</x:v>
@@ -10203,13 +10287,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C206" s="10" t="s">
-        <x:v>289</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D206" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E206" s="10" t="s">
-        <x:v>294</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="F206" s="10" t="s">
         <x:v>3</x:v>
@@ -10237,13 +10321,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C207" s="10" t="s">
-        <x:v>289</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D207" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E207" s="10" t="s">
-        <x:v>295</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="F207" s="10" t="s">
         <x:v>3</x:v>
@@ -10271,13 +10355,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C208" s="10" t="s">
-        <x:v>289</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D208" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E208" s="10" t="s">
-        <x:v>296</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="F208" s="10" t="s">
         <x:v>3</x:v>
@@ -10305,13 +10389,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C209" s="10" t="s">
-        <x:v>289</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D209" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E209" s="10" t="s">
-        <x:v>297</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="F209" s="10" t="s">
         <x:v>3</x:v>
@@ -10339,13 +10423,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C210" s="10" t="s">
-        <x:v>289</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D210" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E210" s="10" t="s">
-        <x:v>298</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="F210" s="10" t="s">
         <x:v>3</x:v>
@@ -10373,13 +10457,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C211" s="10" t="s">
-        <x:v>289</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D211" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E211" s="10" t="s">
-        <x:v>299</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="F211" s="10" t="s">
         <x:v>3</x:v>
@@ -10407,13 +10491,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C212" s="10" t="s">
-        <x:v>289</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D212" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E212" s="10" t="s">
-        <x:v>300</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="F212" s="10" t="s">
         <x:v>3</x:v>
@@ -10441,13 +10525,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C213" s="10" t="s">
-        <x:v>289</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D213" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E213" s="10" t="s">
-        <x:v>301</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="F213" s="10" t="s">
         <x:v>3</x:v>
@@ -10475,13 +10559,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C214" s="10" t="s">
-        <x:v>289</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D214" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E214" s="10" t="s">
-        <x:v>302</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="F214" s="10" t="s">
         <x:v>3</x:v>
@@ -10509,13 +10593,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C215" s="10" t="s">
-        <x:v>289</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D215" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E215" s="10" t="s">
-        <x:v>303</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="F215" s="10" t="s">
         <x:v>3</x:v>
@@ -10543,13 +10627,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C216" s="10" t="s">
-        <x:v>289</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D216" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E216" s="10" t="s">
-        <x:v>304</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="F216" s="10" t="s">
         <x:v>3</x:v>
@@ -10577,13 +10661,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C217" s="10" t="s">
-        <x:v>289</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D217" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E217" s="10" t="s">
-        <x:v>305</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="F217" s="10" t="s">
         <x:v>3</x:v>
@@ -10611,13 +10695,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C218" s="10" t="s">
-        <x:v>289</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D218" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E218" s="10" t="s">
-        <x:v>306</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F218" s="10" t="s">
         <x:v>3</x:v>
@@ -10645,13 +10729,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C219" s="10" t="s">
-        <x:v>289</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D219" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E219" s="10" t="s">
-        <x:v>307</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="F219" s="10" t="s">
         <x:v>3</x:v>
@@ -10679,13 +10763,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C220" s="10" t="s">
-        <x:v>289</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D220" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E220" s="10" t="s">
-        <x:v>308</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="F220" s="10" t="s">
         <x:v>3</x:v>
@@ -10713,13 +10797,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C221" s="10" t="s">
-        <x:v>289</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D221" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E221" s="10" t="s">
-        <x:v>309</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="F221" s="10" t="s">
         <x:v>3</x:v>
@@ -10747,13 +10831,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C222" s="10" t="s">
-        <x:v>289</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D222" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E222" s="10" t="s">
-        <x:v>310</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="F222" s="10" t="s">
         <x:v>3</x:v>
@@ -10781,13 +10865,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C223" s="10" t="s">
-        <x:v>289</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D223" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E223" s="10" t="s">
-        <x:v>311</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="F223" s="10" t="s">
         <x:v>3</x:v>
@@ -10815,13 +10899,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C224" s="10" t="s">
-        <x:v>289</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D224" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E224" s="10" t="s">
-        <x:v>312</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="F224" s="10" t="s">
         <x:v>3</x:v>
@@ -10849,13 +10933,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C225" s="10" t="s">
-        <x:v>313</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="D225" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E225" s="10" t="s">
-        <x:v>314</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="F225" s="10" t="s">
         <x:v>3</x:v>
@@ -10883,13 +10967,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C226" s="10" t="s">
-        <x:v>313</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="D226" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E226" s="10" t="s">
-        <x:v>315</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="F226" s="10" t="s">
         <x:v>3</x:v>
@@ -10917,13 +11001,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C227" s="10" t="s">
-        <x:v>313</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="D227" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E227" s="10" t="s">
-        <x:v>316</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="F227" s="10" t="s">
         <x:v>3</x:v>
@@ -10951,13 +11035,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C228" s="10" t="s">
-        <x:v>313</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="D228" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E228" s="10" t="s">
-        <x:v>317</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="F228" s="10" t="s">
         <x:v>3</x:v>
@@ -10985,13 +11069,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C229" s="10" t="s">
-        <x:v>313</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="D229" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E229" s="10" t="s">
-        <x:v>318</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="F229" s="10" t="s">
         <x:v>3</x:v>
@@ -11019,13 +11103,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C230" s="10" t="s">
-        <x:v>313</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="D230" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E230" s="10" t="s">
-        <x:v>319</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="F230" s="10" t="s">
         <x:v>3</x:v>
@@ -11053,13 +11137,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C231" s="10" t="s">
-        <x:v>313</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="D231" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E231" s="10" t="s">
-        <x:v>320</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="F231" s="10" t="s">
         <x:v>3</x:v>
@@ -11087,7 +11171,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C232" s="10" t="s">
-        <x:v>313</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="D232" s="10" t="s">
         <x:v>78</x:v>
@@ -11121,13 +11205,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C233" s="10" t="s">
-        <x:v>313</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="D233" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E233" s="10" t="s">
-        <x:v>321</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="F233" s="10" t="s">
         <x:v>3</x:v>
@@ -11155,13 +11239,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C234" s="10" t="s">
-        <x:v>313</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="D234" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E234" s="10" t="s">
-        <x:v>322</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="F234" s="10" t="s">
         <x:v>3</x:v>
@@ -11189,13 +11273,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C235" s="10" t="s">
-        <x:v>313</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="D235" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E235" s="10" t="s">
-        <x:v>323</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="F235" s="10" t="s">
         <x:v>3</x:v>
@@ -11223,13 +11307,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C236" s="10" t="s">
-        <x:v>313</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="D236" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E236" s="10" t="s">
-        <x:v>324</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="F236" s="10" t="s">
         <x:v>3</x:v>
@@ -11257,13 +11341,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C237" s="10" t="s">
-        <x:v>325</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="D237" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E237" s="10" t="s">
-        <x:v>326</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="F237" s="10" t="s">
         <x:v>3</x:v>
@@ -11291,13 +11375,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C238" s="10" t="s">
-        <x:v>325</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="D238" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E238" s="10" t="s">
-        <x:v>327</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="F238" s="10" t="s">
         <x:v>3</x:v>
@@ -11325,13 +11409,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C239" s="10" t="s">
-        <x:v>325</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="D239" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E239" s="10" t="s">
-        <x:v>328</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="F239" s="10" t="s">
         <x:v>3</x:v>
@@ -11359,13 +11443,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C240" s="10" t="s">
-        <x:v>325</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="D240" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E240" s="10" t="s">
-        <x:v>329</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="F240" s="10" t="s">
         <x:v>3</x:v>
@@ -11393,13 +11477,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C241" s="10" t="s">
-        <x:v>325</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="D241" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E241" s="10" t="s">
-        <x:v>330</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="F241" s="10" t="s">
         <x:v>3</x:v>
@@ -11427,13 +11511,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C242" s="10" t="s">
-        <x:v>325</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="D242" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E242" s="10" t="s">
-        <x:v>331</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="F242" s="10" t="s">
         <x:v>3</x:v>
@@ -11461,13 +11545,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C243" s="10" t="s">
-        <x:v>325</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="D243" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E243" s="10" t="s">
-        <x:v>332</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="F243" s="10" t="s">
         <x:v>3</x:v>
@@ -11495,13 +11579,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C244" s="10" t="s">
-        <x:v>325</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="D244" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E244" s="10" t="s">
-        <x:v>333</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="F244" s="10" t="s">
         <x:v>3</x:v>
@@ -11529,13 +11613,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C245" s="10" t="s">
-        <x:v>325</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="D245" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E245" s="10" t="s">
-        <x:v>334</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="F245" s="10" t="s">
         <x:v>3</x:v>
@@ -11563,13 +11647,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C246" s="10" t="s">
-        <x:v>325</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="D246" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E246" s="10" t="s">
-        <x:v>335</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="F246" s="10" t="s">
         <x:v>3</x:v>
@@ -11597,13 +11681,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C247" s="10" t="s">
-        <x:v>325</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="D247" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E247" s="10" t="s">
-        <x:v>336</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="F247" s="10" t="s">
         <x:v>3</x:v>
@@ -11631,13 +11715,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C248" s="10" t="s">
-        <x:v>325</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="D248" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E248" s="10" t="s">
-        <x:v>337</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="F248" s="10" t="s">
         <x:v>3</x:v>
@@ -11665,13 +11749,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C249" s="10" t="s">
-        <x:v>325</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="D249" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E249" s="10" t="s">
-        <x:v>338</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="F249" s="10" t="s">
         <x:v>3</x:v>
@@ -11699,13 +11783,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C250" s="10" t="s">
-        <x:v>325</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="D250" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E250" s="10" t="s">
-        <x:v>339</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="F250" s="10" t="s">
         <x:v>3</x:v>
@@ -11733,13 +11817,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C251" s="10" t="s">
-        <x:v>325</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="D251" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E251" s="10" t="s">
-        <x:v>340</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="F251" s="10" t="s">
         <x:v>3</x:v>
@@ -11767,13 +11851,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C252" s="10" t="s">
-        <x:v>325</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="D252" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E252" s="10" t="s">
-        <x:v>341</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="F252" s="10" t="s">
         <x:v>3</x:v>
@@ -11801,13 +11885,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C253" s="10" t="s">
-        <x:v>325</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="D253" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E253" s="10" t="s">
-        <x:v>342</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="F253" s="10" t="s">
         <x:v>3</x:v>
@@ -11835,13 +11919,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C254" s="10" t="s">
-        <x:v>343</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="D254" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E254" s="10" t="s">
-        <x:v>344</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="F254" s="10" t="s">
         <x:v>3</x:v>
@@ -11869,13 +11953,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C255" s="10" t="s">
-        <x:v>343</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="D255" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E255" s="10" t="s">
-        <x:v>345</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="F255" s="10" t="s">
         <x:v>3</x:v>
@@ -11903,13 +11987,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C256" s="10" t="s">
-        <x:v>343</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="D256" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E256" s="10" t="s">
-        <x:v>346</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="F256" s="10" t="s">
         <x:v>3</x:v>
@@ -11937,13 +12021,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C257" s="10" t="s">
-        <x:v>343</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="D257" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E257" s="10" t="s">
-        <x:v>347</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="F257" s="10" t="s">
         <x:v>3</x:v>
@@ -11971,13 +12055,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C258" s="10" t="s">
-        <x:v>343</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="D258" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E258" s="10" t="s">
-        <x:v>348</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="F258" s="10" t="s">
         <x:v>3</x:v>
@@ -12005,13 +12089,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C259" s="10" t="s">
-        <x:v>343</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="D259" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E259" s="10" t="s">
-        <x:v>349</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="F259" s="10" t="s">
         <x:v>3</x:v>
@@ -12039,13 +12123,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C260" s="10" t="s">
-        <x:v>343</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="D260" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E260" s="10" t="s">
-        <x:v>350</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="F260" s="10" t="s">
         <x:v>3</x:v>
@@ -12073,13 +12157,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C261" s="10" t="s">
-        <x:v>343</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="D261" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E261" s="10" t="s">
-        <x:v>351</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="F261" s="10" t="s">
         <x:v>3</x:v>
@@ -12107,13 +12191,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C262" s="10" t="s">
-        <x:v>343</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="D262" s="10" t="s">
-        <x:v>352</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="E262" s="10" t="s">
-        <x:v>353</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="F262" s="10" t="s">
         <x:v>3</x:v>
@@ -12141,13 +12225,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C263" s="10" t="s">
-        <x:v>343</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="D263" s="10" t="s">
-        <x:v>352</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="E263" s="10" t="s">
-        <x:v>354</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="F263" s="10" t="s">
         <x:v>3</x:v>
@@ -12175,13 +12259,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C264" s="10" t="s">
-        <x:v>343</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="D264" s="10" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="E264" s="10" t="s">
         <x:v>352</x:v>
-      </x:c>
-      <x:c r="E264" s="10" t="s">
-        <x:v>355</x:v>
       </x:c>
       <x:c r="F264" s="10" t="s">
         <x:v>3</x:v>
@@ -12209,13 +12293,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C265" s="10" t="s">
-        <x:v>343</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="D265" s="10" t="s">
-        <x:v>352</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="E265" s="10" t="s">
-        <x:v>356</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="F265" s="10" t="s">
         <x:v>3</x:v>
@@ -12243,13 +12327,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C266" s="10" t="s">
-        <x:v>343</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="D266" s="10" t="s">
-        <x:v>352</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="E266" s="10" t="s">
-        <x:v>357</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="F266" s="10" t="s">
         <x:v>3</x:v>
@@ -12277,13 +12361,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C267" s="10" t="s">
-        <x:v>343</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="D267" s="10" t="s">
-        <x:v>352</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="E267" s="10" t="s">
-        <x:v>358</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="F267" s="10" t="s">
         <x:v>3</x:v>
@@ -12311,13 +12395,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C268" s="10" t="s">
-        <x:v>343</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="D268" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E268" s="10" t="s">
-        <x:v>359</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="F268" s="10" t="s">
         <x:v>3</x:v>
@@ -12345,13 +12429,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C269" s="10" t="s">
-        <x:v>343</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="D269" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E269" s="10" t="s">
-        <x:v>360</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="F269" s="10" t="s">
         <x:v>3</x:v>
@@ -12379,13 +12463,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C270" s="10" t="s">
-        <x:v>343</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="D270" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E270" s="10" t="s">
-        <x:v>361</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="F270" s="10" t="s">
         <x:v>3</x:v>
@@ -12413,13 +12497,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C271" s="10" t="s">
-        <x:v>343</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="D271" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E271" s="10" t="s">
-        <x:v>362</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="F271" s="10" t="s">
         <x:v>3</x:v>
@@ -12447,13 +12531,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C272" s="10" t="s">
-        <x:v>343</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="D272" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E272" s="10" t="s">
-        <x:v>363</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="F272" s="10" t="s">
         <x:v>3</x:v>
@@ -12481,13 +12565,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C273" s="10" t="s">
-        <x:v>343</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="D273" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E273" s="10" t="s">
-        <x:v>364</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="F273" s="10" t="s">
         <x:v>3</x:v>
@@ -12515,13 +12599,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C274" s="10" t="s">
-        <x:v>343</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="D274" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E274" s="10" t="s">
-        <x:v>365</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="F274" s="10" t="s">
         <x:v>3</x:v>
@@ -12549,13 +12633,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C275" s="10" t="s">
-        <x:v>343</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="D275" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E275" s="10" t="s">
-        <x:v>366</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="F275" s="10" t="s">
         <x:v>3</x:v>
@@ -12583,13 +12667,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C276" s="10" t="s">
-        <x:v>367</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="D276" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E276" s="10" t="s">
-        <x:v>368</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="F276" s="10" t="s">
         <x:v>3</x:v>
@@ -12617,13 +12701,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C277" s="10" t="s">
-        <x:v>367</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="D277" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E277" s="10" t="s">
-        <x:v>369</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="F277" s="10" t="s">
         <x:v>3</x:v>
@@ -12651,13 +12735,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C278" s="10" t="s">
-        <x:v>367</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="D278" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E278" s="10" t="s">
-        <x:v>370</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="F278" s="10" t="s">
         <x:v>3</x:v>
@@ -12685,13 +12769,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C279" s="10" t="s">
-        <x:v>367</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="D279" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E279" s="10" t="s">
-        <x:v>371</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="F279" s="10" t="s">
         <x:v>3</x:v>
@@ -12719,13 +12803,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C280" s="10" t="s">
-        <x:v>367</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="D280" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E280" s="10" t="s">
-        <x:v>372</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="F280" s="10" t="s">
         <x:v>3</x:v>
@@ -12753,13 +12837,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C281" s="10" t="s">
-        <x:v>367</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="D281" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E281" s="10" t="s">
-        <x:v>373</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="F281" s="10" t="s">
         <x:v>3</x:v>
@@ -12787,13 +12871,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C282" s="10" t="s">
-        <x:v>367</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="D282" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E282" s="10" t="s">
-        <x:v>374</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="F282" s="10" t="s">
         <x:v>3</x:v>
@@ -12821,13 +12905,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C283" s="10" t="s">
-        <x:v>367</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="D283" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E283" s="10" t="s">
-        <x:v>375</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="F283" s="10" t="s">
         <x:v>3</x:v>
@@ -12855,13 +12939,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C284" s="10" t="s">
-        <x:v>367</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="D284" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E284" s="10" t="s">
-        <x:v>376</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="F284" s="10" t="s">
         <x:v>3</x:v>
@@ -12889,13 +12973,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C285" s="10" t="s">
-        <x:v>367</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="D285" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E285" s="10" t="s">
-        <x:v>377</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="F285" s="10" t="s">
         <x:v>3</x:v>
@@ -12923,13 +13007,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C286" s="10" t="s">
-        <x:v>367</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="D286" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E286" s="10" t="s">
-        <x:v>378</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="F286" s="10" t="s">
         <x:v>3</x:v>
@@ -12957,13 +13041,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C287" s="10" t="s">
-        <x:v>367</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="D287" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E287" s="10" t="s">
-        <x:v>379</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="F287" s="10" t="s">
         <x:v>3</x:v>
@@ -12991,13 +13075,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C288" s="10" t="s">
-        <x:v>367</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="D288" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E288" s="10" t="s">
-        <x:v>380</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="F288" s="10" t="s">
         <x:v>3</x:v>
@@ -13025,13 +13109,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C289" s="10" t="s">
-        <x:v>367</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="D289" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E289" s="10" t="s">
-        <x:v>381</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="F289" s="10" t="s">
         <x:v>3</x:v>
@@ -13059,13 +13143,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C290" s="10" t="s">
-        <x:v>367</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="D290" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E290" s="10" t="s">
-        <x:v>382</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="F290" s="10" t="s">
         <x:v>3</x:v>
@@ -13093,13 +13177,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C291" s="10" t="s">
-        <x:v>367</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="D291" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E291" s="10" t="s">
-        <x:v>383</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="F291" s="10" t="s">
         <x:v>3</x:v>
@@ -13127,13 +13211,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C292" s="10" t="s">
-        <x:v>367</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="D292" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E292" s="10" t="s">
-        <x:v>384</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="F292" s="10" t="s">
         <x:v>3</x:v>
@@ -13161,13 +13245,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C293" s="10" t="s">
-        <x:v>385</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D293" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E293" s="10" t="s">
-        <x:v>386</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="F293" s="10" t="s">
         <x:v>3</x:v>
@@ -13195,13 +13279,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C294" s="10" t="s">
-        <x:v>385</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D294" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E294" s="10" t="s">
-        <x:v>387</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="F294" s="10" t="s">
         <x:v>3</x:v>
@@ -13229,13 +13313,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C295" s="10" t="s">
-        <x:v>385</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D295" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E295" s="10" t="s">
-        <x:v>388</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="F295" s="10" t="s">
         <x:v>3</x:v>
@@ -13263,13 +13347,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C296" s="10" t="s">
-        <x:v>385</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D296" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E296" s="10" t="s">
-        <x:v>389</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="F296" s="10" t="s">
         <x:v>3</x:v>
@@ -13297,13 +13381,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C297" s="10" t="s">
-        <x:v>385</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D297" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E297" s="10" t="s">
-        <x:v>390</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="F297" s="10" t="s">
         <x:v>3</x:v>
@@ -13331,13 +13415,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C298" s="10" t="s">
-        <x:v>385</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D298" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E298" s="10" t="s">
-        <x:v>391</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="F298" s="10" t="s">
         <x:v>3</x:v>
@@ -13365,13 +13449,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C299" s="10" t="s">
-        <x:v>385</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D299" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E299" s="10" t="s">
-        <x:v>392</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="F299" s="10" t="s">
         <x:v>3</x:v>
@@ -13399,13 +13483,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C300" s="10" t="s">
-        <x:v>385</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D300" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E300" s="10" t="s">
-        <x:v>393</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="F300" s="10" t="s">
         <x:v>3</x:v>
@@ -13433,13 +13517,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C301" s="10" t="s">
-        <x:v>394</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="D301" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E301" s="10" t="s">
-        <x:v>395</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="F301" s="10" t="s">
         <x:v>3</x:v>
@@ -13467,13 +13551,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C302" s="10" t="s">
-        <x:v>394</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="D302" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E302" s="10" t="s">
-        <x:v>396</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="F302" s="10" t="s">
         <x:v>3</x:v>
@@ -13501,13 +13585,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C303" s="10" t="s">
-        <x:v>394</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="D303" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E303" s="10" t="s">
-        <x:v>397</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="F303" s="10" t="s">
         <x:v>3</x:v>
@@ -13535,13 +13619,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C304" s="10" t="s">
-        <x:v>394</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="D304" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E304" s="10" t="s">
-        <x:v>398</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="F304" s="10" t="s">
         <x:v>3</x:v>
@@ -13569,13 +13653,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C305" s="10" t="s">
-        <x:v>394</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="D305" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E305" s="10" t="s">
-        <x:v>399</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="F305" s="10" t="s">
         <x:v>3</x:v>
@@ -13603,13 +13687,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C306" s="10" t="s">
-        <x:v>394</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="D306" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E306" s="10" t="s">
-        <x:v>400</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="F306" s="10" t="s">
         <x:v>3</x:v>
@@ -13637,13 +13721,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C307" s="10" t="s">
-        <x:v>394</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="D307" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E307" s="10" t="s">
-        <x:v>401</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="F307" s="10" t="s">
         <x:v>3</x:v>
@@ -13671,13 +13755,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C308" s="10" t="s">
-        <x:v>394</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="D308" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E308" s="10" t="s">
-        <x:v>402</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="F308" s="10" t="s">
         <x:v>3</x:v>
@@ -13705,13 +13789,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C309" s="10" t="s">
-        <x:v>394</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="D309" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E309" s="10" t="s">
-        <x:v>377</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="F309" s="10" t="s">
         <x:v>3</x:v>
@@ -13739,13 +13823,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C310" s="10" t="s">
-        <x:v>394</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="D310" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E310" s="10" t="s">
-        <x:v>403</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="F310" s="10" t="s">
         <x:v>3</x:v>
@@ -13773,13 +13857,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C311" s="10" t="s">
-        <x:v>394</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="D311" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E311" s="10" t="s">
-        <x:v>404</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="F311" s="10" t="s">
         <x:v>3</x:v>
@@ -13807,13 +13891,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C312" s="10" t="s">
-        <x:v>394</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="D312" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E312" s="10" t="s">
-        <x:v>405</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="F312" s="10" t="s">
         <x:v>3</x:v>
@@ -13841,13 +13925,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C313" s="10" t="s">
-        <x:v>394</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="D313" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E313" s="10" t="s">
-        <x:v>406</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="F313" s="10" t="s">
         <x:v>3</x:v>
@@ -13875,13 +13959,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C314" s="10" t="s">
-        <x:v>394</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="D314" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E314" s="10" t="s">
-        <x:v>407</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="F314" s="10" t="s">
         <x:v>3</x:v>
@@ -13909,13 +13993,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C315" s="10" t="s">
-        <x:v>394</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="D315" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E315" s="10" t="s">
-        <x:v>408</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="F315" s="10" t="s">
         <x:v>3</x:v>
@@ -13943,13 +14027,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C316" s="10" t="s">
-        <x:v>394</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="D316" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E316" s="10" t="s">
-        <x:v>409</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="F316" s="10" t="s">
         <x:v>3</x:v>
@@ -13977,13 +14061,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C317" s="10" t="s">
-        <x:v>410</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="D317" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E317" s="10" t="s">
-        <x:v>411</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="F317" s="10" t="s">
         <x:v>3</x:v>
@@ -14011,13 +14095,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C318" s="10" t="s">
-        <x:v>410</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="D318" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E318" s="10" t="s">
-        <x:v>412</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="F318" s="10" t="s">
         <x:v>3</x:v>
@@ -14045,13 +14129,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C319" s="10" t="s">
-        <x:v>410</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="D319" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E319" s="10" t="s">
-        <x:v>413</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="F319" s="10" t="s">
         <x:v>3</x:v>
@@ -14079,13 +14163,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C320" s="10" t="s">
-        <x:v>410</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="D320" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E320" s="10" t="s">
-        <x:v>414</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="F320" s="10" t="s">
         <x:v>3</x:v>
@@ -14113,13 +14197,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C321" s="10" t="s">
-        <x:v>410</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="D321" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E321" s="10" t="s">
-        <x:v>415</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="F321" s="10" t="s">
         <x:v>3</x:v>
@@ -14147,13 +14231,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C322" s="10" t="s">
-        <x:v>410</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="D322" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E322" s="10" t="s">
-        <x:v>416</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="F322" s="10" t="s">
         <x:v>3</x:v>
@@ -14181,13 +14265,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C323" s="10" t="s">
-        <x:v>410</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="D323" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E323" s="10" t="s">
-        <x:v>417</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="F323" s="10" t="s">
         <x:v>3</x:v>
@@ -14215,13 +14299,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C324" s="10" t="s">
-        <x:v>410</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="D324" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E324" s="10" t="s">
-        <x:v>418</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="F324" s="10" t="s">
         <x:v>3</x:v>
@@ -14249,13 +14333,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C325" s="10" t="s">
-        <x:v>410</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="D325" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E325" s="10" t="s">
-        <x:v>419</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="F325" s="10" t="s">
         <x:v>3</x:v>
@@ -14283,13 +14367,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C326" s="10" t="s">
-        <x:v>410</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="D326" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E326" s="10" t="s">
-        <x:v>420</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="F326" s="10" t="s">
         <x:v>3</x:v>
@@ -14317,13 +14401,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C327" s="10" t="s">
-        <x:v>410</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="D327" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E327" s="10" t="s">
-        <x:v>421</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="F327" s="10" t="s">
         <x:v>3</x:v>
@@ -14351,13 +14435,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C328" s="10" t="s">
-        <x:v>410</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="D328" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E328" s="10" t="s">
-        <x:v>422</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="F328" s="10" t="s">
         <x:v>3</x:v>
@@ -14385,13 +14469,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C329" s="10" t="s">
-        <x:v>410</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="D329" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E329" s="10" t="s">
-        <x:v>423</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="F329" s="10" t="s">
         <x:v>3</x:v>
@@ -14419,13 +14503,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C330" s="10" t="s">
-        <x:v>410</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="D330" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E330" s="10" t="s">
-        <x:v>424</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="F330" s="10" t="s">
         <x:v>3</x:v>
@@ -14453,13 +14537,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C331" s="10" t="s">
-        <x:v>410</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="D331" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E331" s="10" t="s">
-        <x:v>425</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="F331" s="10" t="s">
         <x:v>3</x:v>
@@ -14487,13 +14571,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C332" s="10" t="s">
-        <x:v>426</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="D332" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E332" s="10" t="s">
-        <x:v>427</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="F332" s="10" t="s">
         <x:v>3</x:v>
@@ -14521,13 +14605,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C333" s="10" t="s">
-        <x:v>426</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="D333" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E333" s="10" t="s">
-        <x:v>428</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="F333" s="10" t="s">
         <x:v>3</x:v>
@@ -14555,13 +14639,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C334" s="10" t="s">
-        <x:v>426</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="D334" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E334" s="10" t="s">
-        <x:v>429</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="F334" s="10" t="s">
         <x:v>3</x:v>
@@ -14589,13 +14673,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C335" s="10" t="s">
-        <x:v>426</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="D335" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E335" s="10" t="s">
-        <x:v>430</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="F335" s="10" t="s">
         <x:v>3</x:v>
@@ -14623,13 +14707,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C336" s="10" t="s">
-        <x:v>426</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="D336" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E336" s="10" t="s">
-        <x:v>431</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="F336" s="10" t="s">
         <x:v>3</x:v>
@@ -14657,13 +14741,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C337" s="10" t="s">
-        <x:v>426</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="D337" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E337" s="10" t="s">
-        <x:v>432</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="F337" s="10" t="s">
         <x:v>3</x:v>
@@ -14691,13 +14775,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C338" s="10" t="s">
-        <x:v>426</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="D338" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E338" s="10" t="s">
-        <x:v>433</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="F338" s="10" t="s">
         <x:v>3</x:v>
@@ -14725,13 +14809,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C339" s="10" t="s">
-        <x:v>426</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="D339" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E339" s="10" t="s">
-        <x:v>434</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="F339" s="10" t="s">
         <x:v>3</x:v>
@@ -14759,13 +14843,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C340" s="10" t="s">
-        <x:v>426</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="D340" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E340" s="10" t="s">
-        <x:v>435</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="F340" s="10" t="s">
         <x:v>3</x:v>
@@ -14793,13 +14877,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C341" s="10" t="s">
-        <x:v>426</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="D341" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E341" s="10" t="s">
-        <x:v>436</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="F341" s="10" t="s">
         <x:v>3</x:v>
@@ -14827,13 +14911,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C342" s="10" t="s">
-        <x:v>426</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="D342" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E342" s="10" t="s">
-        <x:v>437</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="F342" s="10" t="s">
         <x:v>3</x:v>
@@ -14861,13 +14945,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C343" s="10" t="s">
-        <x:v>426</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="D343" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E343" s="10" t="s">
-        <x:v>438</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="F343" s="10" t="s">
         <x:v>3</x:v>
@@ -14895,13 +14979,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C344" s="10" t="s">
-        <x:v>426</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="D344" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E344" s="10" t="s">
-        <x:v>439</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="F344" s="10" t="s">
         <x:v>3</x:v>
@@ -14929,13 +15013,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C345" s="10" t="s">
-        <x:v>426</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="D345" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E345" s="10" t="s">
-        <x:v>440</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="F345" s="10" t="s">
         <x:v>3</x:v>
@@ -14963,13 +15047,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C346" s="10" t="s">
-        <x:v>441</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="D346" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E346" s="10" t="s">
-        <x:v>442</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="F346" s="10" t="s">
         <x:v>3</x:v>
@@ -14997,13 +15081,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C347" s="10" t="s">
-        <x:v>441</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="D347" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E347" s="10" t="s">
-        <x:v>443</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="F347" s="10" t="s">
         <x:v>3</x:v>
@@ -15031,13 +15115,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C348" s="10" t="s">
-        <x:v>441</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="D348" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E348" s="10" t="s">
-        <x:v>444</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="F348" s="10" t="s">
         <x:v>3</x:v>
@@ -15065,13 +15149,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C349" s="10" t="s">
-        <x:v>441</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="D349" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E349" s="10" t="s">
-        <x:v>445</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="F349" s="10" t="s">
         <x:v>3</x:v>
@@ -15099,13 +15183,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C350" s="10" t="s">
-        <x:v>441</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="D350" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E350" s="10" t="s">
-        <x:v>446</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="F350" s="10" t="s">
         <x:v>3</x:v>
@@ -15133,13 +15217,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C351" s="10" t="s">
-        <x:v>441</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="D351" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E351" s="10" t="s">
-        <x:v>447</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="F351" s="10" t="s">
         <x:v>3</x:v>
@@ -15167,13 +15251,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C352" s="10" t="s">
-        <x:v>441</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="D352" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E352" s="10" t="s">
-        <x:v>448</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="F352" s="10" t="s">
         <x:v>3</x:v>
@@ -15201,13 +15285,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C353" s="10" t="s">
-        <x:v>441</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="D353" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E353" s="10" t="s">
-        <x:v>449</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="F353" s="10" t="s">
         <x:v>3</x:v>
@@ -15235,13 +15319,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C354" s="10" t="s">
-        <x:v>441</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="D354" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E354" s="10" t="s">
-        <x:v>450</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="F354" s="10" t="s">
         <x:v>3</x:v>
@@ -15269,13 +15353,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C355" s="10" t="s">
-        <x:v>441</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="D355" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E355" s="10" t="s">
-        <x:v>451</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="F355" s="10" t="s">
         <x:v>3</x:v>
@@ -15303,13 +15387,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C356" s="10" t="s">
-        <x:v>441</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="D356" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E356" s="10" t="s">
-        <x:v>452</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="F356" s="10" t="s">
         <x:v>3</x:v>
@@ -15337,13 +15421,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C357" s="10" t="s">
-        <x:v>453</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="D357" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E357" s="10" t="s">
-        <x:v>454</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="F357" s="10" t="s">
         <x:v>3</x:v>
@@ -15371,13 +15455,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C358" s="10" t="s">
-        <x:v>453</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="D358" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E358" s="10" t="s">
-        <x:v>455</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="F358" s="10" t="s">
         <x:v>3</x:v>
@@ -15405,13 +15489,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C359" s="10" t="s">
-        <x:v>453</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="D359" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E359" s="10" t="s">
-        <x:v>456</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="F359" s="10" t="s">
         <x:v>3</x:v>
@@ -15439,13 +15523,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C360" s="10" t="s">
-        <x:v>453</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="D360" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E360" s="10" t="s">
-        <x:v>457</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="F360" s="10" t="s">
         <x:v>3</x:v>
@@ -15473,13 +15557,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C361" s="10" t="s">
-        <x:v>453</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="D361" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E361" s="10" t="s">
-        <x:v>458</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="F361" s="10" t="s">
         <x:v>3</x:v>
@@ -15507,13 +15591,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C362" s="10" t="s">
-        <x:v>453</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="D362" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E362" s="10" t="s">
-        <x:v>459</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="F362" s="10" t="s">
         <x:v>3</x:v>
@@ -15541,13 +15625,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C363" s="10" t="s">
-        <x:v>453</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="D363" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E363" s="10" t="s">
-        <x:v>460</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="F363" s="10" t="s">
         <x:v>3</x:v>
@@ -15575,13 +15659,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C364" s="10" t="s">
-        <x:v>453</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="D364" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E364" s="10" t="s">
-        <x:v>461</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="F364" s="10" t="s">
         <x:v>3</x:v>
@@ -15609,13 +15693,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C365" s="10" t="s">
-        <x:v>453</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="D365" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E365" s="10" t="s">
-        <x:v>462</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F365" s="10" t="s">
         <x:v>3</x:v>
@@ -15643,13 +15727,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C366" s="10" t="s">
-        <x:v>463</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="D366" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E366" s="10" t="s">
-        <x:v>464</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="F366" s="10" t="s">
         <x:v>3</x:v>
@@ -15677,13 +15761,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C367" s="10" t="s">
-        <x:v>463</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="D367" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E367" s="10" t="s">
-        <x:v>465</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="F367" s="10" t="s">
         <x:v>3</x:v>
@@ -15711,13 +15795,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C368" s="10" t="s">
-        <x:v>463</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="D368" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E368" s="10" t="s">
-        <x:v>466</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="F368" s="10" t="s">
         <x:v>3</x:v>
@@ -15745,13 +15829,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C369" s="10" t="s">
-        <x:v>463</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="D369" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E369" s="10" t="s">
-        <x:v>467</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="F369" s="10" t="s">
         <x:v>3</x:v>
@@ -15779,13 +15863,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C370" s="10" t="s">
-        <x:v>463</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="D370" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E370" s="10" t="s">
-        <x:v>468</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="F370" s="10" t="s">
         <x:v>3</x:v>
@@ -15813,13 +15897,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C371" s="10" t="s">
-        <x:v>463</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="D371" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E371" s="10" t="s">
-        <x:v>469</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="F371" s="10" t="s">
         <x:v>3</x:v>
@@ -15847,13 +15931,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C372" s="10" t="s">
-        <x:v>463</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="D372" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E372" s="10" t="s">
-        <x:v>470</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="F372" s="10" t="s">
         <x:v>3</x:v>
@@ -15881,13 +15965,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C373" s="10" t="s">
-        <x:v>463</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="D373" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E373" s="10" t="s">
-        <x:v>471</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="F373" s="10" t="s">
         <x:v>3</x:v>
@@ -15915,13 +15999,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C374" s="10" t="s">
-        <x:v>463</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="D374" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E374" s="10" t="s">
-        <x:v>472</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="F374" s="10" t="s">
         <x:v>3</x:v>
@@ -15949,13 +16033,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C375" s="10" t="s">
-        <x:v>463</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="D375" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E375" s="10" t="s">
-        <x:v>473</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="F375" s="10" t="s">
         <x:v>3</x:v>
@@ -15983,13 +16067,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C376" s="10" t="s">
-        <x:v>463</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="D376" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E376" s="10" t="s">
-        <x:v>474</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="F376" s="10" t="s">
         <x:v>3</x:v>
@@ -16017,13 +16101,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C377" s="10" t="s">
-        <x:v>463</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="D377" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E377" s="10" t="s">
-        <x:v>475</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="F377" s="10" t="s">
         <x:v>3</x:v>
@@ -16051,13 +16135,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C378" s="10" t="s">
-        <x:v>476</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="D378" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E378" s="10" t="s">
-        <x:v>477</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="F378" s="10" t="s">
         <x:v>3</x:v>
@@ -16085,13 +16169,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C379" s="10" t="s">
-        <x:v>476</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="D379" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E379" s="10" t="s">
-        <x:v>478</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="F379" s="10" t="s">
         <x:v>3</x:v>
@@ -16119,13 +16203,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C380" s="10" t="s">
-        <x:v>476</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="D380" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E380" s="10" t="s">
-        <x:v>479</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="F380" s="10" t="s">
         <x:v>3</x:v>
@@ -16153,13 +16237,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C381" s="10" t="s">
-        <x:v>476</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="D381" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E381" s="10" t="s">
-        <x:v>480</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="F381" s="10" t="s">
         <x:v>3</x:v>
@@ -16187,13 +16271,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C382" s="10" t="s">
-        <x:v>476</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="D382" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E382" s="10" t="s">
-        <x:v>481</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="F382" s="10" t="s">
         <x:v>3</x:v>
@@ -16221,13 +16305,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C383" s="10" t="s">
-        <x:v>476</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="D383" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E383" s="10" t="s">
-        <x:v>482</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="F383" s="10" t="s">
         <x:v>3</x:v>
@@ -16255,13 +16339,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C384" s="10" t="s">
-        <x:v>476</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="D384" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E384" s="10" t="s">
-        <x:v>483</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="F384" s="10" t="s">
         <x:v>3</x:v>
@@ -16289,13 +16373,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C385" s="10" t="s">
-        <x:v>476</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="D385" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E385" s="10" t="s">
-        <x:v>484</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="F385" s="10" t="s">
         <x:v>3</x:v>
@@ -16323,13 +16407,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C386" s="10" t="s">
-        <x:v>476</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="D386" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E386" s="10" t="s">
-        <x:v>485</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="F386" s="10" t="s">
         <x:v>3</x:v>
@@ -16357,13 +16441,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C387" s="10" t="s">
-        <x:v>476</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="D387" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E387" s="10" t="s">
-        <x:v>403</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="F387" s="10" t="s">
         <x:v>3</x:v>
@@ -16391,13 +16475,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C388" s="10" t="s">
-        <x:v>476</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="D388" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E388" s="10" t="s">
-        <x:v>486</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="F388" s="10" t="s">
         <x:v>3</x:v>
@@ -16425,13 +16509,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C389" s="10" t="s">
-        <x:v>476</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="D389" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E389" s="10" t="s">
-        <x:v>487</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="F389" s="10" t="s">
         <x:v>3</x:v>
@@ -16459,13 +16543,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C390" s="10" t="s">
-        <x:v>476</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="D390" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E390" s="10" t="s">
-        <x:v>488</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="F390" s="10" t="s">
         <x:v>3</x:v>
@@ -16493,13 +16577,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C391" s="10" t="s">
-        <x:v>476</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="D391" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E391" s="10" t="s">
-        <x:v>489</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="F391" s="10" t="s">
         <x:v>3</x:v>
@@ -16527,13 +16611,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C392" s="10" t="s">
-        <x:v>476</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="D392" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E392" s="10" t="s">
-        <x:v>490</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="F392" s="10" t="s">
         <x:v>3</x:v>
@@ -16561,13 +16645,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C393" s="10" t="s">
-        <x:v>476</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="D393" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E393" s="10" t="s">
-        <x:v>491</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="F393" s="10" t="s">
         <x:v>3</x:v>
@@ -16595,13 +16679,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C394" s="10" t="s">
-        <x:v>492</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="D394" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E394" s="10" t="s">
-        <x:v>493</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="F394" s="10" t="s">
         <x:v>3</x:v>
@@ -16629,13 +16713,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C395" s="10" t="s">
-        <x:v>492</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="D395" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E395" s="10" t="s">
-        <x:v>494</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="F395" s="10" t="s">
         <x:v>3</x:v>
@@ -16663,13 +16747,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C396" s="10" t="s">
-        <x:v>492</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="D396" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E396" s="10" t="s">
-        <x:v>495</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="F396" s="10" t="s">
         <x:v>3</x:v>
@@ -16697,13 +16781,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C397" s="10" t="s">
-        <x:v>492</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="D397" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E397" s="10" t="s">
-        <x:v>496</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="F397" s="10" t="s">
         <x:v>3</x:v>
@@ -16731,13 +16815,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C398" s="10" t="s">
-        <x:v>492</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="D398" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E398" s="10" t="s">
-        <x:v>497</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="F398" s="10" t="s">
         <x:v>3</x:v>
@@ -16765,13 +16849,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C399" s="10" t="s">
-        <x:v>492</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="D399" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E399" s="10" t="s">
-        <x:v>498</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="F399" s="10" t="s">
         <x:v>3</x:v>
@@ -16799,13 +16883,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C400" s="10" t="s">
-        <x:v>492</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="D400" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E400" s="10" t="s">
-        <x:v>499</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="F400" s="10" t="s">
         <x:v>3</x:v>
@@ -16833,13 +16917,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C401" s="10" t="s">
-        <x:v>492</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="D401" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E401" s="10" t="s">
-        <x:v>500</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="F401" s="10" t="s">
         <x:v>3</x:v>
@@ -16867,13 +16951,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C402" s="10" t="s">
-        <x:v>501</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="D402" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E402" s="10" t="s">
-        <x:v>502</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="F402" s="10" t="s">
         <x:v>3</x:v>
@@ -16901,13 +16985,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C403" s="10" t="s">
-        <x:v>501</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="D403" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E403" s="10" t="s">
-        <x:v>503</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="F403" s="10" t="s">
         <x:v>3</x:v>
@@ -16935,13 +17019,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C404" s="10" t="s">
-        <x:v>501</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="D404" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E404" s="10" t="s">
-        <x:v>504</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="F404" s="10" t="s">
         <x:v>3</x:v>
@@ -16969,13 +17053,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C405" s="10" t="s">
-        <x:v>501</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="D405" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E405" s="10" t="s">
-        <x:v>505</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="F405" s="10" t="s">
         <x:v>3</x:v>
@@ -17003,13 +17087,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C406" s="10" t="s">
-        <x:v>501</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="D406" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E406" s="10" t="s">
-        <x:v>506</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="F406" s="10" t="s">
         <x:v>3</x:v>
@@ -17037,13 +17121,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C407" s="10" t="s">
-        <x:v>501</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="D407" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E407" s="10" t="s">
-        <x:v>507</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="F407" s="10" t="s">
         <x:v>3</x:v>
@@ -17071,13 +17155,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C408" s="10" t="s">
-        <x:v>501</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="D408" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E408" s="10" t="s">
-        <x:v>508</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="F408" s="10" t="s">
         <x:v>3</x:v>
@@ -17105,13 +17189,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C409" s="10" t="s">
-        <x:v>501</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="D409" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E409" s="10" t="s">
-        <x:v>509</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="F409" s="10" t="s">
         <x:v>3</x:v>
@@ -17139,13 +17223,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C410" s="10" t="s">
-        <x:v>501</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="D410" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E410" s="10" t="s">
-        <x:v>449</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="F410" s="10" t="s">
         <x:v>3</x:v>
@@ -17173,13 +17257,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C411" s="10" t="s">
-        <x:v>501</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="D411" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E411" s="10" t="s">
-        <x:v>510</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="F411" s="10" t="s">
         <x:v>3</x:v>
@@ -17207,13 +17291,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C412" s="10" t="s">
-        <x:v>501</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="D412" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E412" s="10" t="s">
-        <x:v>511</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="F412" s="10" t="s">
         <x:v>3</x:v>
@@ -17241,13 +17325,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C413" s="10" t="s">
-        <x:v>501</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="D413" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E413" s="10" t="s">
-        <x:v>512</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="F413" s="10" t="s">
         <x:v>3</x:v>
@@ -17275,13 +17359,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C414" s="10" t="s">
-        <x:v>501</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="D414" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E414" s="10" t="s">
-        <x:v>513</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="F414" s="10" t="s">
         <x:v>3</x:v>
@@ -17309,13 +17393,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C415" s="10" t="s">
-        <x:v>501</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="D415" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E415" s="10" t="s">
-        <x:v>514</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="F415" s="10" t="s">
         <x:v>3</x:v>
@@ -17343,13 +17427,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C416" s="10" t="s">
-        <x:v>515</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="D416" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E416" s="10" t="s">
-        <x:v>516</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="F416" s="10" t="s">
         <x:v>3</x:v>
@@ -17377,13 +17461,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C417" s="10" t="s">
-        <x:v>515</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="D417" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E417" s="10" t="s">
-        <x:v>517</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="F417" s="10" t="s">
         <x:v>3</x:v>
@@ -17411,13 +17495,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C418" s="10" t="s">
-        <x:v>515</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="D418" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E418" s="10" t="s">
-        <x:v>518</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="F418" s="10" t="s">
         <x:v>3</x:v>
@@ -17445,13 +17529,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C419" s="10" t="s">
-        <x:v>515</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="D419" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E419" s="10" t="s">
-        <x:v>519</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="F419" s="10" t="s">
         <x:v>3</x:v>
@@ -17479,13 +17563,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C420" s="10" t="s">
-        <x:v>515</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="D420" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E420" s="10" t="s">
-        <x:v>520</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="F420" s="10" t="s">
         <x:v>3</x:v>
@@ -17513,13 +17597,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C421" s="10" t="s">
-        <x:v>515</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="D421" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E421" s="10" t="s">
-        <x:v>521</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="F421" s="10" t="s">
         <x:v>3</x:v>
@@ -17547,13 +17631,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C422" s="10" t="s">
-        <x:v>515</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="D422" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E422" s="10" t="s">
-        <x:v>522</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="F422" s="10" t="s">
         <x:v>3</x:v>
@@ -17581,13 +17665,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C423" s="10" t="s">
-        <x:v>515</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="D423" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E423" s="10" t="s">
-        <x:v>523</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="F423" s="10" t="s">
         <x:v>3</x:v>
@@ -17615,13 +17699,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C424" s="10" t="s">
-        <x:v>515</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="D424" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E424" s="10" t="s">
-        <x:v>524</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="F424" s="10" t="s">
         <x:v>3</x:v>
@@ -17649,13 +17733,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C425" s="10" t="s">
-        <x:v>515</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="D425" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E425" s="10" t="s">
-        <x:v>525</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="F425" s="10" t="s">
         <x:v>3</x:v>
@@ -17683,13 +17767,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C426" s="10" t="s">
-        <x:v>515</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="D426" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E426" s="10" t="s">
-        <x:v>526</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="F426" s="10" t="s">
         <x:v>3</x:v>
@@ -17717,13 +17801,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C427" s="10" t="s">
-        <x:v>515</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="D427" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E427" s="10" t="s">
-        <x:v>527</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="F427" s="10" t="s">
         <x:v>3</x:v>
@@ -17751,13 +17835,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C428" s="10" t="s">
-        <x:v>515</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="D428" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E428" s="10" t="s">
-        <x:v>528</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="F428" s="10" t="s">
         <x:v>3</x:v>
@@ -17785,13 +17869,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C429" s="10" t="s">
-        <x:v>515</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="D429" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E429" s="10" t="s">
-        <x:v>529</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="F429" s="10" t="s">
         <x:v>3</x:v>
@@ -17819,13 +17903,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C430" s="10" t="s">
-        <x:v>515</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="D430" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E430" s="10" t="s">
-        <x:v>530</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="F430" s="10" t="s">
         <x:v>3</x:v>
@@ -17853,13 +17937,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C431" s="10" t="s">
-        <x:v>531</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="D431" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E431" s="10" t="s">
-        <x:v>532</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="F431" s="10" t="s">
         <x:v>3</x:v>
@@ -17887,13 +17971,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C432" s="10" t="s">
-        <x:v>531</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="D432" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E432" s="10" t="s">
-        <x:v>533</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="F432" s="10" t="s">
         <x:v>3</x:v>
@@ -17921,13 +18005,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C433" s="10" t="s">
-        <x:v>531</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="D433" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E433" s="10" t="s">
-        <x:v>534</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="F433" s="10" t="s">
         <x:v>3</x:v>
@@ -17955,13 +18039,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C434" s="10" t="s">
-        <x:v>531</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="D434" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E434" s="10" t="s">
-        <x:v>535</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="F434" s="10" t="s">
         <x:v>3</x:v>
@@ -17989,13 +18073,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C435" s="10" t="s">
-        <x:v>531</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="D435" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E435" s="10" t="s">
-        <x:v>536</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="F435" s="10" t="s">
         <x:v>3</x:v>
@@ -18023,13 +18107,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C436" s="10" t="s">
-        <x:v>531</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="D436" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E436" s="10" t="s">
-        <x:v>537</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="F436" s="10" t="s">
         <x:v>3</x:v>
@@ -18057,13 +18141,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C437" s="10" t="s">
-        <x:v>531</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="D437" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E437" s="10" t="s">
-        <x:v>538</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="F437" s="10" t="s">
         <x:v>3</x:v>
@@ -18091,13 +18175,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C438" s="10" t="s">
-        <x:v>531</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="D438" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E438" s="10" t="s">
-        <x:v>539</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="F438" s="10" t="s">
         <x:v>3</x:v>
@@ -18125,13 +18209,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C439" s="10" t="s">
-        <x:v>531</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="D439" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E439" s="10" t="s">
-        <x:v>540</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="F439" s="10" t="s">
         <x:v>3</x:v>
@@ -18159,13 +18243,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C440" s="10" t="s">
-        <x:v>531</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="D440" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E440" s="10" t="s">
-        <x:v>541</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="F440" s="10" t="s">
         <x:v>3</x:v>
@@ -18193,13 +18277,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C441" s="10" t="s">
-        <x:v>531</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="D441" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E441" s="10" t="s">
-        <x:v>542</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="F441" s="10" t="s">
         <x:v>3</x:v>
@@ -18227,13 +18311,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C442" s="10" t="s">
-        <x:v>531</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="D442" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E442" s="10" t="s">
-        <x:v>422</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="F442" s="10" t="s">
         <x:v>3</x:v>
@@ -18261,13 +18345,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C443" s="10" t="s">
-        <x:v>531</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="D443" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E443" s="10" t="s">
-        <x:v>543</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="F443" s="10" t="s">
         <x:v>3</x:v>
@@ -18295,13 +18379,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C444" s="10" t="s">
-        <x:v>531</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="D444" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E444" s="10" t="s">
-        <x:v>544</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="F444" s="10" t="s">
         <x:v>3</x:v>
@@ -18329,13 +18413,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C445" s="10" t="s">
-        <x:v>545</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="D445" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E445" s="10" t="s">
-        <x:v>546</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="F445" s="10" t="s">
         <x:v>3</x:v>
@@ -18363,13 +18447,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C446" s="10" t="s">
-        <x:v>545</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="D446" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E446" s="10" t="s">
-        <x:v>547</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="F446" s="10" t="s">
         <x:v>3</x:v>
@@ -18397,13 +18481,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C447" s="10" t="s">
-        <x:v>545</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="D447" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E447" s="10" t="s">
-        <x:v>548</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="F447" s="10" t="s">
         <x:v>3</x:v>
@@ -18431,13 +18515,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C448" s="10" t="s">
-        <x:v>545</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="D448" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E448" s="10" t="s">
-        <x:v>549</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="F448" s="10" t="s">
         <x:v>3</x:v>
@@ -18465,13 +18549,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C449" s="10" t="s">
-        <x:v>545</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="D449" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E449" s="10" t="s">
-        <x:v>550</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="F449" s="10" t="s">
         <x:v>3</x:v>
@@ -18499,13 +18583,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C450" s="10" t="s">
-        <x:v>545</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="D450" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E450" s="10" t="s">
-        <x:v>551</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="F450" s="10" t="s">
         <x:v>3</x:v>
@@ -18533,13 +18617,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C451" s="10" t="s">
-        <x:v>545</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="D451" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E451" s="10" t="s">
-        <x:v>552</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="F451" s="10" t="s">
         <x:v>3</x:v>
@@ -18567,13 +18651,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C452" s="10" t="s">
-        <x:v>545</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="D452" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E452" s="10" t="s">
-        <x:v>553</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="F452" s="10" t="s">
         <x:v>3</x:v>
@@ -18601,13 +18685,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C453" s="10" t="s">
-        <x:v>545</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="D453" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E453" s="10" t="s">
-        <x:v>554</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="F453" s="10" t="s">
         <x:v>3</x:v>
@@ -18635,13 +18719,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C454" s="10" t="s">
-        <x:v>545</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="D454" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E454" s="10" t="s">
-        <x:v>555</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="F454" s="10" t="s">
         <x:v>3</x:v>
@@ -18669,13 +18753,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C455" s="10" t="s">
-        <x:v>545</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="D455" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E455" s="10" t="s">
-        <x:v>556</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="F455" s="10" t="s">
         <x:v>3</x:v>
@@ -18703,13 +18787,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C456" s="10" t="s">
-        <x:v>545</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="D456" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E456" s="10" t="s">
-        <x:v>557</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="F456" s="10" t="s">
         <x:v>3</x:v>
@@ -18737,13 +18821,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C457" s="10" t="s">
-        <x:v>545</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="D457" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E457" s="10" t="s">
-        <x:v>558</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="F457" s="10" t="s">
         <x:v>3</x:v>
@@ -18771,13 +18855,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C458" s="10" t="s">
-        <x:v>559</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="D458" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E458" s="10" t="s">
-        <x:v>560</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="F458" s="10" t="s">
         <x:v>3</x:v>
@@ -18805,13 +18889,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C459" s="10" t="s">
-        <x:v>559</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="D459" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E459" s="10" t="s">
-        <x:v>561</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="F459" s="10" t="s">
         <x:v>3</x:v>
@@ -18839,13 +18923,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C460" s="10" t="s">
-        <x:v>559</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="D460" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E460" s="10" t="s">
-        <x:v>562</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="F460" s="10" t="s">
         <x:v>3</x:v>
@@ -18873,13 +18957,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C461" s="10" t="s">
-        <x:v>559</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="D461" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E461" s="10" t="s">
-        <x:v>563</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="F461" s="10" t="s">
         <x:v>3</x:v>
@@ -18907,13 +18991,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C462" s="10" t="s">
-        <x:v>559</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="D462" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E462" s="10" t="s">
-        <x:v>564</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="F462" s="10" t="s">
         <x:v>3</x:v>
@@ -18941,13 +19025,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C463" s="10" t="s">
-        <x:v>559</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="D463" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E463" s="10" t="s">
-        <x:v>565</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="F463" s="10" t="s">
         <x:v>3</x:v>
@@ -18975,13 +19059,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C464" s="10" t="s">
-        <x:v>559</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="D464" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E464" s="10" t="s">
-        <x:v>566</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="F464" s="10" t="s">
         <x:v>3</x:v>
@@ -19009,13 +19093,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C465" s="10" t="s">
-        <x:v>559</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="D465" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E465" s="10" t="s">
-        <x:v>567</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="F465" s="10" t="s">
         <x:v>3</x:v>
@@ -19043,13 +19127,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C466" s="10" t="s">
-        <x:v>559</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="D466" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E466" s="10" t="s">
-        <x:v>568</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="F466" s="10" t="s">
         <x:v>3</x:v>
@@ -19077,13 +19161,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C467" s="10" t="s">
-        <x:v>559</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="D467" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E467" s="10" t="s">
-        <x:v>569</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="F467" s="10" t="s">
         <x:v>3</x:v>
@@ -19111,13 +19195,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C468" s="10" t="s">
-        <x:v>559</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="D468" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E468" s="10" t="s">
-        <x:v>570</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="F468" s="10" t="s">
         <x:v>3</x:v>
@@ -19145,13 +19229,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C469" s="10" t="s">
-        <x:v>559</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="D469" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E469" s="10" t="s">
-        <x:v>571</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="F469" s="10" t="s">
         <x:v>3</x:v>
@@ -19179,13 +19263,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C470" s="10" t="s">
-        <x:v>559</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="D470" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E470" s="10" t="s">
-        <x:v>572</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="F470" s="10" t="s">
         <x:v>3</x:v>
@@ -19213,13 +19297,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C471" s="10" t="s">
-        <x:v>559</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="D471" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E471" s="10" t="s">
-        <x:v>487</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="F471" s="10" t="s">
         <x:v>3</x:v>
@@ -19247,13 +19331,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C472" s="10" t="s">
-        <x:v>559</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="D472" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E472" s="10" t="s">
-        <x:v>573</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="F472" s="10" t="s">
         <x:v>3</x:v>
@@ -19281,13 +19365,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C473" s="10" t="s">
-        <x:v>559</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="D473" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E473" s="10" t="s">
-        <x:v>574</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="F473" s="10" t="s">
         <x:v>3</x:v>
@@ -19315,13 +19399,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C474" s="10" t="s">
-        <x:v>575</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="D474" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E474" s="10" t="s">
-        <x:v>576</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="F474" s="10" t="s">
         <x:v>3</x:v>
@@ -19349,13 +19433,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C475" s="10" t="s">
-        <x:v>575</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="D475" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E475" s="10" t="s">
-        <x:v>577</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="F475" s="10" t="s">
         <x:v>3</x:v>
@@ -19383,13 +19467,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C476" s="10" t="s">
-        <x:v>575</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="D476" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E476" s="10" t="s">
-        <x:v>578</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="F476" s="10" t="s">
         <x:v>3</x:v>
@@ -19417,13 +19501,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C477" s="10" t="s">
-        <x:v>575</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="D477" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E477" s="10" t="s">
-        <x:v>579</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="F477" s="10" t="s">
         <x:v>3</x:v>
@@ -19451,13 +19535,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C478" s="10" t="s">
-        <x:v>575</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="D478" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E478" s="10" t="s">
-        <x:v>580</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="F478" s="10" t="s">
         <x:v>3</x:v>
@@ -19485,13 +19569,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C479" s="10" t="s">
-        <x:v>575</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="D479" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E479" s="10" t="s">
-        <x:v>581</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="F479" s="10" t="s">
         <x:v>3</x:v>
@@ -19519,13 +19603,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C480" s="10" t="s">
-        <x:v>575</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="D480" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E480" s="10" t="s">
-        <x:v>582</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="F480" s="10" t="s">
         <x:v>3</x:v>
@@ -19553,13 +19637,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C481" s="10" t="s">
-        <x:v>575</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="D481" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E481" s="10" t="s">
-        <x:v>583</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="F481" s="10" t="s">
         <x:v>3</x:v>
@@ -19587,13 +19671,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C482" s="10" t="s">
-        <x:v>575</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="D482" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E482" s="10" t="s">
-        <x:v>584</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="F482" s="10" t="s">
         <x:v>3</x:v>
@@ -19621,13 +19705,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C483" s="10" t="s">
-        <x:v>575</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="D483" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E483" s="10" t="s">
-        <x:v>585</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="F483" s="10" t="s">
         <x:v>3</x:v>
@@ -19655,13 +19739,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C484" s="10" t="s">
-        <x:v>575</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="D484" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E484" s="10" t="s">
-        <x:v>586</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="F484" s="10" t="s">
         <x:v>3</x:v>
@@ -19689,13 +19773,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C485" s="10" t="s">
-        <x:v>575</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="D485" s="10" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E485" s="10" t="s">
-        <x:v>587</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="F485" s="10" t="s">
         <x:v>3</x:v>
@@ -19723,13 +19807,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C486" s="10" t="s">
-        <x:v>575</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="D486" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E486" s="10" t="s">
-        <x:v>588</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="F486" s="10" t="s">
         <x:v>3</x:v>
@@ -19757,13 +19841,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C487" s="10" t="s">
-        <x:v>575</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="D487" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E487" s="10" t="s">
-        <x:v>589</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="F487" s="10" t="s">
         <x:v>3</x:v>
@@ -19791,13 +19875,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C488" s="10" t="s">
-        <x:v>575</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="D488" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E488" s="10" t="s">
-        <x:v>590</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="F488" s="10" t="s">
         <x:v>3</x:v>
@@ -19825,13 +19909,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C489" s="10" t="s">
-        <x:v>575</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="D489" s="10" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E489" s="10" t="s">
-        <x:v>591</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="F489" s="10" t="s">
         <x:v>3</x:v>
@@ -19859,13 +19943,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C490" s="10" t="s">
-        <x:v>592</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="D490" s="10" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E490" s="10" t="s">
-        <x:v>594</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="F490" s="10" t="s">
         <x:v>3</x:v>
@@ -19893,13 +19977,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C491" s="10" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="D491" s="10" t="s">
+        <x:v>590</x:v>
+      </x:c>
+      <x:c r="E491" s="10" t="s">
         <x:v>592</x:v>
-      </x:c>
-      <x:c r="D491" s="10" t="s">
-        <x:v>593</x:v>
-      </x:c>
-      <x:c r="E491" s="10" t="s">
-        <x:v>595</x:v>
       </x:c>
       <x:c r="F491" s="10" t="s">
         <x:v>3</x:v>
@@ -19927,13 +20011,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C492" s="10" t="s">
-        <x:v>592</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="D492" s="10" t="s">
+        <x:v>590</x:v>
+      </x:c>
+      <x:c r="E492" s="10" t="s">
         <x:v>593</x:v>
-      </x:c>
-      <x:c r="E492" s="10" t="s">
-        <x:v>596</x:v>
       </x:c>
       <x:c r="F492" s="10" t="s">
         <x:v>3</x:v>
@@ -19961,13 +20045,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C493" s="10" t="s">
-        <x:v>592</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="D493" s="10" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E493" s="10" t="s">
-        <x:v>597</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="F493" s="10" t="s">
         <x:v>3</x:v>
@@ -19995,13 +20079,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C494" s="10" t="s">
-        <x:v>592</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="D494" s="10" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E494" s="10" t="s">
-        <x:v>598</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="F494" s="10" t="s">
         <x:v>3</x:v>
@@ -20029,13 +20113,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C495" s="10" t="s">
-        <x:v>592</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="D495" s="10" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E495" s="10" t="s">
-        <x:v>599</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="F495" s="10" t="s">
         <x:v>3</x:v>
@@ -20063,13 +20147,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C496" s="10" t="s">
-        <x:v>592</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="D496" s="10" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E496" s="10" t="s">
-        <x:v>600</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="F496" s="10" t="s">
         <x:v>3</x:v>
@@ -20097,13 +20181,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C497" t="s">
-        <x:v>592</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="D497" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E497" t="s">
-        <x:v>601</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="F497" t="s">
         <x:v>3</x:v>
@@ -20131,13 +20215,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C498" t="s">
-        <x:v>592</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="D498" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E498" t="s">
-        <x:v>602</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="F498" t="s">
         <x:v>3</x:v>
@@ -20165,13 +20249,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C499" t="s">
-        <x:v>592</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="D499" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E499" t="s">
-        <x:v>603</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="F499" t="s">
         <x:v>3</x:v>
@@ -20199,13 +20283,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C500" t="s">
-        <x:v>592</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="D500" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E500" t="s">
-        <x:v>604</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="F500" t="s">
         <x:v>3</x:v>
@@ -20233,13 +20317,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C501" t="s">
-        <x:v>592</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="D501" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E501" t="s">
-        <x:v>605</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="F501" t="s">
         <x:v>3</x:v>
@@ -20267,13 +20351,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C502" t="s">
-        <x:v>592</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="D502" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E502" t="s">
-        <x:v>606</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="F502" t="s">
         <x:v>3</x:v>
@@ -20301,13 +20385,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C503" t="s">
-        <x:v>592</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="D503" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E503" t="s">
-        <x:v>607</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="F503" t="s">
         <x:v>3</x:v>
@@ -20335,13 +20419,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C504" t="s">
-        <x:v>592</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="D504" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E504" t="s">
-        <x:v>608</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="F504" t="s">
         <x:v>3</x:v>
@@ -20369,13 +20453,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C505" t="s">
-        <x:v>592</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="D505" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E505" t="s">
-        <x:v>609</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="F505" t="s">
         <x:v>3</x:v>
@@ -20403,13 +20487,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C506" t="s">
-        <x:v>592</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="D506" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E506" t="s">
-        <x:v>610</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="F506" t="s">
         <x:v>3</x:v>
@@ -20437,10 +20521,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C507" t="s">
-        <x:v>592</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="D507" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E507" t="s">
         <x:v>17</x:v>
@@ -20471,13 +20555,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C508" t="s">
-        <x:v>592</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="D508" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E508" t="s">
-        <x:v>611</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="F508" t="s">
         <x:v>3</x:v>
@@ -20505,13 +20589,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C509" t="s">
-        <x:v>592</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="D509" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E509" t="s">
-        <x:v>612</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="F509" t="s">
         <x:v>3</x:v>
@@ -20539,13 +20623,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C510" t="s">
-        <x:v>613</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="D510" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E510" t="s">
-        <x:v>614</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="F510" t="s">
         <x:v>3</x:v>
@@ -20573,13 +20657,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C511" t="s">
-        <x:v>613</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="D511" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E511" t="s">
-        <x:v>615</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="F511" t="s">
         <x:v>3</x:v>
@@ -20607,13 +20691,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C512" t="s">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="D512" t="s">
+        <x:v>590</x:v>
+      </x:c>
+      <x:c r="E512" t="s">
         <x:v>613</x:v>
-      </x:c>
-      <x:c r="D512" t="s">
-        <x:v>593</x:v>
-      </x:c>
-      <x:c r="E512" t="s">
-        <x:v>616</x:v>
       </x:c>
       <x:c r="F512" t="s">
         <x:v>3</x:v>
@@ -20641,13 +20725,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C513" t="s">
-        <x:v>613</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="D513" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E513" t="s">
-        <x:v>617</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="F513" t="s">
         <x:v>3</x:v>
@@ -20675,13 +20759,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C514" t="s">
-        <x:v>613</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="D514" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E514" t="s">
-        <x:v>618</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="F514" t="s">
         <x:v>3</x:v>
@@ -20709,13 +20793,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C515" t="s">
-        <x:v>613</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="D515" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E515" t="s">
-        <x:v>619</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="F515" t="s">
         <x:v>3</x:v>
@@ -20743,13 +20827,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C516" t="s">
-        <x:v>613</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="D516" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E516" t="s">
-        <x:v>620</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="F516" t="s">
         <x:v>3</x:v>
@@ -20777,13 +20861,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C517" t="s">
-        <x:v>613</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="D517" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E517" t="s">
-        <x:v>621</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="F517" t="s">
         <x:v>3</x:v>
@@ -20811,13 +20895,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C518" t="s">
-        <x:v>613</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="D518" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E518" t="s">
-        <x:v>622</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="F518" t="s">
         <x:v>3</x:v>
@@ -20845,13 +20929,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C519" t="s">
-        <x:v>613</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="D519" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E519" t="s">
-        <x:v>623</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="F519" t="s">
         <x:v>3</x:v>
@@ -20879,13 +20963,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C520" t="s">
-        <x:v>613</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="D520" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E520" t="s">
-        <x:v>624</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="F520" t="s">
         <x:v>3</x:v>
@@ -20913,13 +20997,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C521" t="s">
-        <x:v>613</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="D521" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E521" t="s">
-        <x:v>625</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="F521" t="s">
         <x:v>3</x:v>
@@ -20947,13 +21031,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C522" t="s">
-        <x:v>613</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="D522" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E522" t="s">
-        <x:v>626</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="F522" t="s">
         <x:v>3</x:v>
@@ -20981,13 +21065,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C523" t="s">
-        <x:v>613</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="D523" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E523" t="s">
-        <x:v>627</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="F523" t="s">
         <x:v>3</x:v>
@@ -21015,13 +21099,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C524" t="s">
-        <x:v>613</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="D524" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E524" t="s">
-        <x:v>628</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="F524" t="s">
         <x:v>3</x:v>
@@ -21049,13 +21133,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C525" t="s">
-        <x:v>613</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="D525" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E525" t="s">
-        <x:v>629</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="F525" t="s">
         <x:v>3</x:v>
@@ -21083,13 +21167,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C526" t="s">
-        <x:v>613</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="D526" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E526" t="s">
-        <x:v>630</x:v>
+        <x:v>627</x:v>
       </x:c>
       <x:c r="F526" t="s">
         <x:v>3</x:v>
@@ -21117,13 +21201,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C527" t="s">
-        <x:v>613</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="D527" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E527" t="s">
-        <x:v>631</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="F527" t="s">
         <x:v>3</x:v>
@@ -21151,13 +21235,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C528" t="s">
-        <x:v>632</x:v>
+        <x:v>629</x:v>
       </x:c>
       <x:c r="D528" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E528" t="s">
-        <x:v>633</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="F528" t="s">
         <x:v>3</x:v>
@@ -21185,13 +21269,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C529" t="s">
-        <x:v>632</x:v>
+        <x:v>629</x:v>
       </x:c>
       <x:c r="D529" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E529" t="s">
-        <x:v>634</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="F529" t="s">
         <x:v>3</x:v>
@@ -21219,13 +21303,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C530" t="s">
+        <x:v>629</x:v>
+      </x:c>
+      <x:c r="D530" t="s">
+        <x:v>590</x:v>
+      </x:c>
+      <x:c r="E530" t="s">
         <x:v>632</x:v>
-      </x:c>
-      <x:c r="D530" t="s">
-        <x:v>593</x:v>
-      </x:c>
-      <x:c r="E530" t="s">
-        <x:v>635</x:v>
       </x:c>
       <x:c r="F530" t="s">
         <x:v>3</x:v>
@@ -21253,13 +21337,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C531" t="s">
-        <x:v>632</x:v>
+        <x:v>629</x:v>
       </x:c>
       <x:c r="D531" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E531" t="s">
-        <x:v>636</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="F531" t="s">
         <x:v>3</x:v>
@@ -21287,13 +21371,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C532" t="s">
-        <x:v>632</x:v>
+        <x:v>629</x:v>
       </x:c>
       <x:c r="D532" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E532" t="s">
-        <x:v>637</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="F532" t="s">
         <x:v>3</x:v>
@@ -21321,13 +21405,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C533" t="s">
-        <x:v>632</x:v>
+        <x:v>629</x:v>
       </x:c>
       <x:c r="D533" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E533" t="s">
-        <x:v>638</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="F533" t="s">
         <x:v>3</x:v>
@@ -21355,13 +21439,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C534" t="s">
-        <x:v>632</x:v>
+        <x:v>629</x:v>
       </x:c>
       <x:c r="D534" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E534" t="s">
-        <x:v>639</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="F534" t="s">
         <x:v>3</x:v>
@@ -26700,7 +26784,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8bc80fb34b924b1b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27716f2640fc48d2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26848,7 +26932,7 @@
       </x:c>
       <x:c r="C5" t="n">
         <x:f>COUNTIFS(Checklist!$B:$B,A5,Checklist!$F:$F,"Chưa làm")</x:f>
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D5" t="n">
         <x:f>COUNTIFS(Checklist!$B:$B,A5,Checklist!$F:$F,"Đang làm")</x:f>
@@ -26856,7 +26940,7 @@
       </x:c>
       <x:c r="E5" t="n">
         <x:f>COUNTIFS(Checklist!$B:$B,A5,Checklist!$F:$F,"Hoàn thành")</x:f>
-        <x:v>100</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="F5" t="n">
         <x:f>COUNTIFS(Checklist!$B:$B,A5,Checklist!$F:$F,"Bị chặn")</x:f>
@@ -26868,7 +26952,7 @@
       </x:c>
       <x:c r="H5" s="6" t="n">
         <x:f t="shared" si="0">IFERROR(E5/B5,0)</x:f>
-        <x:v>0.6535947712418301</x:v>
+        <x:v>0.7712418300653595</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -27173,7 +27257,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43692765fc344e4f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d089eeeac314785"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
